--- a/Results/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
+++ b/Results/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>408.0844050706104</v>
+        <v>408.0844050706268</v>
       </c>
       <c r="C2" t="n">
-        <v>375.205130059704</v>
+        <v>375.2051300597032</v>
       </c>
       <c r="D2" t="n">
-        <v>1490.45748222319</v>
+        <v>1490.457482223186</v>
       </c>
       <c r="E2" t="n">
-        <v>375.205130059704</v>
+        <v>375.2051300597032</v>
       </c>
       <c r="F2" t="n">
-        <v>375.205130059704</v>
+        <v>375.2051300597032</v>
       </c>
       <c r="G2" t="n">
-        <v>836.7773601002432</v>
+        <v>836.7773601002343</v>
       </c>
       <c r="H2" t="n">
-        <v>2608.002443786369</v>
+        <v>2608.002443786356</v>
       </c>
       <c r="I2" t="n">
-        <v>375.205130059704</v>
+        <v>375.2051300597032</v>
       </c>
       <c r="J2" t="n">
-        <v>704.2831307156409</v>
+        <v>704.2831307156262</v>
       </c>
       <c r="K2" t="n">
-        <v>523.5460598837774</v>
+        <v>523.5460598837703</v>
       </c>
       <c r="L2" t="n">
-        <v>2286.972212175713</v>
+        <v>330.8268586249813</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.65687052377781</v>
+        <v>35.65687052377783</v>
       </c>
       <c r="C3" t="n">
-        <v>33.68074942874813</v>
+        <v>33.68074942874819</v>
       </c>
       <c r="D3" t="n">
-        <v>35.65687052377781</v>
+        <v>35.65687052377783</v>
       </c>
       <c r="E3" t="n">
-        <v>33.8248061684053</v>
+        <v>33.8248061684054</v>
       </c>
       <c r="F3" t="n">
-        <v>33.82480616840529</v>
+        <v>33.82480616840537</v>
       </c>
       <c r="G3" t="n">
-        <v>35.48235461852919</v>
+        <v>35.48235461852929</v>
       </c>
       <c r="H3" t="n">
-        <v>35.65687052377781</v>
+        <v>35.65687052377783</v>
       </c>
       <c r="I3" t="n">
-        <v>34.54931642253382</v>
+        <v>34.54931642253401</v>
       </c>
       <c r="J3" t="n">
-        <v>35.65687052377781</v>
+        <v>35.65687052377783</v>
       </c>
       <c r="K3" t="n">
-        <v>35.65687052377781</v>
+        <v>35.65687052377783</v>
       </c>
       <c r="L3" t="n">
-        <v>35.65687052377781</v>
+        <v>35.65687052377783</v>
       </c>
     </row>
     <row r="4">
@@ -595,31 +595,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>232.8232613364283</v>
+        <v>149.8979535870587</v>
       </c>
       <c r="C4" t="n">
-        <v>147.9249159232166</v>
+        <v>147.9249159232165</v>
       </c>
       <c r="D4" t="n">
-        <v>151.5226933284324</v>
+        <v>151.522631696272</v>
       </c>
       <c r="E4" t="n">
-        <v>136.9025460103955</v>
+        <v>136.9025460103958</v>
       </c>
       <c r="F4" t="n">
-        <v>148.7729653216365</v>
+        <v>148.7729653216367</v>
       </c>
       <c r="G4" t="n">
         <v>232.6487454311795</v>
       </c>
       <c r="H4" t="n">
-        <v>231.5102789151362</v>
+        <v>231.510278915136</v>
       </c>
       <c r="I4" t="n">
-        <v>231.7157072351842</v>
+        <v>148.7903994858146</v>
       </c>
       <c r="J4" t="n">
-        <v>156.0776153022077</v>
+        <v>156.0776153022124</v>
       </c>
       <c r="K4" t="n">
         <v>149.5989656583114</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.8320674189094</v>
+        <v>64.83206741890943</v>
       </c>
       <c r="C5" t="n">
-        <v>63.72451331766568</v>
+        <v>63.72451331766578</v>
       </c>
       <c r="D5" t="n">
-        <v>64.83150378717326</v>
+        <v>64.83150378717332</v>
       </c>
       <c r="E5" t="n">
-        <v>63.71044632745473</v>
+        <v>63.71044632745487</v>
       </c>
       <c r="F5" t="n">
-        <v>63.71044632745473</v>
+        <v>63.71044632745487</v>
       </c>
       <c r="G5" t="n">
-        <v>64.65755151366095</v>
+        <v>64.65755151366102</v>
       </c>
       <c r="H5" t="n">
-        <v>64.8320674189094</v>
+        <v>64.83206741890943</v>
       </c>
       <c r="I5" t="n">
-        <v>63.72451331766568</v>
+        <v>63.72451331766578</v>
       </c>
       <c r="J5" t="n">
-        <v>64.8320674189094</v>
+        <v>64.83206741890943</v>
       </c>
       <c r="K5" t="n">
-        <v>64.8320674189094</v>
+        <v>64.83206741890943</v>
       </c>
       <c r="L5" t="n">
-        <v>64.8320674189094</v>
+        <v>64.83206741890943</v>
       </c>
     </row>
     <row r="6">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144.9051130134649</v>
+        <v>144.9051130134648</v>
       </c>
       <c r="C6" t="n">
-        <v>216.0186607185889</v>
+        <v>216.018660718589</v>
       </c>
       <c r="D6" t="n">
-        <v>232.1000195980189</v>
+        <v>232.1000195980191</v>
       </c>
       <c r="E6" t="n">
         <v>196.2669723852205</v>
@@ -690,22 +690,22 @@
         <v>146.0787559854717</v>
       </c>
       <c r="G6" t="n">
-        <v>216.9502816377245</v>
+        <v>216.9502816377244</v>
       </c>
       <c r="H6" t="n">
-        <v>217.1247975429766</v>
+        <v>217.1247975429769</v>
       </c>
       <c r="I6" t="n">
-        <v>216.0172434417293</v>
+        <v>216.0172434417292</v>
       </c>
       <c r="J6" t="n">
-        <v>217.1389907853385</v>
+        <v>217.1389907853383</v>
       </c>
       <c r="K6" t="n">
-        <v>143.5635952952725</v>
+        <v>143.5635952952724</v>
       </c>
       <c r="L6" t="n">
-        <v>292.5642969504912</v>
+        <v>292.5642969504917</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142.7509955549808</v>
+        <v>142.7509955549811</v>
       </c>
       <c r="C7" t="n">
-        <v>172.4815900215827</v>
+        <v>172.4815900215823</v>
       </c>
       <c r="D7" t="n">
-        <v>173.5891380332334</v>
+        <v>173.5891380332338</v>
       </c>
       <c r="E7" t="n">
-        <v>208.068107894203</v>
+        <v>208.0681078942034</v>
       </c>
       <c r="F7" t="n">
-        <v>172.4815530652106</v>
+        <v>172.4815530652098</v>
       </c>
       <c r="G7" t="n">
-        <v>173.4146282175781</v>
+        <v>173.4146282175778</v>
       </c>
       <c r="H7" t="n">
-        <v>173.5891441228261</v>
+        <v>173.5891441228263</v>
       </c>
       <c r="I7" t="n">
-        <v>172.4815900215827</v>
+        <v>172.4815900215823</v>
       </c>
       <c r="J7" t="n">
-        <v>173.5891441228261</v>
+        <v>173.5891441228263</v>
       </c>
       <c r="K7" t="n">
-        <v>134.7584120641642</v>
+        <v>155.7213971706129</v>
       </c>
       <c r="L7" t="n">
-        <v>173.5891441228261</v>
+        <v>173.5891441228263</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.80562123640964</v>
+        <v>82.80562123641141</v>
       </c>
       <c r="C8" t="n">
-        <v>49.11242631413123</v>
+        <v>49.11242631413121</v>
       </c>
       <c r="D8" t="n">
-        <v>59.72123136933308</v>
+        <v>59.7212313693331</v>
       </c>
       <c r="E8" t="n">
-        <v>49.11242631413123</v>
+        <v>49.11242631413121</v>
       </c>
       <c r="F8" t="n">
-        <v>49.11242631413123</v>
+        <v>49.11242631413121</v>
       </c>
       <c r="G8" t="n">
-        <v>74.02051779762982</v>
+        <v>74.02051779762998</v>
       </c>
       <c r="H8" t="n">
-        <v>41.98776974610143</v>
+        <v>41.98776974610141</v>
       </c>
       <c r="I8" t="n">
-        <v>49.11242631413123</v>
+        <v>49.11242631413121</v>
       </c>
       <c r="J8" t="n">
-        <v>77.29911592075364</v>
+        <v>77.29911592075371</v>
       </c>
       <c r="K8" t="n">
-        <v>80.46330989216902</v>
+        <v>80.46330989216915</v>
       </c>
       <c r="L8" t="n">
-        <v>85.14966229775789</v>
+        <v>85.14966229775793</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.95082205911757</v>
+        <v>85.95082205911763</v>
       </c>
       <c r="C9" t="n">
-        <v>52.30773405646397</v>
+        <v>52.30773405646395</v>
       </c>
       <c r="D9" t="n">
-        <v>76.54949516878372</v>
+        <v>76.54949516878384</v>
       </c>
       <c r="E9" t="n">
-        <v>52.30773405646397</v>
+        <v>52.30773405646395</v>
       </c>
       <c r="F9" t="n">
-        <v>52.30773405646397</v>
+        <v>52.30773405646395</v>
       </c>
       <c r="G9" t="n">
-        <v>82.31302720024726</v>
+        <v>82.31302720024736</v>
       </c>
       <c r="H9" t="n">
-        <v>69.37048090091683</v>
+        <v>69.37048090091687</v>
       </c>
       <c r="I9" t="n">
-        <v>52.30773405646397</v>
+        <v>52.30773405646395</v>
       </c>
       <c r="J9" t="n">
-        <v>83.71282529807681</v>
+        <v>83.71282529807682</v>
       </c>
       <c r="K9" t="n">
-        <v>84.99730758954992</v>
+        <v>84.99730758954996</v>
       </c>
       <c r="L9" t="n">
-        <v>86.90900363609981</v>
+        <v>86.90900363609988</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249.9260087418486</v>
+        <v>249.9260087418476</v>
       </c>
       <c r="C2" t="n">
-        <v>223.4856829529591</v>
+        <v>223.4856829529575</v>
       </c>
       <c r="D2" t="n">
-        <v>232.0214582845721</v>
+        <v>232.0214582845722</v>
       </c>
       <c r="E2" t="n">
-        <v>223.4856829529591</v>
+        <v>223.4856829529575</v>
       </c>
       <c r="F2" t="n">
-        <v>223.4856829529591</v>
+        <v>223.4856829529575</v>
       </c>
       <c r="G2" t="n">
-        <v>240.3477657233063</v>
+        <v>240.3477657233017</v>
       </c>
       <c r="H2" t="n">
-        <v>244.5368367612791</v>
+        <v>244.5368367612785</v>
       </c>
       <c r="I2" t="n">
-        <v>223.4856829529591</v>
+        <v>223.4856829529575</v>
       </c>
       <c r="J2" t="n">
-        <v>343.8415473830703</v>
+        <v>343.8415473830702</v>
       </c>
       <c r="K2" t="n">
-        <v>176.9804209411028</v>
+        <v>176.9804209411029</v>
       </c>
       <c r="L2" t="n">
-        <v>184.7910632991135</v>
+        <v>191.7092692051723</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.31081576366506</v>
+        <v>33.310815763665</v>
       </c>
       <c r="C3" t="n">
-        <v>31.79568093463141</v>
+        <v>31.79568093463133</v>
       </c>
       <c r="D3" t="n">
-        <v>33.31081576366506</v>
+        <v>33.310815763665</v>
       </c>
       <c r="E3" t="n">
-        <v>31.89424241017444</v>
+        <v>31.89424241017433</v>
       </c>
       <c r="F3" t="n">
-        <v>31.89424241017444</v>
+        <v>31.89424241017434</v>
       </c>
       <c r="G3" t="n">
-        <v>33.15135328481123</v>
+        <v>33.15135328481115</v>
       </c>
       <c r="H3" t="n">
-        <v>33.31081576366506</v>
+        <v>33.310815763665</v>
       </c>
       <c r="I3" t="n">
-        <v>32.2992502794192</v>
+        <v>32.29925027941912</v>
       </c>
       <c r="J3" t="n">
-        <v>33.31081576366506</v>
+        <v>33.310815763665</v>
       </c>
       <c r="K3" t="n">
-        <v>33.31081576366506</v>
+        <v>33.310815763665</v>
       </c>
       <c r="L3" t="n">
-        <v>33.31081576366506</v>
+        <v>33.310815763665</v>
       </c>
     </row>
     <row r="4">
@@ -994,31 +994,31 @@
         <v>200.879902300267</v>
       </c>
       <c r="C4" t="n">
-        <v>130.5685320358248</v>
+        <v>130.5685320358245</v>
       </c>
       <c r="D4" t="n">
-        <v>131.7597650995112</v>
+        <v>199.2634145806905</v>
       </c>
       <c r="E4" t="n">
-        <v>121.0156238260926</v>
+        <v>121.0156238260925</v>
       </c>
       <c r="F4" t="n">
-        <v>130.8055474109711</v>
+        <v>130.805547410971</v>
       </c>
       <c r="G4" t="n">
-        <v>200.7204398214126</v>
+        <v>131.6323249995551</v>
       </c>
       <c r="H4" t="n">
-        <v>199.3373857826484</v>
+        <v>199.3373857826483</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7802219941628</v>
+        <v>130.7802219941627</v>
       </c>
       <c r="J4" t="n">
-        <v>199.0810494786129</v>
+        <v>199.0810494786128</v>
       </c>
       <c r="K4" t="n">
-        <v>131.6539225650448</v>
+        <v>131.6539225650438</v>
       </c>
       <c r="L4" t="n">
         <v>131.8123512196125</v>
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.84331549644753</v>
+        <v>55.84331549644738</v>
       </c>
       <c r="C5" t="n">
-        <v>54.83175001220162</v>
+        <v>54.83175001220144</v>
       </c>
       <c r="D5" t="n">
-        <v>55.84285180090758</v>
+        <v>55.8428518009074</v>
       </c>
       <c r="E5" t="n">
-        <v>54.82123796443666</v>
+        <v>54.82123796443649</v>
       </c>
       <c r="F5" t="n">
-        <v>54.82123796443666</v>
+        <v>54.82123796443649</v>
       </c>
       <c r="G5" t="n">
-        <v>55.68385301759366</v>
+        <v>55.68385301759352</v>
       </c>
       <c r="H5" t="n">
-        <v>55.84331549644753</v>
+        <v>55.84331549644738</v>
       </c>
       <c r="I5" t="n">
-        <v>54.83175001220162</v>
+        <v>54.83175001220144</v>
       </c>
       <c r="J5" t="n">
-        <v>55.84331549644753</v>
+        <v>55.84331549644738</v>
       </c>
       <c r="K5" t="n">
-        <v>55.84331549644753</v>
+        <v>55.84331549644738</v>
       </c>
       <c r="L5" t="n">
-        <v>55.84331549644753</v>
+        <v>55.84331549644738</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123.2157281563322</v>
+        <v>123.2157281563319</v>
       </c>
       <c r="C6" t="n">
-        <v>181.2219897706147</v>
+        <v>181.2219897706142</v>
       </c>
       <c r="D6" t="n">
-        <v>194.4687456562287</v>
+        <v>194.4687456562284</v>
       </c>
       <c r="E6" t="n">
-        <v>165.081409577234</v>
+        <v>165.0814095772335</v>
       </c>
       <c r="F6" t="n">
-        <v>124.0688756288237</v>
+        <v>124.0688756288233</v>
       </c>
       <c r="G6" t="n">
-        <v>182.0719885812206</v>
+        <v>182.0719885812199</v>
       </c>
       <c r="H6" t="n">
-        <v>182.2314510600755</v>
+        <v>182.2314510600751</v>
       </c>
       <c r="I6" t="n">
-        <v>181.2198855758284</v>
+        <v>181.219885575828</v>
       </c>
       <c r="J6" t="n">
-        <v>182.2430493458926</v>
+        <v>182.2430493458921</v>
       </c>
       <c r="K6" t="n">
-        <v>122.1194808042108</v>
+        <v>122.1194808042105</v>
       </c>
       <c r="L6" t="n">
-        <v>243.8783084524513</v>
+        <v>243.8783084524506</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100.0680749520671</v>
+        <v>100.0680749520667</v>
       </c>
       <c r="C7" t="n">
-        <v>118.3417052209389</v>
+        <v>118.3417052209385</v>
       </c>
       <c r="D7" t="n">
-        <v>119.3532772737982</v>
+        <v>119.3532772737978</v>
       </c>
       <c r="E7" t="n">
-        <v>140.5964120108704</v>
+        <v>140.59641201087</v>
       </c>
       <c r="F7" t="n">
-        <v>118.341700313039</v>
+        <v>118.3417003130386</v>
       </c>
       <c r="G7" t="n">
-        <v>119.1938082263309</v>
+        <v>119.1938082263305</v>
       </c>
       <c r="H7" t="n">
-        <v>119.3532707051847</v>
+        <v>119.3532707051844</v>
       </c>
       <c r="I7" t="n">
-        <v>118.3417052209389</v>
+        <v>118.3417052209385</v>
       </c>
       <c r="J7" t="n">
-        <v>119.3532707051847</v>
+        <v>119.3532707051844</v>
       </c>
       <c r="K7" t="n">
-        <v>108.1793553097619</v>
+        <v>108.1793553097613</v>
       </c>
       <c r="L7" t="n">
-        <v>119.3532707051847</v>
+        <v>119.3532707051844</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.84379479190891</v>
+        <v>82.84379479190882</v>
       </c>
       <c r="C8" t="n">
-        <v>49.47093784397969</v>
+        <v>49.47093784397967</v>
       </c>
       <c r="D8" t="n">
-        <v>83.37140864248093</v>
+        <v>83.37140864248089</v>
       </c>
       <c r="E8" t="n">
-        <v>49.47093784397969</v>
+        <v>49.47093784397967</v>
       </c>
       <c r="F8" t="n">
-        <v>49.47093784397969</v>
+        <v>49.47093784397967</v>
       </c>
       <c r="G8" t="n">
-        <v>83.19051021015096</v>
+        <v>83.1905102101509</v>
       </c>
       <c r="H8" t="n">
-        <v>83.60429983088352</v>
+        <v>83.60429983088349</v>
       </c>
       <c r="I8" t="n">
-        <v>49.47093784397969</v>
+        <v>49.47093784397967</v>
       </c>
       <c r="J8" t="n">
-        <v>80.9631629069505</v>
+        <v>80.96316290695046</v>
       </c>
       <c r="K8" t="n">
-        <v>84.74790920829751</v>
+        <v>84.74790920829753</v>
       </c>
       <c r="L8" t="n">
-        <v>84.90955748125326</v>
+        <v>84.86462646123559</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.42114984482455</v>
+        <v>84.4211498448245</v>
       </c>
       <c r="C9" t="n">
-        <v>51.12835016847358</v>
+        <v>51.12835016847356</v>
       </c>
       <c r="D9" t="n">
-        <v>84.63614397100872</v>
+        <v>84.63614397100862</v>
       </c>
       <c r="E9" t="n">
-        <v>51.12835016847358</v>
+        <v>51.12835016847356</v>
       </c>
       <c r="F9" t="n">
-        <v>51.12835016847358</v>
+        <v>51.12835016847356</v>
       </c>
       <c r="G9" t="n">
-        <v>84.54022566223902</v>
+        <v>84.54022566223895</v>
       </c>
       <c r="H9" t="n">
-        <v>84.73419128725791</v>
+        <v>84.73419128725794</v>
       </c>
       <c r="I9" t="n">
-        <v>51.12835016847358</v>
+        <v>51.12835016847356</v>
       </c>
       <c r="J9" t="n">
-        <v>83.65753711587958</v>
+        <v>83.65753711587951</v>
       </c>
       <c r="K9" t="n">
-        <v>85.19681040392092</v>
+        <v>85.19681040392096</v>
       </c>
       <c r="L9" t="n">
-        <v>85.26418739282889</v>
+        <v>85.2641873928288</v>
       </c>
     </row>
   </sheetData>
@@ -1307,34 +1307,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>153.805889901716</v>
+        <v>153.805889901721</v>
       </c>
       <c r="C2" t="n">
-        <v>192.7077995843785</v>
+        <v>192.7077995843788</v>
       </c>
       <c r="D2" t="n">
-        <v>835.2240548025389</v>
+        <v>835.2240548025443</v>
       </c>
       <c r="E2" t="n">
-        <v>247.2262879838227</v>
+        <v>247.2262879838231</v>
       </c>
       <c r="F2" t="n">
-        <v>247.2262879838227</v>
+        <v>247.2262879838231</v>
       </c>
       <c r="G2" t="n">
-        <v>484.279517225381</v>
+        <v>484.2795172253723</v>
       </c>
       <c r="H2" t="n">
         <v>1242.011838424447</v>
       </c>
       <c r="I2" t="n">
-        <v>247.2262879838227</v>
+        <v>247.2262879838231</v>
       </c>
       <c r="J2" t="n">
-        <v>550.1007226345789</v>
+        <v>550.1007226345804</v>
       </c>
       <c r="K2" t="n">
-        <v>336.5405068717727</v>
+        <v>336.5405068717826</v>
       </c>
       <c r="L2" t="n">
         <v>539.833240016615</v>
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.53663371949862</v>
+        <v>34.53663371949865</v>
       </c>
       <c r="C3" t="n">
-        <v>33.41185162749318</v>
+        <v>33.41185162749314</v>
       </c>
       <c r="D3" t="n">
-        <v>34.53663371949862</v>
+        <v>34.53663371949867</v>
       </c>
       <c r="E3" t="n">
-        <v>32.92683665681616</v>
+        <v>32.92683665681596</v>
       </c>
       <c r="F3" t="n">
-        <v>32.92683665681615</v>
+        <v>32.92683665681595</v>
       </c>
       <c r="G3" t="n">
-        <v>34.37271041065229</v>
+        <v>34.3727104106522</v>
       </c>
       <c r="H3" t="n">
-        <v>34.53663371949862</v>
+        <v>34.53663371949867</v>
       </c>
       <c r="I3" t="n">
-        <v>33.49841119510502</v>
+        <v>33.49841119510492</v>
       </c>
       <c r="J3" t="n">
-        <v>34.53663371949861</v>
+        <v>34.53663371949867</v>
       </c>
       <c r="K3" t="n">
-        <v>34.53663371949862</v>
+        <v>34.53663371949867</v>
       </c>
       <c r="L3" t="n">
-        <v>34.53663371949862</v>
+        <v>34.53663371949867</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>213.0214130910861</v>
+        <v>138.6951628655318</v>
       </c>
       <c r="C4" t="n">
-        <v>137.8839071480101</v>
+        <v>137.8839071480099</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5189856248392</v>
+        <v>139.5189074795001</v>
       </c>
       <c r="E4" t="n">
-        <v>126.995719561849</v>
+        <v>126.9957195618489</v>
       </c>
       <c r="F4" t="n">
         <v>137.6403108413481</v>
       </c>
       <c r="G4" t="n">
-        <v>212.8574897822403</v>
+        <v>212.8574897822404</v>
       </c>
       <c r="H4" t="n">
-        <v>212.8123869709358</v>
+        <v>212.8123869709359</v>
       </c>
       <c r="I4" t="n">
-        <v>211.9831905666929</v>
+        <v>211.9831905666935</v>
       </c>
       <c r="J4" t="n">
         <v>211.6303860402627</v>
       </c>
       <c r="K4" t="n">
-        <v>138.543656459876</v>
+        <v>138.5436564598756</v>
       </c>
       <c r="L4" t="n">
-        <v>138.7997071230558</v>
+        <v>138.7997071230557</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.53325099782828</v>
+        <v>60.53325099782835</v>
       </c>
       <c r="C5" t="n">
-        <v>60.42451780104113</v>
+        <v>60.42451780104108</v>
       </c>
       <c r="D5" t="n">
-        <v>60.53285247562701</v>
+        <v>60.53285247562707</v>
       </c>
       <c r="E5" t="n">
-        <v>59.49692079225292</v>
+        <v>59.49692079225291</v>
       </c>
       <c r="F5" t="n">
-        <v>59.49692079225292</v>
+        <v>59.49692079225291</v>
       </c>
       <c r="G5" t="n">
-        <v>60.36932768898187</v>
+        <v>60.36932768898178</v>
       </c>
       <c r="H5" t="n">
-        <v>60.53325099782828</v>
+        <v>60.53325099782835</v>
       </c>
       <c r="I5" t="n">
-        <v>59.49502847343454</v>
+        <v>59.4950284734345</v>
       </c>
       <c r="J5" t="n">
-        <v>60.53325099782828</v>
+        <v>60.53325099782835</v>
       </c>
       <c r="K5" t="n">
-        <v>60.53325099782828</v>
+        <v>60.53325099782835</v>
       </c>
       <c r="L5" t="n">
-        <v>60.53325099782828</v>
+        <v>60.53325099782835</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133.8632873781847</v>
+        <v>133.8632873781846</v>
       </c>
       <c r="C6" t="n">
-        <v>199.42673065139</v>
+        <v>199.4267306516369</v>
       </c>
       <c r="D6" t="n">
-        <v>213.134652350422</v>
+        <v>213.1346523504217</v>
       </c>
       <c r="E6" t="n">
-        <v>180.538949828303</v>
+        <v>180.5389498283028</v>
       </c>
       <c r="F6" t="n">
-        <v>134.9076558728362</v>
+        <v>134.9076558728361</v>
       </c>
       <c r="G6" t="n">
         <v>199.3563295361437</v>
       </c>
       <c r="H6" t="n">
-        <v>199.5202528450557</v>
+        <v>199.5202528450556</v>
       </c>
       <c r="I6" t="n">
-        <v>198.4820303205965</v>
+        <v>198.4820303205963</v>
       </c>
       <c r="J6" t="n">
-        <v>199.5331563247211</v>
+        <v>199.533156324721</v>
       </c>
       <c r="K6" t="n">
         <v>132.6436755357946</v>
       </c>
       <c r="L6" t="n">
-        <v>268.1044434260325</v>
+        <v>268.1044434260322</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118.313101652769</v>
+        <v>118.3131016527691</v>
       </c>
       <c r="C7" t="n">
         <v>142.4813102394507</v>
       </c>
       <c r="D7" t="n">
-        <v>142.5900466263029</v>
+        <v>142.5900466263027</v>
       </c>
       <c r="E7" t="n">
-        <v>169.5668783455392</v>
+        <v>169.5668783455399</v>
       </c>
       <c r="F7" t="n">
-        <v>141.5518037007329</v>
+        <v>141.5518037007325</v>
       </c>
       <c r="G7" t="n">
-        <v>142.4261201273913</v>
+        <v>142.4261201273908</v>
       </c>
       <c r="H7" t="n">
-        <v>142.5900434362379</v>
+        <v>142.5900434362372</v>
       </c>
       <c r="I7" t="n">
         <v>141.5518209118441</v>
       </c>
       <c r="J7" t="n">
-        <v>142.5900434362379</v>
+        <v>142.5900434362372</v>
       </c>
       <c r="K7" t="n">
-        <v>112.0210394852854</v>
+        <v>128.5238893657265</v>
       </c>
       <c r="L7" t="n">
-        <v>142.5900434362379</v>
+        <v>142.5900434362372</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.84334298957436</v>
+        <v>30.84334298957424</v>
       </c>
       <c r="C8" t="n">
-        <v>26.2330310659343</v>
+        <v>26.23303106593428</v>
       </c>
       <c r="D8" t="n">
-        <v>23.33283459290364</v>
+        <v>23.33283459290334</v>
       </c>
       <c r="E8" t="n">
-        <v>42.17695367714153</v>
+        <v>42.17695367714152</v>
       </c>
       <c r="F8" t="n">
-        <v>42.17695367714153</v>
+        <v>42.17695367714152</v>
       </c>
       <c r="G8" t="n">
-        <v>67.26711411372139</v>
+        <v>67.26711411372142</v>
       </c>
       <c r="H8" t="n">
         <v>17.16958251464332</v>
       </c>
       <c r="I8" t="n">
-        <v>42.17695367714153</v>
+        <v>42.17695367714152</v>
       </c>
       <c r="J8" t="n">
-        <v>66.1311188464358</v>
+        <v>66.13111884643567</v>
       </c>
       <c r="K8" t="n">
-        <v>144.6296931928792</v>
+        <v>144.6296931928788</v>
       </c>
       <c r="L8" t="n">
-        <v>24.95351044707929</v>
+        <v>24.95351044707932</v>
       </c>
     </row>
     <row r="9">
@@ -1590,16 +1590,16 @@
         <v>32.25790601828461</v>
       </c>
       <c r="C9" t="n">
-        <v>27.65818010029135</v>
+        <v>27.65818010029131</v>
       </c>
       <c r="D9" t="n">
-        <v>33.42609727636483</v>
+        <v>33.42609727636487</v>
       </c>
       <c r="E9" t="n">
-        <v>44.11723995822205</v>
+        <v>44.117239958222</v>
       </c>
       <c r="F9" t="n">
-        <v>44.11723995822205</v>
+        <v>44.117239958222</v>
       </c>
       <c r="G9" t="n">
         <v>71.83670729292841</v>
@@ -1608,16 +1608,16 @@
         <v>30.9373923389164</v>
       </c>
       <c r="I9" t="n">
-        <v>44.11723995822205</v>
+        <v>44.117239958222</v>
       </c>
       <c r="J9" t="n">
         <v>71.42198596386154</v>
       </c>
       <c r="K9" t="n">
-        <v>146.1579199804114</v>
+        <v>146.1579199804113</v>
       </c>
       <c r="L9" t="n">
-        <v>30.21137913454776</v>
+        <v>30.21137913454772</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119.5510801883936</v>
+        <v>119.5510801883931</v>
       </c>
       <c r="C2" t="n">
-        <v>188.7288202762803</v>
+        <v>188.7288202762735</v>
       </c>
       <c r="D2" t="n">
-        <v>597.8941965709472</v>
+        <v>597.894196570947</v>
       </c>
       <c r="E2" t="n">
-        <v>187.3913349313348</v>
+        <v>187.3913349313343</v>
       </c>
       <c r="F2" t="n">
-        <v>187.3913349313348</v>
+        <v>187.3913349313343</v>
       </c>
       <c r="G2" t="n">
-        <v>330.2349855313209</v>
+        <v>330.23498553131</v>
       </c>
       <c r="H2" t="n">
-        <v>696.4236405097788</v>
+        <v>696.4236405097782</v>
       </c>
       <c r="I2" t="n">
-        <v>187.3913349313348</v>
+        <v>187.3913349313343</v>
       </c>
       <c r="J2" t="n">
-        <v>371.3087594552597</v>
+        <v>371.3087594552593</v>
       </c>
       <c r="K2" t="n">
-        <v>215.5757448959252</v>
+        <v>215.5757448959246</v>
       </c>
       <c r="L2" t="n">
-        <v>247.5610727203474</v>
+        <v>247.561072720347</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.23209715581754</v>
+        <v>34.23209715581718</v>
       </c>
       <c r="C3" t="n">
-        <v>33.17807866077258</v>
+        <v>33.17807866077253</v>
       </c>
       <c r="D3" t="n">
-        <v>34.23209715581754</v>
+        <v>34.23209715581718</v>
       </c>
       <c r="E3" t="n">
-        <v>32.83400708082713</v>
+        <v>32.83400708082704</v>
       </c>
       <c r="F3" t="n">
-        <v>32.83400708082713</v>
+        <v>32.83400708082708</v>
       </c>
       <c r="G3" t="n">
-        <v>34.07115309985794</v>
+        <v>34.07115309985775</v>
       </c>
       <c r="H3" t="n">
-        <v>34.23209715581754</v>
+        <v>34.23209715581718</v>
       </c>
       <c r="I3" t="n">
-        <v>33.2129954066796</v>
+        <v>33.21299540667955</v>
       </c>
       <c r="J3" t="n">
-        <v>34.23209715581754</v>
+        <v>34.23209715581718</v>
       </c>
       <c r="K3" t="n">
-        <v>34.23209715581754</v>
+        <v>34.23209715581718</v>
       </c>
       <c r="L3" t="n">
-        <v>34.23209715581754</v>
+        <v>34.23209715581718</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>202.4843439176426</v>
+        <v>202.4843439176421</v>
       </c>
       <c r="C4" t="n">
-        <v>132.0136009668151</v>
+        <v>132.0136009668144</v>
       </c>
       <c r="D4" t="n">
-        <v>133.1692075288685</v>
+        <v>201.4621273686061</v>
       </c>
       <c r="E4" t="n">
         <v>121.602732451836</v>
       </c>
       <c r="F4" t="n">
-        <v>131.5692274770063</v>
+        <v>131.5692274770062</v>
       </c>
       <c r="G4" t="n">
-        <v>132.430049580967</v>
+        <v>132.4300495809667</v>
       </c>
       <c r="H4" t="n">
-        <v>202.8321352290338</v>
+        <v>202.8321352290334</v>
       </c>
       <c r="I4" t="n">
-        <v>131.5718918877887</v>
+        <v>131.5718918877886</v>
       </c>
       <c r="J4" t="n">
-        <v>137.843415885914</v>
+        <v>137.8434158859137</v>
       </c>
       <c r="K4" t="n">
-        <v>132.4198495939639</v>
+        <v>132.4198495939638</v>
       </c>
       <c r="L4" t="n">
-        <v>132.6183509954425</v>
+        <v>132.6183509954421</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.38436185912137</v>
+        <v>58.38436185912121</v>
       </c>
       <c r="C5" t="n">
         <v>58.28088085066567</v>
       </c>
       <c r="D5" t="n">
-        <v>58.38400981838609</v>
+        <v>58.38400981838613</v>
       </c>
       <c r="E5" t="n">
-        <v>57.4076638495771</v>
+        <v>57.40766384957709</v>
       </c>
       <c r="F5" t="n">
-        <v>57.4076638495771</v>
+        <v>57.40766384957709</v>
       </c>
       <c r="G5" t="n">
-        <v>58.22341780316179</v>
+        <v>58.22341780316178</v>
       </c>
       <c r="H5" t="n">
-        <v>58.38436185912137</v>
+        <v>58.38436185912121</v>
       </c>
       <c r="I5" t="n">
-        <v>57.36526010998355</v>
+        <v>57.36526010998351</v>
       </c>
       <c r="J5" t="n">
-        <v>58.38436185912137</v>
+        <v>58.38436185912121</v>
       </c>
       <c r="K5" t="n">
-        <v>58.38436185912137</v>
+        <v>58.38436185912121</v>
       </c>
       <c r="L5" t="n">
-        <v>58.38436185912137</v>
+        <v>58.38436185912121</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>127.7158787371701</v>
+        <v>127.7158787371698</v>
       </c>
       <c r="C6" t="n">
-        <v>189.4349457283731</v>
+        <v>189.4349457286771</v>
       </c>
       <c r="D6" t="n">
-        <v>202.2935839313085</v>
+        <v>202.2935839313082</v>
       </c>
       <c r="E6" t="n">
         <v>171.6202258444989</v>
       </c>
       <c r="F6" t="n">
-        <v>128.6802779504087</v>
+        <v>128.6802779504085</v>
       </c>
       <c r="G6" t="n">
-        <v>189.3243493525409</v>
+        <v>189.324349352541</v>
       </c>
       <c r="H6" t="n">
-        <v>189.4852934086919</v>
+        <v>189.4852934086916</v>
       </c>
       <c r="I6" t="n">
         <v>188.4661916593627</v>
       </c>
       <c r="J6" t="n">
-        <v>189.4974328722932</v>
+        <v>189.497432872293</v>
       </c>
       <c r="K6" t="n">
-        <v>126.5684801466603</v>
+        <v>126.5684801466599</v>
       </c>
       <c r="L6" t="n">
-        <v>254.008612111573</v>
+        <v>254.0086121115725</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106.3530091326787</v>
+        <v>106.3530091326785</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2268702460905</v>
+        <v>127.2268702460903</v>
       </c>
       <c r="D7" t="n">
-        <v>127.3303565572286</v>
+        <v>127.3303565572284</v>
       </c>
       <c r="E7" t="n">
         <v>150.5186491323527</v>
       </c>
       <c r="F7" t="n">
-        <v>126.3112389584274</v>
+        <v>126.3112389584273</v>
       </c>
       <c r="G7" t="n">
-        <v>127.1694071985866</v>
+        <v>127.1694071985863</v>
       </c>
       <c r="H7" t="n">
-        <v>127.3303512545461</v>
+        <v>127.3303512545458</v>
       </c>
       <c r="I7" t="n">
-        <v>126.3112495054081</v>
+        <v>126.3112495054082</v>
       </c>
       <c r="J7" t="n">
-        <v>127.3303512545461</v>
+        <v>127.3303512545458</v>
       </c>
       <c r="K7" t="n">
-        <v>115.1759990750529</v>
+        <v>115.1759990750526</v>
       </c>
       <c r="L7" t="n">
-        <v>127.3303512545461</v>
+        <v>127.3303512545458</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.22591955806435</v>
+        <v>31.2259195580644</v>
       </c>
       <c r="C8" t="n">
-        <v>25.93977085287139</v>
+        <v>25.93977085287161</v>
       </c>
       <c r="D8" t="n">
-        <v>27.67588858395616</v>
+        <v>27.67588858395611</v>
       </c>
       <c r="E8" t="n">
-        <v>43.11221104488295</v>
+        <v>43.11221104488301</v>
       </c>
       <c r="F8" t="n">
-        <v>43.11221104488295</v>
+        <v>43.11221104488301</v>
       </c>
       <c r="G8" t="n">
-        <v>70.03228799023334</v>
+        <v>70.03228799023331</v>
       </c>
       <c r="H8" t="n">
-        <v>27.12213585216868</v>
+        <v>27.12213585216853</v>
       </c>
       <c r="I8" t="n">
-        <v>43.11221104488295</v>
+        <v>43.11221104488301</v>
       </c>
       <c r="J8" t="n">
-        <v>69.26585897978305</v>
+        <v>69.26585897978295</v>
       </c>
       <c r="K8" t="n">
         <v>146.7837081064747</v>
       </c>
       <c r="L8" t="n">
-        <v>30.25334329449315</v>
+        <v>30.25334329449301</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.25462758416887</v>
+        <v>32.25462758416871</v>
       </c>
       <c r="C9" t="n">
-        <v>27.432106607275</v>
+        <v>27.43210660727507</v>
       </c>
       <c r="D9" t="n">
-        <v>34.95782032134466</v>
+        <v>34.95782032134463</v>
       </c>
       <c r="E9" t="n">
-        <v>44.36436016157593</v>
+        <v>44.36436016157598</v>
       </c>
       <c r="F9" t="n">
-        <v>44.36436016157593</v>
+        <v>44.36436016157598</v>
       </c>
       <c r="G9" t="n">
-        <v>72.78034307763515</v>
+        <v>72.78034307763498</v>
       </c>
       <c r="H9" t="n">
-        <v>34.74429715375617</v>
+        <v>34.7442971537559</v>
       </c>
       <c r="I9" t="n">
-        <v>44.36436016157593</v>
+        <v>44.36436016157598</v>
       </c>
       <c r="J9" t="n">
-        <v>72.48300526538904</v>
+        <v>72.48300526538895</v>
       </c>
       <c r="K9" t="n">
-        <v>146.8085414384958</v>
+        <v>146.8085414384956</v>
       </c>
       <c r="L9" t="n">
-        <v>32.19360957930049</v>
+        <v>32.19360957930037</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100.418520805983</v>
+        <v>100.4185208059831</v>
       </c>
       <c r="C2" t="n">
-        <v>177.3834385069242</v>
+        <v>177.3834385069253</v>
       </c>
       <c r="D2" t="n">
-        <v>445.4929266523079</v>
+        <v>445.492926652308</v>
       </c>
       <c r="E2" t="n">
-        <v>141.7517452141939</v>
+        <v>141.7517452141923</v>
       </c>
       <c r="F2" t="n">
-        <v>141.7517452141939</v>
+        <v>141.7517452141923</v>
       </c>
       <c r="G2" t="n">
-        <v>239.9327957715644</v>
+        <v>239.9327957715425</v>
       </c>
       <c r="H2" t="n">
-        <v>430.5294371160463</v>
+        <v>430.529437116045</v>
       </c>
       <c r="I2" t="n">
-        <v>141.7517452141939</v>
+        <v>141.7517452141923</v>
       </c>
       <c r="J2" t="n">
-        <v>228.9780939387209</v>
+        <v>228.9780939387203</v>
       </c>
       <c r="K2" t="n">
-        <v>159.447226157689</v>
+        <v>159.4472261576891</v>
       </c>
       <c r="L2" t="n">
-        <v>163.4816160649818</v>
+        <v>163.4816160649821</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.07085988126757</v>
+        <v>34.07085988126759</v>
       </c>
       <c r="C3" t="n">
-        <v>33.05321759053055</v>
+        <v>33.05321759053058</v>
       </c>
       <c r="D3" t="n">
-        <v>34.07085988126757</v>
+        <v>34.07085988126759</v>
       </c>
       <c r="E3" t="n">
-        <v>32.72429416614018</v>
+        <v>32.72429416614005</v>
       </c>
       <c r="F3" t="n">
-        <v>32.72429416614018</v>
+        <v>32.72429416614005</v>
       </c>
       <c r="G3" t="n">
-        <v>33.91154680160085</v>
+        <v>33.91154680160086</v>
       </c>
       <c r="H3" t="n">
-        <v>34.07085988126757</v>
+        <v>34.07085988126759</v>
       </c>
       <c r="I3" t="n">
-        <v>33.06222036230588</v>
+        <v>33.06222036230609</v>
       </c>
       <c r="J3" t="n">
-        <v>34.07085988126757</v>
+        <v>34.07085988126759</v>
       </c>
       <c r="K3" t="n">
-        <v>34.07085988126757</v>
+        <v>34.07085988126759</v>
       </c>
       <c r="L3" t="n">
-        <v>34.07085988126757</v>
+        <v>34.07085988126759</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>201.7451648541642</v>
+        <v>132.1687273450332</v>
       </c>
       <c r="C4" t="n">
-        <v>131.7105805580886</v>
+        <v>131.710580558075</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5823997341531</v>
+        <v>132.5823997341501</v>
       </c>
       <c r="E4" t="n">
-        <v>121.2574953322677</v>
+        <v>121.257495332268</v>
       </c>
       <c r="F4" t="n">
         <v>131.1563751045059</v>
       </c>
       <c r="G4" t="n">
-        <v>132.0094142653664</v>
+        <v>201.5858517744981</v>
       </c>
       <c r="H4" t="n">
         <v>202.0734399927276</v>
       </c>
       <c r="I4" t="n">
-        <v>131.1600878260713</v>
+        <v>200.7365253352028</v>
       </c>
       <c r="J4" t="n">
-        <v>137.3631039610076</v>
+        <v>200.4656850174503</v>
       </c>
       <c r="K4" t="n">
         <v>132.0192215287398</v>
       </c>
       <c r="L4" t="n">
-        <v>132.1766044600765</v>
+        <v>132.1766044600769</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.84998969825286</v>
+        <v>57.8499896982529</v>
       </c>
       <c r="C5" t="n">
-        <v>57.7497223539208</v>
+        <v>57.74972235392084</v>
       </c>
       <c r="D5" t="n">
-        <v>57.84963342880931</v>
+        <v>57.84963342880929</v>
       </c>
       <c r="E5" t="n">
-        <v>56.89213344579181</v>
+        <v>56.89213344579173</v>
       </c>
       <c r="F5" t="n">
-        <v>56.89213344579181</v>
+        <v>56.89213344579173</v>
       </c>
       <c r="G5" t="n">
-        <v>57.69067661858624</v>
+        <v>57.69067661858605</v>
       </c>
       <c r="H5" t="n">
-        <v>57.84998969825286</v>
+        <v>57.8499896982529</v>
       </c>
       <c r="I5" t="n">
-        <v>56.84135017929145</v>
+        <v>56.84135017929131</v>
       </c>
       <c r="J5" t="n">
-        <v>57.84998969825286</v>
+        <v>57.8499896982529</v>
       </c>
       <c r="K5" t="n">
-        <v>57.84998969825286</v>
+        <v>57.8499896982529</v>
       </c>
       <c r="L5" t="n">
-        <v>57.84998969825286</v>
+        <v>57.8499896982529</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>126.9834917405942</v>
+        <v>126.983491740594</v>
       </c>
       <c r="C6" t="n">
-        <v>188.3016375712786</v>
+        <v>188.3016375709247</v>
       </c>
       <c r="D6" t="n">
-        <v>201.0636536358903</v>
+        <v>201.0636536358905</v>
       </c>
       <c r="E6" t="n">
         <v>170.60600545656</v>
       </c>
       <c r="F6" t="n">
-        <v>127.9502917859661</v>
+        <v>127.9502917859662</v>
       </c>
       <c r="G6" t="n">
-        <v>188.18150022399</v>
+        <v>188.1815002239898</v>
       </c>
       <c r="H6" t="n">
-        <v>188.34081330385</v>
+        <v>188.3408133038501</v>
       </c>
       <c r="I6" t="n">
         <v>187.332173784695</v>
       </c>
       <c r="J6" t="n">
-        <v>188.3528717791562</v>
+        <v>188.3528717791561</v>
       </c>
       <c r="K6" t="n">
         <v>125.8437479910902</v>
       </c>
       <c r="L6" t="n">
-        <v>252.4336662964267</v>
+        <v>252.4336662964268</v>
       </c>
     </row>
     <row r="7">
@@ -2299,34 +2299,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100.970376992</v>
+        <v>100.9703769919997</v>
       </c>
       <c r="C7" t="n">
-        <v>120.3820373431715</v>
+        <v>120.3820373431718</v>
       </c>
       <c r="D7" t="n">
-        <v>120.4823105226758</v>
+        <v>120.4823105226757</v>
       </c>
       <c r="E7" t="n">
         <v>141.9900116705486</v>
       </c>
       <c r="F7" t="n">
-        <v>119.4736574774984</v>
+        <v>119.4736574774983</v>
       </c>
       <c r="G7" t="n">
-        <v>120.3229916078371</v>
+        <v>120.3229916078369</v>
       </c>
       <c r="H7" t="n">
         <v>120.4823046875035</v>
       </c>
       <c r="I7" t="n">
-        <v>119.4736651685422</v>
+        <v>119.4736651685423</v>
       </c>
       <c r="J7" t="n">
         <v>120.4823046875035</v>
       </c>
       <c r="K7" t="n">
-        <v>108.7183496725056</v>
+        <v>95.91330333975036</v>
       </c>
       <c r="L7" t="n">
         <v>120.4823046875035</v>
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.45153157207482</v>
+        <v>31.45153157207486</v>
       </c>
       <c r="C8" t="n">
-        <v>25.97137153607486</v>
+        <v>25.97137153607489</v>
       </c>
       <c r="D8" t="n">
-        <v>30.97490487506742</v>
+        <v>30.9749048750675</v>
       </c>
       <c r="E8" t="n">
-        <v>43.888218268967</v>
+        <v>43.88821826896711</v>
       </c>
       <c r="F8" t="n">
-        <v>43.888218268967</v>
+        <v>43.88821826896711</v>
       </c>
       <c r="G8" t="n">
-        <v>71.92636078205599</v>
+        <v>71.92636078205578</v>
       </c>
       <c r="H8" t="n">
-        <v>32.42448717434855</v>
+        <v>32.42448717434864</v>
       </c>
       <c r="I8" t="n">
-        <v>43.888218268967</v>
+        <v>43.88821826896711</v>
       </c>
       <c r="J8" t="n">
-        <v>72.14072548261407</v>
+        <v>72.14072548261431</v>
       </c>
       <c r="K8" t="n">
         <v>148.1281191978712</v>
       </c>
       <c r="L8" t="n">
-        <v>31.76434701938748</v>
+        <v>31.76434701938749</v>
       </c>
     </row>
     <row r="9">
@@ -2382,34 +2382,34 @@
         <v>32.2153621920467</v>
       </c>
       <c r="C9" t="n">
-        <v>27.3081104496459</v>
+        <v>27.30811044964591</v>
       </c>
       <c r="D9" t="n">
-        <v>36.05984884874838</v>
+        <v>36.05984884874847</v>
       </c>
       <c r="E9" t="n">
-        <v>44.4927694204325</v>
+        <v>44.49276942043255</v>
       </c>
       <c r="F9" t="n">
-        <v>44.4927694204325</v>
+        <v>44.49276942043255</v>
       </c>
       <c r="G9" t="n">
-        <v>73.41074861161324</v>
+        <v>73.41074861161329</v>
       </c>
       <c r="H9" t="n">
         <v>36.65703678077307</v>
       </c>
       <c r="I9" t="n">
-        <v>44.4927694204325</v>
+        <v>44.49276942043255</v>
       </c>
       <c r="J9" t="n">
-        <v>73.40947125368393</v>
+        <v>73.409471253684</v>
       </c>
       <c r="K9" t="n">
-        <v>147.3453817360241</v>
+        <v>147.3453817360242</v>
       </c>
       <c r="L9" t="n">
-        <v>32.65646301447444</v>
+        <v>32.65646301447445</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116.5107253538644</v>
+        <v>116.5107253538645</v>
       </c>
       <c r="C2" t="n">
-        <v>161.1439906150657</v>
+        <v>161.1439906150658</v>
       </c>
       <c r="D2" t="n">
-        <v>519.9052507227576</v>
+        <v>519.9052507227595</v>
       </c>
       <c r="E2" t="n">
-        <v>196.8062126276208</v>
+        <v>196.8062126276212</v>
       </c>
       <c r="F2" t="n">
-        <v>196.8062126276208</v>
+        <v>196.8062126276212</v>
       </c>
       <c r="G2" t="n">
-        <v>349.3963930928383</v>
+        <v>349.3963930928358</v>
       </c>
       <c r="H2" t="n">
-        <v>1004.161385287358</v>
+        <v>1004.161385287359</v>
       </c>
       <c r="I2" t="n">
-        <v>196.8062126276208</v>
+        <v>196.8062126276212</v>
       </c>
       <c r="J2" t="n">
-        <v>528.396803304326</v>
+        <v>528.3968033043255</v>
       </c>
       <c r="K2" t="n">
-        <v>264.0083523823187</v>
+        <v>264.0083523823184</v>
       </c>
       <c r="L2" t="n">
-        <v>528.9125242425836</v>
+        <v>528.9125242425841</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.02595885034165</v>
+        <v>34.02595885034164</v>
       </c>
       <c r="C3" t="n">
-        <v>32.97203073662598</v>
+        <v>32.972030736626</v>
       </c>
       <c r="D3" t="n">
-        <v>34.02595885034165</v>
+        <v>34.02595885034164</v>
       </c>
       <c r="E3" t="n">
-        <v>32.7299994122964</v>
+        <v>32.72999941229633</v>
       </c>
       <c r="F3" t="n">
-        <v>32.72999941229637</v>
+        <v>32.72999941229633</v>
       </c>
       <c r="G3" t="n">
-        <v>33.86541890175344</v>
+        <v>33.86541890175346</v>
       </c>
       <c r="H3" t="n">
-        <v>34.02595885034165</v>
+        <v>34.02595885034164</v>
       </c>
       <c r="I3" t="n">
-        <v>33.00910553105659</v>
+        <v>33.00910553105657</v>
       </c>
       <c r="J3" t="n">
-        <v>34.02595885034165</v>
+        <v>34.02595885034164</v>
       </c>
       <c r="K3" t="n">
-        <v>34.02595885034165</v>
+        <v>34.02595885034164</v>
       </c>
       <c r="L3" t="n">
-        <v>34.02595885034165</v>
+        <v>34.02595885034164</v>
       </c>
     </row>
     <row r="4">
@@ -2575,34 +2575,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>211.5619073458496</v>
+        <v>137.9425585735734</v>
       </c>
       <c r="C4" t="n">
-        <v>137.2862459675079</v>
+        <v>137.2862459675076</v>
       </c>
       <c r="D4" t="n">
-        <v>138.3325191982779</v>
+        <v>138.3325191982725</v>
       </c>
       <c r="E4" t="n">
-        <v>126.4223729865619</v>
+        <v>126.4223729865624</v>
       </c>
       <c r="F4" t="n">
-        <v>136.9312803481974</v>
+        <v>136.9312803481973</v>
       </c>
       <c r="G4" t="n">
         <v>137.7820186249851</v>
       </c>
       <c r="H4" t="n">
-        <v>211.2410754122504</v>
+        <v>211.2410754122502</v>
       </c>
       <c r="I4" t="n">
-        <v>210.5450540265648</v>
+        <v>136.9257052542883</v>
       </c>
       <c r="J4" t="n">
-        <v>210.1399221813102</v>
+        <v>210.1399221813101</v>
       </c>
       <c r="K4" t="n">
-        <v>137.8419955057379</v>
+        <v>137.8419955057377</v>
       </c>
       <c r="L4" t="n">
         <v>138.0550245343694</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.31009710967129</v>
+        <v>59.31009710967125</v>
       </c>
       <c r="C5" t="n">
-        <v>59.20651589428831</v>
+        <v>59.20651589428824</v>
       </c>
       <c r="D5" t="n">
-        <v>59.30970625975664</v>
+        <v>59.30970625975658</v>
       </c>
       <c r="E5" t="n">
-        <v>58.36355311814543</v>
+        <v>58.36355311814535</v>
       </c>
       <c r="F5" t="n">
-        <v>58.36355311814543</v>
+        <v>58.36355311814535</v>
       </c>
       <c r="G5" t="n">
-        <v>59.14955716108302</v>
+        <v>59.14955716108297</v>
       </c>
       <c r="H5" t="n">
-        <v>59.31009710967129</v>
+        <v>59.31009710967125</v>
       </c>
       <c r="I5" t="n">
-        <v>58.2932437903862</v>
+        <v>58.29324379038615</v>
       </c>
       <c r="J5" t="n">
-        <v>59.31009710967129</v>
+        <v>59.31009710967125</v>
       </c>
       <c r="K5" t="n">
-        <v>59.31009710967129</v>
+        <v>59.31009710967125</v>
       </c>
       <c r="L5" t="n">
-        <v>59.31009710967129</v>
+        <v>59.31009710967125</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>132.1306318650758</v>
+        <v>132.1306318650756</v>
       </c>
       <c r="C6" t="n">
-        <v>196.8384730102667</v>
+        <v>196.8384730102661</v>
       </c>
       <c r="D6" t="n">
-        <v>210.2840526758635</v>
+        <v>210.2840526758629</v>
       </c>
       <c r="E6" t="n">
-        <v>178.2132688003759</v>
+        <v>178.2132688003756</v>
       </c>
       <c r="F6" t="n">
-        <v>133.2078280691442</v>
+        <v>133.2078280691438</v>
       </c>
       <c r="G6" t="n">
-        <v>196.7011136805851</v>
+        <v>196.7011136805849</v>
       </c>
       <c r="H6" t="n">
-        <v>196.861653629224</v>
+        <v>196.8616536292234</v>
       </c>
       <c r="I6" t="n">
-        <v>195.8448003098882</v>
+        <v>195.8448003098879</v>
       </c>
       <c r="J6" t="n">
-        <v>196.8743751342957</v>
+        <v>196.8743751342953</v>
       </c>
       <c r="K6" t="n">
-        <v>130.9282199023593</v>
+        <v>130.928219902359</v>
       </c>
       <c r="L6" t="n">
-        <v>264.478618586439</v>
+        <v>264.4786185864381</v>
       </c>
     </row>
     <row r="7">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114.3183852075004</v>
+        <v>114.3183852075003</v>
       </c>
       <c r="C7" t="n">
         <v>137.463142390021</v>
@@ -2704,28 +2704,28 @@
         <v>137.5667254559366</v>
       </c>
       <c r="E7" t="n">
-        <v>163.3779430002519</v>
+        <v>163.3779430002518</v>
       </c>
       <c r="F7" t="n">
-        <v>136.5498554657074</v>
+        <v>136.5498554657075</v>
       </c>
       <c r="G7" t="n">
-        <v>137.4061836568158</v>
+        <v>137.4061836568156</v>
       </c>
       <c r="H7" t="n">
-        <v>137.566723605404</v>
+        <v>137.5667236054039</v>
       </c>
       <c r="I7" t="n">
-        <v>136.5498702861188</v>
+        <v>136.5498702861187</v>
       </c>
       <c r="J7" t="n">
-        <v>137.566723605404</v>
+        <v>137.5667236054039</v>
       </c>
       <c r="K7" t="n">
-        <v>108.2929152691113</v>
+        <v>108.2929152691115</v>
       </c>
       <c r="L7" t="n">
-        <v>137.566723605404</v>
+        <v>137.5667236054039</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.24152483911652</v>
+        <v>32.24152483911651</v>
       </c>
       <c r="C8" t="n">
-        <v>26.56487465455827</v>
+        <v>26.56487465455824</v>
       </c>
       <c r="D8" t="n">
-        <v>29.9933501949944</v>
+        <v>29.9933501949943</v>
       </c>
       <c r="E8" t="n">
-        <v>42.92217252002938</v>
+        <v>42.92217252002936</v>
       </c>
       <c r="F8" t="n">
-        <v>42.92217252002938</v>
+        <v>42.92217252002936</v>
       </c>
       <c r="G8" t="n">
-        <v>69.85030102319786</v>
+        <v>69.85030102319777</v>
       </c>
       <c r="H8" t="n">
-        <v>21.39156377429394</v>
+        <v>21.3915637742939</v>
       </c>
       <c r="I8" t="n">
-        <v>42.92217252002938</v>
+        <v>42.92217252002936</v>
       </c>
       <c r="J8" t="n">
-        <v>66.06874404948604</v>
+        <v>66.06874404948601</v>
       </c>
       <c r="K8" t="n">
-        <v>145.6144610875486</v>
+        <v>145.6144610875483</v>
       </c>
       <c r="L8" t="n">
-        <v>24.78500035835186</v>
+        <v>24.78500035835183</v>
       </c>
     </row>
     <row r="9">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.15397122142994</v>
+        <v>33.15397122142992</v>
       </c>
       <c r="C9" t="n">
-        <v>27.57829293816935</v>
+        <v>27.57829293816933</v>
       </c>
       <c r="D9" t="n">
-        <v>35.78028334649606</v>
+        <v>35.78028334649603</v>
       </c>
       <c r="E9" t="n">
         <v>44.18870725157949</v>
@@ -2790,22 +2790,22 @@
         <v>44.18870725157949</v>
       </c>
       <c r="G9" t="n">
-        <v>72.63604488813007</v>
+        <v>72.63604488813009</v>
       </c>
       <c r="H9" t="n">
-        <v>32.294047275351</v>
+        <v>32.29404727535099</v>
       </c>
       <c r="I9" t="n">
         <v>44.18870725157949</v>
       </c>
       <c r="J9" t="n">
-        <v>71.08855302269372</v>
+        <v>71.08855302269366</v>
       </c>
       <c r="K9" t="n">
-        <v>146.1671260643635</v>
+        <v>146.1671260643633</v>
       </c>
       <c r="L9" t="n">
-        <v>29.92198226687296</v>
+        <v>29.92198226687292</v>
       </c>
     </row>
   </sheetData>
@@ -2894,34 +2894,34 @@
         <v>103.3081020888935</v>
       </c>
       <c r="C2" t="n">
-        <v>156.3162966363878</v>
+        <v>156.316296636388</v>
       </c>
       <c r="D2" t="n">
-        <v>155.9234167650048</v>
+        <v>155.9234167650049</v>
       </c>
       <c r="E2" t="n">
-        <v>165.7148273278712</v>
+        <v>165.7148273278739</v>
       </c>
       <c r="F2" t="n">
-        <v>165.7148273278712</v>
+        <v>165.7148273278739</v>
       </c>
       <c r="G2" t="n">
-        <v>159.9344149488044</v>
+        <v>159.9344149488054</v>
       </c>
       <c r="H2" t="n">
-        <v>212.7781268534477</v>
+        <v>212.7781268534479</v>
       </c>
       <c r="I2" t="n">
-        <v>165.7148273278712</v>
+        <v>165.7148273278739</v>
       </c>
       <c r="J2" t="n">
-        <v>255.0066875947315</v>
+        <v>255.0066875947318</v>
       </c>
       <c r="K2" t="n">
-        <v>145.1838009934165</v>
+        <v>145.1838009934166</v>
       </c>
       <c r="L2" t="n">
-        <v>186.4247909142284</v>
+        <v>186.4247909142287</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.62827358908615</v>
+        <v>33.62827358908616</v>
       </c>
       <c r="C3" t="n">
         <v>32.69664801578453</v>
       </c>
       <c r="D3" t="n">
-        <v>33.62827358908615</v>
+        <v>33.62827358908616</v>
       </c>
       <c r="E3" t="n">
         <v>32.52390506678805</v>
       </c>
       <c r="F3" t="n">
-        <v>32.52390506678806</v>
+        <v>32.52390506678805</v>
       </c>
       <c r="G3" t="n">
         <v>33.47324172042738</v>
       </c>
       <c r="H3" t="n">
-        <v>33.62827358908615</v>
+        <v>33.62827358908616</v>
       </c>
       <c r="I3" t="n">
         <v>32.64673652425927</v>
       </c>
       <c r="J3" t="n">
-        <v>33.62827358908615</v>
+        <v>33.62827358908616</v>
       </c>
       <c r="K3" t="n">
-        <v>33.62827358908615</v>
+        <v>33.62827358908616</v>
       </c>
       <c r="L3" t="n">
-        <v>33.62827358908615</v>
+        <v>33.62827358908616</v>
       </c>
     </row>
     <row r="4">
@@ -2974,25 +2974,25 @@
         <v>131.6973636052138</v>
       </c>
       <c r="C4" t="n">
-        <v>131.3196972240847</v>
+        <v>131.319697224085</v>
       </c>
       <c r="D4" t="n">
-        <v>199.5219108454669</v>
+        <v>131.615226673812</v>
       </c>
       <c r="E4" t="n">
-        <v>120.997274101708</v>
+        <v>120.9972741017079</v>
       </c>
       <c r="F4" t="n">
-        <v>130.7429743046539</v>
+        <v>130.7429743046537</v>
       </c>
       <c r="G4" t="n">
-        <v>131.542331736555</v>
+        <v>200.5245195609703</v>
       </c>
       <c r="H4" t="n">
         <v>200.797509373814</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7158265403869</v>
+        <v>199.6980143648023</v>
       </c>
       <c r="J4" t="n">
         <v>136.8816912318781</v>
@@ -3001,7 +3001,7 @@
         <v>131.6110472087909</v>
       </c>
       <c r="L4" t="n">
-        <v>131.7112718427869</v>
+        <v>131.7112718427867</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.73065617254063</v>
+        <v>56.73065617254074</v>
       </c>
       <c r="C5" t="n">
-        <v>56.63446821961377</v>
+        <v>56.63446821961381</v>
       </c>
       <c r="D5" t="n">
-        <v>56.73030603415403</v>
+        <v>56.73030603415413</v>
       </c>
       <c r="E5" t="n">
-        <v>55.83937550330994</v>
+        <v>55.83937550331003</v>
       </c>
       <c r="F5" t="n">
-        <v>55.83937550330994</v>
+        <v>55.83937550331003</v>
       </c>
       <c r="G5" t="n">
-        <v>56.57562430388201</v>
+        <v>56.57562430388207</v>
       </c>
       <c r="H5" t="n">
-        <v>56.73065617254063</v>
+        <v>56.73065617254074</v>
       </c>
       <c r="I5" t="n">
-        <v>55.74911910771384</v>
+        <v>55.74911910771391</v>
       </c>
       <c r="J5" t="n">
-        <v>56.73065617254063</v>
+        <v>56.73065617254074</v>
       </c>
       <c r="K5" t="n">
-        <v>56.73065617254063</v>
+        <v>56.73065617254074</v>
       </c>
       <c r="L5" t="n">
-        <v>56.73065617254063</v>
+        <v>56.73065617254074</v>
       </c>
     </row>
     <row r="6">
@@ -3051,16 +3051,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.2615926882041</v>
+        <v>125.2615926882042</v>
       </c>
       <c r="C6" t="n">
-        <v>185.6332263066214</v>
+        <v>185.6332263066215</v>
       </c>
       <c r="D6" t="n">
-        <v>198.1487729629223</v>
+        <v>198.1487729629224</v>
       </c>
       <c r="E6" t="n">
-        <v>168.2269113245816</v>
+        <v>168.2269113245814</v>
       </c>
       <c r="F6" t="n">
         <v>126.2477181164817</v>
@@ -3072,16 +3072,16 @@
         <v>185.6308203401742</v>
       </c>
       <c r="I6" t="n">
-        <v>184.6492832751815</v>
+        <v>184.6492832751816</v>
       </c>
       <c r="J6" t="n">
-        <v>185.6426846268946</v>
+        <v>185.6426846268947</v>
       </c>
       <c r="K6" t="n">
         <v>124.140203290446</v>
       </c>
       <c r="L6" t="n">
-        <v>248.6915266194231</v>
+        <v>248.691526619423</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.774115466153</v>
+        <v>101.7741154661531</v>
       </c>
       <c r="C7" t="n">
-        <v>121.458261677585</v>
+        <v>121.4582616775851</v>
       </c>
       <c r="D7" t="n">
         <v>121.5544554869212</v>
       </c>
       <c r="E7" t="n">
-        <v>143.3989981540275</v>
+        <v>143.3989981540276</v>
       </c>
       <c r="F7" t="n">
-        <v>120.5729078292142</v>
+        <v>120.5729078292143</v>
       </c>
       <c r="G7" t="n">
         <v>121.3994177618532</v>
       </c>
       <c r="H7" t="n">
-        <v>121.5544496305119</v>
+        <v>121.554449630512</v>
       </c>
       <c r="I7" t="n">
         <v>120.5729125656851</v>
       </c>
       <c r="J7" t="n">
-        <v>121.5544496305119</v>
+        <v>121.554449630512</v>
       </c>
       <c r="K7" t="n">
-        <v>110.0936487955069</v>
+        <v>96.64747662258056</v>
       </c>
       <c r="L7" t="n">
-        <v>121.5544496305119</v>
+        <v>121.554449630512</v>
       </c>
     </row>
     <row r="8">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.39178077874357</v>
+        <v>32.39178077874358</v>
       </c>
       <c r="C8" t="n">
         <v>26.14046043465797</v>
@@ -3140,28 +3140,28 @@
         <v>37.66585374732855</v>
       </c>
       <c r="E8" t="n">
-        <v>43.00548765412401</v>
+        <v>43.00548765412402</v>
       </c>
       <c r="F8" t="n">
-        <v>43.00548765412401</v>
+        <v>43.00548765412402</v>
       </c>
       <c r="G8" t="n">
-        <v>73.36617402600243</v>
+        <v>73.36617402600251</v>
       </c>
       <c r="H8" t="n">
-        <v>36.73633216987943</v>
+        <v>36.73633216987945</v>
       </c>
       <c r="I8" t="n">
-        <v>43.00548765412401</v>
+        <v>43.00548765412402</v>
       </c>
       <c r="J8" t="n">
-        <v>70.91445016173648</v>
+        <v>70.91445016173645</v>
       </c>
       <c r="K8" t="n">
-        <v>147.3391243831614</v>
+        <v>147.3391243831617</v>
       </c>
       <c r="L8" t="n">
-        <v>30.86232642113449</v>
+        <v>30.8623264211345</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.18125873378367</v>
+        <v>33.18125873378369</v>
       </c>
       <c r="C9" t="n">
-        <v>27.1883979832606</v>
+        <v>27.18839798326061</v>
       </c>
       <c r="D9" t="n">
         <v>38.57123772335738</v>
       </c>
       <c r="E9" t="n">
-        <v>43.96077500536154</v>
+        <v>43.96077500536156</v>
       </c>
       <c r="F9" t="n">
-        <v>43.96077500536154</v>
+        <v>43.96077500536156</v>
       </c>
       <c r="G9" t="n">
-        <v>73.73685862718992</v>
+        <v>73.73685862718996</v>
       </c>
       <c r="H9" t="n">
         <v>38.19524360524102</v>
       </c>
       <c r="I9" t="n">
-        <v>43.96077500536154</v>
+        <v>43.96077500536156</v>
       </c>
       <c r="J9" t="n">
-        <v>72.55277456701828</v>
+        <v>72.55277456701829</v>
       </c>
       <c r="K9" t="n">
-        <v>146.3711181551492</v>
+        <v>146.3711181551495</v>
       </c>
       <c r="L9" t="n">
-        <v>32.05014302255373</v>
+        <v>32.05014302255376</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86.92518736735684</v>
+        <v>86.92518736735681</v>
       </c>
       <c r="C2" t="n">
-        <v>141.6176582057857</v>
+        <v>141.6176582057855</v>
       </c>
       <c r="D2" t="n">
-        <v>151.7213545127889</v>
+        <v>151.7213545127887</v>
       </c>
       <c r="E2" t="n">
-        <v>143.9515846879993</v>
+        <v>143.9515846879985</v>
       </c>
       <c r="F2" t="n">
-        <v>143.9515846879993</v>
+        <v>143.9515846879985</v>
       </c>
       <c r="G2" t="n">
-        <v>141.849543930333</v>
+        <v>141.8495439303324</v>
       </c>
       <c r="H2" t="n">
-        <v>171.8332732477233</v>
+        <v>171.8332732477231</v>
       </c>
       <c r="I2" t="n">
-        <v>143.9515846879993</v>
+        <v>143.9515846879985</v>
       </c>
       <c r="J2" t="n">
-        <v>170.1108745309247</v>
+        <v>170.1108745309248</v>
       </c>
       <c r="K2" t="n">
-        <v>127.683891726396</v>
+        <v>127.6838917263956</v>
       </c>
       <c r="L2" t="n">
-        <v>144.2087629792358</v>
+        <v>144.2087629792356</v>
       </c>
     </row>
     <row r="3">
@@ -3330,25 +3330,25 @@
         <v>33.7907434775792</v>
       </c>
       <c r="C3" t="n">
-        <v>32.85673704833354</v>
+        <v>32.85673704833351</v>
       </c>
       <c r="D3" t="n">
         <v>33.7907434775792</v>
       </c>
       <c r="E3" t="n">
-        <v>32.63546364679193</v>
+        <v>32.63546364679186</v>
       </c>
       <c r="F3" t="n">
-        <v>32.63546364679192</v>
+        <v>32.63546364679185</v>
       </c>
       <c r="G3" t="n">
-        <v>33.6352949103996</v>
+        <v>33.63529491040205</v>
       </c>
       <c r="H3" t="n">
         <v>33.7907434775792</v>
       </c>
       <c r="I3" t="n">
-        <v>32.80670207419738</v>
+        <v>32.80670207420022</v>
       </c>
       <c r="J3" t="n">
         <v>33.7907434775792</v>
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.9272043961424</v>
+        <v>200.9272043961422</v>
       </c>
       <c r="C4" t="n">
-        <v>131.4820307778951</v>
+        <v>131.482030777895</v>
       </c>
       <c r="D4" t="n">
         <v>131.7932744471842</v>
@@ -3382,22 +3382,22 @@
         <v>130.8939203906289</v>
       </c>
       <c r="G4" t="n">
-        <v>200.7717558289626</v>
+        <v>200.7717558289623</v>
       </c>
       <c r="H4" t="n">
-        <v>201.1343468137242</v>
+        <v>201.1343468137241</v>
       </c>
       <c r="I4" t="n">
-        <v>130.8713249372908</v>
+        <v>130.8713249372906</v>
       </c>
       <c r="J4" t="n">
-        <v>199.6165563838085</v>
+        <v>199.6165563838086</v>
       </c>
       <c r="K4" t="n">
-        <v>131.7712084456769</v>
+        <v>131.7712084456753</v>
       </c>
       <c r="L4" t="n">
-        <v>131.8623487078525</v>
+        <v>131.8623487078524</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.71134648959032</v>
+        <v>56.7113464895903</v>
       </c>
       <c r="C5" t="n">
-        <v>56.61483904631382</v>
+        <v>56.61483904631375</v>
       </c>
       <c r="D5" t="n">
-        <v>56.71098530310027</v>
+        <v>56.71098530310023</v>
       </c>
       <c r="E5" t="n">
-        <v>55.80884218235553</v>
+        <v>55.80884218235543</v>
       </c>
       <c r="F5" t="n">
-        <v>55.80884218235553</v>
+        <v>55.80884218235543</v>
       </c>
       <c r="G5" t="n">
-        <v>56.55589792241069</v>
+        <v>56.55589792241065</v>
       </c>
       <c r="H5" t="n">
-        <v>56.71134648959032</v>
+        <v>56.7113464895903</v>
       </c>
       <c r="I5" t="n">
-        <v>55.72730508620847</v>
+        <v>55.72730508620837</v>
       </c>
       <c r="J5" t="n">
-        <v>56.71134648959032</v>
+        <v>56.7113464895903</v>
       </c>
       <c r="K5" t="n">
-        <v>56.71134648959032</v>
+        <v>56.7113464895903</v>
       </c>
       <c r="L5" t="n">
-        <v>56.71134648959032</v>
+        <v>56.7113464895903</v>
       </c>
     </row>
     <row r="6">
@@ -3447,34 +3447,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.2571714960268</v>
+        <v>125.257171496027</v>
       </c>
       <c r="C6" t="n">
         <v>185.5529856878796</v>
       </c>
       <c r="D6" t="n">
-        <v>198.0632183965425</v>
+        <v>198.0632183965423</v>
       </c>
       <c r="E6" t="n">
-        <v>168.1637095604813</v>
+        <v>168.1637095604812</v>
       </c>
       <c r="F6" t="n">
-        <v>126.2334675816813</v>
+        <v>126.2334675816812</v>
       </c>
       <c r="G6" t="n">
-        <v>185.4037513954275</v>
+        <v>185.4037513954273</v>
       </c>
       <c r="H6" t="n">
         <v>185.5591999627805</v>
       </c>
       <c r="I6" t="n">
-        <v>184.5751585592252</v>
+        <v>184.5751585592251</v>
       </c>
       <c r="J6" t="n">
         <v>185.5710510411593</v>
       </c>
       <c r="K6" t="n">
-        <v>124.1370303577365</v>
+        <v>124.1370303577366</v>
       </c>
       <c r="L6" t="n">
         <v>248.5497110724195</v>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.44146068101621</v>
+        <v>98.44146068101622</v>
       </c>
       <c r="C7" t="n">
         <v>117.1755986651603</v>
@@ -3496,7 +3496,7 @@
         <v>117.2721121205853</v>
       </c>
       <c r="E7" t="n">
-        <v>138.0182302848612</v>
+        <v>138.0182302848611</v>
       </c>
       <c r="F7" t="n">
         <v>116.2880603817454</v>
@@ -3508,13 +3508,13 @@
         <v>117.2721061084368</v>
       </c>
       <c r="I7" t="n">
-        <v>116.288064705055</v>
+        <v>116.2880647050549</v>
       </c>
       <c r="J7" t="n">
         <v>117.2721061084368</v>
       </c>
       <c r="K7" t="n">
-        <v>106.3615587228328</v>
+        <v>105.9189037893854</v>
       </c>
       <c r="L7" t="n">
         <v>117.2721061084368</v>
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.29705702209459</v>
+        <v>33.29705702209455</v>
       </c>
       <c r="C8" t="n">
-        <v>26.39622116569852</v>
+        <v>26.39622116569851</v>
       </c>
       <c r="D8" t="n">
-        <v>37.64883896859979</v>
+        <v>37.64883896859978</v>
       </c>
       <c r="E8" t="n">
         <v>43.42870921131162</v>
@@ -3542,22 +3542,22 @@
         <v>43.42870921131162</v>
       </c>
       <c r="G8" t="n">
-        <v>73.91222430035762</v>
+        <v>73.91222430035756</v>
       </c>
       <c r="H8" t="n">
-        <v>37.49758219044017</v>
+        <v>37.49758219044016</v>
       </c>
       <c r="I8" t="n">
         <v>43.42870921131162</v>
       </c>
       <c r="J8" t="n">
-        <v>72.83781372266699</v>
+        <v>72.83781372266691</v>
       </c>
       <c r="K8" t="n">
-        <v>148.2423148102327</v>
+        <v>148.2423148102326</v>
       </c>
       <c r="L8" t="n">
-        <v>31.67508742391203</v>
+        <v>31.67508742391202</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.84747835843961</v>
+        <v>33.84747835843957</v>
       </c>
       <c r="C9" t="n">
         <v>27.23725568976714</v>
       </c>
       <c r="D9" t="n">
-        <v>38.49398311257259</v>
+        <v>38.49398311257254</v>
       </c>
       <c r="E9" t="n">
-        <v>44.07266852634393</v>
+        <v>44.07266852634392</v>
       </c>
       <c r="F9" t="n">
-        <v>44.07266852634393</v>
+        <v>44.07266852634392</v>
       </c>
       <c r="G9" t="n">
-        <v>74.02579255766474</v>
+        <v>74.0257925576647</v>
       </c>
       <c r="H9" t="n">
-        <v>38.43415214476246</v>
+        <v>38.43415214476244</v>
       </c>
       <c r="I9" t="n">
-        <v>44.07266852634393</v>
+        <v>44.07266852634392</v>
       </c>
       <c r="J9" t="n">
-        <v>73.30918895853961</v>
+        <v>73.30918895853952</v>
       </c>
       <c r="K9" t="n">
         <v>147.0134552749606</v>
       </c>
       <c r="L9" t="n">
-        <v>32.33448046635844</v>
+        <v>32.33448046635841</v>
       </c>
     </row>
   </sheetData>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117.2070136106042</v>
+        <v>117.2070136105715</v>
       </c>
       <c r="C2" t="n">
-        <v>170.7281443133368</v>
+        <v>170.7281443133369</v>
       </c>
       <c r="D2" t="n">
-        <v>210.5820383690395</v>
+        <v>210.5820383689993</v>
       </c>
       <c r="E2" t="n">
         <v>192.2063230167402</v>
@@ -3698,22 +3698,22 @@
         <v>192.2063230167402</v>
       </c>
       <c r="G2" t="n">
-        <v>224.9475555846505</v>
+        <v>224.9475555846375</v>
       </c>
       <c r="H2" t="n">
-        <v>852.5641928623418</v>
+        <v>852.5641928623018</v>
       </c>
       <c r="I2" t="n">
         <v>192.2063230167402</v>
       </c>
       <c r="J2" t="n">
-        <v>219.1738397841708</v>
+        <v>219.1738397841361</v>
       </c>
       <c r="K2" t="n">
-        <v>188.048544934757</v>
+        <v>188.0485449347208</v>
       </c>
       <c r="L2" t="n">
-        <v>455.2073439299548</v>
+        <v>455.2073439299133</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.72171754742257</v>
+        <v>33.72171754740493</v>
       </c>
       <c r="C3" t="n">
-        <v>32.76300080770095</v>
+        <v>32.76300080770094</v>
       </c>
       <c r="D3" t="n">
-        <v>33.72171754742257</v>
+        <v>33.72171754740493</v>
       </c>
       <c r="E3" t="n">
-        <v>32.56907445155265</v>
+        <v>32.56907445155272</v>
       </c>
       <c r="F3" t="n">
-        <v>32.56907445155265</v>
+        <v>32.56907445155272</v>
       </c>
       <c r="G3" t="n">
-        <v>33.56547923851586</v>
+        <v>33.56547923850734</v>
       </c>
       <c r="H3" t="n">
-        <v>33.72171754742257</v>
+        <v>33.72171754740493</v>
       </c>
       <c r="I3" t="n">
-        <v>32.73223316531952</v>
+        <v>32.73223316531975</v>
       </c>
       <c r="J3" t="n">
-        <v>33.72171754742257</v>
+        <v>33.72171754740493</v>
       </c>
       <c r="K3" t="n">
-        <v>33.72171754742257</v>
+        <v>33.72171754740493</v>
       </c>
       <c r="L3" t="n">
-        <v>33.72171754742257</v>
+        <v>33.72171754740493</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>210.4257317660333</v>
+        <v>137.3438594479896</v>
       </c>
       <c r="C4" t="n">
-        <v>136.8909562929623</v>
+        <v>136.8909562929624</v>
       </c>
       <c r="D4" t="n">
-        <v>137.2788259825482</v>
+        <v>137.2788259825422</v>
       </c>
       <c r="E4" t="n">
-        <v>126.046184595153</v>
+        <v>126.0461845951531</v>
       </c>
       <c r="F4" t="n">
-        <v>136.3782980015126</v>
+        <v>136.3782980015125</v>
       </c>
       <c r="G4" t="n">
-        <v>210.2694934571262</v>
+        <v>210.2694934571067</v>
       </c>
       <c r="H4" t="n">
-        <v>210.0449486880531</v>
+        <v>210.0449486880247</v>
       </c>
       <c r="I4" t="n">
-        <v>136.3543750659296</v>
+        <v>209.4362473839309</v>
       </c>
       <c r="J4" t="n">
-        <v>208.9594073381655</v>
+        <v>208.9594073381528</v>
       </c>
       <c r="K4" t="n">
-        <v>137.2499876868169</v>
+        <v>137.2499876867807</v>
       </c>
       <c r="L4" t="n">
-        <v>137.433586106188</v>
+        <v>137.4335861061751</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.34728117733005</v>
+        <v>58.34728117733626</v>
       </c>
       <c r="C5" t="n">
-        <v>58.24962076688352</v>
+        <v>58.24962076688349</v>
       </c>
       <c r="D5" t="n">
-        <v>58.34689487974245</v>
+        <v>58.34689487970982</v>
       </c>
       <c r="E5" t="n">
-        <v>57.4413023975158</v>
+        <v>57.44130239751581</v>
       </c>
       <c r="F5" t="n">
-        <v>57.4413023975158</v>
+        <v>57.44130239751581</v>
       </c>
       <c r="G5" t="n">
-        <v>58.19104286842315</v>
+        <v>58.19104286840117</v>
       </c>
       <c r="H5" t="n">
-        <v>58.34728117733005</v>
+        <v>58.34728117733626</v>
       </c>
       <c r="I5" t="n">
         <v>57.35779679522724</v>
       </c>
       <c r="J5" t="n">
-        <v>58.34728117733005</v>
+        <v>58.34728117733626</v>
       </c>
       <c r="K5" t="n">
-        <v>58.34728117733005</v>
+        <v>58.34728117733626</v>
       </c>
       <c r="L5" t="n">
-        <v>58.34728117733005</v>
+        <v>58.34728117733626</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130.6741056816126</v>
+        <v>130.674105681589</v>
       </c>
       <c r="C6" t="n">
-        <v>194.5412112857186</v>
+        <v>194.5412112857184</v>
       </c>
       <c r="D6" t="n">
-        <v>207.7902934841443</v>
+        <v>207.7902934841278</v>
       </c>
       <c r="E6" t="n">
-        <v>176.1710966923445</v>
+        <v>176.1710966923449</v>
       </c>
       <c r="F6" t="n">
-        <v>131.7593083651291</v>
+        <v>131.7593083651293</v>
       </c>
       <c r="G6" t="n">
-        <v>194.3897949124524</v>
+        <v>194.3897949124325</v>
       </c>
       <c r="H6" t="n">
-        <v>194.5460332214075</v>
+        <v>194.5460332213937</v>
       </c>
       <c r="I6" t="n">
-        <v>193.5565488392565</v>
+        <v>193.5565488392566</v>
       </c>
       <c r="J6" t="n">
-        <v>194.5585858897831</v>
+        <v>194.5585858897775</v>
       </c>
       <c r="K6" t="n">
-        <v>129.4876518351787</v>
+        <v>129.4876518351554</v>
       </c>
       <c r="L6" t="n">
-        <v>261.2656024249316</v>
+        <v>261.2656024249096</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.986137315198</v>
+        <v>110.9861373151682</v>
       </c>
       <c r="C7" t="n">
-        <v>133.2441535787597</v>
+        <v>133.2441535787598</v>
       </c>
       <c r="D7" t="n">
-        <v>133.3418133853483</v>
+        <v>133.3418133853326</v>
       </c>
       <c r="E7" t="n">
-        <v>158.1502893127422</v>
+        <v>158.1502893127423</v>
       </c>
       <c r="F7" t="n">
-        <v>132.3523163163817</v>
+        <v>132.3523163163818</v>
       </c>
       <c r="G7" t="n">
-        <v>133.1855756802994</v>
+        <v>133.185575680278</v>
       </c>
       <c r="H7" t="n">
-        <v>133.3418139892062</v>
+        <v>133.3418139892024</v>
       </c>
       <c r="I7" t="n">
-        <v>132.3523296071034</v>
+        <v>132.3523296071037</v>
       </c>
       <c r="J7" t="n">
-        <v>133.3418139892062</v>
+        <v>133.3418139892024</v>
       </c>
       <c r="K7" t="n">
-        <v>119.8633286593282</v>
+        <v>120.3888468727844</v>
       </c>
       <c r="L7" t="n">
-        <v>133.3418139892062</v>
+        <v>133.3418139892024</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.27810950552492</v>
+        <v>32.27810950551294</v>
       </c>
       <c r="C8" t="n">
         <v>26.23087880769722</v>
       </c>
       <c r="D8" t="n">
-        <v>36.76953651602203</v>
+        <v>36.76953651602052</v>
       </c>
       <c r="E8" t="n">
-        <v>42.68680381628658</v>
+        <v>42.68680381628661</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68680381628658</v>
+        <v>42.68680381628661</v>
       </c>
       <c r="G8" t="n">
-        <v>72.18879924185454</v>
+        <v>72.18879924184409</v>
       </c>
       <c r="H8" t="n">
-        <v>24.10937738589385</v>
+        <v>24.10937738589122</v>
       </c>
       <c r="I8" t="n">
-        <v>42.68680381628658</v>
+        <v>42.68680381628661</v>
       </c>
       <c r="J8" t="n">
-        <v>72.07282876434067</v>
+        <v>72.07282876433892</v>
       </c>
       <c r="K8" t="n">
-        <v>146.5289018265884</v>
+        <v>146.52890182658</v>
       </c>
       <c r="L8" t="n">
-        <v>25.88255655688491</v>
+        <v>25.88255655687458</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.19831108228986</v>
+        <v>33.19831108228358</v>
       </c>
       <c r="C9" t="n">
         <v>27.37452836717105</v>
       </c>
       <c r="D9" t="n">
-        <v>38.32609156643252</v>
+        <v>38.32609156641254</v>
       </c>
       <c r="E9" t="n">
-        <v>43.89784770664691</v>
+        <v>43.89784770664694</v>
       </c>
       <c r="F9" t="n">
-        <v>43.89784770664691</v>
+        <v>43.89784770664694</v>
       </c>
       <c r="G9" t="n">
-        <v>73.32756673145158</v>
+        <v>73.3275667314453</v>
       </c>
       <c r="H9" t="n">
-        <v>33.18420469407231</v>
+        <v>33.18420469405835</v>
       </c>
       <c r="I9" t="n">
-        <v>43.89784770664691</v>
+        <v>43.89784770664694</v>
       </c>
       <c r="J9" t="n">
-        <v>73.08184417087655</v>
+        <v>73.08184417086485</v>
       </c>
       <c r="K9" t="n">
-        <v>146.0593943277048</v>
+        <v>146.0593943276943</v>
       </c>
       <c r="L9" t="n">
-        <v>30.15215183147566</v>
+        <v>30.15215183146859</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105.001082999016</v>
+        <v>105.0010829990151</v>
       </c>
       <c r="C2" t="n">
-        <v>160.9552989639604</v>
+        <v>160.9552989639599</v>
       </c>
       <c r="D2" t="n">
-        <v>153.8711174156847</v>
+        <v>153.8711174156837</v>
       </c>
       <c r="E2" t="n">
-        <v>162.5264268503079</v>
+        <v>162.5264268503046</v>
       </c>
       <c r="F2" t="n">
-        <v>162.5264268503079</v>
+        <v>162.5264268503046</v>
       </c>
       <c r="G2" t="n">
-        <v>148.747154545668</v>
+        <v>148.7471545456644</v>
       </c>
       <c r="H2" t="n">
-        <v>177.0006965532554</v>
+        <v>177.0006965532544</v>
       </c>
       <c r="I2" t="n">
-        <v>162.5264268503079</v>
+        <v>162.5264268503046</v>
       </c>
       <c r="J2" t="n">
-        <v>184.652714942944</v>
+        <v>184.6527149429432</v>
       </c>
       <c r="K2" t="n">
-        <v>140.6410254781334</v>
+        <v>140.6410254781321</v>
       </c>
       <c r="L2" t="n">
-        <v>149.2501217993026</v>
+        <v>149.2501217993013</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.50378407960456</v>
+        <v>33.50378407960429</v>
       </c>
       <c r="C3" t="n">
-        <v>32.57418369681265</v>
+        <v>32.57418369681262</v>
       </c>
       <c r="D3" t="n">
-        <v>33.50378407960456</v>
+        <v>33.50378407960429</v>
       </c>
       <c r="E3" t="n">
-        <v>32.475532825672</v>
+        <v>32.47553282567199</v>
       </c>
       <c r="F3" t="n">
-        <v>32.475532825672</v>
+        <v>32.47553282567198</v>
       </c>
       <c r="G3" t="n">
-        <v>33.34899031876866</v>
+        <v>33.34899031876837</v>
       </c>
       <c r="H3" t="n">
-        <v>33.50378407960456</v>
+        <v>33.50378407960429</v>
       </c>
       <c r="I3" t="n">
-        <v>32.5236769459456</v>
+        <v>32.52367694594545</v>
       </c>
       <c r="J3" t="n">
-        <v>33.50378407960456</v>
+        <v>33.50378407960429</v>
       </c>
       <c r="K3" t="n">
-        <v>33.50378407960456</v>
+        <v>33.50378407960429</v>
       </c>
       <c r="L3" t="n">
-        <v>33.50378407960456</v>
+        <v>33.50378407960429</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.4826667655665</v>
+        <v>131.5829759727751</v>
       </c>
       <c r="C4" t="n">
-        <v>131.2281554049262</v>
+        <v>131.2281554049266</v>
       </c>
       <c r="D4" t="n">
-        <v>131.5100896033973</v>
+        <v>131.5100113808302</v>
       </c>
       <c r="E4" t="n">
-        <v>120.9068795828336</v>
+        <v>120.9068795828334</v>
       </c>
       <c r="F4" t="n">
-        <v>130.6338412324735</v>
+        <v>130.6338412324734</v>
       </c>
       <c r="G4" t="n">
-        <v>131.4281822119393</v>
+        <v>131.4281822119391</v>
       </c>
       <c r="H4" t="n">
-        <v>200.5628122960845</v>
+        <v>200.5628122960843</v>
       </c>
       <c r="I4" t="n">
-        <v>130.6028688391164</v>
+        <v>199.5025596319074</v>
       </c>
       <c r="J4" t="n">
-        <v>136.7391750513912</v>
+        <v>199.1499639807623</v>
       </c>
       <c r="K4" t="n">
-        <v>131.5036760440365</v>
+        <v>131.5036760440363</v>
       </c>
       <c r="L4" t="n">
-        <v>131.5851703431968</v>
+        <v>131.5851703431967</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.3021638474091</v>
+        <v>56.30216384740896</v>
       </c>
       <c r="C5" t="n">
-        <v>56.20670945622784</v>
+        <v>56.20670945622778</v>
       </c>
       <c r="D5" t="n">
-        <v>56.30182022899723</v>
+        <v>56.30182022899708</v>
       </c>
       <c r="E5" t="n">
-        <v>55.4323559645735</v>
+        <v>55.43235596457355</v>
       </c>
       <c r="F5" t="n">
-        <v>55.4323559645735</v>
+        <v>55.43235596457355</v>
       </c>
       <c r="G5" t="n">
-        <v>56.14737008657305</v>
+        <v>56.14737008657295</v>
       </c>
       <c r="H5" t="n">
-        <v>56.3021638474091</v>
+        <v>56.30216384740896</v>
       </c>
       <c r="I5" t="n">
         <v>55.32205671375007</v>
       </c>
       <c r="J5" t="n">
-        <v>56.3021638474091</v>
+        <v>56.30216384740896</v>
       </c>
       <c r="K5" t="n">
-        <v>56.3021638474091</v>
+        <v>56.30216384740896</v>
       </c>
       <c r="L5" t="n">
-        <v>56.3021638474091</v>
+        <v>56.30216384740896</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>124.5656577336884</v>
+        <v>124.5656577336879</v>
       </c>
       <c r="C6" t="n">
-        <v>184.5357783245758</v>
+        <v>184.5357783245754</v>
       </c>
       <c r="D6" t="n">
-        <v>196.9441665627697</v>
+        <v>196.9441665627689</v>
       </c>
       <c r="E6" t="n">
-        <v>167.243373196446</v>
+        <v>167.2433731964462</v>
       </c>
       <c r="F6" t="n">
-        <v>125.5518108613363</v>
+        <v>125.5518108613356</v>
       </c>
       <c r="G6" t="n">
-        <v>184.3587815645632</v>
+        <v>184.3587815645618</v>
       </c>
       <c r="H6" t="n">
-        <v>184.5135753255596</v>
+        <v>184.5135753255589</v>
       </c>
       <c r="I6" t="n">
-        <v>183.5334681917402</v>
+        <v>183.5334681917394</v>
       </c>
       <c r="J6" t="n">
-        <v>184.5253568127225</v>
+        <v>184.5253568127218</v>
       </c>
       <c r="K6" t="n">
-        <v>123.4520943866023</v>
+        <v>123.4520943866017</v>
       </c>
       <c r="L6" t="n">
-        <v>247.1341880176071</v>
+        <v>247.1341880176061</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.2172381219483</v>
+        <v>101.2172381219474</v>
       </c>
       <c r="C7" t="n">
-        <v>120.7571982606067</v>
+        <v>120.7571982606059</v>
       </c>
       <c r="D7" t="n">
-        <v>120.8526585284277</v>
+        <v>120.8526585284268</v>
       </c>
       <c r="E7" t="n">
-        <v>142.5313976221668</v>
+        <v>142.5313976221664</v>
       </c>
       <c r="F7" t="n">
-        <v>119.8725413279383</v>
+        <v>119.8725413279377</v>
       </c>
       <c r="G7" t="n">
-        <v>120.6978588909518</v>
+        <v>120.697858890951</v>
       </c>
       <c r="H7" t="n">
-        <v>120.8526526517879</v>
+        <v>120.8526526517871</v>
       </c>
       <c r="I7" t="n">
-        <v>119.8725455181287</v>
+        <v>119.8725455181281</v>
       </c>
       <c r="J7" t="n">
-        <v>120.8526526517879</v>
+        <v>120.8526526517871</v>
       </c>
       <c r="K7" t="n">
-        <v>96.12815932653615</v>
+        <v>109.4758188306747</v>
       </c>
       <c r="L7" t="n">
-        <v>120.8526526517879</v>
+        <v>120.8526526517871</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35.42778551943387</v>
+        <v>35.42778551943381</v>
       </c>
       <c r="C8" t="n">
         <v>26.15520119506518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.49116327904927</v>
+        <v>37.49116327904929</v>
       </c>
       <c r="E8" t="n">
-        <v>42.95031178758204</v>
+        <v>42.95031178758205</v>
       </c>
       <c r="F8" t="n">
-        <v>42.95031178758204</v>
+        <v>42.95031178758206</v>
       </c>
       <c r="G8" t="n">
-        <v>73.69008582645809</v>
+        <v>73.69008582645806</v>
       </c>
       <c r="H8" t="n">
         <v>37.28158345346975</v>
       </c>
       <c r="I8" t="n">
-        <v>42.95031178758204</v>
+        <v>42.95031178758206</v>
       </c>
       <c r="J8" t="n">
-        <v>72.2077198476199</v>
+        <v>72.20771984761981</v>
       </c>
       <c r="K8" t="n">
-        <v>146.3011687607508</v>
+        <v>146.301168760751</v>
       </c>
       <c r="L8" t="n">
-        <v>31.4608557095431</v>
+        <v>31.46085570954308</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.19325890396084</v>
+        <v>36.19325890396074</v>
       </c>
       <c r="C9" t="n">
-        <v>27.26677188657279</v>
+        <v>27.26677188657278</v>
       </c>
       <c r="D9" t="n">
-        <v>38.37121760825908</v>
+        <v>38.37121760825906</v>
       </c>
       <c r="E9" t="n">
-        <v>43.86290301676583</v>
+        <v>43.86290301676576</v>
       </c>
       <c r="F9" t="n">
-        <v>43.86290301676583</v>
+        <v>43.86290301676576</v>
       </c>
       <c r="G9" t="n">
-        <v>73.9035680640611</v>
+        <v>73.90356806406103</v>
       </c>
       <c r="H9" t="n">
         <v>38.28773731509732</v>
       </c>
       <c r="I9" t="n">
-        <v>43.86290301676583</v>
+        <v>43.86290301676576</v>
       </c>
       <c r="J9" t="n">
-        <v>72.88554055799315</v>
+        <v>72.88554055799312</v>
       </c>
       <c r="K9" t="n">
-        <v>145.2865420884977</v>
+        <v>145.2865420884976</v>
       </c>
       <c r="L9" t="n">
-        <v>32.18694697647837</v>
+        <v>32.18694697647828</v>
       </c>
     </row>
   </sheetData>
@@ -4475,13 +4475,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.50171429729468</v>
+        <v>89.5017142972948</v>
       </c>
       <c r="C2" t="n">
-        <v>145.2453453550563</v>
+        <v>145.2453453550594</v>
       </c>
       <c r="D2" t="n">
-        <v>150.6824351342629</v>
+        <v>150.682435134263</v>
       </c>
       <c r="E2" t="n">
         <v>143.5835784117011</v>
@@ -4490,22 +4490,22 @@
         <v>143.5835784117011</v>
       </c>
       <c r="G2" t="n">
-        <v>141.4268071456567</v>
+        <v>141.426807145656</v>
       </c>
       <c r="H2" t="n">
-        <v>168.2831851021037</v>
+        <v>168.2831851021038</v>
       </c>
       <c r="I2" t="n">
         <v>143.5835784117011</v>
       </c>
       <c r="J2" t="n">
-        <v>172.3479023195404</v>
+        <v>172.3479023195405</v>
       </c>
       <c r="K2" t="n">
         <v>133.9161247780787</v>
       </c>
       <c r="L2" t="n">
-        <v>143.0410283334779</v>
+        <v>143.0410283334778</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.61630938278149</v>
+        <v>33.61630938278159</v>
       </c>
       <c r="C3" t="n">
-        <v>32.6763605398281</v>
+        <v>32.67636053982795</v>
       </c>
       <c r="D3" t="n">
-        <v>33.61630938278149</v>
+        <v>33.61630938278159</v>
       </c>
       <c r="E3" t="n">
-        <v>32.52772857580768</v>
+        <v>32.52772857580775</v>
       </c>
       <c r="F3" t="n">
-        <v>32.52772857580762</v>
+        <v>32.52772857580774</v>
       </c>
       <c r="G3" t="n">
-        <v>33.46039835451733</v>
+        <v>33.46039835451738</v>
       </c>
       <c r="H3" t="n">
-        <v>33.61630938278149</v>
+        <v>33.61630938278159</v>
       </c>
       <c r="I3" t="n">
-        <v>32.62910221331591</v>
+        <v>32.62910221331601</v>
       </c>
       <c r="J3" t="n">
-        <v>33.61630938278149</v>
+        <v>33.61630938278159</v>
       </c>
       <c r="K3" t="n">
-        <v>33.61630938278149</v>
+        <v>33.61630938278159</v>
       </c>
       <c r="L3" t="n">
-        <v>33.61630938278149</v>
+        <v>33.61630938278159</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.6669424567114</v>
+        <v>131.6931598738542</v>
       </c>
       <c r="C4" t="n">
-        <v>131.3237103280785</v>
+        <v>131.3237103280792</v>
       </c>
       <c r="D4" t="n">
-        <v>131.6284810732344</v>
+        <v>131.6284810732345</v>
       </c>
       <c r="E4" t="n">
-        <v>120.9809375554101</v>
+        <v>120.9809375554102</v>
       </c>
       <c r="F4" t="n">
         <v>130.7319653110395</v>
       </c>
       <c r="G4" t="n">
-        <v>200.511031428447</v>
+        <v>200.5110314284468</v>
       </c>
       <c r="H4" t="n">
         <v>200.8203924446277</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7059527043887</v>
+        <v>199.6797352872453</v>
       </c>
       <c r="J4" t="n">
-        <v>199.3425360137322</v>
+        <v>136.8494551476501</v>
       </c>
       <c r="K4" t="n">
         <v>131.6197014004369</v>
       </c>
       <c r="L4" t="n">
-        <v>131.7019377275211</v>
+        <v>131.7019377275208</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.24527014434258</v>
+        <v>56.24527014434255</v>
       </c>
       <c r="C5" t="n">
-        <v>56.14899886390238</v>
+        <v>56.14899886390229</v>
       </c>
       <c r="D5" t="n">
-        <v>56.24491404948752</v>
+        <v>56.24491404948754</v>
       </c>
       <c r="E5" t="n">
-        <v>55.3599500387071</v>
+        <v>55.35995003870717</v>
       </c>
       <c r="F5" t="n">
-        <v>55.3599500387071</v>
+        <v>55.35995003870717</v>
       </c>
       <c r="G5" t="n">
-        <v>56.08935911607839</v>
+        <v>56.08935911607834</v>
       </c>
       <c r="H5" t="n">
-        <v>56.24527014434258</v>
+        <v>56.24527014434255</v>
       </c>
       <c r="I5" t="n">
-        <v>55.25806297487695</v>
+        <v>55.25806297487697</v>
       </c>
       <c r="J5" t="n">
-        <v>56.24527014434258</v>
+        <v>56.24527014434255</v>
       </c>
       <c r="K5" t="n">
-        <v>56.24527014434258</v>
+        <v>56.24527014434255</v>
       </c>
       <c r="L5" t="n">
-        <v>56.24527014434258</v>
+        <v>56.24527014434255</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>124.4918271690012</v>
+        <v>124.4918271690015</v>
       </c>
       <c r="C6" t="n">
-        <v>184.3490014218886</v>
+        <v>184.3490014218889</v>
       </c>
       <c r="D6" t="n">
         <v>196.7446250809783</v>
       </c>
       <c r="E6" t="n">
-        <v>167.0795997208624</v>
+        <v>167.0795997208629</v>
       </c>
       <c r="F6" t="n">
-        <v>125.4625689579048</v>
+        <v>125.4625689579049</v>
       </c>
       <c r="G6" t="n">
         <v>184.1797129400368</v>
       </c>
       <c r="H6" t="n">
-        <v>184.3356239684704</v>
+        <v>184.3356239684705</v>
       </c>
       <c r="I6" t="n">
-        <v>183.3484167988355</v>
+        <v>183.3484167988352</v>
       </c>
       <c r="J6" t="n">
-        <v>184.347384991954</v>
+        <v>184.3473849919541</v>
       </c>
       <c r="K6" t="n">
         <v>123.3801979191127</v>
       </c>
       <c r="L6" t="n">
-        <v>246.8474737856494</v>
+        <v>246.8474737856499</v>
       </c>
     </row>
     <row r="7">
@@ -4675,16 +4675,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.02799802763592</v>
+        <v>98.02799802763589</v>
       </c>
       <c r="C7" t="n">
-        <v>116.6602399798676</v>
+        <v>116.6602399798675</v>
       </c>
       <c r="D7" t="n">
         <v>116.756517167297</v>
       </c>
       <c r="E7" t="n">
-        <v>137.3816114510202</v>
+        <v>137.38161145102</v>
       </c>
       <c r="F7" t="n">
         <v>115.7692999776296</v>
@@ -4693,19 +4693,19 @@
         <v>116.6006002320435</v>
       </c>
       <c r="H7" t="n">
-        <v>116.7565112603076</v>
+        <v>116.7565112603077</v>
       </c>
       <c r="I7" t="n">
         <v>115.7693040908421</v>
       </c>
       <c r="J7" t="n">
-        <v>116.7565112603076</v>
+        <v>116.7565112603077</v>
       </c>
       <c r="K7" t="n">
-        <v>105.4648855309831</v>
+        <v>105.464885530983</v>
       </c>
       <c r="L7" t="n">
-        <v>116.7565112603076</v>
+        <v>116.7565112603077</v>
       </c>
     </row>
     <row r="8">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44.30375310203685</v>
+        <v>44.3037531020368</v>
       </c>
       <c r="C8" t="n">
         <v>26.4931936527344</v>
@@ -4724,28 +4724,28 @@
         <v>37.40071364713583</v>
       </c>
       <c r="E8" t="n">
-        <v>43.21151611283797</v>
+        <v>43.211516112838</v>
       </c>
       <c r="F8" t="n">
-        <v>43.21151611283797</v>
+        <v>43.211516112838</v>
       </c>
       <c r="G8" t="n">
-        <v>74.61104781532543</v>
+        <v>74.61104781532542</v>
       </c>
       <c r="H8" t="n">
-        <v>37.30069431176196</v>
+        <v>37.30069431176199</v>
       </c>
       <c r="I8" t="n">
-        <v>43.21151611283797</v>
+        <v>43.211516112838</v>
       </c>
       <c r="J8" t="n">
-        <v>72.40233319802157</v>
+        <v>72.40233319802168</v>
       </c>
       <c r="K8" t="n">
-        <v>147.3726130245868</v>
+        <v>147.3726130245866</v>
       </c>
       <c r="L8" t="n">
-        <v>31.48462319114591</v>
+        <v>31.4846231911459</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44.71775580883019</v>
+        <v>44.71775580883018</v>
       </c>
       <c r="C9" t="n">
-        <v>27.38289364000311</v>
+        <v>27.38289364000306</v>
       </c>
       <c r="D9" t="n">
-        <v>38.2360681149332</v>
+        <v>38.23606811493321</v>
       </c>
       <c r="E9" t="n">
-        <v>43.85474822742529</v>
+        <v>43.85474822742533</v>
       </c>
       <c r="F9" t="n">
-        <v>43.85474822742529</v>
+        <v>43.85474822742533</v>
       </c>
       <c r="G9" t="n">
         <v>74.70882078304547</v>
       </c>
       <c r="H9" t="n">
-        <v>38.19703713916533</v>
+        <v>38.19703713916537</v>
       </c>
       <c r="I9" t="n">
-        <v>43.85474822742529</v>
+        <v>43.85474822742533</v>
       </c>
       <c r="J9" t="n">
-        <v>72.91135421063859</v>
+        <v>72.91135421063866</v>
       </c>
       <c r="K9" t="n">
-        <v>146.245705170691</v>
+        <v>146.2457051706908</v>
       </c>
       <c r="L9" t="n">
-        <v>32.13359352008876</v>
+        <v>32.13359352008875</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>381.2745780932843</v>
+        <v>381.2745780932839</v>
       </c>
       <c r="C2" t="n">
-        <v>285.5522713084178</v>
+        <v>285.5522713084183</v>
       </c>
       <c r="D2" t="n">
-        <v>1345.572469537032</v>
+        <v>1345.572469537033</v>
       </c>
       <c r="E2" t="n">
-        <v>285.5522713084178</v>
+        <v>285.5522713084183</v>
       </c>
       <c r="F2" t="n">
-        <v>285.5522713084178</v>
+        <v>285.5522713084183</v>
       </c>
       <c r="G2" t="n">
-        <v>773.8248026204955</v>
+        <v>773.8248026204953</v>
       </c>
       <c r="H2" t="n">
-        <v>2275.070907381289</v>
+        <v>2275.070907381297</v>
       </c>
       <c r="I2" t="n">
-        <v>285.5522713084178</v>
+        <v>285.5522713084183</v>
       </c>
       <c r="J2" t="n">
-        <v>590.6128384072341</v>
+        <v>590.6128384072333</v>
       </c>
       <c r="K2" t="n">
-        <v>431.51074829386</v>
+        <v>431.5107482938612</v>
       </c>
       <c r="L2" t="n">
-        <v>384.7268137327322</v>
+        <v>384.7268137327308</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.05370851408651</v>
+        <v>35.05370851408644</v>
       </c>
       <c r="C3" t="n">
-        <v>33.06614660054112</v>
+        <v>33.06614660054095</v>
       </c>
       <c r="D3" t="n">
-        <v>35.05370851408651</v>
+        <v>35.05370851408644</v>
       </c>
       <c r="E3" t="n">
-        <v>33.20395281434635</v>
+        <v>33.20395281434625</v>
       </c>
       <c r="F3" t="n">
-        <v>33.20395281434635</v>
+        <v>33.20395281434624</v>
       </c>
       <c r="G3" t="n">
-        <v>34.87706058458215</v>
+        <v>34.877060584582</v>
       </c>
       <c r="H3" t="n">
-        <v>35.05370851408651</v>
+        <v>35.05370851408644</v>
       </c>
       <c r="I3" t="n">
-        <v>33.9325383139175</v>
+        <v>33.93253831391748</v>
       </c>
       <c r="J3" t="n">
-        <v>35.05370851408651</v>
+        <v>35.05370851408644</v>
       </c>
       <c r="K3" t="n">
-        <v>35.05370851408651</v>
+        <v>35.05370851408644</v>
       </c>
       <c r="L3" t="n">
-        <v>35.05370851408651</v>
+        <v>35.05370851408644</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>219.2737640040894</v>
+        <v>219.2737640040892</v>
       </c>
       <c r="C4" t="n">
-        <v>139.7428540264059</v>
+        <v>139.7428540264056</v>
       </c>
       <c r="D4" t="n">
-        <v>143.2748533832657</v>
+        <v>143.2748533832651</v>
       </c>
       <c r="E4" t="n">
         <v>129.4423862782563</v>
       </c>
       <c r="F4" t="n">
-        <v>140.6164400263045</v>
+        <v>140.6164400263043</v>
       </c>
       <c r="G4" t="n">
-        <v>141.6053276111545</v>
+        <v>219.0971160745844</v>
       </c>
       <c r="H4" t="n">
-        <v>142.4310335114306</v>
+        <v>218.0475372878674</v>
       </c>
       <c r="I4" t="n">
-        <v>218.1525938039201</v>
+        <v>218.1525938039198</v>
       </c>
       <c r="J4" t="n">
         <v>217.4285903272202</v>
       </c>
       <c r="K4" t="n">
-        <v>141.4247255743493</v>
+        <v>141.4247255743492</v>
       </c>
       <c r="L4" t="n">
-        <v>142.3465365764484</v>
+        <v>142.3465365764483</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.02132674843713</v>
+        <v>62.02132674843708</v>
       </c>
       <c r="C5" t="n">
-        <v>60.9001565482683</v>
+        <v>60.90015654826816</v>
       </c>
       <c r="D5" t="n">
-        <v>62.02080761689553</v>
+        <v>62.02080761689545</v>
       </c>
       <c r="E5" t="n">
-        <v>60.88421851417667</v>
+        <v>60.88421851417647</v>
       </c>
       <c r="F5" t="n">
-        <v>60.88421851417667</v>
+        <v>60.88421851417647</v>
       </c>
       <c r="G5" t="n">
-        <v>61.84467881893278</v>
+        <v>61.84467881893266</v>
       </c>
       <c r="H5" t="n">
-        <v>62.02132674843713</v>
+        <v>62.02132674843708</v>
       </c>
       <c r="I5" t="n">
-        <v>60.9001565482683</v>
+        <v>60.90015654826816</v>
       </c>
       <c r="J5" t="n">
-        <v>62.02132674843713</v>
+        <v>62.02132674843708</v>
       </c>
       <c r="K5" t="n">
-        <v>62.02132674843713</v>
+        <v>62.02132674843708</v>
       </c>
       <c r="L5" t="n">
-        <v>62.02132674843713</v>
+        <v>62.02132674843708</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>136.7985931882245</v>
+        <v>136.7985931882244</v>
       </c>
       <c r="C6" t="n">
-        <v>202.906160108575</v>
+        <v>202.9061601085753</v>
       </c>
       <c r="D6" t="n">
-        <v>217.9693434757998</v>
+        <v>217.9693434758001</v>
       </c>
       <c r="E6" t="n">
-        <v>184.5193740068168</v>
+        <v>184.5193740068171</v>
       </c>
       <c r="F6" t="n">
-        <v>137.7993165626652</v>
+        <v>137.7993165626653</v>
       </c>
       <c r="G6" t="n">
-        <v>203.8520875733496</v>
+        <v>203.8520875733495</v>
       </c>
       <c r="H6" t="n">
-        <v>204.0287355028578</v>
+        <v>204.0287355028582</v>
       </c>
       <c r="I6" t="n">
-        <v>202.9075653026845</v>
+        <v>202.9075653026849</v>
       </c>
       <c r="J6" t="n">
-        <v>204.0419481568229</v>
+        <v>204.0419481568231</v>
       </c>
       <c r="K6" t="n">
-        <v>135.5497587783372</v>
+        <v>135.5497587783373</v>
       </c>
       <c r="L6" t="n">
-        <v>274.2562408478589</v>
+        <v>274.2562408478591</v>
       </c>
     </row>
     <row r="7">
@@ -5074,31 +5074,31 @@
         <v>127.260837712171</v>
       </c>
       <c r="C7" t="n">
-        <v>152.7641146610617</v>
+        <v>152.7641146610616</v>
       </c>
       <c r="D7" t="n">
         <v>153.8852816137554</v>
       </c>
       <c r="E7" t="n">
-        <v>183.488118404021</v>
+        <v>183.4881184040209</v>
       </c>
       <c r="F7" t="n">
         <v>152.7640820194908</v>
       </c>
       <c r="G7" t="n">
-        <v>153.7086369317263</v>
+        <v>153.7086369317262</v>
       </c>
       <c r="H7" t="n">
         <v>153.8852848612307</v>
       </c>
       <c r="I7" t="n">
-        <v>152.7641146610617</v>
+        <v>152.7641146610616</v>
       </c>
       <c r="J7" t="n">
         <v>153.8852848612307</v>
       </c>
       <c r="K7" t="n">
-        <v>138.4589742549272</v>
+        <v>138.4589742549273</v>
       </c>
       <c r="L7" t="n">
         <v>153.8852848612307</v>
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.51026184614433</v>
+        <v>82.51026184614429</v>
       </c>
       <c r="C8" t="n">
-        <v>50.19248364649616</v>
+        <v>50.19248364649624</v>
       </c>
       <c r="D8" t="n">
         <v>60.30404095652325</v>
       </c>
       <c r="E8" t="n">
-        <v>50.19248364649616</v>
+        <v>50.19248364649624</v>
       </c>
       <c r="F8" t="n">
-        <v>50.19248364649616</v>
+        <v>50.19248364649624</v>
       </c>
       <c r="G8" t="n">
-        <v>73.81764499207198</v>
+        <v>73.81764499207206</v>
       </c>
       <c r="H8" t="n">
-        <v>44.82315303607827</v>
+        <v>44.82315303607812</v>
       </c>
       <c r="I8" t="n">
-        <v>50.19248364649616</v>
+        <v>50.19248364649624</v>
       </c>
       <c r="J8" t="n">
-        <v>78.50002505779857</v>
+        <v>78.50002505779854</v>
       </c>
       <c r="K8" t="n">
-        <v>81.47811170890138</v>
+        <v>81.47811170890134</v>
       </c>
       <c r="L8" t="n">
-        <v>50.27317007347093</v>
+        <v>83.31851410510198</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.64498295172852</v>
+        <v>85.64498295172855</v>
       </c>
       <c r="C9" t="n">
-        <v>52.47334494821682</v>
+        <v>52.47334494821683</v>
       </c>
       <c r="D9" t="n">
-        <v>76.60130475281007</v>
+        <v>76.60130475281005</v>
       </c>
       <c r="E9" t="n">
-        <v>52.47334494821682</v>
+        <v>52.47334494821683</v>
       </c>
       <c r="F9" t="n">
-        <v>52.47334494821682</v>
+        <v>52.47334494821683</v>
       </c>
       <c r="G9" t="n">
-        <v>82.03860740570389</v>
+        <v>82.03860740570386</v>
       </c>
       <c r="H9" t="n">
-        <v>70.33683585787952</v>
+        <v>70.33683585787939</v>
       </c>
       <c r="I9" t="n">
-        <v>52.47334494821682</v>
+        <v>52.47334494821683</v>
       </c>
       <c r="J9" t="n">
-        <v>84.01582663932338</v>
+        <v>84.01582663932336</v>
       </c>
       <c r="K9" t="n">
-        <v>85.22501820320622</v>
+        <v>85.22501820320616</v>
       </c>
       <c r="L9" t="n">
-        <v>72.54471448837194</v>
+        <v>85.97877558700316</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>357.3204045500432</v>
+        <v>357.320404550043</v>
       </c>
       <c r="C2" t="n">
-        <v>310.910822921803</v>
+        <v>310.9108229218026</v>
       </c>
       <c r="D2" t="n">
-        <v>1167.40880055876</v>
+        <v>1167.408800558753</v>
       </c>
       <c r="E2" t="n">
-        <v>310.910822921803</v>
+        <v>310.9108229218026</v>
       </c>
       <c r="F2" t="n">
-        <v>310.910822921803</v>
+        <v>310.9108229218026</v>
       </c>
       <c r="G2" t="n">
-        <v>703.3856293162737</v>
+        <v>703.3856293162771</v>
       </c>
       <c r="H2" t="n">
-        <v>1870.27789693566</v>
+        <v>1870.277896935659</v>
       </c>
       <c r="I2" t="n">
-        <v>310.910822921803</v>
+        <v>310.9108229218026</v>
       </c>
       <c r="J2" t="n">
-        <v>435.578623165792</v>
+        <v>435.5786231657919</v>
       </c>
       <c r="K2" t="n">
-        <v>389.9986793564684</v>
+        <v>389.9986793564682</v>
       </c>
       <c r="L2" t="n">
-        <v>1826.096925627252</v>
+        <v>405.0260966396122</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.81194185608437</v>
+        <v>34.81194185608433</v>
       </c>
       <c r="C3" t="n">
-        <v>32.92908681963623</v>
+        <v>32.9290868196362</v>
       </c>
       <c r="D3" t="n">
-        <v>34.81194185608437</v>
+        <v>34.81194185608435</v>
       </c>
       <c r="E3" t="n">
-        <v>33.05770550550925</v>
+        <v>33.05770550550922</v>
       </c>
       <c r="F3" t="n">
-        <v>33.05770550550927</v>
+        <v>33.05770550550922</v>
       </c>
       <c r="G3" t="n">
-        <v>34.63760372951073</v>
+        <v>34.63760372951075</v>
       </c>
       <c r="H3" t="n">
-        <v>34.81194185608437</v>
+        <v>34.81194185608435</v>
       </c>
       <c r="I3" t="n">
-        <v>33.70554288309906</v>
+        <v>33.70554288309896</v>
       </c>
       <c r="J3" t="n">
-        <v>34.81194185608437</v>
+        <v>34.81194185608435</v>
       </c>
       <c r="K3" t="n">
-        <v>34.81194185608437</v>
+        <v>34.81194185608435</v>
       </c>
       <c r="L3" t="n">
-        <v>34.81194185608437</v>
+        <v>34.81194185608435</v>
       </c>
     </row>
     <row r="4">
@@ -5347,13 +5347,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134.2991762773312</v>
+        <v>206.3681480438691</v>
       </c>
       <c r="C4" t="n">
-        <v>132.4464959709918</v>
+        <v>132.4464959709917</v>
       </c>
       <c r="D4" t="n">
-        <v>135.5527057286754</v>
+        <v>135.552705728677</v>
       </c>
       <c r="E4" t="n">
         <v>122.8509843030583</v>
@@ -5362,22 +5362,22 @@
         <v>133.1799401441012</v>
       </c>
       <c r="G4" t="n">
-        <v>134.1248381507576</v>
+        <v>206.1938099172954</v>
       </c>
       <c r="H4" t="n">
-        <v>205.1904368445296</v>
+        <v>205.1904368445294</v>
       </c>
       <c r="I4" t="n">
-        <v>133.1927773043456</v>
+        <v>205.2617490708836</v>
       </c>
       <c r="J4" t="n">
-        <v>139.6228423184344</v>
+        <v>204.6453703234994</v>
       </c>
       <c r="K4" t="n">
-        <v>133.9712959439493</v>
+        <v>133.9712959439492</v>
       </c>
       <c r="L4" t="n">
-        <v>134.7912689163543</v>
+        <v>134.7912689163544</v>
       </c>
     </row>
     <row r="5">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.58135786773276</v>
+        <v>59.58135786773269</v>
       </c>
       <c r="C5" t="n">
-        <v>58.47495889474745</v>
+        <v>58.4749588947474</v>
       </c>
       <c r="D5" t="n">
-        <v>59.58087690934613</v>
+        <v>59.58087690934609</v>
       </c>
       <c r="E5" t="n">
         <v>58.45809254351603</v>
@@ -5402,22 +5402,22 @@
         <v>58.45809254351603</v>
       </c>
       <c r="G5" t="n">
-        <v>59.40701974115919</v>
+        <v>59.40701974115915</v>
       </c>
       <c r="H5" t="n">
-        <v>59.58135786773276</v>
+        <v>59.58135786773271</v>
       </c>
       <c r="I5" t="n">
-        <v>58.47495889474745</v>
+        <v>58.4749588947474</v>
       </c>
       <c r="J5" t="n">
-        <v>59.58135786773276</v>
+        <v>59.58135786773271</v>
       </c>
       <c r="K5" t="n">
-        <v>59.58135786773276</v>
+        <v>59.58135786773271</v>
       </c>
       <c r="L5" t="n">
-        <v>59.58135786773276</v>
+        <v>59.58135786773271</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>129.0547373113983</v>
+        <v>129.054737311398</v>
       </c>
       <c r="C6" t="n">
-        <v>190.1727873983668</v>
+        <v>190.1727873985252</v>
       </c>
       <c r="D6" t="n">
-        <v>204.1858422930965</v>
+        <v>204.1858422930961</v>
       </c>
       <c r="E6" t="n">
-        <v>173.1543155908026</v>
+        <v>173.1543155908024</v>
       </c>
       <c r="F6" t="n">
-        <v>129.9110879159079</v>
+        <v>129.9110879159077</v>
       </c>
       <c r="G6" t="n">
-        <v>191.1081704235966</v>
+        <v>191.1081704235962</v>
       </c>
       <c r="H6" t="n">
-        <v>191.2825085501781</v>
+        <v>191.2825085501775</v>
       </c>
       <c r="I6" t="n">
-        <v>190.1761095771847</v>
+        <v>190.1761095771845</v>
       </c>
       <c r="J6" t="n">
-        <v>191.2947380945589</v>
+        <v>191.2947380945585</v>
       </c>
       <c r="K6" t="n">
-        <v>127.8988245124882</v>
+        <v>127.8988245124879</v>
       </c>
       <c r="L6" t="n">
-        <v>256.2846190146929</v>
+        <v>256.2846190146921</v>
       </c>
     </row>
     <row r="7">
@@ -5470,34 +5470,34 @@
         <v>115.3511704170623</v>
       </c>
       <c r="C7" t="n">
-        <v>137.5398396878741</v>
+        <v>137.5398396878736</v>
       </c>
       <c r="D7" t="n">
-        <v>138.6462382166511</v>
+        <v>138.6462382166508</v>
       </c>
       <c r="E7" t="n">
-        <v>164.4218208820928</v>
+        <v>164.4218208820923</v>
       </c>
       <c r="F7" t="n">
-        <v>137.5398131099862</v>
+        <v>137.5398131099857</v>
       </c>
       <c r="G7" t="n">
-        <v>138.4719005342859</v>
+        <v>138.4719005342855</v>
       </c>
       <c r="H7" t="n">
-        <v>138.6462386608595</v>
+        <v>138.646238660859</v>
       </c>
       <c r="I7" t="n">
-        <v>137.5398396878741</v>
+        <v>137.5398396878736</v>
       </c>
       <c r="J7" t="n">
-        <v>138.6462386608595</v>
+        <v>138.646238660859</v>
       </c>
       <c r="K7" t="n">
-        <v>109.3135897020854</v>
+        <v>109.3135897020851</v>
       </c>
       <c r="L7" t="n">
-        <v>138.6462386608595</v>
+        <v>138.646238660859</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.39769039231622</v>
+        <v>82.39769039231625</v>
       </c>
       <c r="C8" t="n">
-        <v>48.94555537841987</v>
+        <v>48.94555537842007</v>
       </c>
       <c r="D8" t="n">
-        <v>61.91260541270379</v>
+        <v>61.91260541270417</v>
       </c>
       <c r="E8" t="n">
-        <v>48.94555537841987</v>
+        <v>48.94555537842007</v>
       </c>
       <c r="F8" t="n">
-        <v>48.94555537841987</v>
+        <v>48.94555537842007</v>
       </c>
       <c r="G8" t="n">
-        <v>73.96284792895798</v>
+        <v>73.96284792895797</v>
       </c>
       <c r="H8" t="n">
-        <v>50.23033143572353</v>
+        <v>50.23033143572354</v>
       </c>
       <c r="I8" t="n">
-        <v>48.94555537841987</v>
+        <v>48.94555537842007</v>
       </c>
       <c r="J8" t="n">
-        <v>81.04215391208031</v>
+        <v>81.04215391208028</v>
       </c>
       <c r="K8" t="n">
-        <v>81.3124483256295</v>
+        <v>81.31244832562953</v>
       </c>
       <c r="L8" t="n">
-        <v>52.76794667911891</v>
+        <v>82.12306672292131</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.49465851889281</v>
+        <v>85.49465851889283</v>
       </c>
       <c r="C9" t="n">
-        <v>51.91454535271891</v>
+        <v>51.91454535271898</v>
       </c>
       <c r="D9" t="n">
-        <v>77.15194056119202</v>
+        <v>77.15194056119212</v>
       </c>
       <c r="E9" t="n">
-        <v>51.91454535271891</v>
+        <v>51.91454535271898</v>
       </c>
       <c r="F9" t="n">
-        <v>51.91454535271891</v>
+        <v>51.91454535271898</v>
       </c>
       <c r="G9" t="n">
-        <v>81.99961056135427</v>
+        <v>81.99961056135423</v>
       </c>
       <c r="H9" t="n">
-        <v>72.42946817628631</v>
+        <v>72.42946817628633</v>
       </c>
       <c r="I9" t="n">
-        <v>51.91454535271891</v>
+        <v>51.91454535271898</v>
       </c>
       <c r="J9" t="n">
-        <v>84.94570595270869</v>
+        <v>84.94570595270876</v>
       </c>
       <c r="K9" t="n">
-        <v>85.05306897338967</v>
+        <v>85.05306897338966</v>
       </c>
       <c r="L9" t="n">
-        <v>85.38816016064679</v>
+        <v>85.38816016064678</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>345.0097914306256</v>
+        <v>345.0097914306147</v>
       </c>
       <c r="C2" t="n">
-        <v>380.3518801804902</v>
+        <v>380.3518801804886</v>
       </c>
       <c r="D2" t="n">
-        <v>1001.124622959806</v>
+        <v>1001.124622959805</v>
       </c>
       <c r="E2" t="n">
-        <v>380.3518801804902</v>
+        <v>380.3518801804886</v>
       </c>
       <c r="F2" t="n">
-        <v>380.3518801804902</v>
+        <v>380.3518801804886</v>
       </c>
       <c r="G2" t="n">
-        <v>635.5935111793813</v>
+        <v>635.5935111793652</v>
       </c>
       <c r="H2" t="n">
-        <v>1528.357000337434</v>
+        <v>1528.357000337442</v>
       </c>
       <c r="I2" t="n">
-        <v>380.3518801804902</v>
+        <v>380.3518801804886</v>
       </c>
       <c r="J2" t="n">
-        <v>415.0992448875651</v>
+        <v>415.0992448875513</v>
       </c>
       <c r="K2" t="n">
-        <v>345.0022874285297</v>
+        <v>345.0022874284992</v>
       </c>
       <c r="L2" t="n">
-        <v>1644.195440518733</v>
+        <v>1644.195440518746</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.94946777382378</v>
+        <v>34.94946777382374</v>
       </c>
       <c r="C3" t="n">
-        <v>33.19681298878078</v>
+        <v>33.1968129887807</v>
       </c>
       <c r="D3" t="n">
-        <v>34.94946777382378</v>
+        <v>34.94946777382373</v>
       </c>
       <c r="E3" t="n">
-        <v>33.32196722453124</v>
+        <v>33.3219672245312</v>
       </c>
       <c r="F3" t="n">
-        <v>33.32196722453125</v>
+        <v>33.32196722453119</v>
       </c>
       <c r="G3" t="n">
-        <v>34.78032765816598</v>
+        <v>34.78032765816594</v>
       </c>
       <c r="H3" t="n">
-        <v>34.94946777382378</v>
+        <v>34.94946777382373</v>
       </c>
       <c r="I3" t="n">
-        <v>33.8762820134419</v>
+        <v>33.87628201344181</v>
       </c>
       <c r="J3" t="n">
-        <v>34.94946777382378</v>
+        <v>34.94946777382373</v>
       </c>
       <c r="K3" t="n">
-        <v>34.94946777382378</v>
+        <v>34.94946777382373</v>
       </c>
       <c r="L3" t="n">
-        <v>34.94946777382378</v>
+        <v>34.94946777382373</v>
       </c>
     </row>
     <row r="4">
@@ -5743,34 +5743,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134.4699045980824</v>
+        <v>134.4699045980825</v>
       </c>
       <c r="C4" t="n">
-        <v>132.8904627543519</v>
+        <v>132.8904627543516</v>
       </c>
       <c r="D4" t="n">
-        <v>204.7767109879911</v>
+        <v>204.7767109879908</v>
       </c>
       <c r="E4" t="n">
-        <v>123.2903713109616</v>
+        <v>123.2903713109615</v>
       </c>
       <c r="F4" t="n">
-        <v>133.4401629507975</v>
+        <v>133.4401629507974</v>
       </c>
       <c r="G4" t="n">
         <v>134.3007644824248</v>
       </c>
       <c r="H4" t="n">
-        <v>205.0146052317651</v>
+        <v>205.0146052317649</v>
       </c>
       <c r="I4" t="n">
-        <v>205.1513030539083</v>
+        <v>205.151303053908</v>
       </c>
       <c r="J4" t="n">
-        <v>204.4887274102063</v>
+        <v>139.7936797025973</v>
       </c>
       <c r="K4" t="n">
-        <v>134.1265469985591</v>
+        <v>134.126546998559</v>
       </c>
       <c r="L4" t="n">
         <v>134.9238791410877</v>
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.45185443031084</v>
+        <v>59.45185443031085</v>
       </c>
       <c r="C5" t="n">
-        <v>58.378668669929</v>
+        <v>58.37866866992888</v>
       </c>
       <c r="D5" t="n">
-        <v>59.45137056682825</v>
+        <v>59.45137056682818</v>
       </c>
       <c r="E5" t="n">
-        <v>58.36445883501113</v>
+        <v>58.36445883501108</v>
       </c>
       <c r="F5" t="n">
-        <v>58.36445883501113</v>
+        <v>58.36445883501108</v>
       </c>
       <c r="G5" t="n">
-        <v>59.28271431465304</v>
+        <v>59.28271431465298</v>
       </c>
       <c r="H5" t="n">
-        <v>59.45185443031084</v>
+        <v>59.4518544303108</v>
       </c>
       <c r="I5" t="n">
-        <v>58.378668669929</v>
+        <v>58.37866866992888</v>
       </c>
       <c r="J5" t="n">
-        <v>59.45185443031084</v>
+        <v>59.4518544303108</v>
       </c>
       <c r="K5" t="n">
-        <v>59.45185443031084</v>
+        <v>59.4518544303108</v>
       </c>
       <c r="L5" t="n">
-        <v>59.45185443031084</v>
+        <v>59.4518544303108</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>128.6180072326252</v>
+        <v>128.6180072326251</v>
       </c>
       <c r="C6" t="n">
-        <v>189.3510889303554</v>
+        <v>189.351088930355</v>
       </c>
       <c r="D6" t="n">
-        <v>203.2412454121649</v>
+        <v>203.2412454121646</v>
       </c>
       <c r="E6" t="n">
-        <v>172.4473965637617</v>
+        <v>172.4473965637612</v>
       </c>
       <c r="F6" t="n">
-        <v>129.4958237707509</v>
+        <v>129.4958237707505</v>
       </c>
       <c r="G6" t="n">
-        <v>190.2559947462468</v>
+        <v>190.2559947462464</v>
       </c>
       <c r="H6" t="n">
-        <v>190.4251348619175</v>
+        <v>190.4251348619169</v>
       </c>
       <c r="I6" t="n">
-        <v>189.3519491015227</v>
+        <v>189.3519491015223</v>
       </c>
       <c r="J6" t="n">
-        <v>190.4372817378196</v>
+        <v>190.4372817378195</v>
       </c>
       <c r="K6" t="n">
-        <v>127.4699081047085</v>
+        <v>127.4699081047083</v>
       </c>
       <c r="L6" t="n">
-        <v>254.987847902728</v>
+        <v>254.9878479027271</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.7435237796734</v>
+        <v>110.7435237796735</v>
       </c>
       <c r="C7" t="n">
-        <v>131.6288303324233</v>
+        <v>131.6288303324232</v>
       </c>
       <c r="D7" t="n">
-        <v>132.7020168030296</v>
+        <v>132.7020168030293</v>
       </c>
       <c r="E7" t="n">
-        <v>156.9684374858672</v>
+        <v>156.9684374858669</v>
       </c>
       <c r="F7" t="n">
-        <v>131.6288079142495</v>
+        <v>131.6288079142493</v>
       </c>
       <c r="G7" t="n">
-        <v>132.5328759771474</v>
+        <v>132.5328759771476</v>
       </c>
       <c r="H7" t="n">
-        <v>132.7020160928052</v>
+        <v>132.7020160928053</v>
       </c>
       <c r="I7" t="n">
-        <v>131.6288303324233</v>
+        <v>131.6288303324232</v>
       </c>
       <c r="J7" t="n">
-        <v>132.7020160928052</v>
+        <v>132.7020160928053</v>
       </c>
       <c r="K7" t="n">
-        <v>119.9791797076497</v>
+        <v>119.9791797076494</v>
       </c>
       <c r="L7" t="n">
-        <v>132.7020160928052</v>
+        <v>132.7020160928053</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.38731958798297</v>
+        <v>82.38731958798309</v>
       </c>
       <c r="C8" t="n">
-        <v>47.14022944300174</v>
+        <v>47.14022944300175</v>
       </c>
       <c r="D8" t="n">
-        <v>65.19383225152056</v>
+        <v>65.1938322515206</v>
       </c>
       <c r="E8" t="n">
-        <v>47.14022944300174</v>
+        <v>47.14022944300175</v>
       </c>
       <c r="F8" t="n">
-        <v>47.14022944300174</v>
+        <v>47.14022944300175</v>
       </c>
       <c r="G8" t="n">
-        <v>75.18482252195351</v>
+        <v>75.18482252195327</v>
       </c>
       <c r="H8" t="n">
-        <v>56.19565468020522</v>
+        <v>56.19565468020521</v>
       </c>
       <c r="I8" t="n">
-        <v>47.14022944300174</v>
+        <v>47.14022944300175</v>
       </c>
       <c r="J8" t="n">
-        <v>81.33355098670791</v>
+        <v>81.3335509867082</v>
       </c>
       <c r="K8" t="n">
-        <v>82.05611081099673</v>
+        <v>82.05611081099728</v>
       </c>
       <c r="L8" t="n">
-        <v>55.91613403412283</v>
+        <v>55.91613403412306</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.3770177156406</v>
+        <v>85.37701771564137</v>
       </c>
       <c r="C9" t="n">
-        <v>51.23340400542962</v>
+        <v>51.23340400542957</v>
       </c>
       <c r="D9" t="n">
-        <v>78.37485430858946</v>
+        <v>78.37485430858953</v>
       </c>
       <c r="E9" t="n">
-        <v>51.23340400542962</v>
+        <v>51.23340400542957</v>
       </c>
       <c r="F9" t="n">
-        <v>51.23340400542962</v>
+        <v>51.23340400542957</v>
       </c>
       <c r="G9" t="n">
-        <v>82.39796589891075</v>
+        <v>82.3979658989108</v>
       </c>
       <c r="H9" t="n">
-        <v>74.73995400667293</v>
+        <v>74.73995400667296</v>
       </c>
       <c r="I9" t="n">
-        <v>51.23340400542962</v>
+        <v>51.23340400542957</v>
       </c>
       <c r="J9" t="n">
-        <v>84.95078760471527</v>
+        <v>84.9507876047153</v>
       </c>
       <c r="K9" t="n">
-        <v>85.24249145934198</v>
+        <v>85.24249145934218</v>
       </c>
       <c r="L9" t="n">
-        <v>74.62060693542725</v>
+        <v>74.62060693542736</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263.109513508241</v>
+        <v>263.1095135082414</v>
       </c>
       <c r="C2" t="n">
-        <v>212.8372987128301</v>
+        <v>212.83729871283</v>
       </c>
       <c r="D2" t="n">
         <v>440.3969237609145</v>
       </c>
       <c r="E2" t="n">
-        <v>212.8372987128301</v>
+        <v>212.83729871283</v>
       </c>
       <c r="F2" t="n">
-        <v>212.8372987128301</v>
+        <v>212.83729871283</v>
       </c>
       <c r="G2" t="n">
-        <v>334.4289273895764</v>
+        <v>334.4289273895762</v>
       </c>
       <c r="H2" t="n">
-        <v>772.1002534568694</v>
+        <v>772.1002534568697</v>
       </c>
       <c r="I2" t="n">
-        <v>212.8372987128301</v>
+        <v>212.83729871283</v>
       </c>
       <c r="J2" t="n">
-        <v>483.3446987475299</v>
+        <v>483.3446987475292</v>
       </c>
       <c r="K2" t="n">
-        <v>298.5960871682573</v>
+        <v>298.5960871682567</v>
       </c>
       <c r="L2" t="n">
-        <v>196.2189844972248</v>
+        <v>616.1880475395415</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.63820744180543</v>
+        <v>33.63820744180535</v>
       </c>
       <c r="C3" t="n">
-        <v>31.97665851092991</v>
+        <v>31.97665851092992</v>
       </c>
       <c r="D3" t="n">
-        <v>33.63820744180543</v>
+        <v>33.63820744180535</v>
       </c>
       <c r="E3" t="n">
-        <v>32.08849482241203</v>
+        <v>32.08849482241202</v>
       </c>
       <c r="F3" t="n">
-        <v>32.08849482241203</v>
+        <v>32.08849482241202</v>
       </c>
       <c r="G3" t="n">
-        <v>33.47455129833422</v>
+        <v>33.47455129833418</v>
       </c>
       <c r="H3" t="n">
-        <v>33.63820744180543</v>
+        <v>33.63820744180535</v>
       </c>
       <c r="I3" t="n">
-        <v>32.59983744444521</v>
+        <v>32.59983744444519</v>
       </c>
       <c r="J3" t="n">
-        <v>33.63820744180543</v>
+        <v>33.63820744180535</v>
       </c>
       <c r="K3" t="n">
-        <v>33.63820744180543</v>
+        <v>33.63820744180535</v>
       </c>
       <c r="L3" t="n">
-        <v>33.63820744180543</v>
+        <v>33.63820744180535</v>
       </c>
     </row>
     <row r="4">
@@ -6139,31 +6139,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139.51474447891</v>
+        <v>139.5147444789099</v>
       </c>
       <c r="C4" t="n">
-        <v>138.0467334658707</v>
+        <v>138.0467334658709</v>
       </c>
       <c r="D4" t="n">
-        <v>139.7879889700387</v>
+        <v>212.4923650129747</v>
       </c>
       <c r="E4" t="n">
-        <v>127.7854253159414</v>
+        <v>127.7854253159412</v>
       </c>
       <c r="F4" t="n">
         <v>138.4618717427944</v>
       </c>
       <c r="G4" t="n">
-        <v>214.0390412616235</v>
+        <v>139.3510883354387</v>
       </c>
       <c r="H4" t="n">
-        <v>212.6360665557695</v>
+        <v>212.6360665557693</v>
       </c>
       <c r="I4" t="n">
-        <v>213.1643274077343</v>
+        <v>138.47637448155</v>
       </c>
       <c r="J4" t="n">
-        <v>212.2619145223951</v>
+        <v>212.2619145223949</v>
       </c>
       <c r="K4" t="n">
         <v>139.482022792655</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.2305188139028</v>
+        <v>58.23051881390278</v>
       </c>
       <c r="C5" t="n">
-        <v>57.19214881654264</v>
+        <v>57.19214881654271</v>
       </c>
       <c r="D5" t="n">
-        <v>58.23002295009227</v>
+        <v>58.2300229500923</v>
       </c>
       <c r="E5" t="n">
-        <v>57.17881194638593</v>
+        <v>57.17881194638601</v>
       </c>
       <c r="F5" t="n">
-        <v>57.17881194638593</v>
+        <v>57.17881194638601</v>
       </c>
       <c r="G5" t="n">
-        <v>58.0668626704317</v>
+        <v>58.06686267043168</v>
       </c>
       <c r="H5" t="n">
-        <v>58.2305188139028</v>
+        <v>58.23051881390278</v>
       </c>
       <c r="I5" t="n">
-        <v>57.19214881654264</v>
+        <v>57.19214881654271</v>
       </c>
       <c r="J5" t="n">
-        <v>58.2305188139028</v>
+        <v>58.23051881390278</v>
       </c>
       <c r="K5" t="n">
-        <v>58.2305188139028</v>
+        <v>58.23051881390278</v>
       </c>
       <c r="L5" t="n">
-        <v>58.2305188139028</v>
+        <v>58.23051881390278</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130.9935658837265</v>
+        <v>130.9935658837267</v>
       </c>
       <c r="C6" t="n">
-        <v>193.9258444298819</v>
+        <v>193.9258444297273</v>
       </c>
       <c r="D6" t="n">
-        <v>208.2284442455249</v>
+        <v>208.2284442455251</v>
       </c>
       <c r="E6" t="n">
-        <v>176.4304239764206</v>
+        <v>176.430423976421</v>
       </c>
       <c r="F6" t="n">
-        <v>131.9752932306715</v>
+        <v>131.9752932306716</v>
       </c>
       <c r="G6" t="n">
-        <v>194.8001434207053</v>
+        <v>194.8001434207056</v>
       </c>
       <c r="H6" t="n">
-        <v>194.9637995641788</v>
+        <v>194.9637995641792</v>
       </c>
       <c r="I6" t="n">
-        <v>193.9254295668165</v>
+        <v>193.9254295668167</v>
       </c>
       <c r="J6" t="n">
-        <v>194.9763715534228</v>
+        <v>194.976371553423</v>
       </c>
       <c r="K6" t="n">
-        <v>129.8052859502818</v>
+        <v>129.8052859502819</v>
       </c>
       <c r="L6" t="n">
-        <v>261.786057752352</v>
+        <v>261.7860577523522</v>
       </c>
     </row>
     <row r="7">
@@ -6259,34 +6259,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114.6552643166908</v>
+        <v>114.6552643166905</v>
       </c>
       <c r="C7" t="n">
-        <v>136.9417234701414</v>
+        <v>136.9417234701411</v>
       </c>
       <c r="D7" t="n">
         <v>137.9800958430004</v>
       </c>
       <c r="E7" t="n">
-        <v>163.8580673405842</v>
+        <v>163.8580673405841</v>
       </c>
       <c r="F7" t="n">
         <v>136.9417102295396</v>
       </c>
       <c r="G7" t="n">
-        <v>137.8164373240302</v>
+        <v>137.8164373240301</v>
       </c>
       <c r="H7" t="n">
         <v>137.9800934675014</v>
       </c>
       <c r="I7" t="n">
-        <v>136.9417234701414</v>
+        <v>136.9417234701411</v>
       </c>
       <c r="J7" t="n">
         <v>137.9800934675014</v>
       </c>
       <c r="K7" t="n">
-        <v>108.6099694836877</v>
+        <v>124.4655968529837</v>
       </c>
       <c r="L7" t="n">
         <v>137.9800934675014</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.34069275486647</v>
+        <v>83.34069275486644</v>
       </c>
       <c r="C8" t="n">
-        <v>50.28925301458093</v>
+        <v>50.28925301458096</v>
       </c>
       <c r="D8" t="n">
-        <v>78.81931578808613</v>
+        <v>78.81931578808607</v>
       </c>
       <c r="E8" t="n">
-        <v>50.28925301458093</v>
+        <v>50.28925301458096</v>
       </c>
       <c r="F8" t="n">
-        <v>50.28925301458093</v>
+        <v>50.28925301458096</v>
       </c>
       <c r="G8" t="n">
-        <v>81.69404077387044</v>
+        <v>81.6940407738704</v>
       </c>
       <c r="H8" t="n">
-        <v>72.32456476665598</v>
+        <v>72.32456476665591</v>
       </c>
       <c r="I8" t="n">
-        <v>50.28925301458093</v>
+        <v>50.28925301458096</v>
       </c>
       <c r="J8" t="n">
-        <v>78.86998044411249</v>
+        <v>78.86998044411246</v>
       </c>
       <c r="K8" t="n">
-        <v>82.42318706102398</v>
+        <v>82.42318706102394</v>
       </c>
       <c r="L8" t="n">
-        <v>76.82008402308809</v>
+        <v>85.26796029057401</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.86249383672602</v>
+        <v>84.86249383672593</v>
       </c>
       <c r="C9" t="n">
-        <v>51.5685869415941</v>
+        <v>51.56858694159406</v>
       </c>
       <c r="D9" t="n">
-        <v>83.0211978006742</v>
+        <v>83.02119780067414</v>
       </c>
       <c r="E9" t="n">
-        <v>51.5685869415941</v>
+        <v>51.56858694159409</v>
       </c>
       <c r="F9" t="n">
-        <v>51.5685869415941</v>
+        <v>51.56858694159409</v>
       </c>
       <c r="G9" t="n">
-        <v>84.15900436907829</v>
+        <v>84.15900436907827</v>
       </c>
       <c r="H9" t="n">
-        <v>80.38987211184558</v>
+        <v>80.38987211184549</v>
       </c>
       <c r="I9" t="n">
-        <v>51.5685869415941</v>
+        <v>51.56858694159409</v>
       </c>
       <c r="J9" t="n">
-        <v>83.04491342298849</v>
+        <v>83.04491342298843</v>
       </c>
       <c r="K9" t="n">
-        <v>84.48907122273626</v>
+        <v>84.48907122273616</v>
       </c>
       <c r="L9" t="n">
-        <v>85.64916280854504</v>
+        <v>82.21481856686562</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>285.2659720949189</v>
+        <v>285.265972094919</v>
       </c>
       <c r="C2" t="n">
-        <v>236.9056470670312</v>
+        <v>236.905647067031</v>
       </c>
       <c r="D2" t="n">
-        <v>213.0237994451819</v>
+        <v>213.023799445182</v>
       </c>
       <c r="E2" t="n">
-        <v>236.9056470670312</v>
+        <v>236.905647067031</v>
       </c>
       <c r="F2" t="n">
-        <v>236.9056470670312</v>
+        <v>236.905647067031</v>
       </c>
       <c r="G2" t="n">
-        <v>238.3089004329049</v>
+        <v>238.3089004329001</v>
       </c>
       <c r="H2" t="n">
-        <v>200.3980045520701</v>
+        <v>200.3980045520702</v>
       </c>
       <c r="I2" t="n">
-        <v>236.9056470670312</v>
+        <v>236.905647067031</v>
       </c>
       <c r="J2" t="n">
-        <v>357.6430660008746</v>
+        <v>357.6430660008745</v>
       </c>
       <c r="K2" t="n">
-        <v>253.0880904942372</v>
+        <v>253.0880904942375</v>
       </c>
       <c r="L2" t="n">
-        <v>148.4032655102179</v>
+        <v>148.4032655102178</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.28094375305023</v>
+        <v>33.28094375305029</v>
       </c>
       <c r="C3" t="n">
-        <v>31.78515807296251</v>
+        <v>31.78515807296249</v>
       </c>
       <c r="D3" t="n">
-        <v>33.28094375305023</v>
+        <v>33.28094375305029</v>
       </c>
       <c r="E3" t="n">
         <v>31.8816266522107</v>
       </c>
       <c r="F3" t="n">
-        <v>31.8816266522107</v>
+        <v>31.88162665221073</v>
       </c>
       <c r="G3" t="n">
-        <v>33.1219559555599</v>
+        <v>33.12195595555987</v>
       </c>
       <c r="H3" t="n">
-        <v>33.28094375305023</v>
+        <v>33.28094375305029</v>
       </c>
       <c r="I3" t="n">
-        <v>32.27236615059999</v>
+        <v>32.27236615059996</v>
       </c>
       <c r="J3" t="n">
-        <v>33.28094375305023</v>
+        <v>33.28094375305029</v>
       </c>
       <c r="K3" t="n">
-        <v>33.28094375305023</v>
+        <v>33.28094375305029</v>
       </c>
       <c r="L3" t="n">
-        <v>33.28094375305023</v>
+        <v>33.28094375305029</v>
       </c>
     </row>
     <row r="4">
@@ -6535,34 +6535,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.8715745561247</v>
+        <v>200.9253611120564</v>
       </c>
       <c r="C4" t="n">
         <v>130.6411545052313</v>
       </c>
       <c r="D4" t="n">
-        <v>131.751494176783</v>
+        <v>131.7514385483436</v>
       </c>
       <c r="E4" t="n">
-        <v>121.085471991146</v>
+        <v>121.0854719911459</v>
       </c>
       <c r="F4" t="n">
         <v>130.8660650746295</v>
       </c>
       <c r="G4" t="n">
-        <v>131.7125867586342</v>
+        <v>131.7125867586343</v>
       </c>
       <c r="H4" t="n">
-        <v>199.3001751003805</v>
+        <v>131.8617037059055</v>
       </c>
       <c r="I4" t="n">
-        <v>130.8629969536743</v>
+        <v>130.8629969536744</v>
       </c>
       <c r="J4" t="n">
-        <v>137.0715725540495</v>
+        <v>199.0844659224919</v>
       </c>
       <c r="K4" t="n">
-        <v>131.8585760566919</v>
+        <v>131.858576056692</v>
       </c>
       <c r="L4" t="n">
         <v>131.8595782927522</v>
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.63327993831446</v>
+        <v>55.63327993831444</v>
       </c>
       <c r="C5" t="n">
-        <v>54.62470233586421</v>
+        <v>54.62470233586424</v>
       </c>
       <c r="D5" t="n">
-        <v>55.63281582197752</v>
+        <v>55.6328158219775</v>
       </c>
       <c r="E5" t="n">
-        <v>54.61518042919586</v>
+        <v>54.61518042919579</v>
       </c>
       <c r="F5" t="n">
-        <v>54.61518042919586</v>
+        <v>54.61518042919579</v>
       </c>
       <c r="G5" t="n">
-        <v>55.47429214082403</v>
+        <v>55.47429214082412</v>
       </c>
       <c r="H5" t="n">
-        <v>55.63327993831446</v>
+        <v>55.63327993831444</v>
       </c>
       <c r="I5" t="n">
-        <v>54.62470233586421</v>
+        <v>54.62470233586424</v>
       </c>
       <c r="J5" t="n">
-        <v>55.63327993831446</v>
+        <v>55.63327993831444</v>
       </c>
       <c r="K5" t="n">
-        <v>55.63327993831446</v>
+        <v>55.63327993831444</v>
       </c>
       <c r="L5" t="n">
-        <v>55.63327993831446</v>
+        <v>55.63327993831444</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122.8687481522071</v>
+        <v>122.868748152207</v>
       </c>
       <c r="C6" t="n">
-        <v>180.6373370463936</v>
+        <v>180.6373370463935</v>
       </c>
       <c r="D6" t="n">
-        <v>193.8301168568933</v>
+        <v>193.830116856893</v>
       </c>
       <c r="E6" t="n">
-        <v>164.5627263000816</v>
+        <v>164.5627263000814</v>
       </c>
       <c r="F6" t="n">
-        <v>123.7178173521553</v>
+        <v>123.7178173521551</v>
       </c>
       <c r="G6" t="n">
         <v>181.48392346089</v>
       </c>
       <c r="H6" t="n">
-        <v>181.6429112583784</v>
+        <v>181.642911258378</v>
       </c>
       <c r="I6" t="n">
-        <v>180.6343336559301</v>
+        <v>180.63433365593</v>
       </c>
       <c r="J6" t="n">
-        <v>181.6544620707873</v>
+        <v>181.654462070787</v>
       </c>
       <c r="K6" t="n">
         <v>121.776987897345</v>
       </c>
       <c r="L6" t="n">
-        <v>243.0374392432981</v>
+        <v>243.037439243298</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102.927539859104</v>
+        <v>102.9275398591039</v>
       </c>
       <c r="C7" t="n">
         <v>121.9857763219378</v>
       </c>
       <c r="D7" t="n">
-        <v>122.9943610380561</v>
+        <v>122.9943610380559</v>
       </c>
       <c r="E7" t="n">
-        <v>145.1424556353148</v>
+        <v>145.1424556353145</v>
       </c>
       <c r="F7" t="n">
-        <v>121.9857722712167</v>
+        <v>121.9857722712165</v>
       </c>
       <c r="G7" t="n">
-        <v>122.8353661268977</v>
+        <v>122.8353661268976</v>
       </c>
       <c r="H7" t="n">
-        <v>122.9943539243881</v>
+        <v>122.9943539243878</v>
       </c>
       <c r="I7" t="n">
         <v>121.9857763219378</v>
       </c>
       <c r="J7" t="n">
-        <v>122.9943539243881</v>
+        <v>122.9943539243878</v>
       </c>
       <c r="K7" t="n">
-        <v>110.8958522785102</v>
+        <v>110.8958522785101</v>
       </c>
       <c r="L7" t="n">
-        <v>122.9943539243881</v>
+        <v>122.9943539243878</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.94083714248636</v>
+        <v>81.94083714248633</v>
       </c>
       <c r="C8" t="n">
         <v>49.00888205668733</v>
       </c>
       <c r="D8" t="n">
-        <v>83.88906616831396</v>
+        <v>83.88906616831397</v>
       </c>
       <c r="E8" t="n">
         <v>49.00888205668733</v>
@@ -6710,22 +6710,22 @@
         <v>49.00888205668733</v>
       </c>
       <c r="G8" t="n">
-        <v>83.18561544015184</v>
+        <v>83.18561544015186</v>
       </c>
       <c r="H8" t="n">
-        <v>84.72338556762915</v>
+        <v>84.72338556762917</v>
       </c>
       <c r="I8" t="n">
         <v>49.00888205668733</v>
       </c>
       <c r="J8" t="n">
-        <v>80.42104120477582</v>
+        <v>80.42104120477579</v>
       </c>
       <c r="K8" t="n">
-        <v>82.65951970173667</v>
+        <v>82.65951970173664</v>
       </c>
       <c r="L8" t="n">
-        <v>85.03628849385818</v>
+        <v>85.03628849385819</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.03309565409515</v>
+        <v>84.03309565409511</v>
       </c>
       <c r="C9" t="n">
         <v>50.87927963956933</v>
       </c>
       <c r="D9" t="n">
-        <v>84.82668265625931</v>
+        <v>84.82668265625929</v>
       </c>
       <c r="E9" t="n">
         <v>50.87927963956933</v>
@@ -6750,7 +6750,7 @@
         <v>50.87927963956933</v>
       </c>
       <c r="G9" t="n">
-        <v>84.5196430074779</v>
+        <v>84.51964300747785</v>
       </c>
       <c r="H9" t="n">
         <v>85.16862831187771</v>
@@ -6762,10 +6762,10 @@
         <v>83.41664270350721</v>
       </c>
       <c r="K9" t="n">
-        <v>84.32604600635925</v>
+        <v>84.32604600635923</v>
       </c>
       <c r="L9" t="n">
-        <v>85.59751096551248</v>
+        <v>85.29541878516733</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>280.1251672319885</v>
+        <v>280.1251672319888</v>
       </c>
       <c r="C2" t="n">
-        <v>232.444642180787</v>
+        <v>232.4446421807866</v>
       </c>
       <c r="D2" t="n">
-        <v>190.4656419959191</v>
+        <v>190.4656419959196</v>
       </c>
       <c r="E2" t="n">
-        <v>232.444642180787</v>
+        <v>232.4446421807866</v>
       </c>
       <c r="F2" t="n">
-        <v>232.444642180787</v>
+        <v>232.4446421807866</v>
       </c>
       <c r="G2" t="n">
-        <v>225.0443848837173</v>
+        <v>225.0443848837208</v>
       </c>
       <c r="H2" t="n">
-        <v>190.9620489182183</v>
+        <v>190.9620489182193</v>
       </c>
       <c r="I2" t="n">
-        <v>232.444642180787</v>
+        <v>232.4446421807866</v>
       </c>
       <c r="J2" t="n">
         <v>343.6046109463705</v>
       </c>
       <c r="K2" t="n">
-        <v>220.1723627787628</v>
+        <v>220.1723627787632</v>
       </c>
       <c r="L2" t="n">
-        <v>184.3302697747878</v>
+        <v>193.0417156788466</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.22662322715989</v>
+        <v>33.22662322715993</v>
       </c>
       <c r="C3" t="n">
-        <v>31.73550156840215</v>
+        <v>31.73550156840219</v>
       </c>
       <c r="D3" t="n">
-        <v>33.22662322715989</v>
+        <v>33.22662322715994</v>
       </c>
       <c r="E3" t="n">
-        <v>31.83223967565382</v>
+        <v>31.83223967565387</v>
       </c>
       <c r="F3" t="n">
-        <v>31.83223967565382</v>
+        <v>31.83223967565385</v>
       </c>
       <c r="G3" t="n">
-        <v>33.06800301465239</v>
+        <v>33.06800301465275</v>
       </c>
       <c r="H3" t="n">
-        <v>33.22662322715989</v>
+        <v>33.22662322715993</v>
       </c>
       <c r="I3" t="n">
-        <v>32.22039140212277</v>
+        <v>32.22039140212287</v>
       </c>
       <c r="J3" t="n">
-        <v>33.22662322715989</v>
+        <v>33.22662322715993</v>
       </c>
       <c r="K3" t="n">
-        <v>33.22662322715989</v>
+        <v>33.22662322715993</v>
       </c>
       <c r="L3" t="n">
-        <v>33.22662322715989</v>
+        <v>33.22662322715993</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.7747808384628</v>
+        <v>131.7747808384629</v>
       </c>
       <c r="C4" t="n">
-        <v>130.5501298970784</v>
+        <v>130.5501298970787</v>
       </c>
       <c r="D4" t="n">
-        <v>199.1013655533145</v>
+        <v>131.6209439194172</v>
       </c>
       <c r="E4" t="n">
-        <v>120.9982723016102</v>
+        <v>120.9982723016099</v>
       </c>
       <c r="F4" t="n">
-        <v>130.7621232549046</v>
+        <v>130.7621232549048</v>
       </c>
       <c r="G4" t="n">
-        <v>131.616160625955</v>
+        <v>200.6652470418867</v>
       </c>
       <c r="H4" t="n">
-        <v>199.1443934795145</v>
+        <v>199.1443934795146</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7685490134256</v>
+        <v>130.7685490134257</v>
       </c>
       <c r="J4" t="n">
-        <v>136.9563448684133</v>
+        <v>198.9267760943383</v>
       </c>
       <c r="K4" t="n">
-        <v>131.7035968397681</v>
+        <v>131.7035968397684</v>
       </c>
       <c r="L4" t="n">
-        <v>131.7572343690953</v>
+        <v>131.7572343690952</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.47212615797066</v>
+        <v>55.47212615797127</v>
       </c>
       <c r="C5" t="n">
-        <v>54.46589433293381</v>
+        <v>54.46589433293406</v>
       </c>
       <c r="D5" t="n">
-        <v>55.47166515620691</v>
+        <v>55.47166515620747</v>
       </c>
       <c r="E5" t="n">
-        <v>54.45562058835162</v>
+        <v>54.45562058835189</v>
       </c>
       <c r="F5" t="n">
-        <v>54.45562058835162</v>
+        <v>54.45562058835189</v>
       </c>
       <c r="G5" t="n">
-        <v>55.31350594546367</v>
+        <v>55.31350594546389</v>
       </c>
       <c r="H5" t="n">
-        <v>55.47212615797066</v>
+        <v>55.47212615797127</v>
       </c>
       <c r="I5" t="n">
-        <v>54.46589433293381</v>
+        <v>54.46589433293406</v>
       </c>
       <c r="J5" t="n">
-        <v>55.47212615797066</v>
+        <v>55.47212615797127</v>
       </c>
       <c r="K5" t="n">
-        <v>55.47212615797066</v>
+        <v>55.47212615797127</v>
       </c>
       <c r="L5" t="n">
-        <v>55.47212615797066</v>
+        <v>55.47212615797127</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122.5694862491228</v>
+        <v>122.5694862491231</v>
       </c>
       <c r="C6" t="n">
-        <v>180.1681926929281</v>
+        <v>180.1681926930718</v>
       </c>
       <c r="D6" t="n">
-        <v>193.323826929885</v>
+        <v>193.3238269298853</v>
       </c>
       <c r="E6" t="n">
-        <v>164.1405586298902</v>
+        <v>164.1405586298904</v>
       </c>
       <c r="F6" t="n">
-        <v>123.4150154580523</v>
+        <v>123.4150154580524</v>
       </c>
       <c r="G6" t="n">
-        <v>181.0135569873285</v>
+        <v>181.0135569873289</v>
       </c>
       <c r="H6" t="n">
-        <v>181.1721771998335</v>
+        <v>181.1721771998338</v>
       </c>
       <c r="I6" t="n">
-        <v>180.1659453747986</v>
+        <v>180.1659453747989</v>
       </c>
       <c r="J6" t="n">
-        <v>181.1836943131557</v>
+        <v>181.1836943131559</v>
       </c>
       <c r="K6" t="n">
-        <v>121.4809111775671</v>
+        <v>121.4809111775672</v>
       </c>
       <c r="L6" t="n">
-        <v>242.3875881802164</v>
+        <v>242.3875881802168</v>
       </c>
     </row>
     <row r="7">
@@ -7051,34 +7051,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.52466711162165</v>
+        <v>99.52466711162199</v>
       </c>
       <c r="C7" t="n">
-        <v>117.6522966531854</v>
+        <v>117.6522966531856</v>
       </c>
       <c r="D7" t="n">
-        <v>118.6585350897653</v>
+        <v>118.6585350897658</v>
       </c>
       <c r="E7" t="n">
-        <v>139.7323680044331</v>
+        <v>139.7323680044332</v>
       </c>
       <c r="F7" t="n">
-        <v>117.6522927018792</v>
+        <v>117.6522927018788</v>
       </c>
       <c r="G7" t="n">
-        <v>118.4999082657152</v>
+        <v>118.4999082657153</v>
       </c>
       <c r="H7" t="n">
         <v>118.6585284782226</v>
       </c>
       <c r="I7" t="n">
-        <v>117.6522966531854</v>
+        <v>117.6522966531856</v>
       </c>
       <c r="J7" t="n">
         <v>118.6585284782226</v>
       </c>
       <c r="K7" t="n">
-        <v>107.5722968387393</v>
+        <v>107.1225141488717</v>
       </c>
       <c r="L7" t="n">
         <v>118.6585284782226</v>
@@ -7094,34 +7094,34 @@
         <v>81.91925181508105</v>
       </c>
       <c r="C8" t="n">
-        <v>49.01955072486184</v>
+        <v>49.01955072486185</v>
       </c>
       <c r="D8" t="n">
         <v>84.33237363263041</v>
       </c>
       <c r="E8" t="n">
-        <v>49.01955072486184</v>
+        <v>49.01955072486185</v>
       </c>
       <c r="F8" t="n">
-        <v>49.01955072486184</v>
+        <v>49.01955072486185</v>
       </c>
       <c r="G8" t="n">
-        <v>83.42218042983514</v>
+        <v>83.42218042983501</v>
       </c>
       <c r="H8" t="n">
-        <v>84.71911060560541</v>
+        <v>84.71911060560545</v>
       </c>
       <c r="I8" t="n">
-        <v>49.01955072486184</v>
+        <v>49.01955072486185</v>
       </c>
       <c r="J8" t="n">
-        <v>80.70155627603647</v>
+        <v>80.70155627603648</v>
       </c>
       <c r="K8" t="n">
-        <v>83.39185919913383</v>
+        <v>83.3918591991339</v>
       </c>
       <c r="L8" t="n">
-        <v>84.75298020613009</v>
+        <v>84.75298020613013</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.952704374579</v>
+        <v>83.95270437457911</v>
       </c>
       <c r="C9" t="n">
-        <v>50.82200272572431</v>
+        <v>50.82200272572435</v>
       </c>
       <c r="D9" t="n">
-        <v>84.93562421601374</v>
+        <v>84.93562421601368</v>
       </c>
       <c r="E9" t="n">
-        <v>50.82200272572431</v>
+        <v>50.82200272572435</v>
       </c>
       <c r="F9" t="n">
-        <v>50.82200272572431</v>
+        <v>50.82200272572435</v>
       </c>
       <c r="G9" t="n">
-        <v>84.54534539894561</v>
+        <v>84.54534539894556</v>
       </c>
       <c r="H9" t="n">
-        <v>85.09517644658473</v>
+        <v>85.09517644658482</v>
       </c>
       <c r="I9" t="n">
-        <v>50.82200272572431</v>
+        <v>50.82200272572435</v>
       </c>
       <c r="J9" t="n">
-        <v>83.45914085624514</v>
+        <v>83.45914085624518</v>
       </c>
       <c r="K9" t="n">
-        <v>84.55267823689263</v>
+        <v>84.55267823689255</v>
       </c>
       <c r="L9" t="n">
-        <v>85.1085282538596</v>
+        <v>85.07468780549323</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>316.5655078329705</v>
+        <v>316.5655078329703</v>
       </c>
       <c r="C2" t="n">
-        <v>256.6498707667241</v>
+        <v>256.649870766724</v>
       </c>
       <c r="D2" t="n">
-        <v>1241.401210069891</v>
+        <v>1241.401210069893</v>
       </c>
       <c r="E2" t="n">
-        <v>256.6498707667241</v>
+        <v>256.649870766724</v>
       </c>
       <c r="F2" t="n">
-        <v>256.6498707667241</v>
+        <v>256.649870766724</v>
       </c>
       <c r="G2" t="n">
-        <v>669.3938627776481</v>
+        <v>669.3938627776456</v>
       </c>
       <c r="H2" t="n">
-        <v>2049.555477788971</v>
+        <v>2049.555477788973</v>
       </c>
       <c r="I2" t="n">
-        <v>256.6498707667241</v>
+        <v>256.649870766724</v>
       </c>
       <c r="J2" t="n">
-        <v>526.1087458254547</v>
+        <v>526.1087458254558</v>
       </c>
       <c r="K2" t="n">
-        <v>404.3336431986019</v>
+        <v>404.3336431986023</v>
       </c>
       <c r="L2" t="n">
-        <v>1818.056018106402</v>
+        <v>1818.056018106403</v>
       </c>
     </row>
     <row r="3">
@@ -7290,25 +7290,25 @@
         <v>34.6113900549776</v>
       </c>
       <c r="C3" t="n">
-        <v>32.6737604745677</v>
+        <v>32.67376047456774</v>
       </c>
       <c r="D3" t="n">
         <v>34.6113900549776</v>
       </c>
       <c r="E3" t="n">
-        <v>32.80654539528426</v>
+        <v>32.8065453952843</v>
       </c>
       <c r="F3" t="n">
-        <v>32.80654539528426</v>
+        <v>32.8065453952843</v>
       </c>
       <c r="G3" t="n">
-        <v>34.43676742127052</v>
+        <v>34.43676742127055</v>
       </c>
       <c r="H3" t="n">
         <v>34.6113900549776</v>
       </c>
       <c r="I3" t="n">
-        <v>33.50306314177295</v>
+        <v>33.50306314177303</v>
       </c>
       <c r="J3" t="n">
         <v>34.6113900549776</v>
@@ -7327,28 +7327,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>141.1650141487015</v>
+        <v>141.1650141487014</v>
       </c>
       <c r="C4" t="n">
         <v>139.2105256872709</v>
       </c>
       <c r="D4" t="n">
-        <v>142.6664362047688</v>
+        <v>142.6664362047714</v>
       </c>
       <c r="E4" t="n">
-        <v>128.9231212926852</v>
+        <v>128.923121292685</v>
       </c>
       <c r="F4" t="n">
-        <v>140.0086932521165</v>
+        <v>140.0086932521164</v>
       </c>
       <c r="G4" t="n">
         <v>217.8169887367401</v>
       </c>
       <c r="H4" t="n">
-        <v>216.7970388578012</v>
+        <v>216.7970388578011</v>
       </c>
       <c r="I4" t="n">
-        <v>140.0566872354969</v>
+        <v>216.8832844572423</v>
       </c>
       <c r="J4" t="n">
         <v>216.1674631456623</v>
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.77547768945306</v>
+        <v>60.77547768945303</v>
       </c>
       <c r="C5" t="n">
-        <v>59.66715077624842</v>
+        <v>59.66715077624849</v>
       </c>
       <c r="D5" t="n">
         <v>60.77496945812464</v>
       </c>
       <c r="E5" t="n">
-        <v>59.65080003798728</v>
+        <v>59.65080003798737</v>
       </c>
       <c r="F5" t="n">
-        <v>59.65080003798728</v>
+        <v>59.65080003798737</v>
       </c>
       <c r="G5" t="n">
         <v>60.60085505574597</v>
       </c>
       <c r="H5" t="n">
-        <v>60.77547768945306</v>
+        <v>60.77547768945303</v>
       </c>
       <c r="I5" t="n">
-        <v>59.66715077624842</v>
+        <v>59.66715077624849</v>
       </c>
       <c r="J5" t="n">
-        <v>60.77547768945306</v>
+        <v>60.77547768945303</v>
       </c>
       <c r="K5" t="n">
-        <v>60.77547768945306</v>
+        <v>60.77547768945303</v>
       </c>
       <c r="L5" t="n">
-        <v>60.77547768945306</v>
+        <v>60.77547768945303</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.9073256110635</v>
+        <v>134.9073256110634</v>
       </c>
       <c r="C6" t="n">
-        <v>199.9535109609428</v>
+        <v>199.9535109611101</v>
       </c>
       <c r="D6" t="n">
-        <v>214.781850400936</v>
+        <v>214.7818504009358</v>
       </c>
       <c r="E6" t="n">
-        <v>181.8604141575718</v>
+        <v>181.8604141575719</v>
       </c>
       <c r="F6" t="n">
         <v>135.8866079115128</v>
       </c>
       <c r="G6" t="n">
-        <v>200.8892390437458</v>
+        <v>200.8892390437457</v>
       </c>
       <c r="H6" t="n">
-        <v>201.0638616774593</v>
+        <v>201.0638616774591</v>
       </c>
       <c r="I6" t="n">
         <v>199.9555347642482</v>
       </c>
       <c r="J6" t="n">
-        <v>201.0768633371425</v>
+        <v>201.0768633371424</v>
       </c>
       <c r="K6" t="n">
-        <v>133.6784339884149</v>
+        <v>133.6784339884147</v>
       </c>
       <c r="L6" t="n">
-        <v>270.169895522785</v>
+        <v>270.1698955227847</v>
       </c>
     </row>
     <row r="7">
@@ -7450,34 +7450,34 @@
         <v>124.2229361968713</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9546601833899</v>
+        <v>148.95466018339</v>
       </c>
       <c r="D7" t="n">
-        <v>150.0629817230762</v>
+        <v>150.0629817230764</v>
       </c>
       <c r="E7" t="n">
-        <v>178.7734863954892</v>
+        <v>178.7734863954894</v>
       </c>
       <c r="F7" t="n">
-        <v>148.9546283665271</v>
+        <v>148.9546283665273</v>
       </c>
       <c r="G7" t="n">
-        <v>149.8883644628874</v>
+        <v>149.8883644628875</v>
       </c>
       <c r="H7" t="n">
-        <v>150.0629870965943</v>
+        <v>150.0629870965946</v>
       </c>
       <c r="I7" t="n">
-        <v>148.9546601833899</v>
+        <v>148.95466018339</v>
       </c>
       <c r="J7" t="n">
-        <v>150.0629870965943</v>
+        <v>150.0629870965946</v>
       </c>
       <c r="K7" t="n">
-        <v>134.4837320572767</v>
+        <v>135.091157863513</v>
       </c>
       <c r="L7" t="n">
-        <v>150.0629870965943</v>
+        <v>150.0629870965946</v>
       </c>
     </row>
     <row r="8">
@@ -7487,13 +7487,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.42075063025077</v>
+        <v>83.42075063025084</v>
       </c>
       <c r="C8" t="n">
         <v>50.26824461477715</v>
       </c>
       <c r="D8" t="n">
-        <v>60.96365314983255</v>
+        <v>60.9636531498326</v>
       </c>
       <c r="E8" t="n">
         <v>50.26824461477715</v>
@@ -7502,10 +7502,10 @@
         <v>50.26824461477715</v>
       </c>
       <c r="G8" t="n">
-        <v>75.26300686996815</v>
+        <v>75.26300686996814</v>
       </c>
       <c r="H8" t="n">
-        <v>45.42227072347139</v>
+        <v>45.42227072347141</v>
       </c>
       <c r="I8" t="n">
         <v>50.26824461477715</v>
@@ -7514,10 +7514,10 @@
         <v>79.28408502656595</v>
       </c>
       <c r="K8" t="n">
-        <v>81.36880108983217</v>
+        <v>81.3688010898322</v>
       </c>
       <c r="L8" t="n">
-        <v>84.95233899805862</v>
+        <v>54.80499735793246</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.66469732606483</v>
+        <v>85.66469732606491</v>
       </c>
       <c r="C9" t="n">
-        <v>52.14524681602401</v>
+        <v>52.14524681602403</v>
       </c>
       <c r="D9" t="n">
-        <v>76.51880515048748</v>
+        <v>76.51880515048755</v>
       </c>
       <c r="E9" t="n">
-        <v>52.14524681602401</v>
+        <v>52.14524681602403</v>
       </c>
       <c r="F9" t="n">
-        <v>52.14524681602401</v>
+        <v>52.14524681602403</v>
       </c>
       <c r="G9" t="n">
-        <v>82.28162491311326</v>
+        <v>82.2816249131133</v>
       </c>
       <c r="H9" t="n">
-        <v>70.22861055077958</v>
+        <v>70.22861055077956</v>
       </c>
       <c r="I9" t="n">
-        <v>52.14524681602401</v>
+        <v>52.14524681602403</v>
       </c>
       <c r="J9" t="n">
-        <v>83.98351772845223</v>
+        <v>83.98351772845226</v>
       </c>
       <c r="K9" t="n">
-        <v>84.82934858102341</v>
+        <v>84.82934858102344</v>
       </c>
       <c r="L9" t="n">
-        <v>86.29142972180354</v>
+        <v>74.03548656091388</v>
       </c>
     </row>
   </sheetData>
@@ -7643,13 +7643,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>265.9308307436857</v>
+        <v>265.9308307436858</v>
       </c>
       <c r="C2" t="n">
-        <v>217.8343081690805</v>
+        <v>217.8343081690804</v>
       </c>
       <c r="D2" t="n">
-        <v>909.5117132715351</v>
+        <v>909.5117132715359</v>
       </c>
       <c r="E2" t="n">
         <v>217.8343081690804</v>
@@ -7658,22 +7658,22 @@
         <v>217.8343081690804</v>
       </c>
       <c r="G2" t="n">
-        <v>420.4458218144042</v>
+        <v>420.445821814405</v>
       </c>
       <c r="H2" t="n">
-        <v>360.1082326665046</v>
+        <v>360.1082326665043</v>
       </c>
       <c r="I2" t="n">
-        <v>217.8343081690805</v>
+        <v>217.8343081690804</v>
       </c>
       <c r="J2" t="n">
-        <v>395.1325480538023</v>
+        <v>395.1325480538021</v>
       </c>
       <c r="K2" t="n">
-        <v>215.246483395058</v>
+        <v>215.2464833950579</v>
       </c>
       <c r="L2" t="n">
-        <v>1052.730164150326</v>
+        <v>183.8666675832683</v>
       </c>
     </row>
     <row r="3">
@@ -7686,25 +7686,25 @@
         <v>33.7297014338904</v>
       </c>
       <c r="C3" t="n">
-        <v>32.01845253335529</v>
+        <v>32.01845253335524</v>
       </c>
       <c r="D3" t="n">
         <v>33.7297014338904</v>
       </c>
       <c r="E3" t="n">
-        <v>32.1298146957018</v>
+        <v>32.12981469570171</v>
       </c>
       <c r="F3" t="n">
-        <v>32.1298146957018</v>
+        <v>32.1298146957017</v>
       </c>
       <c r="G3" t="n">
-        <v>33.5623396842333</v>
+        <v>33.56233968423329</v>
       </c>
       <c r="H3" t="n">
-        <v>33.72970143389036</v>
+        <v>33.7297014338904</v>
       </c>
       <c r="I3" t="n">
-        <v>32.66772664688644</v>
+        <v>32.66772664688639</v>
       </c>
       <c r="J3" t="n">
         <v>33.7297014338904</v>
@@ -7723,31 +7723,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>132.5629299779156</v>
+        <v>202.8904879390038</v>
       </c>
       <c r="C4" t="n">
         <v>130.9857851743999</v>
       </c>
       <c r="D4" t="n">
-        <v>133.788787123806</v>
+        <v>133.7887871238026</v>
       </c>
       <c r="E4" t="n">
-        <v>121.4205794822475</v>
+        <v>121.4205794822474</v>
       </c>
       <c r="F4" t="n">
-        <v>131.4801035011088</v>
+        <v>131.4801035011089</v>
       </c>
       <c r="G4" t="n">
-        <v>202.7231261893463</v>
+        <v>132.3955682282587</v>
       </c>
       <c r="H4" t="n">
-        <v>201.368836823859</v>
+        <v>201.3688368238592</v>
       </c>
       <c r="I4" t="n">
         <v>201.8285131519996</v>
       </c>
       <c r="J4" t="n">
-        <v>201.1309448171156</v>
+        <v>137.8172108651421</v>
       </c>
       <c r="K4" t="n">
         <v>132.2563412442653</v>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.01556953390974</v>
+        <v>57.0155695339098</v>
       </c>
       <c r="C5" t="n">
-        <v>55.95359474690573</v>
+        <v>55.95359474690578</v>
       </c>
       <c r="D5" t="n">
-        <v>57.01510400497794</v>
+        <v>57.01510400497793</v>
       </c>
       <c r="E5" t="n">
         <v>55.93936264589145</v>
@@ -7778,22 +7778,22 @@
         <v>55.93936264589145</v>
       </c>
       <c r="G5" t="n">
-        <v>56.84820778425266</v>
+        <v>56.84820778425261</v>
       </c>
       <c r="H5" t="n">
-        <v>57.01556953390974</v>
+        <v>57.0155695339098</v>
       </c>
       <c r="I5" t="n">
-        <v>55.95359474690573</v>
+        <v>55.95359474690578</v>
       </c>
       <c r="J5" t="n">
-        <v>57.01556953390974</v>
+        <v>57.0155695339098</v>
       </c>
       <c r="K5" t="n">
-        <v>57.01556953390974</v>
+        <v>57.0155695339098</v>
       </c>
       <c r="L5" t="n">
-        <v>57.01556953390974</v>
+        <v>57.0155695339098</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.2058614893285</v>
+        <v>125.2058614893286</v>
       </c>
       <c r="C6" t="n">
-        <v>184.3173874988042</v>
+        <v>184.3173874989527</v>
       </c>
       <c r="D6" t="n">
-        <v>197.8582076679448</v>
+        <v>197.8582076679446</v>
       </c>
       <c r="E6" t="n">
-        <v>167.860184681134</v>
+        <v>167.8601846811341</v>
       </c>
       <c r="F6" t="n">
-        <v>126.0431201361578</v>
+        <v>126.0431201361576</v>
       </c>
       <c r="G6" t="n">
-        <v>185.2132246962861</v>
+        <v>185.2132246962863</v>
       </c>
       <c r="H6" t="n">
         <v>185.3805864459427</v>
       </c>
       <c r="I6" t="n">
-        <v>184.3186116589393</v>
+        <v>184.3186116589391</v>
       </c>
       <c r="J6" t="n">
-        <v>185.392412508457</v>
+        <v>185.3924125084571</v>
       </c>
       <c r="K6" t="n">
         <v>124.0880850790902</v>
       </c>
       <c r="L6" t="n">
-        <v>248.2381183963272</v>
+        <v>248.2381183963271</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107.7447239379979</v>
+        <v>107.7447239379978</v>
       </c>
       <c r="C7" t="n">
-        <v>128.0450351721216</v>
+        <v>128.0450351721215</v>
       </c>
       <c r="D7" t="n">
-        <v>129.1070207987559</v>
+        <v>129.1070207987558</v>
       </c>
       <c r="E7" t="n">
         <v>152.6966611550728</v>
       </c>
       <c r="F7" t="n">
-        <v>128.0450280276259</v>
+        <v>128.0450280276257</v>
       </c>
       <c r="G7" t="n">
         <v>128.9396482094683</v>
       </c>
       <c r="H7" t="n">
-        <v>129.1070099591257</v>
+        <v>129.1070099591255</v>
       </c>
       <c r="I7" t="n">
-        <v>128.0450351721216</v>
+        <v>128.0450351721215</v>
       </c>
       <c r="J7" t="n">
-        <v>129.1070099591257</v>
+        <v>129.1070099591255</v>
       </c>
       <c r="K7" t="n">
-        <v>116.7296221014278</v>
+        <v>102.2080758945706</v>
       </c>
       <c r="L7" t="n">
-        <v>129.1070099591257</v>
+        <v>129.1070099591255</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.2062885352001</v>
+        <v>83.20628853520014</v>
       </c>
       <c r="C8" t="n">
-        <v>50.11566601249946</v>
+        <v>50.11566601249942</v>
       </c>
       <c r="D8" t="n">
-        <v>65.60999020229775</v>
+        <v>65.60999020229774</v>
       </c>
       <c r="E8" t="n">
-        <v>50.11566601249946</v>
+        <v>50.11566601249942</v>
       </c>
       <c r="F8" t="n">
-        <v>50.11566601249946</v>
+        <v>50.11566601249942</v>
       </c>
       <c r="G8" t="n">
-        <v>79.23465703093828</v>
+        <v>79.23465703093832</v>
       </c>
       <c r="H8" t="n">
         <v>81.52405890587141</v>
       </c>
       <c r="I8" t="n">
-        <v>50.11566601249946</v>
+        <v>50.11566601249942</v>
       </c>
       <c r="J8" t="n">
-        <v>80.52305522968278</v>
+        <v>80.5230552296828</v>
       </c>
       <c r="K8" t="n">
-        <v>84.4706773103519</v>
+        <v>84.47067731035195</v>
       </c>
       <c r="L8" t="n">
-        <v>85.63891084656737</v>
+        <v>66.92237646503153</v>
       </c>
     </row>
     <row r="9">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.9884405859208</v>
+        <v>84.98844058592077</v>
       </c>
       <c r="C9" t="n">
         <v>51.65324228202687</v>
@@ -7938,7 +7938,7 @@
         <v>51.65324228202687</v>
       </c>
       <c r="G9" t="n">
-        <v>83.32842899262847</v>
+        <v>83.32842899262855</v>
       </c>
       <c r="H9" t="n">
         <v>84.30917853436458</v>
@@ -7947,13 +7947,13 @@
         <v>51.65324228202687</v>
       </c>
       <c r="J9" t="n">
-        <v>83.89837592077014</v>
+        <v>83.89837592077015</v>
       </c>
       <c r="K9" t="n">
-        <v>85.50359770616882</v>
+        <v>85.50359770616886</v>
       </c>
       <c r="L9" t="n">
-        <v>85.98089055640787</v>
+        <v>78.37196492033051</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
+++ b/Results/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>408.0844050706268</v>
+        <v>408.084405070633</v>
       </c>
       <c r="C2" t="n">
-        <v>375.2051300597032</v>
+        <v>375.2051300597033</v>
       </c>
       <c r="D2" t="n">
-        <v>1490.457482223186</v>
+        <v>1490.457482223189</v>
       </c>
       <c r="E2" t="n">
-        <v>375.2051300597032</v>
+        <v>375.2051300597033</v>
       </c>
       <c r="F2" t="n">
-        <v>375.2051300597032</v>
+        <v>375.2051300597033</v>
       </c>
       <c r="G2" t="n">
-        <v>836.7773601002343</v>
+        <v>836.7773601002324</v>
       </c>
       <c r="H2" t="n">
-        <v>2608.002443786356</v>
+        <v>2608.002443786355</v>
       </c>
       <c r="I2" t="n">
-        <v>375.2051300597032</v>
+        <v>375.2051300597033</v>
       </c>
       <c r="J2" t="n">
-        <v>704.2831307156262</v>
+        <v>704.2831307156397</v>
       </c>
       <c r="K2" t="n">
-        <v>523.5460598837703</v>
+        <v>523.5460598837706</v>
       </c>
       <c r="L2" t="n">
-        <v>330.8268586249813</v>
+        <v>2286.972212175716</v>
       </c>
     </row>
     <row r="3">
@@ -555,16 +555,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.65687052377783</v>
+        <v>35.65687052377778</v>
       </c>
       <c r="C3" t="n">
-        <v>33.68074942874819</v>
+        <v>33.68074942874816</v>
       </c>
       <c r="D3" t="n">
-        <v>35.65687052377783</v>
+        <v>35.65687052377778</v>
       </c>
       <c r="E3" t="n">
-        <v>33.8248061684054</v>
+        <v>33.82480616840537</v>
       </c>
       <c r="F3" t="n">
         <v>33.82480616840537</v>
@@ -573,19 +573,19 @@
         <v>35.48235461852929</v>
       </c>
       <c r="H3" t="n">
-        <v>35.65687052377783</v>
+        <v>35.65687052377778</v>
       </c>
       <c r="I3" t="n">
-        <v>34.54931642253401</v>
+        <v>34.54931642253398</v>
       </c>
       <c r="J3" t="n">
-        <v>35.65687052377783</v>
+        <v>35.65687052377778</v>
       </c>
       <c r="K3" t="n">
-        <v>35.65687052377783</v>
+        <v>35.65687052377778</v>
       </c>
       <c r="L3" t="n">
-        <v>35.65687052377783</v>
+        <v>35.65687052377778</v>
       </c>
     </row>
     <row r="4">
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>149.8979535870587</v>
+        <v>149.8979535870586</v>
       </c>
       <c r="C4" t="n">
-        <v>147.9249159232165</v>
+        <v>147.9249159232158</v>
       </c>
       <c r="D4" t="n">
-        <v>151.522631696272</v>
+        <v>151.5226933284323</v>
       </c>
       <c r="E4" t="n">
-        <v>136.9025460103958</v>
+        <v>136.9025460103956</v>
       </c>
       <c r="F4" t="n">
-        <v>148.7729653216367</v>
+        <v>148.7729653216366</v>
       </c>
       <c r="G4" t="n">
-        <v>232.6487454311795</v>
+        <v>232.6487454311798</v>
       </c>
       <c r="H4" t="n">
         <v>231.510278915136</v>
       </c>
       <c r="I4" t="n">
-        <v>148.7903994858146</v>
+        <v>231.7157072351844</v>
       </c>
       <c r="J4" t="n">
-        <v>156.0776153022124</v>
+        <v>230.8249235454228</v>
       </c>
       <c r="K4" t="n">
-        <v>149.5989656583114</v>
+        <v>149.5989656583111</v>
       </c>
       <c r="L4" t="n">
         <v>150.5138706559962</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.83206741890943</v>
+        <v>64.83206741890935</v>
       </c>
       <c r="C5" t="n">
-        <v>63.72451331766578</v>
+        <v>63.72451331766555</v>
       </c>
       <c r="D5" t="n">
-        <v>64.83150378717332</v>
+        <v>64.8315037871733</v>
       </c>
       <c r="E5" t="n">
-        <v>63.71044632745487</v>
+        <v>63.71044632745474</v>
       </c>
       <c r="F5" t="n">
-        <v>63.71044632745487</v>
+        <v>63.71044632745474</v>
       </c>
       <c r="G5" t="n">
-        <v>64.65755151366102</v>
+        <v>64.65755151366092</v>
       </c>
       <c r="H5" t="n">
-        <v>64.83206741890943</v>
+        <v>64.83206741890935</v>
       </c>
       <c r="I5" t="n">
-        <v>63.72451331766578</v>
+        <v>63.72451331766555</v>
       </c>
       <c r="J5" t="n">
-        <v>64.83206741890943</v>
+        <v>64.83206741890935</v>
       </c>
       <c r="K5" t="n">
-        <v>64.83206741890943</v>
+        <v>64.83206741890935</v>
       </c>
       <c r="L5" t="n">
-        <v>64.83206741890943</v>
+        <v>64.83206741890935</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144.9051130134648</v>
+        <v>144.9051130134647</v>
       </c>
       <c r="C6" t="n">
-        <v>216.018660718589</v>
+        <v>216.0186607187701</v>
       </c>
       <c r="D6" t="n">
-        <v>232.1000195980191</v>
+        <v>232.1000195980187</v>
       </c>
       <c r="E6" t="n">
-        <v>196.2669723852205</v>
+        <v>196.2669723852203</v>
       </c>
       <c r="F6" t="n">
-        <v>146.0787559854717</v>
+        <v>146.0787559854716</v>
       </c>
       <c r="G6" t="n">
-        <v>216.9502816377244</v>
+        <v>216.9502816377243</v>
       </c>
       <c r="H6" t="n">
         <v>217.1247975429769</v>
       </c>
       <c r="I6" t="n">
-        <v>216.0172434417292</v>
+        <v>216.0172434417289</v>
       </c>
       <c r="J6" t="n">
-        <v>217.1389907853383</v>
+        <v>217.1389907853381</v>
       </c>
       <c r="K6" t="n">
-        <v>143.5635952952724</v>
+        <v>143.5635952952725</v>
       </c>
       <c r="L6" t="n">
-        <v>292.5642969504917</v>
+        <v>292.5642969504912</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142.7509955549811</v>
+        <v>142.750995554981</v>
       </c>
       <c r="C7" t="n">
-        <v>172.4815900215823</v>
+        <v>172.4815900215825</v>
       </c>
       <c r="D7" t="n">
-        <v>173.5891380332338</v>
+        <v>173.5891380332333</v>
       </c>
       <c r="E7" t="n">
-        <v>208.0681078942034</v>
+        <v>208.0681078942028</v>
       </c>
       <c r="F7" t="n">
-        <v>172.4815530652098</v>
+        <v>172.4815530652096</v>
       </c>
       <c r="G7" t="n">
-        <v>173.4146282175778</v>
+        <v>173.4146282175779</v>
       </c>
       <c r="H7" t="n">
-        <v>173.5891441228263</v>
+        <v>173.5891441228264</v>
       </c>
       <c r="I7" t="n">
-        <v>172.4815900215823</v>
+        <v>172.4815900215825</v>
       </c>
       <c r="J7" t="n">
-        <v>173.5891441228263</v>
+        <v>173.5891441228264</v>
       </c>
       <c r="K7" t="n">
-        <v>155.7213971706129</v>
+        <v>134.7584120641641</v>
       </c>
       <c r="L7" t="n">
-        <v>173.5891441228263</v>
+        <v>173.5891441228264</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.80562123641141</v>
+        <v>82.80562123641091</v>
       </c>
       <c r="C8" t="n">
-        <v>49.11242631413121</v>
+        <v>49.11242631413115</v>
       </c>
       <c r="D8" t="n">
-        <v>59.7212313693331</v>
+        <v>59.72123136933297</v>
       </c>
       <c r="E8" t="n">
-        <v>49.11242631413121</v>
+        <v>49.11242631413115</v>
       </c>
       <c r="F8" t="n">
-        <v>49.11242631413121</v>
+        <v>49.11242631413115</v>
       </c>
       <c r="G8" t="n">
         <v>74.02051779762998</v>
       </c>
       <c r="H8" t="n">
-        <v>41.98776974610141</v>
+        <v>41.98776974610143</v>
       </c>
       <c r="I8" t="n">
-        <v>49.11242631413121</v>
+        <v>49.11242631413115</v>
       </c>
       <c r="J8" t="n">
-        <v>77.29911592075371</v>
+        <v>77.29911592075361</v>
       </c>
       <c r="K8" t="n">
-        <v>80.46330989216915</v>
+        <v>80.46330989216936</v>
       </c>
       <c r="L8" t="n">
-        <v>85.14966229775793</v>
+        <v>85.14966229775783</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.95082205911763</v>
+        <v>85.95082205911766</v>
       </c>
       <c r="C9" t="n">
-        <v>52.30773405646395</v>
+        <v>52.30773405646393</v>
       </c>
       <c r="D9" t="n">
-        <v>76.54949516878384</v>
+        <v>76.54949516878368</v>
       </c>
       <c r="E9" t="n">
-        <v>52.30773405646395</v>
+        <v>52.30773405646393</v>
       </c>
       <c r="F9" t="n">
-        <v>52.30773405646395</v>
+        <v>52.30773405646393</v>
       </c>
       <c r="G9" t="n">
-        <v>82.31302720024736</v>
+        <v>82.31302720024728</v>
       </c>
       <c r="H9" t="n">
-        <v>69.37048090091687</v>
+        <v>69.37048090091683</v>
       </c>
       <c r="I9" t="n">
-        <v>52.30773405646395</v>
+        <v>52.30773405646393</v>
       </c>
       <c r="J9" t="n">
-        <v>83.71282529807682</v>
+        <v>83.71282529807674</v>
       </c>
       <c r="K9" t="n">
-        <v>84.99730758954996</v>
+        <v>84.99730758954985</v>
       </c>
       <c r="L9" t="n">
-        <v>86.90900363609988</v>
+        <v>72.41003668683855</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249.9260087418476</v>
+        <v>249.9260087418482</v>
       </c>
       <c r="C2" t="n">
-        <v>223.4856829529575</v>
+        <v>223.4856829529589</v>
       </c>
       <c r="D2" t="n">
-        <v>232.0214582845722</v>
+        <v>232.0214582845723</v>
       </c>
       <c r="E2" t="n">
-        <v>223.4856829529575</v>
+        <v>223.4856829529589</v>
       </c>
       <c r="F2" t="n">
-        <v>223.4856829529575</v>
+        <v>223.4856829529589</v>
       </c>
       <c r="G2" t="n">
-        <v>240.3477657233017</v>
+        <v>240.3477657232995</v>
       </c>
       <c r="H2" t="n">
-        <v>244.5368367612785</v>
+        <v>244.536836761279</v>
       </c>
       <c r="I2" t="n">
-        <v>223.4856829529575</v>
+        <v>223.4856829529589</v>
       </c>
       <c r="J2" t="n">
         <v>343.8415473830702</v>
       </c>
       <c r="K2" t="n">
-        <v>176.9804209411029</v>
+        <v>176.9804209411032</v>
       </c>
       <c r="L2" t="n">
-        <v>191.7092692051723</v>
+        <v>191.7092692051725</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.310815763665</v>
+        <v>33.31081576366508</v>
       </c>
       <c r="C3" t="n">
-        <v>31.79568093463133</v>
+        <v>31.79568093463136</v>
       </c>
       <c r="D3" t="n">
-        <v>33.310815763665</v>
+        <v>33.31081576366508</v>
       </c>
       <c r="E3" t="n">
-        <v>31.89424241017433</v>
+        <v>31.89424241017442</v>
       </c>
       <c r="F3" t="n">
-        <v>31.89424241017434</v>
+        <v>31.89424241017441</v>
       </c>
       <c r="G3" t="n">
-        <v>33.15135328481115</v>
+        <v>33.15135328481121</v>
       </c>
       <c r="H3" t="n">
-        <v>33.310815763665</v>
+        <v>33.31081576366508</v>
       </c>
       <c r="I3" t="n">
-        <v>32.29925027941912</v>
+        <v>32.2992502794192</v>
       </c>
       <c r="J3" t="n">
-        <v>33.310815763665</v>
+        <v>33.31081576366508</v>
       </c>
       <c r="K3" t="n">
-        <v>33.310815763665</v>
+        <v>33.31081576366508</v>
       </c>
       <c r="L3" t="n">
-        <v>33.310815763665</v>
+        <v>33.31081576366508</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.879902300267</v>
+        <v>131.7917874784089</v>
       </c>
       <c r="C4" t="n">
-        <v>130.5685320358245</v>
+        <v>130.568532035825</v>
       </c>
       <c r="D4" t="n">
-        <v>199.2634145806905</v>
+        <v>199.2634145806902</v>
       </c>
       <c r="E4" t="n">
-        <v>121.0156238260925</v>
+        <v>121.0156238260924</v>
       </c>
       <c r="F4" t="n">
-        <v>130.805547410971</v>
+        <v>130.8055474109712</v>
       </c>
       <c r="G4" t="n">
-        <v>131.6323249995551</v>
+        <v>200.7204398214126</v>
       </c>
       <c r="H4" t="n">
-        <v>199.3373857826483</v>
+        <v>199.3373857826484</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7802219941627</v>
+        <v>130.7802219941628</v>
       </c>
       <c r="J4" t="n">
-        <v>199.0810494786128</v>
+        <v>137.0134072911319</v>
       </c>
       <c r="K4" t="n">
-        <v>131.6539225650438</v>
+        <v>131.653922565045</v>
       </c>
       <c r="L4" t="n">
-        <v>131.8123512196125</v>
+        <v>131.8123512196127</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.84331549644738</v>
+        <v>55.84331549644753</v>
       </c>
       <c r="C5" t="n">
-        <v>54.83175001220144</v>
+        <v>54.83175001220153</v>
       </c>
       <c r="D5" t="n">
-        <v>55.8428518009074</v>
+        <v>55.84285180090761</v>
       </c>
       <c r="E5" t="n">
-        <v>54.82123796443649</v>
+        <v>54.82123796443658</v>
       </c>
       <c r="F5" t="n">
-        <v>54.82123796443649</v>
+        <v>54.82123796443658</v>
       </c>
       <c r="G5" t="n">
-        <v>55.68385301759352</v>
+        <v>55.68385301759379</v>
       </c>
       <c r="H5" t="n">
-        <v>55.84331549644738</v>
+        <v>55.84331549644753</v>
       </c>
       <c r="I5" t="n">
-        <v>54.83175001220144</v>
+        <v>54.83175001220153</v>
       </c>
       <c r="J5" t="n">
-        <v>55.84331549644738</v>
+        <v>55.84331549644753</v>
       </c>
       <c r="K5" t="n">
-        <v>55.84331549644738</v>
+        <v>55.84331549644753</v>
       </c>
       <c r="L5" t="n">
-        <v>55.84331549644738</v>
+        <v>55.84331549644753</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123.2157281563319</v>
+        <v>123.2157281563321</v>
       </c>
       <c r="C6" t="n">
-        <v>181.2219897706142</v>
+        <v>181.2219897707594</v>
       </c>
       <c r="D6" t="n">
-        <v>194.4687456562284</v>
+        <v>194.4687456562291</v>
       </c>
       <c r="E6" t="n">
-        <v>165.0814095772335</v>
+        <v>165.0814095772338</v>
       </c>
       <c r="F6" t="n">
-        <v>124.0688756288233</v>
+        <v>124.0688756288237</v>
       </c>
       <c r="G6" t="n">
-        <v>182.0719885812199</v>
+        <v>182.0719885812205</v>
       </c>
       <c r="H6" t="n">
-        <v>182.2314510600751</v>
+        <v>182.2314510600754</v>
       </c>
       <c r="I6" t="n">
-        <v>181.219885575828</v>
+        <v>181.2198855758284</v>
       </c>
       <c r="J6" t="n">
-        <v>182.2430493458921</v>
+        <v>182.2430493458924</v>
       </c>
       <c r="K6" t="n">
-        <v>122.1194808042105</v>
+        <v>122.1194808042108</v>
       </c>
       <c r="L6" t="n">
-        <v>243.8783084524506</v>
+        <v>243.8783084524514</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100.0680749520667</v>
+        <v>100.068074952067</v>
       </c>
       <c r="C7" t="n">
-        <v>118.3417052209385</v>
+        <v>118.3417052209387</v>
       </c>
       <c r="D7" t="n">
-        <v>119.3532772737978</v>
+        <v>119.3532772737971</v>
       </c>
       <c r="E7" t="n">
-        <v>140.59641201087</v>
+        <v>140.5964120108708</v>
       </c>
       <c r="F7" t="n">
-        <v>118.3417003130386</v>
+        <v>118.3417003130383</v>
       </c>
       <c r="G7" t="n">
-        <v>119.1938082263305</v>
+        <v>119.1938082263311</v>
       </c>
       <c r="H7" t="n">
-        <v>119.3532707051844</v>
+        <v>119.3532707051843</v>
       </c>
       <c r="I7" t="n">
-        <v>118.3417052209385</v>
+        <v>118.3417052209387</v>
       </c>
       <c r="J7" t="n">
-        <v>119.3532707051844</v>
+        <v>119.3532707051843</v>
       </c>
       <c r="K7" t="n">
-        <v>108.1793553097613</v>
+        <v>108.1793553097614</v>
       </c>
       <c r="L7" t="n">
-        <v>119.3532707051844</v>
+        <v>119.3532707051843</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.84379479190882</v>
+        <v>82.84379479190881</v>
       </c>
       <c r="C8" t="n">
-        <v>49.47093784397967</v>
+        <v>49.47093784397973</v>
       </c>
       <c r="D8" t="n">
-        <v>83.37140864248089</v>
+        <v>83.37140864248084</v>
       </c>
       <c r="E8" t="n">
-        <v>49.47093784397967</v>
+        <v>49.47093784397973</v>
       </c>
       <c r="F8" t="n">
-        <v>49.47093784397967</v>
+        <v>49.47093784397973</v>
       </c>
       <c r="G8" t="n">
-        <v>83.1905102101509</v>
+        <v>83.19051021015085</v>
       </c>
       <c r="H8" t="n">
-        <v>83.60429983088349</v>
+        <v>83.60429983088339</v>
       </c>
       <c r="I8" t="n">
-        <v>49.47093784397967</v>
+        <v>49.47093784397973</v>
       </c>
       <c r="J8" t="n">
-        <v>80.96316290695046</v>
+        <v>80.96316290695047</v>
       </c>
       <c r="K8" t="n">
-        <v>84.74790920829753</v>
+        <v>84.74790920829727</v>
       </c>
       <c r="L8" t="n">
-        <v>84.86462646123559</v>
+        <v>84.86462646123537</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.4211498448245</v>
+        <v>84.42114984482448</v>
       </c>
       <c r="C9" t="n">
-        <v>51.12835016847356</v>
+        <v>51.12835016847361</v>
       </c>
       <c r="D9" t="n">
-        <v>84.63614397100862</v>
+        <v>84.63614397100858</v>
       </c>
       <c r="E9" t="n">
-        <v>51.12835016847356</v>
+        <v>51.12835016847361</v>
       </c>
       <c r="F9" t="n">
-        <v>51.12835016847356</v>
+        <v>51.12835016847361</v>
       </c>
       <c r="G9" t="n">
-        <v>84.54022566223895</v>
+        <v>84.5402256622389</v>
       </c>
       <c r="H9" t="n">
-        <v>84.73419128725794</v>
+        <v>84.73419128725779</v>
       </c>
       <c r="I9" t="n">
-        <v>51.12835016847356</v>
+        <v>51.12835016847361</v>
       </c>
       <c r="J9" t="n">
-        <v>83.65753711587951</v>
+        <v>83.65753711587948</v>
       </c>
       <c r="K9" t="n">
-        <v>85.19681040392096</v>
+        <v>85.19681040392088</v>
       </c>
       <c r="L9" t="n">
-        <v>85.2641873928288</v>
+        <v>85.2459435446731</v>
       </c>
     </row>
   </sheetData>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>153.805889901721</v>
+        <v>153.805889901716</v>
       </c>
       <c r="C2" t="n">
-        <v>192.7077995843788</v>
+        <v>192.7077995843784</v>
       </c>
       <c r="D2" t="n">
-        <v>835.2240548025443</v>
+        <v>835.2240548025441</v>
       </c>
       <c r="E2" t="n">
         <v>247.2262879838231</v>
@@ -1322,7 +1322,7 @@
         <v>247.2262879838231</v>
       </c>
       <c r="G2" t="n">
-        <v>484.2795172253723</v>
+        <v>484.2795172253802</v>
       </c>
       <c r="H2" t="n">
         <v>1242.011838424447</v>
@@ -1331,13 +1331,13 @@
         <v>247.2262879838231</v>
       </c>
       <c r="J2" t="n">
-        <v>550.1007226345804</v>
+        <v>550.1007226345787</v>
       </c>
       <c r="K2" t="n">
-        <v>336.5405068717826</v>
+        <v>336.540506871771</v>
       </c>
       <c r="L2" t="n">
-        <v>539.833240016615</v>
+        <v>539.8332400166147</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.53663371949865</v>
+        <v>34.53663371949874</v>
       </c>
       <c r="C3" t="n">
         <v>33.41185162749314</v>
       </c>
       <c r="D3" t="n">
-        <v>34.53663371949867</v>
+        <v>34.53663371949872</v>
       </c>
       <c r="E3" t="n">
-        <v>32.92683665681596</v>
+        <v>32.92683665681617</v>
       </c>
       <c r="F3" t="n">
-        <v>32.92683665681595</v>
+        <v>32.92683665681617</v>
       </c>
       <c r="G3" t="n">
-        <v>34.3727104106522</v>
+        <v>34.37271041065235</v>
       </c>
       <c r="H3" t="n">
-        <v>34.53663371949867</v>
+        <v>34.53663371949874</v>
       </c>
       <c r="I3" t="n">
-        <v>33.49841119510492</v>
+        <v>33.49841119510494</v>
       </c>
       <c r="J3" t="n">
-        <v>34.53663371949867</v>
+        <v>34.53663371949874</v>
       </c>
       <c r="K3" t="n">
-        <v>34.53663371949867</v>
+        <v>34.53663371949872</v>
       </c>
       <c r="L3" t="n">
-        <v>34.53663371949867</v>
+        <v>34.53663371949872</v>
       </c>
     </row>
     <row r="4">
@@ -1387,28 +1387,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138.6951628655318</v>
+        <v>213.0214130910863</v>
       </c>
       <c r="C4" t="n">
         <v>137.8839071480099</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5189074795001</v>
+        <v>139.5189856248378</v>
       </c>
       <c r="E4" t="n">
-        <v>126.9957195618489</v>
+        <v>126.9957195618488</v>
       </c>
       <c r="F4" t="n">
         <v>137.6403108413481</v>
       </c>
       <c r="G4" t="n">
-        <v>212.8574897822404</v>
+        <v>138.5312395566855</v>
       </c>
       <c r="H4" t="n">
-        <v>212.8123869709359</v>
+        <v>212.8123869709358</v>
       </c>
       <c r="I4" t="n">
-        <v>211.9831905666935</v>
+        <v>137.656940341138</v>
       </c>
       <c r="J4" t="n">
         <v>211.6303860402627</v>
@@ -1417,7 +1417,7 @@
         <v>138.5436564598756</v>
       </c>
       <c r="L4" t="n">
-        <v>138.7997071230557</v>
+        <v>138.7997071230558</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.53325099782835</v>
+        <v>60.53325099782839</v>
       </c>
       <c r="C5" t="n">
-        <v>60.42451780104108</v>
+        <v>60.42451780104112</v>
       </c>
       <c r="D5" t="n">
-        <v>60.53285247562707</v>
+        <v>60.53285247562703</v>
       </c>
       <c r="E5" t="n">
-        <v>59.49692079225291</v>
+        <v>59.49692079225292</v>
       </c>
       <c r="F5" t="n">
-        <v>59.49692079225291</v>
+        <v>59.49692079225292</v>
       </c>
       <c r="G5" t="n">
-        <v>60.36932768898178</v>
+        <v>60.36932768898187</v>
       </c>
       <c r="H5" t="n">
-        <v>60.53325099782835</v>
+        <v>60.53325099782839</v>
       </c>
       <c r="I5" t="n">
-        <v>59.4950284734345</v>
+        <v>59.49502847343457</v>
       </c>
       <c r="J5" t="n">
-        <v>60.53325099782835</v>
+        <v>60.53325099782839</v>
       </c>
       <c r="K5" t="n">
-        <v>60.53325099782835</v>
+        <v>60.53325099782839</v>
       </c>
       <c r="L5" t="n">
-        <v>60.53325099782835</v>
+        <v>60.53325099782839</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133.8632873781846</v>
+        <v>133.863287378185</v>
       </c>
       <c r="C6" t="n">
         <v>199.4267306516369</v>
       </c>
       <c r="D6" t="n">
-        <v>213.1346523504217</v>
+        <v>213.1346523504221</v>
       </c>
       <c r="E6" t="n">
-        <v>180.5389498283028</v>
+        <v>180.5389498283029</v>
       </c>
       <c r="F6" t="n">
-        <v>134.9076558728361</v>
+        <v>134.9076558728364</v>
       </c>
       <c r="G6" t="n">
-        <v>199.3563295361437</v>
+        <v>199.3563295361439</v>
       </c>
       <c r="H6" t="n">
-        <v>199.5202528450556</v>
+        <v>199.5202528450558</v>
       </c>
       <c r="I6" t="n">
-        <v>198.4820303205963</v>
+        <v>198.4820303205967</v>
       </c>
       <c r="J6" t="n">
-        <v>199.533156324721</v>
+        <v>199.5331563247214</v>
       </c>
       <c r="K6" t="n">
-        <v>132.6436755357946</v>
+        <v>132.6436755357947</v>
       </c>
       <c r="L6" t="n">
-        <v>268.1044434260322</v>
+        <v>268.1044434260329</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118.3131016527691</v>
+        <v>118.3131016527689</v>
       </c>
       <c r="C7" t="n">
-        <v>142.4813102394507</v>
+        <v>142.4813102394505</v>
       </c>
       <c r="D7" t="n">
-        <v>142.5900466263027</v>
+        <v>142.5900466263031</v>
       </c>
       <c r="E7" t="n">
-        <v>169.5668783455399</v>
+        <v>169.5668783455391</v>
       </c>
       <c r="F7" t="n">
-        <v>141.5518037007325</v>
+        <v>141.5518037007326</v>
       </c>
       <c r="G7" t="n">
-        <v>142.4261201273908</v>
+        <v>142.4261201273912</v>
       </c>
       <c r="H7" t="n">
-        <v>142.5900434362372</v>
+        <v>142.5900434362378</v>
       </c>
       <c r="I7" t="n">
-        <v>141.5518209118441</v>
+        <v>141.5518209118439</v>
       </c>
       <c r="J7" t="n">
-        <v>142.5900434362372</v>
+        <v>142.5900434362378</v>
       </c>
       <c r="K7" t="n">
         <v>128.5238893657265</v>
       </c>
       <c r="L7" t="n">
-        <v>142.5900434362372</v>
+        <v>142.5900434362378</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.84334298957424</v>
+        <v>30.84334298957436</v>
       </c>
       <c r="C8" t="n">
-        <v>26.23303106593428</v>
+        <v>26.23303106593429</v>
       </c>
       <c r="D8" t="n">
-        <v>23.33283459290334</v>
+        <v>23.33283459290335</v>
       </c>
       <c r="E8" t="n">
-        <v>42.17695367714152</v>
+        <v>42.17695367714153</v>
       </c>
       <c r="F8" t="n">
-        <v>42.17695367714152</v>
+        <v>42.17695367714153</v>
       </c>
       <c r="G8" t="n">
-        <v>67.26711411372142</v>
+        <v>67.26711411372141</v>
       </c>
       <c r="H8" t="n">
-        <v>17.16958251464332</v>
+        <v>17.16958251464334</v>
       </c>
       <c r="I8" t="n">
-        <v>42.17695367714152</v>
+        <v>42.17695367714153</v>
       </c>
       <c r="J8" t="n">
-        <v>66.13111884643567</v>
+        <v>66.13111884643577</v>
       </c>
       <c r="K8" t="n">
-        <v>144.6296931928788</v>
+        <v>144.6296931928793</v>
       </c>
       <c r="L8" t="n">
-        <v>24.95351044707932</v>
+        <v>24.95351044707931</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.25790601828461</v>
+        <v>32.25790601828464</v>
       </c>
       <c r="C9" t="n">
-        <v>27.65818010029131</v>
+        <v>27.65818010029134</v>
       </c>
       <c r="D9" t="n">
-        <v>33.42609727636487</v>
+        <v>33.42609727636486</v>
       </c>
       <c r="E9" t="n">
-        <v>44.117239958222</v>
+        <v>44.11723995822203</v>
       </c>
       <c r="F9" t="n">
-        <v>44.117239958222</v>
+        <v>44.11723995822203</v>
       </c>
       <c r="G9" t="n">
-        <v>71.83670729292841</v>
+        <v>71.83670729292845</v>
       </c>
       <c r="H9" t="n">
-        <v>30.9373923389164</v>
+        <v>30.93739233891642</v>
       </c>
       <c r="I9" t="n">
-        <v>44.117239958222</v>
+        <v>44.11723995822203</v>
       </c>
       <c r="J9" t="n">
         <v>71.42198596386154</v>
       </c>
       <c r="K9" t="n">
-        <v>146.1579199804113</v>
+        <v>146.1579199804116</v>
       </c>
       <c r="L9" t="n">
-        <v>30.21137913454772</v>
+        <v>30.21137913454776</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119.5510801883931</v>
+        <v>119.5510801883929</v>
       </c>
       <c r="C2" t="n">
-        <v>188.7288202762735</v>
+        <v>188.7288202762851</v>
       </c>
       <c r="D2" t="n">
-        <v>597.894196570947</v>
+        <v>597.8941965709472</v>
       </c>
       <c r="E2" t="n">
-        <v>187.3913349313343</v>
+        <v>187.3913349313373</v>
       </c>
       <c r="F2" t="n">
-        <v>187.3913349313343</v>
+        <v>187.3913349313373</v>
       </c>
       <c r="G2" t="n">
-        <v>330.23498553131</v>
+        <v>330.2349855313158</v>
       </c>
       <c r="H2" t="n">
-        <v>696.4236405097782</v>
+        <v>696.423640509779</v>
       </c>
       <c r="I2" t="n">
-        <v>187.3913349313343</v>
+        <v>187.3913349313373</v>
       </c>
       <c r="J2" t="n">
         <v>371.3087594552593</v>
       </c>
       <c r="K2" t="n">
-        <v>215.5757448959246</v>
+        <v>215.5757448959242</v>
       </c>
       <c r="L2" t="n">
-        <v>247.561072720347</v>
+        <v>247.5610727203473</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.23209715581718</v>
+        <v>34.23209715581746</v>
       </c>
       <c r="C3" t="n">
-        <v>33.17807866077253</v>
+        <v>33.17807866077258</v>
       </c>
       <c r="D3" t="n">
-        <v>34.23209715581718</v>
+        <v>34.23209715581746</v>
       </c>
       <c r="E3" t="n">
-        <v>32.83400708082704</v>
+        <v>32.83400708082713</v>
       </c>
       <c r="F3" t="n">
-        <v>32.83400708082708</v>
+        <v>32.83400708082713</v>
       </c>
       <c r="G3" t="n">
-        <v>34.07115309985775</v>
+        <v>34.0711530998579</v>
       </c>
       <c r="H3" t="n">
-        <v>34.23209715581718</v>
+        <v>34.23209715581746</v>
       </c>
       <c r="I3" t="n">
-        <v>33.21299540667955</v>
+        <v>33.21299540667962</v>
       </c>
       <c r="J3" t="n">
-        <v>34.23209715581718</v>
+        <v>34.23209715581746</v>
       </c>
       <c r="K3" t="n">
-        <v>34.23209715581718</v>
+        <v>34.23209715581746</v>
       </c>
       <c r="L3" t="n">
-        <v>34.23209715581718</v>
+        <v>34.23209715581746</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>202.4843439176421</v>
+        <v>202.4843439176423</v>
       </c>
       <c r="C4" t="n">
-        <v>132.0136009668144</v>
+        <v>132.013600966814</v>
       </c>
       <c r="D4" t="n">
-        <v>201.4621273686061</v>
+        <v>201.4621273686066</v>
       </c>
       <c r="E4" t="n">
         <v>121.602732451836</v>
       </c>
       <c r="F4" t="n">
-        <v>131.5692274770062</v>
+        <v>131.5692274770063</v>
       </c>
       <c r="G4" t="n">
-        <v>132.4300495809667</v>
+        <v>202.3233998616823</v>
       </c>
       <c r="H4" t="n">
-        <v>202.8321352290334</v>
+        <v>202.8321352290338</v>
       </c>
       <c r="I4" t="n">
-        <v>131.5718918877886</v>
+        <v>131.5718918877887</v>
       </c>
       <c r="J4" t="n">
-        <v>137.8434158859137</v>
+        <v>137.8434158859136</v>
       </c>
       <c r="K4" t="n">
-        <v>132.4198495939638</v>
+        <v>132.4198495939635</v>
       </c>
       <c r="L4" t="n">
-        <v>132.6183509954421</v>
+        <v>132.6183509954423</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.38436185912121</v>
+        <v>58.3843618591214</v>
       </c>
       <c r="C5" t="n">
-        <v>58.28088085066567</v>
+        <v>58.2808808506657</v>
       </c>
       <c r="D5" t="n">
-        <v>58.38400981838613</v>
+        <v>58.38400981838603</v>
       </c>
       <c r="E5" t="n">
-        <v>57.40766384957709</v>
+        <v>57.40766384957718</v>
       </c>
       <c r="F5" t="n">
-        <v>57.40766384957709</v>
+        <v>57.40766384957718</v>
       </c>
       <c r="G5" t="n">
         <v>58.22341780316178</v>
       </c>
       <c r="H5" t="n">
-        <v>58.38436185912121</v>
+        <v>58.3843618591214</v>
       </c>
       <c r="I5" t="n">
-        <v>57.36526010998351</v>
+        <v>57.36526010998357</v>
       </c>
       <c r="J5" t="n">
-        <v>58.38436185912121</v>
+        <v>58.3843618591214</v>
       </c>
       <c r="K5" t="n">
-        <v>58.38436185912121</v>
+        <v>58.3843618591214</v>
       </c>
       <c r="L5" t="n">
-        <v>58.38436185912121</v>
+        <v>58.3843618591214</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>127.7158787371698</v>
+        <v>127.7158787371701</v>
       </c>
       <c r="C6" t="n">
-        <v>189.4349457286771</v>
+        <v>189.4349457283733</v>
       </c>
       <c r="D6" t="n">
-        <v>202.2935839313082</v>
+        <v>202.2935839313083</v>
       </c>
       <c r="E6" t="n">
-        <v>171.6202258444989</v>
+        <v>171.620225844499</v>
       </c>
       <c r="F6" t="n">
-        <v>128.6802779504085</v>
+        <v>128.6802779504086</v>
       </c>
       <c r="G6" t="n">
-        <v>189.324349352541</v>
+        <v>189.3243493525409</v>
       </c>
       <c r="H6" t="n">
-        <v>189.4852934086916</v>
+        <v>189.4852934086918</v>
       </c>
       <c r="I6" t="n">
-        <v>188.4661916593627</v>
+        <v>188.4661916593626</v>
       </c>
       <c r="J6" t="n">
-        <v>189.497432872293</v>
+        <v>189.4974328722932</v>
       </c>
       <c r="K6" t="n">
-        <v>126.5684801466599</v>
+        <v>126.5684801466601</v>
       </c>
       <c r="L6" t="n">
-        <v>254.0086121115725</v>
+        <v>254.0086121115727</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106.3530091326785</v>
+        <v>106.3530091326788</v>
       </c>
       <c r="C7" t="n">
         <v>127.2268702460903</v>
       </c>
       <c r="D7" t="n">
-        <v>127.3303565572284</v>
+        <v>127.3303565572287</v>
       </c>
       <c r="E7" t="n">
-        <v>150.5186491323527</v>
+        <v>150.5186491323528</v>
       </c>
       <c r="F7" t="n">
-        <v>126.3112389584273</v>
+        <v>126.3112389584276</v>
       </c>
       <c r="G7" t="n">
         <v>127.1694071985863</v>
       </c>
       <c r="H7" t="n">
-        <v>127.3303512545458</v>
+        <v>127.3303512545462</v>
       </c>
       <c r="I7" t="n">
-        <v>126.3112495054082</v>
+        <v>126.3112495054083</v>
       </c>
       <c r="J7" t="n">
-        <v>127.3303512545458</v>
+        <v>127.3303512545462</v>
       </c>
       <c r="K7" t="n">
-        <v>115.1759990750526</v>
+        <v>115.1759990750527</v>
       </c>
       <c r="L7" t="n">
-        <v>127.3303512545458</v>
+        <v>127.3303512545462</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.2259195580644</v>
+        <v>31.22591955806444</v>
       </c>
       <c r="C8" t="n">
-        <v>25.93977085287161</v>
+        <v>25.93977085287131</v>
       </c>
       <c r="D8" t="n">
-        <v>27.67588858395611</v>
+        <v>27.67588858395618</v>
       </c>
       <c r="E8" t="n">
-        <v>43.11221104488301</v>
+        <v>43.11221104488302</v>
       </c>
       <c r="F8" t="n">
-        <v>43.11221104488301</v>
+        <v>43.11221104488302</v>
       </c>
       <c r="G8" t="n">
-        <v>70.03228799023331</v>
+        <v>70.03228799023323</v>
       </c>
       <c r="H8" t="n">
-        <v>27.12213585216853</v>
+        <v>27.12213585216862</v>
       </c>
       <c r="I8" t="n">
-        <v>43.11221104488301</v>
+        <v>43.11221104488302</v>
       </c>
       <c r="J8" t="n">
-        <v>69.26585897978295</v>
+        <v>69.26585897978302</v>
       </c>
       <c r="K8" t="n">
-        <v>146.7837081064747</v>
+        <v>146.7837081064748</v>
       </c>
       <c r="L8" t="n">
-        <v>30.25334329449301</v>
+        <v>30.25334329449312</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.25462758416871</v>
+        <v>32.25462758416879</v>
       </c>
       <c r="C9" t="n">
-        <v>27.43210660727507</v>
+        <v>27.432106607275</v>
       </c>
       <c r="D9" t="n">
-        <v>34.95782032134463</v>
+        <v>34.9578203213446</v>
       </c>
       <c r="E9" t="n">
-        <v>44.36436016157598</v>
+        <v>44.36436016157601</v>
       </c>
       <c r="F9" t="n">
-        <v>44.36436016157598</v>
+        <v>44.36436016157601</v>
       </c>
       <c r="G9" t="n">
-        <v>72.78034307763498</v>
+        <v>72.78034307763504</v>
       </c>
       <c r="H9" t="n">
-        <v>34.7442971537559</v>
+        <v>34.74429715375607</v>
       </c>
       <c r="I9" t="n">
-        <v>44.36436016157598</v>
+        <v>44.36436016157601</v>
       </c>
       <c r="J9" t="n">
-        <v>72.48300526538895</v>
+        <v>72.48300526538904</v>
       </c>
       <c r="K9" t="n">
-        <v>146.8085414384956</v>
+        <v>146.8085414384957</v>
       </c>
       <c r="L9" t="n">
-        <v>32.19360957930037</v>
+        <v>32.19360957930047</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100.4185208059831</v>
+        <v>100.418520805983</v>
       </c>
       <c r="C2" t="n">
-        <v>177.3834385069253</v>
+        <v>177.3834385069241</v>
       </c>
       <c r="D2" t="n">
-        <v>445.492926652308</v>
+        <v>445.4929266523063</v>
       </c>
       <c r="E2" t="n">
-        <v>141.7517452141923</v>
+        <v>141.7517452141921</v>
       </c>
       <c r="F2" t="n">
-        <v>141.7517452141923</v>
+        <v>141.7517452141921</v>
       </c>
       <c r="G2" t="n">
-        <v>239.9327957715425</v>
+        <v>239.9327957715607</v>
       </c>
       <c r="H2" t="n">
-        <v>430.529437116045</v>
+        <v>430.5294371160444</v>
       </c>
       <c r="I2" t="n">
-        <v>141.7517452141923</v>
+        <v>141.7517452141921</v>
       </c>
       <c r="J2" t="n">
-        <v>228.9780939387203</v>
+        <v>228.9780939387207</v>
       </c>
       <c r="K2" t="n">
-        <v>159.4472261576891</v>
+        <v>159.4472261576886</v>
       </c>
       <c r="L2" t="n">
-        <v>163.4816160649821</v>
+        <v>163.4816160649817</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.07085988126759</v>
+        <v>34.07085988126749</v>
       </c>
       <c r="C3" t="n">
-        <v>33.05321759053058</v>
+        <v>33.05321759053056</v>
       </c>
       <c r="D3" t="n">
-        <v>34.07085988126759</v>
+        <v>34.07085988126749</v>
       </c>
       <c r="E3" t="n">
-        <v>32.72429416614005</v>
+        <v>32.72429416614</v>
       </c>
       <c r="F3" t="n">
-        <v>32.72429416614005</v>
+        <v>32.72429416614001</v>
       </c>
       <c r="G3" t="n">
-        <v>33.91154680160086</v>
+        <v>33.91154680160085</v>
       </c>
       <c r="H3" t="n">
-        <v>34.07085988126759</v>
+        <v>34.07085988126749</v>
       </c>
       <c r="I3" t="n">
-        <v>33.06222036230609</v>
+        <v>33.06222036230606</v>
       </c>
       <c r="J3" t="n">
-        <v>34.07085988126759</v>
+        <v>34.07085988126749</v>
       </c>
       <c r="K3" t="n">
-        <v>34.07085988126759</v>
+        <v>34.07085988126749</v>
       </c>
       <c r="L3" t="n">
-        <v>34.07085988126759</v>
+        <v>34.07085988126749</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>132.1687273450332</v>
+        <v>132.1687273450329</v>
       </c>
       <c r="C4" t="n">
-        <v>131.710580558075</v>
+        <v>131.7105805580752</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5823997341501</v>
+        <v>132.5823182428507</v>
       </c>
       <c r="E4" t="n">
-        <v>121.257495332268</v>
+        <v>121.2574953322677</v>
       </c>
       <c r="F4" t="n">
-        <v>131.1563751045059</v>
+        <v>131.1563751045058</v>
       </c>
       <c r="G4" t="n">
-        <v>201.5858517744981</v>
+        <v>201.5858517744978</v>
       </c>
       <c r="H4" t="n">
-        <v>202.0734399927276</v>
+        <v>202.0734399927275</v>
       </c>
       <c r="I4" t="n">
-        <v>200.7365253352028</v>
+        <v>200.7365253352026</v>
       </c>
       <c r="J4" t="n">
         <v>200.4656850174503</v>
       </c>
       <c r="K4" t="n">
-        <v>132.0192215287398</v>
+        <v>132.0192215287391</v>
       </c>
       <c r="L4" t="n">
-        <v>132.1766044600769</v>
+        <v>132.1766044600764</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.8499896982529</v>
+        <v>57.84998969825277</v>
       </c>
       <c r="C5" t="n">
-        <v>57.74972235392084</v>
+        <v>57.74972235392073</v>
       </c>
       <c r="D5" t="n">
-        <v>57.84963342880929</v>
+        <v>57.84963342880917</v>
       </c>
       <c r="E5" t="n">
-        <v>56.89213344579173</v>
+        <v>56.89213344579162</v>
       </c>
       <c r="F5" t="n">
-        <v>56.89213344579173</v>
+        <v>56.89213344579162</v>
       </c>
       <c r="G5" t="n">
         <v>57.69067661858605</v>
       </c>
       <c r="H5" t="n">
-        <v>57.8499896982529</v>
+        <v>57.84998969825277</v>
       </c>
       <c r="I5" t="n">
-        <v>56.84135017929131</v>
+        <v>56.84135017929124</v>
       </c>
       <c r="J5" t="n">
-        <v>57.8499896982529</v>
+        <v>57.84998969825277</v>
       </c>
       <c r="K5" t="n">
-        <v>57.8499896982529</v>
+        <v>57.84998969825277</v>
       </c>
       <c r="L5" t="n">
-        <v>57.8499896982529</v>
+        <v>57.84998969825277</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>126.983491740594</v>
+        <v>126.9834917405938</v>
       </c>
       <c r="C6" t="n">
-        <v>188.3016375709247</v>
+        <v>188.3016375712784</v>
       </c>
       <c r="D6" t="n">
-        <v>201.0636536358905</v>
+        <v>201.0636536358903</v>
       </c>
       <c r="E6" t="n">
-        <v>170.60600545656</v>
+        <v>170.6060054565599</v>
       </c>
       <c r="F6" t="n">
-        <v>127.9502917859662</v>
+        <v>127.9502917859658</v>
       </c>
       <c r="G6" t="n">
-        <v>188.1815002239898</v>
+        <v>188.1815002239895</v>
       </c>
       <c r="H6" t="n">
         <v>188.3408133038501</v>
       </c>
       <c r="I6" t="n">
-        <v>187.332173784695</v>
+        <v>187.3321737846949</v>
       </c>
       <c r="J6" t="n">
-        <v>188.3528717791561</v>
+        <v>188.3528717791559</v>
       </c>
       <c r="K6" t="n">
-        <v>125.8437479910902</v>
+        <v>125.8437479910899</v>
       </c>
       <c r="L6" t="n">
-        <v>252.4336662964268</v>
+        <v>252.4336662964263</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100.9703769919997</v>
+        <v>100.9703769919996</v>
       </c>
       <c r="C7" t="n">
-        <v>120.3820373431718</v>
+        <v>120.3820373431712</v>
       </c>
       <c r="D7" t="n">
-        <v>120.4823105226757</v>
+        <v>120.4823105226754</v>
       </c>
       <c r="E7" t="n">
-        <v>141.9900116705486</v>
+        <v>141.9900116705482</v>
       </c>
       <c r="F7" t="n">
-        <v>119.4736574774983</v>
+        <v>119.4736574774981</v>
       </c>
       <c r="G7" t="n">
-        <v>120.3229916078369</v>
+        <v>120.3229916078365</v>
       </c>
       <c r="H7" t="n">
-        <v>120.4823046875035</v>
+        <v>120.4823046875034</v>
       </c>
       <c r="I7" t="n">
-        <v>119.4736651685423</v>
+        <v>119.4736651685418</v>
       </c>
       <c r="J7" t="n">
-        <v>120.4823046875035</v>
+        <v>120.4823046875034</v>
       </c>
       <c r="K7" t="n">
-        <v>95.91330333975036</v>
+        <v>108.7183496725055</v>
       </c>
       <c r="L7" t="n">
-        <v>120.4823046875035</v>
+        <v>120.4823046875034</v>
       </c>
     </row>
     <row r="8">
@@ -2342,34 +2342,34 @@
         <v>31.45153157207486</v>
       </c>
       <c r="C8" t="n">
-        <v>25.97137153607489</v>
+        <v>25.97137153607486</v>
       </c>
       <c r="D8" t="n">
-        <v>30.9749048750675</v>
+        <v>30.97490487506742</v>
       </c>
       <c r="E8" t="n">
-        <v>43.88821826896711</v>
+        <v>43.88821826896708</v>
       </c>
       <c r="F8" t="n">
-        <v>43.88821826896711</v>
+        <v>43.88821826896708</v>
       </c>
       <c r="G8" t="n">
-        <v>71.92636078205578</v>
+        <v>71.92636078205602</v>
       </c>
       <c r="H8" t="n">
-        <v>32.42448717434864</v>
+        <v>32.42448717434862</v>
       </c>
       <c r="I8" t="n">
-        <v>43.88821826896711</v>
+        <v>43.88821826896708</v>
       </c>
       <c r="J8" t="n">
-        <v>72.14072548261431</v>
+        <v>72.14072548261412</v>
       </c>
       <c r="K8" t="n">
-        <v>148.1281191978712</v>
+        <v>148.1281191978711</v>
       </c>
       <c r="L8" t="n">
-        <v>31.76434701938749</v>
+        <v>31.76434701938747</v>
       </c>
     </row>
     <row r="9">
@@ -2382,34 +2382,34 @@
         <v>32.2153621920467</v>
       </c>
       <c r="C9" t="n">
-        <v>27.30811044964591</v>
+        <v>27.30811044964589</v>
       </c>
       <c r="D9" t="n">
-        <v>36.05984884874847</v>
+        <v>36.05984884874838</v>
       </c>
       <c r="E9" t="n">
-        <v>44.49276942043255</v>
+        <v>44.4927694204325</v>
       </c>
       <c r="F9" t="n">
-        <v>44.49276942043255</v>
+        <v>44.4927694204325</v>
       </c>
       <c r="G9" t="n">
-        <v>73.41074861161329</v>
+        <v>73.4107486116133</v>
       </c>
       <c r="H9" t="n">
-        <v>36.65703678077307</v>
+        <v>36.65703678077304</v>
       </c>
       <c r="I9" t="n">
-        <v>44.49276942043255</v>
+        <v>44.4927694204325</v>
       </c>
       <c r="J9" t="n">
-        <v>73.409471253684</v>
+        <v>73.40947125368396</v>
       </c>
       <c r="K9" t="n">
         <v>147.3453817360242</v>
       </c>
       <c r="L9" t="n">
-        <v>32.65646301447445</v>
+        <v>32.65646301447442</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116.5107253538645</v>
+        <v>116.5107253538644</v>
       </c>
       <c r="C2" t="n">
         <v>161.1439906150658</v>
       </c>
       <c r="D2" t="n">
-        <v>519.9052507227595</v>
+        <v>519.905250722758</v>
       </c>
       <c r="E2" t="n">
-        <v>196.8062126276212</v>
+        <v>196.8062126276204</v>
       </c>
       <c r="F2" t="n">
-        <v>196.8062126276212</v>
+        <v>196.8062126276204</v>
       </c>
       <c r="G2" t="n">
-        <v>349.3963930928358</v>
+        <v>349.3963930928408</v>
       </c>
       <c r="H2" t="n">
-        <v>1004.161385287359</v>
+        <v>1004.161385287357</v>
       </c>
       <c r="I2" t="n">
-        <v>196.8062126276212</v>
+        <v>196.8062126276204</v>
       </c>
       <c r="J2" t="n">
-        <v>528.3968033043255</v>
+        <v>528.3968033043258</v>
       </c>
       <c r="K2" t="n">
-        <v>264.0083523823184</v>
+        <v>264.0083523823186</v>
       </c>
       <c r="L2" t="n">
-        <v>528.9125242425841</v>
+        <v>528.9125242425832</v>
       </c>
     </row>
     <row r="3">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.02595885034164</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="C3" t="n">
         <v>32.972030736626</v>
       </c>
       <c r="D3" t="n">
-        <v>34.02595885034164</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="E3" t="n">
         <v>32.72999941229633</v>
@@ -2553,19 +2553,19 @@
         <v>33.86541890175346</v>
       </c>
       <c r="H3" t="n">
-        <v>34.02595885034164</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="I3" t="n">
-        <v>33.00910553105657</v>
+        <v>33.00910553105656</v>
       </c>
       <c r="J3" t="n">
-        <v>34.02595885034164</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="K3" t="n">
-        <v>34.02595885034164</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="L3" t="n">
-        <v>34.02595885034164</v>
+        <v>34.02595885034167</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137.9425585735734</v>
+        <v>137.9425585735733</v>
       </c>
       <c r="C4" t="n">
-        <v>137.2862459675076</v>
+        <v>137.2862459675069</v>
       </c>
       <c r="D4" t="n">
-        <v>138.3325191982725</v>
+        <v>138.3324406557909</v>
       </c>
       <c r="E4" t="n">
-        <v>126.4223729865624</v>
+        <v>126.422372986562</v>
       </c>
       <c r="F4" t="n">
-        <v>136.9312803481973</v>
+        <v>136.9312803481972</v>
       </c>
       <c r="G4" t="n">
-        <v>137.7820186249851</v>
+        <v>137.782018624985</v>
       </c>
       <c r="H4" t="n">
-        <v>211.2410754122502</v>
+        <v>211.2410754122504</v>
       </c>
       <c r="I4" t="n">
-        <v>136.9257052542883</v>
+        <v>210.5450540265649</v>
       </c>
       <c r="J4" t="n">
-        <v>210.1399221813101</v>
+        <v>143.5282801664664</v>
       </c>
       <c r="K4" t="n">
         <v>137.8419955057377</v>
       </c>
       <c r="L4" t="n">
-        <v>138.0550245343694</v>
+        <v>138.0550245343693</v>
       </c>
     </row>
     <row r="5">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.31009710967125</v>
+        <v>59.31009710967133</v>
       </c>
       <c r="C5" t="n">
-        <v>59.20651589428824</v>
+        <v>59.20651589428829</v>
       </c>
       <c r="D5" t="n">
-        <v>59.30970625975658</v>
+        <v>59.30970625975668</v>
       </c>
       <c r="E5" t="n">
         <v>58.36355311814535</v>
@@ -2630,22 +2630,22 @@
         <v>58.36355311814535</v>
       </c>
       <c r="G5" t="n">
-        <v>59.14955716108297</v>
+        <v>59.14955716108301</v>
       </c>
       <c r="H5" t="n">
-        <v>59.31009710967125</v>
+        <v>59.31009710967133</v>
       </c>
       <c r="I5" t="n">
-        <v>58.29324379038615</v>
+        <v>58.29324379038611</v>
       </c>
       <c r="J5" t="n">
-        <v>59.31009710967125</v>
+        <v>59.31009710967133</v>
       </c>
       <c r="K5" t="n">
-        <v>59.31009710967125</v>
+        <v>59.31009710967133</v>
       </c>
       <c r="L5" t="n">
-        <v>59.31009710967125</v>
+        <v>59.31009710967133</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>132.1306318650756</v>
+        <v>132.1306318650759</v>
       </c>
       <c r="C6" t="n">
-        <v>196.8384730102661</v>
+        <v>196.8384730105102</v>
       </c>
       <c r="D6" t="n">
-        <v>210.2840526758629</v>
+        <v>210.2840526758631</v>
       </c>
       <c r="E6" t="n">
-        <v>178.2132688003756</v>
+        <v>178.2132688003759</v>
       </c>
       <c r="F6" t="n">
-        <v>133.2078280691438</v>
+        <v>133.2078280691441</v>
       </c>
       <c r="G6" t="n">
-        <v>196.7011136805849</v>
+        <v>196.7011136805851</v>
       </c>
       <c r="H6" t="n">
-        <v>196.8616536292234</v>
+        <v>196.861653629224</v>
       </c>
       <c r="I6" t="n">
-        <v>195.8448003098879</v>
+        <v>195.8448003098882</v>
       </c>
       <c r="J6" t="n">
-        <v>196.8743751342953</v>
+        <v>196.8743751342956</v>
       </c>
       <c r="K6" t="n">
-        <v>130.928219902359</v>
+        <v>130.9282199023592</v>
       </c>
       <c r="L6" t="n">
-        <v>264.4786185864381</v>
+        <v>264.4786185864388</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114.3183852075003</v>
+        <v>114.3183852075002</v>
       </c>
       <c r="C7" t="n">
-        <v>137.463142390021</v>
+        <v>137.4631423900209</v>
       </c>
       <c r="D7" t="n">
-        <v>137.5667254559366</v>
+        <v>137.5667254559364</v>
       </c>
       <c r="E7" t="n">
-        <v>163.3779430002518</v>
+        <v>163.3779430002516</v>
       </c>
       <c r="F7" t="n">
-        <v>136.5498554657075</v>
+        <v>136.5498554657073</v>
       </c>
       <c r="G7" t="n">
-        <v>137.4061836568156</v>
+        <v>137.4061836568157</v>
       </c>
       <c r="H7" t="n">
-        <v>137.5667236054039</v>
+        <v>137.566723605404</v>
       </c>
       <c r="I7" t="n">
-        <v>136.5498702861187</v>
+        <v>136.5498702861186</v>
       </c>
       <c r="J7" t="n">
-        <v>137.5667236054039</v>
+        <v>137.566723605404</v>
       </c>
       <c r="K7" t="n">
-        <v>108.2929152691115</v>
+        <v>124.096545812724</v>
       </c>
       <c r="L7" t="n">
-        <v>137.5667236054039</v>
+        <v>137.566723605404</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.24152483911651</v>
+        <v>32.24152483911655</v>
       </c>
       <c r="C8" t="n">
-        <v>26.56487465455824</v>
+        <v>26.56487465455825</v>
       </c>
       <c r="D8" t="n">
-        <v>29.9933501949943</v>
+        <v>29.99335019499441</v>
       </c>
       <c r="E8" t="n">
-        <v>42.92217252002936</v>
+        <v>42.92217252002939</v>
       </c>
       <c r="F8" t="n">
-        <v>42.92217252002936</v>
+        <v>42.92217252002939</v>
       </c>
       <c r="G8" t="n">
-        <v>69.85030102319777</v>
+        <v>69.85030102319783</v>
       </c>
       <c r="H8" t="n">
-        <v>21.3915637742939</v>
+        <v>21.39156377429394</v>
       </c>
       <c r="I8" t="n">
-        <v>42.92217252002936</v>
+        <v>42.92217252002939</v>
       </c>
       <c r="J8" t="n">
-        <v>66.06874404948601</v>
+        <v>66.06874404948603</v>
       </c>
       <c r="K8" t="n">
-        <v>145.6144610875483</v>
+        <v>145.6144610875484</v>
       </c>
       <c r="L8" t="n">
-        <v>24.78500035835183</v>
+        <v>24.78500035835186</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.15397122142992</v>
+        <v>33.15397122142995</v>
       </c>
       <c r="C9" t="n">
-        <v>27.57829293816933</v>
+        <v>27.57829293816934</v>
       </c>
       <c r="D9" t="n">
-        <v>35.78028334649603</v>
+        <v>35.78028334649606</v>
       </c>
       <c r="E9" t="n">
-        <v>44.18870725157949</v>
+        <v>44.18870725157948</v>
       </c>
       <c r="F9" t="n">
-        <v>44.18870725157949</v>
+        <v>44.18870725157948</v>
       </c>
       <c r="G9" t="n">
         <v>72.63604488813009</v>
       </c>
       <c r="H9" t="n">
-        <v>32.29404727535099</v>
+        <v>32.29404727535101</v>
       </c>
       <c r="I9" t="n">
-        <v>44.18870725157949</v>
+        <v>44.18870725157948</v>
       </c>
       <c r="J9" t="n">
-        <v>71.08855302269366</v>
+        <v>71.0885530226937</v>
       </c>
       <c r="K9" t="n">
         <v>146.1671260643633</v>
       </c>
       <c r="L9" t="n">
-        <v>29.92198226687292</v>
+        <v>29.92198226687295</v>
       </c>
     </row>
   </sheetData>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103.3081020888935</v>
+        <v>103.3081020888934</v>
       </c>
       <c r="C2" t="n">
-        <v>156.316296636388</v>
+        <v>156.3162966363878</v>
       </c>
       <c r="D2" t="n">
-        <v>155.9234167650049</v>
+        <v>155.923416765005</v>
       </c>
       <c r="E2" t="n">
-        <v>165.7148273278739</v>
+        <v>165.7148273278712</v>
       </c>
       <c r="F2" t="n">
-        <v>165.7148273278739</v>
+        <v>165.7148273278712</v>
       </c>
       <c r="G2" t="n">
-        <v>159.9344149488054</v>
+        <v>159.9344149488039</v>
       </c>
       <c r="H2" t="n">
-        <v>212.7781268534479</v>
+        <v>212.7781268534478</v>
       </c>
       <c r="I2" t="n">
-        <v>165.7148273278739</v>
+        <v>165.7148273278712</v>
       </c>
       <c r="J2" t="n">
-        <v>255.0066875947318</v>
+        <v>255.0066875947317</v>
       </c>
       <c r="K2" t="n">
-        <v>145.1838009934166</v>
+        <v>145.1838009934165</v>
       </c>
       <c r="L2" t="n">
         <v>186.4247909142287</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.62827358908616</v>
+        <v>33.62827358908619</v>
       </c>
       <c r="C3" t="n">
-        <v>32.69664801578453</v>
+        <v>32.69664801578458</v>
       </c>
       <c r="D3" t="n">
-        <v>33.62827358908616</v>
+        <v>33.62827358908619</v>
       </c>
       <c r="E3" t="n">
-        <v>32.52390506678805</v>
+        <v>32.52390506678806</v>
       </c>
       <c r="F3" t="n">
-        <v>32.52390506678805</v>
+        <v>32.52390506678806</v>
       </c>
       <c r="G3" t="n">
-        <v>33.47324172042738</v>
+        <v>33.4732417204274</v>
       </c>
       <c r="H3" t="n">
-        <v>33.62827358908616</v>
+        <v>33.62827358908619</v>
       </c>
       <c r="I3" t="n">
-        <v>32.64673652425927</v>
+        <v>32.64673652425925</v>
       </c>
       <c r="J3" t="n">
-        <v>33.62827358908616</v>
+        <v>33.62827358908619</v>
       </c>
       <c r="K3" t="n">
-        <v>33.62827358908616</v>
+        <v>33.62827358908619</v>
       </c>
       <c r="L3" t="n">
-        <v>33.62827358908616</v>
+        <v>33.62827358908619</v>
       </c>
     </row>
     <row r="4">
@@ -2971,34 +2971,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.6973636052138</v>
+        <v>131.697363605214</v>
       </c>
       <c r="C4" t="n">
-        <v>131.319697224085</v>
+        <v>131.3196972240848</v>
       </c>
       <c r="D4" t="n">
-        <v>131.615226673812</v>
+        <v>199.521910845467</v>
       </c>
       <c r="E4" t="n">
         <v>120.9972741017079</v>
       </c>
       <c r="F4" t="n">
-        <v>130.7429743046537</v>
+        <v>130.742974304654</v>
       </c>
       <c r="G4" t="n">
-        <v>200.5245195609703</v>
+        <v>131.542331736555</v>
       </c>
       <c r="H4" t="n">
-        <v>200.797509373814</v>
+        <v>200.7975093738141</v>
       </c>
       <c r="I4" t="n">
-        <v>199.6980143648023</v>
+        <v>199.6980143648025</v>
       </c>
       <c r="J4" t="n">
-        <v>136.8816912318781</v>
+        <v>199.355381660611</v>
       </c>
       <c r="K4" t="n">
-        <v>131.6110472087909</v>
+        <v>131.611047208791</v>
       </c>
       <c r="L4" t="n">
         <v>131.7112718427867</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.73065617254074</v>
+        <v>56.73065617254072</v>
       </c>
       <c r="C5" t="n">
-        <v>56.63446821961381</v>
+        <v>56.63446821961384</v>
       </c>
       <c r="D5" t="n">
-        <v>56.73030603415413</v>
+        <v>56.73030603415411</v>
       </c>
       <c r="E5" t="n">
-        <v>55.83937550331003</v>
+        <v>55.83937550330999</v>
       </c>
       <c r="F5" t="n">
-        <v>55.83937550331003</v>
+        <v>55.83937550330999</v>
       </c>
       <c r="G5" t="n">
-        <v>56.57562430388207</v>
+        <v>56.57562430388204</v>
       </c>
       <c r="H5" t="n">
-        <v>56.73065617254074</v>
+        <v>56.73065617254072</v>
       </c>
       <c r="I5" t="n">
-        <v>55.74911910771391</v>
+        <v>55.74911910771399</v>
       </c>
       <c r="J5" t="n">
-        <v>56.73065617254074</v>
+        <v>56.73065617254072</v>
       </c>
       <c r="K5" t="n">
-        <v>56.73065617254074</v>
+        <v>56.73065617254072</v>
       </c>
       <c r="L5" t="n">
-        <v>56.73065617254074</v>
+        <v>56.73065617254072</v>
       </c>
     </row>
     <row r="6">
@@ -3054,34 +3054,34 @@
         <v>125.2615926882042</v>
       </c>
       <c r="C6" t="n">
-        <v>185.6332263066215</v>
+        <v>185.6332263063183</v>
       </c>
       <c r="D6" t="n">
-        <v>198.1487729629224</v>
+        <v>198.1487729629225</v>
       </c>
       <c r="E6" t="n">
         <v>168.2269113245814</v>
       </c>
       <c r="F6" t="n">
-        <v>126.2477181164817</v>
+        <v>126.2477181164814</v>
       </c>
       <c r="G6" t="n">
         <v>185.4757884713497</v>
       </c>
       <c r="H6" t="n">
-        <v>185.6308203401742</v>
+        <v>185.630820340174</v>
       </c>
       <c r="I6" t="n">
-        <v>184.6492832751816</v>
+        <v>184.6492832751813</v>
       </c>
       <c r="J6" t="n">
-        <v>185.6426846268947</v>
+        <v>185.6426846268948</v>
       </c>
       <c r="K6" t="n">
         <v>124.140203290446</v>
       </c>
       <c r="L6" t="n">
-        <v>248.691526619423</v>
+        <v>248.6915266194226</v>
       </c>
     </row>
     <row r="7">
@@ -3094,34 +3094,34 @@
         <v>101.7741154661531</v>
       </c>
       <c r="C7" t="n">
-        <v>121.4582616775851</v>
+        <v>121.458261677585</v>
       </c>
       <c r="D7" t="n">
-        <v>121.5544554869212</v>
+        <v>121.5544554869211</v>
       </c>
       <c r="E7" t="n">
-        <v>143.3989981540276</v>
+        <v>143.3989981540275</v>
       </c>
       <c r="F7" t="n">
-        <v>120.5729078292143</v>
+        <v>120.5729078292145</v>
       </c>
       <c r="G7" t="n">
-        <v>121.3994177618532</v>
+        <v>121.3994177618533</v>
       </c>
       <c r="H7" t="n">
-        <v>121.554449630512</v>
+        <v>121.5544496305119</v>
       </c>
       <c r="I7" t="n">
-        <v>120.5729125656851</v>
+        <v>120.5729125656852</v>
       </c>
       <c r="J7" t="n">
-        <v>121.554449630512</v>
+        <v>121.5544496305119</v>
       </c>
       <c r="K7" t="n">
-        <v>96.64747662258056</v>
+        <v>110.0936487955069</v>
       </c>
       <c r="L7" t="n">
-        <v>121.554449630512</v>
+        <v>121.5544496305119</v>
       </c>
     </row>
     <row r="8">
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.39178077874358</v>
+        <v>32.39178077874355</v>
       </c>
       <c r="C8" t="n">
         <v>26.14046043465797</v>
       </c>
       <c r="D8" t="n">
-        <v>37.66585374732855</v>
+        <v>37.66585374732854</v>
       </c>
       <c r="E8" t="n">
-        <v>43.00548765412402</v>
+        <v>43.00548765412405</v>
       </c>
       <c r="F8" t="n">
-        <v>43.00548765412402</v>
+        <v>43.00548765412404</v>
       </c>
       <c r="G8" t="n">
-        <v>73.36617402600251</v>
+        <v>73.36617402600244</v>
       </c>
       <c r="H8" t="n">
-        <v>36.73633216987945</v>
+        <v>36.73633216987946</v>
       </c>
       <c r="I8" t="n">
-        <v>43.00548765412402</v>
+        <v>43.00548765412405</v>
       </c>
       <c r="J8" t="n">
-        <v>70.91445016173645</v>
+        <v>70.91445016173651</v>
       </c>
       <c r="K8" t="n">
-        <v>147.3391243831617</v>
+        <v>147.3391243831613</v>
       </c>
       <c r="L8" t="n">
         <v>30.8623264211345</v>
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.18125873378369</v>
+        <v>33.18125873378368</v>
       </c>
       <c r="C9" t="n">
-        <v>27.18839798326061</v>
+        <v>27.18839798326062</v>
       </c>
       <c r="D9" t="n">
-        <v>38.57123772335738</v>
+        <v>38.5712377233574</v>
       </c>
       <c r="E9" t="n">
-        <v>43.96077500536156</v>
+        <v>43.96077500536157</v>
       </c>
       <c r="F9" t="n">
-        <v>43.96077500536156</v>
+        <v>43.96077500536157</v>
       </c>
       <c r="G9" t="n">
-        <v>73.73685862718996</v>
+        <v>73.73685862718983</v>
       </c>
       <c r="H9" t="n">
         <v>38.19524360524102</v>
       </c>
       <c r="I9" t="n">
-        <v>43.96077500536156</v>
+        <v>43.96077500536157</v>
       </c>
       <c r="J9" t="n">
-        <v>72.55277456701829</v>
+        <v>72.55277456701825</v>
       </c>
       <c r="K9" t="n">
-        <v>146.3711181551495</v>
+        <v>146.3711181551492</v>
       </c>
       <c r="L9" t="n">
-        <v>32.05014302255376</v>
+        <v>32.05014302255375</v>
       </c>
     </row>
   </sheetData>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86.92518736735681</v>
+        <v>86.92518736735556</v>
       </c>
       <c r="C2" t="n">
-        <v>141.6176582057855</v>
+        <v>141.6176582057836</v>
       </c>
       <c r="D2" t="n">
-        <v>151.7213545127887</v>
+        <v>151.7213545127888</v>
       </c>
       <c r="E2" t="n">
-        <v>143.9515846879985</v>
+        <v>143.9515846879989</v>
       </c>
       <c r="F2" t="n">
-        <v>143.9515846879985</v>
+        <v>143.9515846879989</v>
       </c>
       <c r="G2" t="n">
-        <v>141.8495439303324</v>
+        <v>141.849543930333</v>
       </c>
       <c r="H2" t="n">
         <v>171.8332732477231</v>
       </c>
       <c r="I2" t="n">
-        <v>143.9515846879985</v>
+        <v>143.9515846879989</v>
       </c>
       <c r="J2" t="n">
         <v>170.1108745309248</v>
       </c>
       <c r="K2" t="n">
-        <v>127.6838917263956</v>
+        <v>127.6838917263954</v>
       </c>
       <c r="L2" t="n">
         <v>144.2087629792356</v>
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.7907434775792</v>
+        <v>33.79074347757878</v>
       </c>
       <c r="C3" t="n">
-        <v>32.85673704833351</v>
+        <v>32.85673704833354</v>
       </c>
       <c r="D3" t="n">
-        <v>33.7907434775792</v>
+        <v>33.79074347757878</v>
       </c>
       <c r="E3" t="n">
-        <v>32.63546364679186</v>
+        <v>32.63546364679188</v>
       </c>
       <c r="F3" t="n">
-        <v>32.63546364679185</v>
+        <v>32.63546364679188</v>
       </c>
       <c r="G3" t="n">
-        <v>33.63529491040205</v>
+        <v>33.63529491039907</v>
       </c>
       <c r="H3" t="n">
-        <v>33.7907434775792</v>
+        <v>33.79074347757878</v>
       </c>
       <c r="I3" t="n">
-        <v>32.80670207420022</v>
+        <v>32.80670207419735</v>
       </c>
       <c r="J3" t="n">
-        <v>33.7907434775792</v>
+        <v>33.79074347757878</v>
       </c>
       <c r="K3" t="n">
-        <v>33.7907434775792</v>
+        <v>33.79074347757878</v>
       </c>
       <c r="L3" t="n">
-        <v>33.7907434775792</v>
+        <v>33.79074347757878</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.9272043961422</v>
+        <v>200.927204396142</v>
       </c>
       <c r="C4" t="n">
-        <v>131.482030777895</v>
+        <v>131.4820307778944</v>
       </c>
       <c r="D4" t="n">
-        <v>131.7932744471842</v>
+        <v>131.7932744471843</v>
       </c>
       <c r="E4" t="n">
-        <v>121.1296542517466</v>
+        <v>121.1296542517467</v>
       </c>
       <c r="F4" t="n">
-        <v>130.8939203906289</v>
+        <v>130.8939203906291</v>
       </c>
       <c r="G4" t="n">
         <v>200.7717558289623</v>
       </c>
       <c r="H4" t="n">
-        <v>201.1343468137241</v>
+        <v>131.8732538115618</v>
       </c>
       <c r="I4" t="n">
-        <v>130.8713249372906</v>
+        <v>199.9431629927599</v>
       </c>
       <c r="J4" t="n">
-        <v>199.6165563838086</v>
+        <v>137.0247404079103</v>
       </c>
       <c r="K4" t="n">
-        <v>131.7712084456753</v>
+        <v>131.7712084456769</v>
       </c>
       <c r="L4" t="n">
-        <v>131.8623487078524</v>
+        <v>131.8623487078521</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.7113464895903</v>
+        <v>56.71134648959034</v>
       </c>
       <c r="C5" t="n">
-        <v>56.61483904631375</v>
+        <v>56.6148390463138</v>
       </c>
       <c r="D5" t="n">
-        <v>56.71098530310023</v>
+        <v>56.71098530310019</v>
       </c>
       <c r="E5" t="n">
-        <v>55.80884218235543</v>
+        <v>55.80884218235551</v>
       </c>
       <c r="F5" t="n">
-        <v>55.80884218235543</v>
+        <v>55.80884218235551</v>
       </c>
       <c r="G5" t="n">
-        <v>56.55589792241065</v>
+        <v>56.55589792241049</v>
       </c>
       <c r="H5" t="n">
-        <v>56.7113464895903</v>
+        <v>56.71134648959034</v>
       </c>
       <c r="I5" t="n">
-        <v>55.72730508620837</v>
+        <v>55.72730508620849</v>
       </c>
       <c r="J5" t="n">
-        <v>56.7113464895903</v>
+        <v>56.71134648959034</v>
       </c>
       <c r="K5" t="n">
-        <v>56.7113464895903</v>
+        <v>56.71134648959034</v>
       </c>
       <c r="L5" t="n">
-        <v>56.7113464895903</v>
+        <v>56.71134648959034</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.257171496027</v>
+        <v>125.2571714960268</v>
       </c>
       <c r="C6" t="n">
-        <v>185.5529856878796</v>
+        <v>185.5529856882498</v>
       </c>
       <c r="D6" t="n">
-        <v>198.0632183965423</v>
+        <v>198.0632183965422</v>
       </c>
       <c r="E6" t="n">
-        <v>168.1637095604812</v>
+        <v>168.1637095604815</v>
       </c>
       <c r="F6" t="n">
-        <v>126.2334675816812</v>
+        <v>126.2334675816813</v>
       </c>
       <c r="G6" t="n">
-        <v>185.4037513954273</v>
+        <v>185.4037513954277</v>
       </c>
       <c r="H6" t="n">
-        <v>185.5591999627805</v>
+        <v>185.5591999627806</v>
       </c>
       <c r="I6" t="n">
-        <v>184.5751585592251</v>
+        <v>184.5751585592252</v>
       </c>
       <c r="J6" t="n">
-        <v>185.5710510411593</v>
+        <v>185.5710510411588</v>
       </c>
       <c r="K6" t="n">
         <v>124.1370303577366</v>
       </c>
       <c r="L6" t="n">
-        <v>248.5497110724195</v>
+        <v>248.5497110724198</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.44146068101622</v>
+        <v>98.44146068101634</v>
       </c>
       <c r="C7" t="n">
-        <v>117.1755986651603</v>
+        <v>117.1755986651605</v>
       </c>
       <c r="D7" t="n">
-        <v>117.2721121205853</v>
+        <v>117.2721121205854</v>
       </c>
       <c r="E7" t="n">
-        <v>138.0182302848611</v>
+        <v>138.0182302848613</v>
       </c>
       <c r="F7" t="n">
-        <v>116.2880603817454</v>
+        <v>116.2880603817456</v>
       </c>
       <c r="G7" t="n">
-        <v>117.1166575412572</v>
+        <v>117.1166575412573</v>
       </c>
       <c r="H7" t="n">
-        <v>117.2721061084368</v>
+        <v>117.2721061084367</v>
       </c>
       <c r="I7" t="n">
-        <v>116.2880647050549</v>
+        <v>116.2880647050551</v>
       </c>
       <c r="J7" t="n">
-        <v>117.2721061084368</v>
+        <v>117.2721061084367</v>
       </c>
       <c r="K7" t="n">
-        <v>105.9189037893854</v>
+        <v>106.3615587228332</v>
       </c>
       <c r="L7" t="n">
-        <v>117.2721061084368</v>
+        <v>117.2721061084367</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.29705702209455</v>
+        <v>33.29705702209451</v>
       </c>
       <c r="C8" t="n">
-        <v>26.39622116569851</v>
+        <v>26.39622116569852</v>
       </c>
       <c r="D8" t="n">
-        <v>37.64883896859978</v>
+        <v>37.64883896859979</v>
       </c>
       <c r="E8" t="n">
-        <v>43.42870921131162</v>
+        <v>43.42870921131165</v>
       </c>
       <c r="F8" t="n">
-        <v>43.42870921131162</v>
+        <v>43.42870921131165</v>
       </c>
       <c r="G8" t="n">
         <v>73.91222430035756</v>
       </c>
       <c r="H8" t="n">
-        <v>37.49758219044016</v>
+        <v>37.49758219044011</v>
       </c>
       <c r="I8" t="n">
-        <v>43.42870921131162</v>
+        <v>43.42870921131165</v>
       </c>
       <c r="J8" t="n">
-        <v>72.83781372266691</v>
+        <v>72.83781372266697</v>
       </c>
       <c r="K8" t="n">
         <v>148.2423148102326</v>
       </c>
       <c r="L8" t="n">
-        <v>31.67508742391202</v>
+        <v>31.67508742391209</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.84747835843957</v>
+        <v>33.84747835843963</v>
       </c>
       <c r="C9" t="n">
         <v>27.23725568976714</v>
       </c>
       <c r="D9" t="n">
-        <v>38.49398311257254</v>
+        <v>38.49398311257272</v>
       </c>
       <c r="E9" t="n">
-        <v>44.07266852634392</v>
+        <v>44.07266852634394</v>
       </c>
       <c r="F9" t="n">
-        <v>44.07266852634392</v>
+        <v>44.07266852634394</v>
       </c>
       <c r="G9" t="n">
-        <v>74.0257925576647</v>
+        <v>74.02579255766463</v>
       </c>
       <c r="H9" t="n">
-        <v>38.43415214476244</v>
+        <v>38.43415214476232</v>
       </c>
       <c r="I9" t="n">
-        <v>44.07266852634392</v>
+        <v>44.07266852634394</v>
       </c>
       <c r="J9" t="n">
-        <v>73.30918895853952</v>
+        <v>73.30918895853964</v>
       </c>
       <c r="K9" t="n">
-        <v>147.0134552749606</v>
+        <v>147.0134552749604</v>
       </c>
       <c r="L9" t="n">
-        <v>32.33448046635841</v>
+        <v>32.33448046635829</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117.2070136105715</v>
+        <v>117.2070136106024</v>
       </c>
       <c r="C2" t="n">
-        <v>170.7281443133369</v>
+        <v>170.7281443133367</v>
       </c>
       <c r="D2" t="n">
-        <v>210.5820383689993</v>
+        <v>210.5820383690381</v>
       </c>
       <c r="E2" t="n">
-        <v>192.2063230167402</v>
+        <v>192.2063230167401</v>
       </c>
       <c r="F2" t="n">
-        <v>192.2063230167402</v>
+        <v>192.2063230167401</v>
       </c>
       <c r="G2" t="n">
-        <v>224.9475555846375</v>
+        <v>224.9475555846267</v>
       </c>
       <c r="H2" t="n">
-        <v>852.5641928623018</v>
+        <v>852.5641928623509</v>
       </c>
       <c r="I2" t="n">
-        <v>192.2063230167402</v>
+        <v>192.2063230167401</v>
       </c>
       <c r="J2" t="n">
-        <v>219.1738397841361</v>
+        <v>219.1738397841669</v>
       </c>
       <c r="K2" t="n">
-        <v>188.0485449347208</v>
+        <v>188.0485449347547</v>
       </c>
       <c r="L2" t="n">
-        <v>455.2073439299133</v>
+        <v>455.2073439299704</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.72171754740493</v>
+        <v>33.72171754742904</v>
       </c>
       <c r="C3" t="n">
         <v>32.76300080770094</v>
       </c>
       <c r="D3" t="n">
-        <v>33.72171754740493</v>
+        <v>33.72171754742904</v>
       </c>
       <c r="E3" t="n">
-        <v>32.56907445155272</v>
+        <v>32.56907445155267</v>
       </c>
       <c r="F3" t="n">
-        <v>32.56907445155272</v>
+        <v>32.56907445155267</v>
       </c>
       <c r="G3" t="n">
-        <v>33.56547923850734</v>
+        <v>33.56547923848701</v>
       </c>
       <c r="H3" t="n">
-        <v>33.72171754740493</v>
+        <v>33.72171754742904</v>
       </c>
       <c r="I3" t="n">
-        <v>32.73223316531975</v>
+        <v>32.73223316531977</v>
       </c>
       <c r="J3" t="n">
-        <v>33.72171754740493</v>
+        <v>33.72171754742904</v>
       </c>
       <c r="K3" t="n">
-        <v>33.72171754740493</v>
+        <v>33.72171754742904</v>
       </c>
       <c r="L3" t="n">
-        <v>33.72171754740493</v>
+        <v>33.72171754742904</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137.3438594479896</v>
+        <v>137.3438594480404</v>
       </c>
       <c r="C4" t="n">
-        <v>136.8909562929624</v>
+        <v>136.8909562929621</v>
       </c>
       <c r="D4" t="n">
-        <v>137.2788259825422</v>
+        <v>137.2788259825617</v>
       </c>
       <c r="E4" t="n">
-        <v>126.0461845951531</v>
+        <v>126.046184595153</v>
       </c>
       <c r="F4" t="n">
-        <v>136.3782980015125</v>
+        <v>136.3782980015123</v>
       </c>
       <c r="G4" t="n">
-        <v>210.2694934571067</v>
+        <v>137.1876211391085</v>
       </c>
       <c r="H4" t="n">
-        <v>210.0449486880247</v>
+        <v>210.044948688043</v>
       </c>
       <c r="I4" t="n">
-        <v>209.4362473839309</v>
+        <v>136.3543750659295</v>
       </c>
       <c r="J4" t="n">
-        <v>208.9594073381528</v>
+        <v>142.8032961962975</v>
       </c>
       <c r="K4" t="n">
-        <v>137.2499876867807</v>
+        <v>137.2499876868072</v>
       </c>
       <c r="L4" t="n">
-        <v>137.4335861061751</v>
+        <v>137.4335861061834</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.34728117733626</v>
+        <v>58.34728117734694</v>
       </c>
       <c r="C5" t="n">
-        <v>58.24962076688349</v>
+        <v>58.24962076688345</v>
       </c>
       <c r="D5" t="n">
-        <v>58.34689487970982</v>
+        <v>58.34689487976114</v>
       </c>
       <c r="E5" t="n">
-        <v>57.44130239751581</v>
+        <v>57.44130239751575</v>
       </c>
       <c r="F5" t="n">
-        <v>57.44130239751581</v>
+        <v>57.44130239751575</v>
       </c>
       <c r="G5" t="n">
-        <v>58.19104286840117</v>
+        <v>58.19104286844237</v>
       </c>
       <c r="H5" t="n">
-        <v>58.34728117733626</v>
+        <v>58.34728117734694</v>
       </c>
       <c r="I5" t="n">
-        <v>57.35779679522724</v>
+        <v>57.3577967952272</v>
       </c>
       <c r="J5" t="n">
-        <v>58.34728117733626</v>
+        <v>58.34728117734694</v>
       </c>
       <c r="K5" t="n">
-        <v>58.34728117733626</v>
+        <v>58.34728117734694</v>
       </c>
       <c r="L5" t="n">
-        <v>58.34728117733626</v>
+        <v>58.34728117734694</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130.674105681589</v>
+        <v>130.6741056816122</v>
       </c>
       <c r="C6" t="n">
-        <v>194.5412112857184</v>
+        <v>194.541211285477</v>
       </c>
       <c r="D6" t="n">
-        <v>207.7902934841278</v>
+        <v>207.7902934841363</v>
       </c>
       <c r="E6" t="n">
-        <v>176.1710966923449</v>
+        <v>176.1710966923448</v>
       </c>
       <c r="F6" t="n">
-        <v>131.7593083651293</v>
+        <v>131.7593083651292</v>
       </c>
       <c r="G6" t="n">
-        <v>194.3897949124325</v>
+        <v>194.3897949124838</v>
       </c>
       <c r="H6" t="n">
-        <v>194.5460332213937</v>
+        <v>194.5460332213927</v>
       </c>
       <c r="I6" t="n">
-        <v>193.5565488392566</v>
+        <v>193.5565488392565</v>
       </c>
       <c r="J6" t="n">
-        <v>194.5585858897775</v>
+        <v>194.5585858897985</v>
       </c>
       <c r="K6" t="n">
-        <v>129.4876518351554</v>
+        <v>129.4876518351719</v>
       </c>
       <c r="L6" t="n">
-        <v>261.2656024249096</v>
+        <v>261.2656024249559</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.9861373151682</v>
+        <v>110.9861373151955</v>
       </c>
       <c r="C7" t="n">
-        <v>133.2441535787598</v>
+        <v>133.2441535787596</v>
       </c>
       <c r="D7" t="n">
-        <v>133.3418133853326</v>
+        <v>133.3418133853675</v>
       </c>
       <c r="E7" t="n">
-        <v>158.1502893127423</v>
+        <v>158.1502893127419</v>
       </c>
       <c r="F7" t="n">
-        <v>132.3523163163818</v>
+        <v>132.3523163163816</v>
       </c>
       <c r="G7" t="n">
-        <v>133.185575680278</v>
+        <v>133.1855756803097</v>
       </c>
       <c r="H7" t="n">
-        <v>133.3418139892024</v>
+        <v>133.3418139892143</v>
       </c>
       <c r="I7" t="n">
-        <v>132.3523296071037</v>
+        <v>132.3523296071033</v>
       </c>
       <c r="J7" t="n">
-        <v>133.3418139892024</v>
+        <v>133.3418139892143</v>
       </c>
       <c r="K7" t="n">
-        <v>120.3888468727844</v>
+        <v>120.3888468728054</v>
       </c>
       <c r="L7" t="n">
-        <v>133.3418139892024</v>
+        <v>133.3418139892143</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.27810950551294</v>
+        <v>32.27810950553072</v>
       </c>
       <c r="C8" t="n">
-        <v>26.23087880769722</v>
+        <v>26.23087880769721</v>
       </c>
       <c r="D8" t="n">
-        <v>36.76953651602052</v>
+        <v>36.76953651602059</v>
       </c>
       <c r="E8" t="n">
-        <v>42.68680381628661</v>
+        <v>42.6868038162866</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68680381628661</v>
+        <v>42.6868038162866</v>
       </c>
       <c r="G8" t="n">
-        <v>72.18879924184409</v>
+        <v>72.18879924185971</v>
       </c>
       <c r="H8" t="n">
-        <v>24.10937738589122</v>
+        <v>24.10937738589742</v>
       </c>
       <c r="I8" t="n">
-        <v>42.68680381628661</v>
+        <v>42.6868038162866</v>
       </c>
       <c r="J8" t="n">
-        <v>72.07282876433892</v>
+        <v>72.07282876433422</v>
       </c>
       <c r="K8" t="n">
-        <v>146.52890182658</v>
+        <v>146.528901826598</v>
       </c>
       <c r="L8" t="n">
-        <v>25.88255655687458</v>
+        <v>25.88255655688679</v>
       </c>
     </row>
     <row r="9">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.19831108228358</v>
+        <v>33.19831108230301</v>
       </c>
       <c r="C9" t="n">
         <v>27.37452836717105</v>
       </c>
       <c r="D9" t="n">
-        <v>38.32609156641254</v>
+        <v>38.32609156643042</v>
       </c>
       <c r="E9" t="n">
         <v>43.89784770664694</v>
@@ -3978,22 +3978,22 @@
         <v>43.89784770664694</v>
       </c>
       <c r="G9" t="n">
-        <v>73.3275667314453</v>
+        <v>73.32756673144793</v>
       </c>
       <c r="H9" t="n">
-        <v>33.18420469405835</v>
+        <v>33.18420469407806</v>
       </c>
       <c r="I9" t="n">
         <v>43.89784770664694</v>
       </c>
       <c r="J9" t="n">
-        <v>73.08184417086485</v>
+        <v>73.08184417087111</v>
       </c>
       <c r="K9" t="n">
-        <v>146.0593943276943</v>
+        <v>146.0593943277162</v>
       </c>
       <c r="L9" t="n">
-        <v>30.15215183146859</v>
+        <v>30.15215183147875</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105.0010829990151</v>
+        <v>105.0010829990157</v>
       </c>
       <c r="C2" t="n">
-        <v>160.9552989639599</v>
+        <v>160.9552989639604</v>
       </c>
       <c r="D2" t="n">
-        <v>153.8711174156837</v>
+        <v>153.8711174156846</v>
       </c>
       <c r="E2" t="n">
-        <v>162.5264268503046</v>
+        <v>162.5264268503054</v>
       </c>
       <c r="F2" t="n">
-        <v>162.5264268503046</v>
+        <v>162.5264268503054</v>
       </c>
       <c r="G2" t="n">
-        <v>148.7471545456644</v>
+        <v>148.7471545456568</v>
       </c>
       <c r="H2" t="n">
-        <v>177.0006965532544</v>
+        <v>177.0006965532546</v>
       </c>
       <c r="I2" t="n">
-        <v>162.5264268503046</v>
+        <v>162.5264268503054</v>
       </c>
       <c r="J2" t="n">
-        <v>184.6527149429432</v>
+        <v>184.6527149429444</v>
       </c>
       <c r="K2" t="n">
-        <v>140.6410254781321</v>
+        <v>140.6410254781322</v>
       </c>
       <c r="L2" t="n">
-        <v>149.2501217993013</v>
+        <v>149.250121799302</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.50378407960429</v>
+        <v>33.5037840796044</v>
       </c>
       <c r="C3" t="n">
-        <v>32.57418369681262</v>
+        <v>32.5741836968126</v>
       </c>
       <c r="D3" t="n">
-        <v>33.50378407960429</v>
+        <v>33.5037840796044</v>
       </c>
       <c r="E3" t="n">
-        <v>32.47553282567199</v>
+        <v>32.47553282567203</v>
       </c>
       <c r="F3" t="n">
-        <v>32.47553282567198</v>
+        <v>32.47553282567203</v>
       </c>
       <c r="G3" t="n">
-        <v>33.34899031876837</v>
+        <v>33.34899031876839</v>
       </c>
       <c r="H3" t="n">
-        <v>33.50378407960429</v>
+        <v>33.5037840796044</v>
       </c>
       <c r="I3" t="n">
-        <v>32.52367694594545</v>
+        <v>32.52367694594559</v>
       </c>
       <c r="J3" t="n">
-        <v>33.50378407960429</v>
+        <v>33.5037840796044</v>
       </c>
       <c r="K3" t="n">
-        <v>33.50378407960429</v>
+        <v>33.5037840796044</v>
       </c>
       <c r="L3" t="n">
-        <v>33.50378407960429</v>
+        <v>33.5037840796044</v>
       </c>
     </row>
     <row r="4">
@@ -4159,34 +4159,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.5829759727751</v>
+        <v>200.482666765566</v>
       </c>
       <c r="C4" t="n">
-        <v>131.2281554049266</v>
+        <v>131.2281554049258</v>
       </c>
       <c r="D4" t="n">
-        <v>131.5100113808302</v>
+        <v>131.5100896033991</v>
       </c>
       <c r="E4" t="n">
-        <v>120.9068795828334</v>
+        <v>120.9068795828337</v>
       </c>
       <c r="F4" t="n">
-        <v>130.6338412324734</v>
+        <v>130.6338412324735</v>
       </c>
       <c r="G4" t="n">
         <v>131.4281822119391</v>
       </c>
       <c r="H4" t="n">
-        <v>200.5628122960843</v>
+        <v>200.5628122960844</v>
       </c>
       <c r="I4" t="n">
-        <v>199.5025596319074</v>
+        <v>199.5025596319072</v>
       </c>
       <c r="J4" t="n">
-        <v>199.1499639807623</v>
+        <v>136.739175051391</v>
       </c>
       <c r="K4" t="n">
-        <v>131.5036760440363</v>
+        <v>131.503676044034</v>
       </c>
       <c r="L4" t="n">
         <v>131.5851703431967</v>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.30216384740896</v>
+        <v>56.30216384740891</v>
       </c>
       <c r="C5" t="n">
-        <v>56.20670945622778</v>
+        <v>56.20670945622776</v>
       </c>
       <c r="D5" t="n">
-        <v>56.30182022899708</v>
+        <v>56.30182022899709</v>
       </c>
       <c r="E5" t="n">
-        <v>55.43235596457355</v>
+        <v>55.43235596457356</v>
       </c>
       <c r="F5" t="n">
-        <v>55.43235596457355</v>
+        <v>55.43235596457356</v>
       </c>
       <c r="G5" t="n">
-        <v>56.14737008657295</v>
+        <v>56.14737008657285</v>
       </c>
       <c r="H5" t="n">
-        <v>56.30216384740896</v>
+        <v>56.30216384740891</v>
       </c>
       <c r="I5" t="n">
-        <v>55.32205671375007</v>
+        <v>55.32205671375012</v>
       </c>
       <c r="J5" t="n">
-        <v>56.30216384740896</v>
+        <v>56.30216384740891</v>
       </c>
       <c r="K5" t="n">
-        <v>56.30216384740896</v>
+        <v>56.30216384740891</v>
       </c>
       <c r="L5" t="n">
-        <v>56.30216384740896</v>
+        <v>56.30216384740891</v>
       </c>
     </row>
     <row r="6">
@@ -4242,34 +4242,34 @@
         <v>124.5656577336879</v>
       </c>
       <c r="C6" t="n">
-        <v>184.5357783245754</v>
+        <v>184.5357783245752</v>
       </c>
       <c r="D6" t="n">
-        <v>196.9441665627689</v>
+        <v>196.9441665627685</v>
       </c>
       <c r="E6" t="n">
-        <v>167.2433731964462</v>
+        <v>167.2433731964458</v>
       </c>
       <c r="F6" t="n">
-        <v>125.5518108613356</v>
+        <v>125.5518108613358</v>
       </c>
       <c r="G6" t="n">
-        <v>184.3587815645618</v>
+        <v>184.3587815645624</v>
       </c>
       <c r="H6" t="n">
-        <v>184.5135753255589</v>
+        <v>184.5135753255587</v>
       </c>
       <c r="I6" t="n">
         <v>183.5334681917394</v>
       </c>
       <c r="J6" t="n">
-        <v>184.5253568127218</v>
+        <v>184.5253568127216</v>
       </c>
       <c r="K6" t="n">
-        <v>123.4520943866017</v>
+        <v>123.4520943866019</v>
       </c>
       <c r="L6" t="n">
-        <v>247.1341880176061</v>
+        <v>247.134188017606</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.2172381219474</v>
+        <v>101.2172381219478</v>
       </c>
       <c r="C7" t="n">
-        <v>120.7571982606059</v>
+        <v>120.7571982606062</v>
       </c>
       <c r="D7" t="n">
-        <v>120.8526585284268</v>
+        <v>120.8526585284269</v>
       </c>
       <c r="E7" t="n">
         <v>142.5313976221664</v>
       </c>
       <c r="F7" t="n">
-        <v>119.8725413279377</v>
+        <v>119.8725413279381</v>
       </c>
       <c r="G7" t="n">
-        <v>120.697858890951</v>
+        <v>120.6978588909513</v>
       </c>
       <c r="H7" t="n">
-        <v>120.8526526517871</v>
+        <v>120.8526526517872</v>
       </c>
       <c r="I7" t="n">
-        <v>119.8725455181281</v>
+        <v>119.8725455181286</v>
       </c>
       <c r="J7" t="n">
-        <v>120.8526526517871</v>
+        <v>120.8526526517872</v>
       </c>
       <c r="K7" t="n">
-        <v>109.4758188306747</v>
+        <v>96.12815932653584</v>
       </c>
       <c r="L7" t="n">
-        <v>120.8526526517871</v>
+        <v>120.8526526517872</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35.42778551943381</v>
+        <v>35.4277855194338</v>
       </c>
       <c r="C8" t="n">
-        <v>26.15520119506518</v>
+        <v>26.15520119506519</v>
       </c>
       <c r="D8" t="n">
-        <v>37.49116327904929</v>
+        <v>37.49116327904923</v>
       </c>
       <c r="E8" t="n">
-        <v>42.95031178758205</v>
+        <v>42.95031178758201</v>
       </c>
       <c r="F8" t="n">
-        <v>42.95031178758206</v>
+        <v>42.95031178758201</v>
       </c>
       <c r="G8" t="n">
-        <v>73.69008582645806</v>
+        <v>73.69008582645812</v>
       </c>
       <c r="H8" t="n">
-        <v>37.28158345346975</v>
+        <v>37.28158345346971</v>
       </c>
       <c r="I8" t="n">
-        <v>42.95031178758206</v>
+        <v>42.95031178758201</v>
       </c>
       <c r="J8" t="n">
-        <v>72.20771984761981</v>
+        <v>72.20771984761974</v>
       </c>
       <c r="K8" t="n">
-        <v>146.301168760751</v>
+        <v>146.3011687607509</v>
       </c>
       <c r="L8" t="n">
-        <v>31.46085570954308</v>
+        <v>31.46085570954309</v>
       </c>
     </row>
     <row r="9">
@@ -4362,34 +4362,34 @@
         <v>36.19325890396074</v>
       </c>
       <c r="C9" t="n">
-        <v>27.26677188657278</v>
+        <v>27.26677188657279</v>
       </c>
       <c r="D9" t="n">
-        <v>38.37121760825906</v>
+        <v>38.37121760825907</v>
       </c>
       <c r="E9" t="n">
-        <v>43.86290301676576</v>
+        <v>43.8629030167658</v>
       </c>
       <c r="F9" t="n">
-        <v>43.86290301676576</v>
+        <v>43.8629030167658</v>
       </c>
       <c r="G9" t="n">
-        <v>73.90356806406103</v>
+        <v>73.90356806406105</v>
       </c>
       <c r="H9" t="n">
-        <v>38.28773731509732</v>
+        <v>38.28773731509725</v>
       </c>
       <c r="I9" t="n">
-        <v>43.86290301676576</v>
+        <v>43.8629030167658</v>
       </c>
       <c r="J9" t="n">
-        <v>72.88554055799312</v>
+        <v>72.8855405579931</v>
       </c>
       <c r="K9" t="n">
         <v>145.2865420884976</v>
       </c>
       <c r="L9" t="n">
-        <v>32.18694697647828</v>
+        <v>32.18694697647827</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.5017142972948</v>
+        <v>89.50171429729468</v>
       </c>
       <c r="C2" t="n">
-        <v>145.2453453550594</v>
+        <v>145.2453453550544</v>
       </c>
       <c r="D2" t="n">
-        <v>150.682435134263</v>
+        <v>150.6824351342627</v>
       </c>
       <c r="E2" t="n">
-        <v>143.5835784117011</v>
+        <v>143.5835784117008</v>
       </c>
       <c r="F2" t="n">
-        <v>143.5835784117011</v>
+        <v>143.5835784117008</v>
       </c>
       <c r="G2" t="n">
-        <v>141.426807145656</v>
+        <v>141.4268071456558</v>
       </c>
       <c r="H2" t="n">
-        <v>168.2831851021038</v>
+        <v>168.2831851021036</v>
       </c>
       <c r="I2" t="n">
-        <v>143.5835784117011</v>
+        <v>143.5835784117008</v>
       </c>
       <c r="J2" t="n">
-        <v>172.3479023195405</v>
+        <v>172.3479023195403</v>
       </c>
       <c r="K2" t="n">
-        <v>133.9161247780787</v>
+        <v>133.9161247780786</v>
       </c>
       <c r="L2" t="n">
-        <v>143.0410283334778</v>
+        <v>143.041028333478</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.61630938278159</v>
+        <v>33.61630938278153</v>
       </c>
       <c r="C3" t="n">
-        <v>32.67636053982795</v>
+        <v>32.67636053982793</v>
       </c>
       <c r="D3" t="n">
-        <v>33.61630938278159</v>
+        <v>33.61630938278153</v>
       </c>
       <c r="E3" t="n">
-        <v>32.52772857580775</v>
+        <v>32.52772857580768</v>
       </c>
       <c r="F3" t="n">
-        <v>32.52772857580774</v>
+        <v>32.52772857580768</v>
       </c>
       <c r="G3" t="n">
-        <v>33.46039835451738</v>
+        <v>33.46039835451734</v>
       </c>
       <c r="H3" t="n">
-        <v>33.61630938278159</v>
+        <v>33.61630938278153</v>
       </c>
       <c r="I3" t="n">
-        <v>32.62910221331601</v>
+        <v>32.62910221331591</v>
       </c>
       <c r="J3" t="n">
-        <v>33.61630938278159</v>
+        <v>33.61630938278153</v>
       </c>
       <c r="K3" t="n">
-        <v>33.61630938278159</v>
+        <v>33.61630938278153</v>
       </c>
       <c r="L3" t="n">
-        <v>33.61630938278159</v>
+        <v>33.61630938278153</v>
       </c>
     </row>
     <row r="4">
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.6931598738542</v>
+        <v>200.6669424567116</v>
       </c>
       <c r="C4" t="n">
         <v>131.3237103280792</v>
       </c>
       <c r="D4" t="n">
-        <v>131.6284810732345</v>
+        <v>131.6284017707448</v>
       </c>
       <c r="E4" t="n">
         <v>120.9809375554102</v>
@@ -4570,22 +4570,22 @@
         <v>130.7319653110395</v>
       </c>
       <c r="G4" t="n">
-        <v>200.5110314284468</v>
+        <v>131.53724884559</v>
       </c>
       <c r="H4" t="n">
-        <v>200.8203924446277</v>
+        <v>200.8203924446276</v>
       </c>
       <c r="I4" t="n">
-        <v>199.6797352872453</v>
+        <v>130.7059527043886</v>
       </c>
       <c r="J4" t="n">
-        <v>136.8494551476501</v>
+        <v>199.3425360137321</v>
       </c>
       <c r="K4" t="n">
-        <v>131.6197014004369</v>
+        <v>131.6197014004368</v>
       </c>
       <c r="L4" t="n">
-        <v>131.7019377275208</v>
+        <v>131.701937727521</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.24527014434255</v>
+        <v>56.24527014434253</v>
       </c>
       <c r="C5" t="n">
-        <v>56.14899886390229</v>
+        <v>56.14899886390223</v>
       </c>
       <c r="D5" t="n">
-        <v>56.24491404948754</v>
+        <v>56.24491404948765</v>
       </c>
       <c r="E5" t="n">
-        <v>55.35995003870717</v>
+        <v>55.35995003870709</v>
       </c>
       <c r="F5" t="n">
-        <v>55.35995003870717</v>
+        <v>55.35995003870709</v>
       </c>
       <c r="G5" t="n">
-        <v>56.08935911607834</v>
+        <v>56.08935911607843</v>
       </c>
       <c r="H5" t="n">
-        <v>56.24527014434255</v>
+        <v>56.24527014434253</v>
       </c>
       <c r="I5" t="n">
-        <v>55.25806297487697</v>
+        <v>55.25806297487691</v>
       </c>
       <c r="J5" t="n">
-        <v>56.24527014434255</v>
+        <v>56.24527014434253</v>
       </c>
       <c r="K5" t="n">
-        <v>56.24527014434255</v>
+        <v>56.24527014434253</v>
       </c>
       <c r="L5" t="n">
-        <v>56.24527014434255</v>
+        <v>56.24527014434253</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>124.4918271690015</v>
+        <v>124.4918271690012</v>
       </c>
       <c r="C6" t="n">
-        <v>184.3490014218889</v>
+        <v>184.3490014215259</v>
       </c>
       <c r="D6" t="n">
-        <v>196.7446250809783</v>
+        <v>196.7446250809782</v>
       </c>
       <c r="E6" t="n">
-        <v>167.0795997208629</v>
+        <v>167.0795997208623</v>
       </c>
       <c r="F6" t="n">
-        <v>125.4625689579049</v>
+        <v>125.4625689579048</v>
       </c>
       <c r="G6" t="n">
-        <v>184.1797129400368</v>
+        <v>184.179712940037</v>
       </c>
       <c r="H6" t="n">
-        <v>184.3356239684705</v>
+        <v>184.3356239684703</v>
       </c>
       <c r="I6" t="n">
-        <v>183.3484167988352</v>
+        <v>183.3484167988354</v>
       </c>
       <c r="J6" t="n">
-        <v>184.3473849919541</v>
+        <v>184.3473849919537</v>
       </c>
       <c r="K6" t="n">
-        <v>123.3801979191127</v>
+        <v>123.3801979191126</v>
       </c>
       <c r="L6" t="n">
-        <v>246.8474737856499</v>
+        <v>246.8474737856494</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.02799802763589</v>
+        <v>98.02799802763577</v>
       </c>
       <c r="C7" t="n">
-        <v>116.6602399798675</v>
+        <v>116.6602399798673</v>
       </c>
       <c r="D7" t="n">
-        <v>116.756517167297</v>
+        <v>116.7565171672969</v>
       </c>
       <c r="E7" t="n">
-        <v>137.38161145102</v>
+        <v>137.3816114510198</v>
       </c>
       <c r="F7" t="n">
-        <v>115.7692999776296</v>
+        <v>115.7692999776295</v>
       </c>
       <c r="G7" t="n">
-        <v>116.6006002320435</v>
+        <v>116.6006002320433</v>
       </c>
       <c r="H7" t="n">
-        <v>116.7565112603077</v>
+        <v>116.7565112603075</v>
       </c>
       <c r="I7" t="n">
-        <v>115.7693040908421</v>
+        <v>115.7693040908418</v>
       </c>
       <c r="J7" t="n">
-        <v>116.7565112603077</v>
+        <v>116.7565112603075</v>
       </c>
       <c r="K7" t="n">
         <v>105.464885530983</v>
       </c>
       <c r="L7" t="n">
-        <v>116.7565112603077</v>
+        <v>116.7565112603075</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44.3037531020368</v>
+        <v>44.30375310203687</v>
       </c>
       <c r="C8" t="n">
-        <v>26.4931936527344</v>
+        <v>26.49319365273436</v>
       </c>
       <c r="D8" t="n">
         <v>37.40071364713583</v>
       </c>
       <c r="E8" t="n">
-        <v>43.211516112838</v>
+        <v>43.21151611283793</v>
       </c>
       <c r="F8" t="n">
-        <v>43.211516112838</v>
+        <v>43.21151611283793</v>
       </c>
       <c r="G8" t="n">
-        <v>74.61104781532542</v>
+        <v>74.61104781532535</v>
       </c>
       <c r="H8" t="n">
-        <v>37.30069431176199</v>
+        <v>37.30069431176201</v>
       </c>
       <c r="I8" t="n">
-        <v>43.211516112838</v>
+        <v>43.21151611283793</v>
       </c>
       <c r="J8" t="n">
-        <v>72.40233319802168</v>
+        <v>72.40233319802165</v>
       </c>
       <c r="K8" t="n">
         <v>147.3726130245866</v>
       </c>
       <c r="L8" t="n">
-        <v>31.4846231911459</v>
+        <v>31.48462319114587</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44.71775580883018</v>
+        <v>44.71775580883019</v>
       </c>
       <c r="C9" t="n">
-        <v>27.38289364000306</v>
+        <v>27.38289364000307</v>
       </c>
       <c r="D9" t="n">
-        <v>38.23606811493321</v>
+        <v>38.2360681149332</v>
       </c>
       <c r="E9" t="n">
-        <v>43.85474822742533</v>
+        <v>43.8547482274253</v>
       </c>
       <c r="F9" t="n">
-        <v>43.85474822742533</v>
+        <v>43.8547482274253</v>
       </c>
       <c r="G9" t="n">
-        <v>74.70882078304547</v>
+        <v>74.7088207830455</v>
       </c>
       <c r="H9" t="n">
-        <v>38.19703713916537</v>
+        <v>38.19703713916533</v>
       </c>
       <c r="I9" t="n">
-        <v>43.85474822742533</v>
+        <v>43.8547482274253</v>
       </c>
       <c r="J9" t="n">
-        <v>72.91135421063866</v>
+        <v>72.91135421063868</v>
       </c>
       <c r="K9" t="n">
         <v>146.2457051706908</v>
       </c>
       <c r="L9" t="n">
-        <v>32.13359352008875</v>
+        <v>32.13359352008882</v>
       </c>
     </row>
   </sheetData>
@@ -4871,34 +4871,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>381.2745780932839</v>
+        <v>381.2745780932896</v>
       </c>
       <c r="C2" t="n">
-        <v>285.5522713084183</v>
+        <v>285.5522713084166</v>
       </c>
       <c r="D2" t="n">
-        <v>1345.572469537033</v>
+        <v>1345.572469537031</v>
       </c>
       <c r="E2" t="n">
-        <v>285.5522713084183</v>
+        <v>285.5522713084166</v>
       </c>
       <c r="F2" t="n">
-        <v>285.5522713084183</v>
+        <v>285.5522713084166</v>
       </c>
       <c r="G2" t="n">
-        <v>773.8248026204953</v>
+        <v>773.8248026204978</v>
       </c>
       <c r="H2" t="n">
-        <v>2275.070907381297</v>
+        <v>2275.070907381289</v>
       </c>
       <c r="I2" t="n">
-        <v>285.5522713084183</v>
+        <v>285.5522713084166</v>
       </c>
       <c r="J2" t="n">
         <v>590.6128384072333</v>
       </c>
       <c r="K2" t="n">
-        <v>431.5107482938612</v>
+        <v>431.510748293862</v>
       </c>
       <c r="L2" t="n">
         <v>384.7268137327308</v>
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.05370851408644</v>
+        <v>35.05370851408649</v>
       </c>
       <c r="C3" t="n">
-        <v>33.06614660054095</v>
+        <v>33.06614660054102</v>
       </c>
       <c r="D3" t="n">
-        <v>35.05370851408644</v>
+        <v>35.05370851408649</v>
       </c>
       <c r="E3" t="n">
-        <v>33.20395281434625</v>
+        <v>33.20395281434634</v>
       </c>
       <c r="F3" t="n">
-        <v>33.20395281434624</v>
+        <v>33.20395281434634</v>
       </c>
       <c r="G3" t="n">
-        <v>34.877060584582</v>
+        <v>34.87706058458205</v>
       </c>
       <c r="H3" t="n">
-        <v>35.05370851408644</v>
+        <v>35.05370851408649</v>
       </c>
       <c r="I3" t="n">
-        <v>33.93253831391748</v>
+        <v>33.93253831391753</v>
       </c>
       <c r="J3" t="n">
-        <v>35.05370851408644</v>
+        <v>35.05370851408649</v>
       </c>
       <c r="K3" t="n">
-        <v>35.05370851408644</v>
+        <v>35.05370851408649</v>
       </c>
       <c r="L3" t="n">
-        <v>35.05370851408644</v>
+        <v>35.05370851408649</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>219.2737640040892</v>
+        <v>141.7819755406586</v>
       </c>
       <c r="C4" t="n">
-        <v>139.7428540264056</v>
+        <v>139.7428540264058</v>
       </c>
       <c r="D4" t="n">
-        <v>143.2748533832651</v>
+        <v>143.2749109140186</v>
       </c>
       <c r="E4" t="n">
-        <v>129.4423862782563</v>
+        <v>129.4423862782562</v>
       </c>
       <c r="F4" t="n">
         <v>140.6164400263043</v>
       </c>
       <c r="G4" t="n">
-        <v>219.0971160745844</v>
+        <v>141.6053276111544</v>
       </c>
       <c r="H4" t="n">
         <v>218.0475372878674</v>
       </c>
       <c r="I4" t="n">
-        <v>218.1525938039198</v>
+        <v>218.15259380392</v>
       </c>
       <c r="J4" t="n">
-        <v>217.4285903272202</v>
+        <v>147.5348807260577</v>
       </c>
       <c r="K4" t="n">
-        <v>141.4247255743492</v>
+        <v>141.4247255743489</v>
       </c>
       <c r="L4" t="n">
-        <v>142.3465365764483</v>
+        <v>142.3465365764484</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.02132674843708</v>
+        <v>62.02132674843702</v>
       </c>
       <c r="C5" t="n">
-        <v>60.90015654826816</v>
+        <v>60.90015654826821</v>
       </c>
       <c r="D5" t="n">
-        <v>62.02080761689545</v>
+        <v>62.0208076168955</v>
       </c>
       <c r="E5" t="n">
-        <v>60.88421851417647</v>
+        <v>60.88421851417654</v>
       </c>
       <c r="F5" t="n">
-        <v>60.88421851417647</v>
+        <v>60.88421851417654</v>
       </c>
       <c r="G5" t="n">
-        <v>61.84467881893266</v>
+        <v>61.84467881893269</v>
       </c>
       <c r="H5" t="n">
-        <v>62.02132674843708</v>
+        <v>62.02132674843702</v>
       </c>
       <c r="I5" t="n">
-        <v>60.90015654826816</v>
+        <v>60.90015654826821</v>
       </c>
       <c r="J5" t="n">
-        <v>62.02132674843708</v>
+        <v>62.02132674843702</v>
       </c>
       <c r="K5" t="n">
-        <v>62.02132674843708</v>
+        <v>62.02132674843702</v>
       </c>
       <c r="L5" t="n">
-        <v>62.02132674843708</v>
+        <v>62.02132674843702</v>
       </c>
     </row>
     <row r="6">
@@ -5031,19 +5031,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>136.7985931882244</v>
+        <v>136.7985931882245</v>
       </c>
       <c r="C6" t="n">
-        <v>202.9061601085753</v>
+        <v>202.9061601087477</v>
       </c>
       <c r="D6" t="n">
-        <v>217.9693434758001</v>
+        <v>217.9693434758</v>
       </c>
       <c r="E6" t="n">
         <v>184.5193740068171</v>
       </c>
       <c r="F6" t="n">
-        <v>137.7993165626653</v>
+        <v>137.7993165626652</v>
       </c>
       <c r="G6" t="n">
         <v>203.8520875733495</v>
@@ -5052,16 +5052,16 @@
         <v>204.0287355028582</v>
       </c>
       <c r="I6" t="n">
-        <v>202.9075653026849</v>
+        <v>202.9075653026847</v>
       </c>
       <c r="J6" t="n">
         <v>204.0419481568231</v>
       </c>
       <c r="K6" t="n">
-        <v>135.5497587783373</v>
+        <v>135.5497587783372</v>
       </c>
       <c r="L6" t="n">
-        <v>274.2562408478591</v>
+        <v>274.2562408478589</v>
       </c>
     </row>
     <row r="7">
@@ -5074,34 +5074,34 @@
         <v>127.260837712171</v>
       </c>
       <c r="C7" t="n">
-        <v>152.7641146610616</v>
+        <v>152.7641146610617</v>
       </c>
       <c r="D7" t="n">
-        <v>153.8852816137554</v>
+        <v>153.8852816137555</v>
       </c>
       <c r="E7" t="n">
-        <v>183.4881184040209</v>
+        <v>183.488118404021</v>
       </c>
       <c r="F7" t="n">
         <v>152.7640820194908</v>
       </c>
       <c r="G7" t="n">
-        <v>153.7086369317262</v>
+        <v>153.7086369317261</v>
       </c>
       <c r="H7" t="n">
-        <v>153.8852848612307</v>
+        <v>153.8852848612306</v>
       </c>
       <c r="I7" t="n">
-        <v>152.7641146610616</v>
+        <v>152.7641146610617</v>
       </c>
       <c r="J7" t="n">
-        <v>153.8852848612307</v>
+        <v>153.8852848612306</v>
       </c>
       <c r="K7" t="n">
-        <v>138.4589742549273</v>
+        <v>138.4589742549274</v>
       </c>
       <c r="L7" t="n">
-        <v>153.8852848612307</v>
+        <v>153.8852848612306</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.51026184614429</v>
+        <v>82.51026184614432</v>
       </c>
       <c r="C8" t="n">
-        <v>50.19248364649624</v>
+        <v>50.19248364649622</v>
       </c>
       <c r="D8" t="n">
-        <v>60.30404095652325</v>
+        <v>60.30404095652334</v>
       </c>
       <c r="E8" t="n">
-        <v>50.19248364649624</v>
+        <v>50.19248364649622</v>
       </c>
       <c r="F8" t="n">
-        <v>50.19248364649624</v>
+        <v>50.19248364649622</v>
       </c>
       <c r="G8" t="n">
-        <v>73.81764499207206</v>
+        <v>73.81764499207196</v>
       </c>
       <c r="H8" t="n">
-        <v>44.82315303607812</v>
+        <v>44.82315303607827</v>
       </c>
       <c r="I8" t="n">
-        <v>50.19248364649624</v>
+        <v>50.19248364649622</v>
       </c>
       <c r="J8" t="n">
-        <v>78.50002505779854</v>
+        <v>78.50002505779855</v>
       </c>
       <c r="K8" t="n">
-        <v>81.47811170890134</v>
+        <v>81.47811170890142</v>
       </c>
       <c r="L8" t="n">
-        <v>83.31851410510198</v>
+        <v>83.31851410510208</v>
       </c>
     </row>
     <row r="9">
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.64498295172855</v>
+        <v>85.64498295172851</v>
       </c>
       <c r="C9" t="n">
         <v>52.47334494821683</v>
       </c>
       <c r="D9" t="n">
-        <v>76.60130475281005</v>
+        <v>76.60130475281011</v>
       </c>
       <c r="E9" t="n">
         <v>52.47334494821683</v>
@@ -5166,22 +5166,22 @@
         <v>52.47334494821683</v>
       </c>
       <c r="G9" t="n">
-        <v>82.03860740570386</v>
+        <v>82.03860740570381</v>
       </c>
       <c r="H9" t="n">
-        <v>70.33683585787939</v>
+        <v>70.33683585787949</v>
       </c>
       <c r="I9" t="n">
         <v>52.47334494821683</v>
       </c>
       <c r="J9" t="n">
-        <v>84.01582663932336</v>
+        <v>84.01582663932349</v>
       </c>
       <c r="K9" t="n">
-        <v>85.22501820320616</v>
+        <v>85.22501820320618</v>
       </c>
       <c r="L9" t="n">
-        <v>85.97877558700316</v>
+        <v>72.54471448837192</v>
       </c>
     </row>
   </sheetData>
@@ -5270,34 +5270,34 @@
         <v>357.320404550043</v>
       </c>
       <c r="C2" t="n">
-        <v>310.9108229218026</v>
+        <v>310.9108229218027</v>
       </c>
       <c r="D2" t="n">
-        <v>1167.408800558753</v>
+        <v>1167.408800558758</v>
       </c>
       <c r="E2" t="n">
-        <v>310.9108229218026</v>
+        <v>310.9108229218027</v>
       </c>
       <c r="F2" t="n">
-        <v>310.9108229218026</v>
+        <v>310.9108229218027</v>
       </c>
       <c r="G2" t="n">
-        <v>703.3856293162771</v>
+        <v>703.3856293162812</v>
       </c>
       <c r="H2" t="n">
-        <v>1870.277896935659</v>
+        <v>1870.277896935655</v>
       </c>
       <c r="I2" t="n">
-        <v>310.9108229218026</v>
+        <v>310.9108229218027</v>
       </c>
       <c r="J2" t="n">
-        <v>435.5786231657919</v>
+        <v>435.5786231657926</v>
       </c>
       <c r="K2" t="n">
-        <v>389.9986793564682</v>
+        <v>389.9986793564685</v>
       </c>
       <c r="L2" t="n">
-        <v>405.0260966396122</v>
+        <v>405.0260966396121</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.81194185608433</v>
+        <v>34.81194185608432</v>
       </c>
       <c r="C3" t="n">
-        <v>32.9290868196362</v>
+        <v>32.92908681963621</v>
       </c>
       <c r="D3" t="n">
-        <v>34.81194185608435</v>
+        <v>34.81194185608431</v>
       </c>
       <c r="E3" t="n">
-        <v>33.05770550550922</v>
+        <v>33.05770550550919</v>
       </c>
       <c r="F3" t="n">
-        <v>33.05770550550922</v>
+        <v>33.0577055055092</v>
       </c>
       <c r="G3" t="n">
-        <v>34.63760372951075</v>
+        <v>34.63760372951079</v>
       </c>
       <c r="H3" t="n">
-        <v>34.81194185608435</v>
+        <v>34.81194185608431</v>
       </c>
       <c r="I3" t="n">
-        <v>33.70554288309896</v>
+        <v>33.70554288309895</v>
       </c>
       <c r="J3" t="n">
-        <v>34.81194185608435</v>
+        <v>34.81194185608431</v>
       </c>
       <c r="K3" t="n">
-        <v>34.81194185608435</v>
+        <v>34.81194185608431</v>
       </c>
       <c r="L3" t="n">
-        <v>34.81194185608435</v>
+        <v>34.81194185608431</v>
       </c>
     </row>
     <row r="4">
@@ -5347,22 +5347,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>206.3681480438691</v>
+        <v>134.299176277331</v>
       </c>
       <c r="C4" t="n">
-        <v>132.4464959709917</v>
+        <v>132.4464959709916</v>
       </c>
       <c r="D4" t="n">
-        <v>135.552705728677</v>
+        <v>135.5527057286754</v>
       </c>
       <c r="E4" t="n">
-        <v>122.8509843030583</v>
+        <v>122.8509843030582</v>
       </c>
       <c r="F4" t="n">
         <v>133.1799401441012</v>
       </c>
       <c r="G4" t="n">
-        <v>206.1938099172954</v>
+        <v>134.1248381507573</v>
       </c>
       <c r="H4" t="n">
         <v>205.1904368445294</v>
@@ -5371,13 +5371,13 @@
         <v>205.2617490708836</v>
       </c>
       <c r="J4" t="n">
-        <v>204.6453703234994</v>
+        <v>139.6228423184341</v>
       </c>
       <c r="K4" t="n">
-        <v>133.9712959439492</v>
+        <v>133.9712959439493</v>
       </c>
       <c r="L4" t="n">
-        <v>134.7912689163544</v>
+        <v>134.7912689163543</v>
       </c>
     </row>
     <row r="5">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.58135786773269</v>
+        <v>59.58135786773288</v>
       </c>
       <c r="C5" t="n">
-        <v>58.4749588947474</v>
+        <v>58.47495889474739</v>
       </c>
       <c r="D5" t="n">
-        <v>59.58087690934609</v>
+        <v>59.58087690934614</v>
       </c>
       <c r="E5" t="n">
         <v>58.45809254351603</v>
@@ -5402,22 +5402,22 @@
         <v>58.45809254351603</v>
       </c>
       <c r="G5" t="n">
-        <v>59.40701974115915</v>
+        <v>59.40701974115914</v>
       </c>
       <c r="H5" t="n">
-        <v>59.58135786773271</v>
+        <v>59.58135786773288</v>
       </c>
       <c r="I5" t="n">
-        <v>58.4749588947474</v>
+        <v>58.47495889474739</v>
       </c>
       <c r="J5" t="n">
-        <v>59.58135786773271</v>
+        <v>59.58135786773288</v>
       </c>
       <c r="K5" t="n">
-        <v>59.58135786773271</v>
+        <v>59.58135786773288</v>
       </c>
       <c r="L5" t="n">
-        <v>59.58135786773271</v>
+        <v>59.58135786773288</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>129.054737311398</v>
+        <v>129.0547373113981</v>
       </c>
       <c r="C6" t="n">
-        <v>190.1727873985252</v>
+        <v>190.1727873985254</v>
       </c>
       <c r="D6" t="n">
-        <v>204.1858422930961</v>
+        <v>204.1858422930963</v>
       </c>
       <c r="E6" t="n">
-        <v>173.1543155908024</v>
+        <v>173.1543155908026</v>
       </c>
       <c r="F6" t="n">
-        <v>129.9110879159077</v>
+        <v>129.9110879159078</v>
       </c>
       <c r="G6" t="n">
-        <v>191.1081704235962</v>
+        <v>191.1081704235963</v>
       </c>
       <c r="H6" t="n">
-        <v>191.2825085501775</v>
+        <v>191.2825085501777</v>
       </c>
       <c r="I6" t="n">
         <v>190.1761095771845</v>
       </c>
       <c r="J6" t="n">
-        <v>191.2947380945585</v>
+        <v>191.2947380945587</v>
       </c>
       <c r="K6" t="n">
-        <v>127.8988245124879</v>
+        <v>127.8988245124881</v>
       </c>
       <c r="L6" t="n">
-        <v>256.2846190146921</v>
+        <v>256.2846190146925</v>
       </c>
     </row>
     <row r="7">
@@ -5470,34 +5470,34 @@
         <v>115.3511704170623</v>
       </c>
       <c r="C7" t="n">
-        <v>137.5398396878736</v>
+        <v>137.5398396878741</v>
       </c>
       <c r="D7" t="n">
-        <v>138.6462382166508</v>
+        <v>138.646238216651</v>
       </c>
       <c r="E7" t="n">
-        <v>164.4218208820923</v>
+        <v>164.4218208820925</v>
       </c>
       <c r="F7" t="n">
-        <v>137.5398131099857</v>
+        <v>137.5398131099859</v>
       </c>
       <c r="G7" t="n">
-        <v>138.4719005342855</v>
+        <v>138.4719005342858</v>
       </c>
       <c r="H7" t="n">
-        <v>138.646238660859</v>
+        <v>138.6462386608595</v>
       </c>
       <c r="I7" t="n">
-        <v>137.5398396878736</v>
+        <v>137.5398396878741</v>
       </c>
       <c r="J7" t="n">
-        <v>138.646238660859</v>
+        <v>138.6462386608595</v>
       </c>
       <c r="K7" t="n">
-        <v>109.3135897020851</v>
+        <v>125.1489844467876</v>
       </c>
       <c r="L7" t="n">
-        <v>138.646238660859</v>
+        <v>138.6462386608595</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.39769039231625</v>
+        <v>82.39769039231626</v>
       </c>
       <c r="C8" t="n">
-        <v>48.94555537842007</v>
+        <v>48.94555537842009</v>
       </c>
       <c r="D8" t="n">
-        <v>61.91260541270417</v>
+        <v>61.91260541270383</v>
       </c>
       <c r="E8" t="n">
-        <v>48.94555537842007</v>
+        <v>48.94555537842009</v>
       </c>
       <c r="F8" t="n">
-        <v>48.94555537842007</v>
+        <v>48.94555537842009</v>
       </c>
       <c r="G8" t="n">
-        <v>73.96284792895797</v>
+        <v>73.96284792895791</v>
       </c>
       <c r="H8" t="n">
-        <v>50.23033143572354</v>
+        <v>50.23033143572361</v>
       </c>
       <c r="I8" t="n">
-        <v>48.94555537842007</v>
+        <v>48.94555537842009</v>
       </c>
       <c r="J8" t="n">
-        <v>81.04215391208028</v>
+        <v>81.04215391208034</v>
       </c>
       <c r="K8" t="n">
-        <v>81.31244832562953</v>
+        <v>81.31244832562955</v>
       </c>
       <c r="L8" t="n">
-        <v>82.12306672292131</v>
+        <v>82.12306672292127</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.49465851889283</v>
+        <v>85.49465851889289</v>
       </c>
       <c r="C9" t="n">
-        <v>51.91454535271898</v>
+        <v>51.91454535271899</v>
       </c>
       <c r="D9" t="n">
-        <v>77.15194056119212</v>
+        <v>77.15194056119208</v>
       </c>
       <c r="E9" t="n">
-        <v>51.91454535271898</v>
+        <v>51.91454535271899</v>
       </c>
       <c r="F9" t="n">
-        <v>51.91454535271898</v>
+        <v>51.91454535271899</v>
       </c>
       <c r="G9" t="n">
-        <v>81.99961056135423</v>
+        <v>81.99961056135419</v>
       </c>
       <c r="H9" t="n">
-        <v>72.42946817628633</v>
+        <v>72.42946817628636</v>
       </c>
       <c r="I9" t="n">
-        <v>51.91454535271898</v>
+        <v>51.91454535271899</v>
       </c>
       <c r="J9" t="n">
-        <v>84.94570595270876</v>
+        <v>84.94570595270878</v>
       </c>
       <c r="K9" t="n">
-        <v>85.05306897338966</v>
+        <v>85.05306897338977</v>
       </c>
       <c r="L9" t="n">
-        <v>85.38816016064678</v>
+        <v>73.45431974453197</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>345.0097914306147</v>
+        <v>345.0097914306155</v>
       </c>
       <c r="C2" t="n">
-        <v>380.3518801804886</v>
+        <v>380.3518801804897</v>
       </c>
       <c r="D2" t="n">
-        <v>1001.124622959805</v>
+        <v>1001.124622959806</v>
       </c>
       <c r="E2" t="n">
-        <v>380.3518801804886</v>
+        <v>380.3518801804897</v>
       </c>
       <c r="F2" t="n">
-        <v>380.3518801804886</v>
+        <v>380.3518801804897</v>
       </c>
       <c r="G2" t="n">
-        <v>635.5935111793652</v>
+        <v>635.5935111793624</v>
       </c>
       <c r="H2" t="n">
-        <v>1528.357000337442</v>
+        <v>1528.35700033744</v>
       </c>
       <c r="I2" t="n">
-        <v>380.3518801804886</v>
+        <v>380.3518801804897</v>
       </c>
       <c r="J2" t="n">
-        <v>415.0992448875513</v>
+        <v>415.0992448875517</v>
       </c>
       <c r="K2" t="n">
-        <v>345.0022874284992</v>
+        <v>345.0022874284989</v>
       </c>
       <c r="L2" t="n">
-        <v>1644.195440518746</v>
+        <v>333.6159697977549</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.94946777382374</v>
+        <v>34.94946777382383</v>
       </c>
       <c r="C3" t="n">
-        <v>33.1968129887807</v>
+        <v>33.19681298878074</v>
       </c>
       <c r="D3" t="n">
-        <v>34.94946777382373</v>
+        <v>34.94946777382382</v>
       </c>
       <c r="E3" t="n">
-        <v>33.3219672245312</v>
+        <v>33.32196722453119</v>
       </c>
       <c r="F3" t="n">
-        <v>33.32196722453119</v>
+        <v>33.32196722453118</v>
       </c>
       <c r="G3" t="n">
-        <v>34.78032765816594</v>
+        <v>34.78032765816592</v>
       </c>
       <c r="H3" t="n">
-        <v>34.94946777382373</v>
+        <v>34.94946777382382</v>
       </c>
       <c r="I3" t="n">
-        <v>33.87628201344181</v>
+        <v>33.87628201344185</v>
       </c>
       <c r="J3" t="n">
-        <v>34.94946777382373</v>
+        <v>34.94946777382383</v>
       </c>
       <c r="K3" t="n">
-        <v>34.94946777382373</v>
+        <v>34.94946777382382</v>
       </c>
       <c r="L3" t="n">
-        <v>34.94946777382373</v>
+        <v>34.94946777382382</v>
       </c>
     </row>
     <row r="4">
@@ -5746,34 +5746,34 @@
         <v>134.4699045980825</v>
       </c>
       <c r="C4" t="n">
-        <v>132.8904627543516</v>
+        <v>132.8904627543526</v>
       </c>
       <c r="D4" t="n">
-        <v>204.7767109879908</v>
+        <v>135.5011180171968</v>
       </c>
       <c r="E4" t="n">
-        <v>123.2903713109615</v>
+        <v>123.2903713109616</v>
       </c>
       <c r="F4" t="n">
         <v>133.4401629507974</v>
       </c>
       <c r="G4" t="n">
-        <v>134.3007644824248</v>
+        <v>206.0553486986319</v>
       </c>
       <c r="H4" t="n">
-        <v>205.0146052317649</v>
+        <v>205.0146052317651</v>
       </c>
       <c r="I4" t="n">
-        <v>205.151303053908</v>
+        <v>133.3967188377007</v>
       </c>
       <c r="J4" t="n">
-        <v>139.7936797025973</v>
+        <v>204.4887274102061</v>
       </c>
       <c r="K4" t="n">
-        <v>134.126546998559</v>
+        <v>134.1265469985591</v>
       </c>
       <c r="L4" t="n">
-        <v>134.9238791410877</v>
+        <v>134.9238791410878</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.45185443031085</v>
+        <v>59.45185443031092</v>
       </c>
       <c r="C5" t="n">
-        <v>58.37866866992888</v>
+        <v>58.37866866992894</v>
       </c>
       <c r="D5" t="n">
-        <v>59.45137056682818</v>
+        <v>59.45137056682825</v>
       </c>
       <c r="E5" t="n">
-        <v>58.36445883501108</v>
+        <v>58.36445883501111</v>
       </c>
       <c r="F5" t="n">
-        <v>58.36445883501108</v>
+        <v>58.36445883501111</v>
       </c>
       <c r="G5" t="n">
-        <v>59.28271431465298</v>
+        <v>59.28271431465303</v>
       </c>
       <c r="H5" t="n">
-        <v>59.4518544303108</v>
+        <v>59.45185443031087</v>
       </c>
       <c r="I5" t="n">
-        <v>58.37866866992888</v>
+        <v>58.37866866992894</v>
       </c>
       <c r="J5" t="n">
-        <v>59.4518544303108</v>
+        <v>59.45185443031087</v>
       </c>
       <c r="K5" t="n">
-        <v>59.4518544303108</v>
+        <v>59.45185443031087</v>
       </c>
       <c r="L5" t="n">
-        <v>59.4518544303108</v>
+        <v>59.45185443031087</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>128.6180072326251</v>
       </c>
       <c r="C6" t="n">
-        <v>189.351088930355</v>
+        <v>189.3510889303554</v>
       </c>
       <c r="D6" t="n">
-        <v>203.2412454121646</v>
+        <v>203.2412454121649</v>
       </c>
       <c r="E6" t="n">
-        <v>172.4473965637612</v>
+        <v>172.4473965637616</v>
       </c>
       <c r="F6" t="n">
-        <v>129.4958237707505</v>
+        <v>129.4958237707507</v>
       </c>
       <c r="G6" t="n">
-        <v>190.2559947462464</v>
+        <v>190.2559947462466</v>
       </c>
       <c r="H6" t="n">
-        <v>190.4251348619169</v>
+        <v>190.4251348619173</v>
       </c>
       <c r="I6" t="n">
-        <v>189.3519491015223</v>
+        <v>189.3519491015226</v>
       </c>
       <c r="J6" t="n">
-        <v>190.4372817378195</v>
+        <v>190.4372817378197</v>
       </c>
       <c r="K6" t="n">
-        <v>127.4699081047083</v>
+        <v>127.4699081047086</v>
       </c>
       <c r="L6" t="n">
-        <v>254.9878479027271</v>
+        <v>254.9878479027276</v>
       </c>
     </row>
     <row r="7">
@@ -5866,34 +5866,34 @@
         <v>110.7435237796735</v>
       </c>
       <c r="C7" t="n">
-        <v>131.6288303324232</v>
+        <v>131.6288303324234</v>
       </c>
       <c r="D7" t="n">
-        <v>132.7020168030293</v>
+        <v>132.7020168030294</v>
       </c>
       <c r="E7" t="n">
-        <v>156.9684374858669</v>
+        <v>156.968437485867</v>
       </c>
       <c r="F7" t="n">
-        <v>131.6288079142493</v>
+        <v>131.6288079142497</v>
       </c>
       <c r="G7" t="n">
-        <v>132.5328759771476</v>
+        <v>132.5328759771474</v>
       </c>
       <c r="H7" t="n">
-        <v>132.7020160928053</v>
+        <v>132.7020160928052</v>
       </c>
       <c r="I7" t="n">
-        <v>131.6288303324232</v>
+        <v>131.6288303324234</v>
       </c>
       <c r="J7" t="n">
-        <v>132.7020160928053</v>
+        <v>132.7020160928052</v>
       </c>
       <c r="K7" t="n">
-        <v>119.9791797076494</v>
+        <v>119.9791797076493</v>
       </c>
       <c r="L7" t="n">
-        <v>132.7020160928053</v>
+        <v>132.7020160928052</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.38731958798309</v>
+        <v>82.38731958798306</v>
       </c>
       <c r="C8" t="n">
-        <v>47.14022944300175</v>
+        <v>47.14022944300176</v>
       </c>
       <c r="D8" t="n">
-        <v>65.1938322515206</v>
+        <v>65.19383225152059</v>
       </c>
       <c r="E8" t="n">
-        <v>47.14022944300175</v>
+        <v>47.14022944300176</v>
       </c>
       <c r="F8" t="n">
-        <v>47.14022944300175</v>
+        <v>47.14022944300176</v>
       </c>
       <c r="G8" t="n">
-        <v>75.18482252195327</v>
+        <v>75.18482252195334</v>
       </c>
       <c r="H8" t="n">
-        <v>56.19565468020521</v>
+        <v>56.19565468020518</v>
       </c>
       <c r="I8" t="n">
-        <v>47.14022944300175</v>
+        <v>47.14022944300176</v>
       </c>
       <c r="J8" t="n">
-        <v>81.3335509867082</v>
+        <v>81.33355098670822</v>
       </c>
       <c r="K8" t="n">
-        <v>82.05611081099728</v>
+        <v>82.05611081099724</v>
       </c>
       <c r="L8" t="n">
-        <v>55.91613403412306</v>
+        <v>55.91613403412285</v>
       </c>
     </row>
     <row r="9">
@@ -5943,34 +5943,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.37701771564137</v>
+        <v>85.37701771564134</v>
       </c>
       <c r="C9" t="n">
-        <v>51.23340400542957</v>
+        <v>51.23340400542963</v>
       </c>
       <c r="D9" t="n">
         <v>78.37485430858953</v>
       </c>
       <c r="E9" t="n">
-        <v>51.23340400542957</v>
+        <v>51.23340400542963</v>
       </c>
       <c r="F9" t="n">
-        <v>51.23340400542957</v>
+        <v>51.23340400542963</v>
       </c>
       <c r="G9" t="n">
-        <v>82.3979658989108</v>
+        <v>82.39796589891084</v>
       </c>
       <c r="H9" t="n">
         <v>74.73995400667296</v>
       </c>
       <c r="I9" t="n">
-        <v>51.23340400542957</v>
+        <v>51.23340400542963</v>
       </c>
       <c r="J9" t="n">
         <v>84.9507876047153</v>
       </c>
       <c r="K9" t="n">
-        <v>85.24249145934218</v>
+        <v>85.24249145934209</v>
       </c>
       <c r="L9" t="n">
         <v>74.62060693542736</v>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263.1095135082414</v>
+        <v>263.1095135082437</v>
       </c>
       <c r="C2" t="n">
-        <v>212.83729871283</v>
+        <v>212.8372987128301</v>
       </c>
       <c r="D2" t="n">
         <v>440.3969237609145</v>
       </c>
       <c r="E2" t="n">
-        <v>212.83729871283</v>
+        <v>212.8372987128301</v>
       </c>
       <c r="F2" t="n">
-        <v>212.83729871283</v>
+        <v>212.8372987128301</v>
       </c>
       <c r="G2" t="n">
-        <v>334.4289273895762</v>
+        <v>334.4289273895753</v>
       </c>
       <c r="H2" t="n">
         <v>772.1002534568697</v>
       </c>
       <c r="I2" t="n">
-        <v>212.83729871283</v>
+        <v>212.8372987128301</v>
       </c>
       <c r="J2" t="n">
-        <v>483.3446987475292</v>
+        <v>483.3446987475294</v>
       </c>
       <c r="K2" t="n">
-        <v>298.5960871682567</v>
+        <v>298.5960871682577</v>
       </c>
       <c r="L2" t="n">
-        <v>616.1880475395415</v>
+        <v>616.1880475395417</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.63820744180535</v>
+        <v>33.63820744180546</v>
       </c>
       <c r="C3" t="n">
-        <v>31.97665851092992</v>
+        <v>31.97665851092988</v>
       </c>
       <c r="D3" t="n">
-        <v>33.63820744180535</v>
+        <v>33.63820744180546</v>
       </c>
       <c r="E3" t="n">
-        <v>32.08849482241202</v>
+        <v>32.08849482241193</v>
       </c>
       <c r="F3" t="n">
-        <v>32.08849482241202</v>
+        <v>32.08849482241195</v>
       </c>
       <c r="G3" t="n">
         <v>33.47455129833418</v>
       </c>
       <c r="H3" t="n">
-        <v>33.63820744180535</v>
+        <v>33.63820744180546</v>
       </c>
       <c r="I3" t="n">
-        <v>32.59983744444519</v>
+        <v>32.59983744444525</v>
       </c>
       <c r="J3" t="n">
-        <v>33.63820744180535</v>
+        <v>33.63820744180546</v>
       </c>
       <c r="K3" t="n">
-        <v>33.63820744180535</v>
+        <v>33.63820744180546</v>
       </c>
       <c r="L3" t="n">
-        <v>33.63820744180535</v>
+        <v>33.63820744180546</v>
       </c>
     </row>
     <row r="4">
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139.5147444789099</v>
+        <v>214.2026974050947</v>
       </c>
       <c r="C4" t="n">
-        <v>138.0467334658709</v>
+        <v>138.0467334658711</v>
       </c>
       <c r="D4" t="n">
-        <v>212.4923650129747</v>
+        <v>212.4923650129745</v>
       </c>
       <c r="E4" t="n">
-        <v>127.7854253159412</v>
+        <v>127.7854253159413</v>
       </c>
       <c r="F4" t="n">
-        <v>138.4618717427944</v>
+        <v>138.4618717427943</v>
       </c>
       <c r="G4" t="n">
-        <v>139.3510883354387</v>
+        <v>214.0390412616235</v>
       </c>
       <c r="H4" t="n">
-        <v>212.6360665557693</v>
+        <v>139.7177036088965</v>
       </c>
       <c r="I4" t="n">
-        <v>138.47637448155</v>
+        <v>213.1643274077341</v>
       </c>
       <c r="J4" t="n">
-        <v>212.2619145223949</v>
+        <v>212.261914522395</v>
       </c>
       <c r="K4" t="n">
-        <v>139.482022792655</v>
+        <v>139.4820227926549</v>
       </c>
       <c r="L4" t="n">
         <v>139.6496323002268</v>
@@ -6182,25 +6182,25 @@
         <v>58.23051881390278</v>
       </c>
       <c r="C5" t="n">
-        <v>57.19214881654271</v>
+        <v>57.19214881654259</v>
       </c>
       <c r="D5" t="n">
-        <v>58.2300229500923</v>
+        <v>58.23002295009228</v>
       </c>
       <c r="E5" t="n">
-        <v>57.17881194638601</v>
+        <v>57.17881194638593</v>
       </c>
       <c r="F5" t="n">
-        <v>57.17881194638601</v>
+        <v>57.17881194638593</v>
       </c>
       <c r="G5" t="n">
-        <v>58.06686267043168</v>
+        <v>58.06686267043166</v>
       </c>
       <c r="H5" t="n">
         <v>58.23051881390278</v>
       </c>
       <c r="I5" t="n">
-        <v>57.19214881654271</v>
+        <v>57.19214881654259</v>
       </c>
       <c r="J5" t="n">
         <v>58.23051881390278</v>
@@ -6222,34 +6222,34 @@
         <v>130.9935658837267</v>
       </c>
       <c r="C6" t="n">
-        <v>193.9258444297273</v>
+        <v>193.9258444297275</v>
       </c>
       <c r="D6" t="n">
-        <v>208.2284442455251</v>
+        <v>208.2284442455254</v>
       </c>
       <c r="E6" t="n">
-        <v>176.430423976421</v>
+        <v>176.4304239764211</v>
       </c>
       <c r="F6" t="n">
-        <v>131.9752932306716</v>
+        <v>131.9752932306715</v>
       </c>
       <c r="G6" t="n">
-        <v>194.8001434207056</v>
+        <v>194.8001434207057</v>
       </c>
       <c r="H6" t="n">
         <v>194.9637995641792</v>
       </c>
       <c r="I6" t="n">
-        <v>193.9254295668167</v>
+        <v>193.9254295668169</v>
       </c>
       <c r="J6" t="n">
-        <v>194.976371553423</v>
+        <v>194.9763715534227</v>
       </c>
       <c r="K6" t="n">
-        <v>129.8052859502819</v>
+        <v>129.8052859502818</v>
       </c>
       <c r="L6" t="n">
-        <v>261.7860577523522</v>
+        <v>261.7860577523523</v>
       </c>
     </row>
     <row r="7">
@@ -6259,13 +6259,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114.6552643166905</v>
+        <v>114.6552643166906</v>
       </c>
       <c r="C7" t="n">
-        <v>136.9417234701411</v>
+        <v>136.9417234701413</v>
       </c>
       <c r="D7" t="n">
-        <v>137.9800958430004</v>
+        <v>137.9800958430005</v>
       </c>
       <c r="E7" t="n">
         <v>163.8580673405841</v>
@@ -6274,19 +6274,19 @@
         <v>136.9417102295396</v>
       </c>
       <c r="G7" t="n">
-        <v>137.8164373240301</v>
+        <v>137.8164373240302</v>
       </c>
       <c r="H7" t="n">
         <v>137.9800934675014</v>
       </c>
       <c r="I7" t="n">
-        <v>136.9417234701411</v>
+        <v>136.9417234701413</v>
       </c>
       <c r="J7" t="n">
         <v>137.9800934675014</v>
       </c>
       <c r="K7" t="n">
-        <v>124.4655968529837</v>
+        <v>124.4655968529838</v>
       </c>
       <c r="L7" t="n">
         <v>137.9800934675014</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.34069275486644</v>
+        <v>83.3406927548664</v>
       </c>
       <c r="C8" t="n">
-        <v>50.28925301458096</v>
+        <v>50.28925301458091</v>
       </c>
       <c r="D8" t="n">
         <v>78.81931578808607</v>
       </c>
       <c r="E8" t="n">
-        <v>50.28925301458096</v>
+        <v>50.28925301458091</v>
       </c>
       <c r="F8" t="n">
-        <v>50.28925301458096</v>
+        <v>50.28925301458091</v>
       </c>
       <c r="G8" t="n">
-        <v>81.6940407738704</v>
+        <v>81.69404077387041</v>
       </c>
       <c r="H8" t="n">
         <v>72.32456476665591</v>
       </c>
       <c r="I8" t="n">
-        <v>50.28925301458096</v>
+        <v>50.28925301458091</v>
       </c>
       <c r="J8" t="n">
-        <v>78.86998044411246</v>
+        <v>78.86998044411247</v>
       </c>
       <c r="K8" t="n">
-        <v>82.42318706102394</v>
+        <v>82.42318706102391</v>
       </c>
       <c r="L8" t="n">
-        <v>85.26796029057401</v>
+        <v>76.82008402308804</v>
       </c>
     </row>
     <row r="9">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.86249383672593</v>
+        <v>84.86249383672597</v>
       </c>
       <c r="C9" t="n">
-        <v>51.56858694159406</v>
+        <v>51.56858694159409</v>
       </c>
       <c r="D9" t="n">
         <v>83.02119780067414</v>
@@ -6354,10 +6354,10 @@
         <v>51.56858694159409</v>
       </c>
       <c r="G9" t="n">
-        <v>84.15900436907827</v>
+        <v>84.15900436907832</v>
       </c>
       <c r="H9" t="n">
-        <v>80.38987211184549</v>
+        <v>80.38987211184552</v>
       </c>
       <c r="I9" t="n">
         <v>51.56858694159409</v>
@@ -6369,7 +6369,7 @@
         <v>84.48907122273616</v>
       </c>
       <c r="L9" t="n">
-        <v>82.21481856686562</v>
+        <v>82.21481856686553</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>285.265972094919</v>
+        <v>285.2659720949189</v>
       </c>
       <c r="C2" t="n">
-        <v>236.905647067031</v>
+        <v>236.9056470670311</v>
       </c>
       <c r="D2" t="n">
-        <v>213.023799445182</v>
+        <v>213.0237994451819</v>
       </c>
       <c r="E2" t="n">
-        <v>236.905647067031</v>
+        <v>236.9056470670311</v>
       </c>
       <c r="F2" t="n">
-        <v>236.905647067031</v>
+        <v>236.9056470670311</v>
       </c>
       <c r="G2" t="n">
-        <v>238.3089004329001</v>
+        <v>238.3089004329057</v>
       </c>
       <c r="H2" t="n">
         <v>200.3980045520702</v>
       </c>
       <c r="I2" t="n">
-        <v>236.905647067031</v>
+        <v>236.9056470670311</v>
       </c>
       <c r="J2" t="n">
-        <v>357.6430660008745</v>
+        <v>357.6430660008749</v>
       </c>
       <c r="K2" t="n">
-        <v>253.0880904942375</v>
+        <v>253.0880904942373</v>
       </c>
       <c r="L2" t="n">
-        <v>148.4032655102178</v>
+        <v>148.403265510218</v>
       </c>
     </row>
     <row r="3">
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.28094375305029</v>
+        <v>33.28094375305024</v>
       </c>
       <c r="C3" t="n">
-        <v>31.78515807296249</v>
+        <v>31.7851580729625</v>
       </c>
       <c r="D3" t="n">
-        <v>33.28094375305029</v>
+        <v>33.28094375305024</v>
       </c>
       <c r="E3" t="n">
         <v>31.8816266522107</v>
@@ -6510,22 +6510,22 @@
         <v>31.88162665221073</v>
       </c>
       <c r="G3" t="n">
-        <v>33.12195595555987</v>
+        <v>33.12195595555992</v>
       </c>
       <c r="H3" t="n">
-        <v>33.28094375305029</v>
+        <v>33.28094375305024</v>
       </c>
       <c r="I3" t="n">
-        <v>32.27236615059996</v>
+        <v>32.27236615059999</v>
       </c>
       <c r="J3" t="n">
-        <v>33.28094375305029</v>
+        <v>33.28094375305024</v>
       </c>
       <c r="K3" t="n">
-        <v>33.28094375305029</v>
+        <v>33.28094375305024</v>
       </c>
       <c r="L3" t="n">
-        <v>33.28094375305029</v>
+        <v>33.28094375305024</v>
       </c>
     </row>
     <row r="4">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.9253611120564</v>
+        <v>200.9253611120565</v>
       </c>
       <c r="C4" t="n">
         <v>130.6411545052313</v>
       </c>
       <c r="D4" t="n">
-        <v>131.7514385483436</v>
+        <v>131.7514941767832</v>
       </c>
       <c r="E4" t="n">
         <v>121.0854719911459</v>
@@ -6550,22 +6550,22 @@
         <v>130.8660650746295</v>
       </c>
       <c r="G4" t="n">
-        <v>131.7125867586343</v>
+        <v>200.7663733145665</v>
       </c>
       <c r="H4" t="n">
-        <v>131.8617037059055</v>
+        <v>199.3001751003806</v>
       </c>
       <c r="I4" t="n">
-        <v>130.8629969536744</v>
+        <v>199.9167835096068</v>
       </c>
       <c r="J4" t="n">
-        <v>199.0844659224919</v>
+        <v>137.0715725540497</v>
       </c>
       <c r="K4" t="n">
         <v>131.858576056692</v>
       </c>
       <c r="L4" t="n">
-        <v>131.8595782927522</v>
+        <v>131.8595782927523</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.63327993831444</v>
+        <v>55.63327993831443</v>
       </c>
       <c r="C5" t="n">
-        <v>54.62470233586424</v>
+        <v>54.62470233586426</v>
       </c>
       <c r="D5" t="n">
         <v>55.6328158219775</v>
       </c>
       <c r="E5" t="n">
-        <v>54.61518042919579</v>
+        <v>54.61518042919583</v>
       </c>
       <c r="F5" t="n">
-        <v>54.61518042919579</v>
+        <v>54.61518042919583</v>
       </c>
       <c r="G5" t="n">
-        <v>55.47429214082412</v>
+        <v>55.47429214082409</v>
       </c>
       <c r="H5" t="n">
-        <v>55.63327993831444</v>
+        <v>55.63327993831443</v>
       </c>
       <c r="I5" t="n">
-        <v>54.62470233586424</v>
+        <v>54.62470233586426</v>
       </c>
       <c r="J5" t="n">
-        <v>55.63327993831444</v>
+        <v>55.63327993831443</v>
       </c>
       <c r="K5" t="n">
-        <v>55.63327993831444</v>
+        <v>55.63327993831443</v>
       </c>
       <c r="L5" t="n">
-        <v>55.63327993831444</v>
+        <v>55.63327993831443</v>
       </c>
     </row>
     <row r="6">
@@ -6615,34 +6615,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122.868748152207</v>
+        <v>122.8687481522071</v>
       </c>
       <c r="C6" t="n">
-        <v>180.6373370463935</v>
+        <v>180.6373370463933</v>
       </c>
       <c r="D6" t="n">
-        <v>193.830116856893</v>
+        <v>193.8301168568931</v>
       </c>
       <c r="E6" t="n">
         <v>164.5627263000814</v>
       </c>
       <c r="F6" t="n">
-        <v>123.7178173521551</v>
+        <v>123.7178173521552</v>
       </c>
       <c r="G6" t="n">
-        <v>181.48392346089</v>
+        <v>181.4839234608899</v>
       </c>
       <c r="H6" t="n">
-        <v>181.642911258378</v>
+        <v>181.6429112583783</v>
       </c>
       <c r="I6" t="n">
         <v>180.63433365593</v>
       </c>
       <c r="J6" t="n">
-        <v>181.654462070787</v>
+        <v>181.6544620707871</v>
       </c>
       <c r="K6" t="n">
-        <v>121.776987897345</v>
+        <v>121.7769878973451</v>
       </c>
       <c r="L6" t="n">
         <v>243.037439243298</v>
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102.9275398591039</v>
+        <v>102.927539859104</v>
       </c>
       <c r="C7" t="n">
         <v>121.9857763219378</v>
       </c>
       <c r="D7" t="n">
-        <v>122.9943610380559</v>
+        <v>122.9943610380561</v>
       </c>
       <c r="E7" t="n">
-        <v>145.1424556353145</v>
+        <v>145.1424556353148</v>
       </c>
       <c r="F7" t="n">
-        <v>121.9857722712165</v>
+        <v>121.9857722712166</v>
       </c>
       <c r="G7" t="n">
-        <v>122.8353661268976</v>
+        <v>122.8353661268978</v>
       </c>
       <c r="H7" t="n">
-        <v>122.9943539243878</v>
+        <v>122.994353924388</v>
       </c>
       <c r="I7" t="n">
         <v>121.9857763219378</v>
       </c>
       <c r="J7" t="n">
-        <v>122.9943539243878</v>
+        <v>122.994353924388</v>
       </c>
       <c r="K7" t="n">
-        <v>110.8958522785101</v>
+        <v>111.3675660384918</v>
       </c>
       <c r="L7" t="n">
-        <v>122.9943539243878</v>
+        <v>122.994353924388</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.94083714248633</v>
+        <v>81.94083714248636</v>
       </c>
       <c r="C8" t="n">
-        <v>49.00888205668733</v>
+        <v>49.00888205668735</v>
       </c>
       <c r="D8" t="n">
         <v>83.88906616831397</v>
       </c>
       <c r="E8" t="n">
-        <v>49.00888205668733</v>
+        <v>49.00888205668735</v>
       </c>
       <c r="F8" t="n">
-        <v>49.00888205668733</v>
+        <v>49.00888205668735</v>
       </c>
       <c r="G8" t="n">
         <v>83.18561544015186</v>
       </c>
       <c r="H8" t="n">
-        <v>84.72338556762917</v>
+        <v>84.72338556762921</v>
       </c>
       <c r="I8" t="n">
-        <v>49.00888205668733</v>
+        <v>49.00888205668735</v>
       </c>
       <c r="J8" t="n">
-        <v>80.42104120477579</v>
+        <v>80.42104120477583</v>
       </c>
       <c r="K8" t="n">
-        <v>82.65951970173664</v>
+        <v>82.65951970173666</v>
       </c>
       <c r="L8" t="n">
-        <v>85.03628849385819</v>
+        <v>85.77940665992564</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.03309565409511</v>
+        <v>84.03309565409519</v>
       </c>
       <c r="C9" t="n">
         <v>50.87927963956933</v>
       </c>
       <c r="D9" t="n">
-        <v>84.82668265625929</v>
+        <v>84.82668265625935</v>
       </c>
       <c r="E9" t="n">
         <v>50.87927963956933</v>
@@ -6750,10 +6750,10 @@
         <v>50.87927963956933</v>
       </c>
       <c r="G9" t="n">
-        <v>84.51964300747785</v>
+        <v>84.5196430074779</v>
       </c>
       <c r="H9" t="n">
-        <v>85.16862831187771</v>
+        <v>85.16862831187768</v>
       </c>
       <c r="I9" t="n">
         <v>50.87927963956933</v>
@@ -6762,10 +6762,10 @@
         <v>83.41664270350721</v>
       </c>
       <c r="K9" t="n">
-        <v>84.32604600635923</v>
+        <v>84.32604600635929</v>
       </c>
       <c r="L9" t="n">
-        <v>85.29541878516733</v>
+        <v>85.59751096551254</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>280.1251672319888</v>
+        <v>280.1251672319885</v>
       </c>
       <c r="C2" t="n">
-        <v>232.4446421807866</v>
+        <v>232.4446421807874</v>
       </c>
       <c r="D2" t="n">
-        <v>190.4656419959196</v>
+        <v>190.4656419959192</v>
       </c>
       <c r="E2" t="n">
-        <v>232.4446421807866</v>
+        <v>232.4446421807874</v>
       </c>
       <c r="F2" t="n">
-        <v>232.4446421807866</v>
+        <v>232.4446421807874</v>
       </c>
       <c r="G2" t="n">
-        <v>225.0443848837208</v>
+        <v>225.044384883719</v>
       </c>
       <c r="H2" t="n">
-        <v>190.9620489182193</v>
+        <v>190.9620489182183</v>
       </c>
       <c r="I2" t="n">
-        <v>232.4446421807866</v>
+        <v>232.4446421807874</v>
       </c>
       <c r="J2" t="n">
-        <v>343.6046109463705</v>
+        <v>343.6046109463699</v>
       </c>
       <c r="K2" t="n">
-        <v>220.1723627787632</v>
+        <v>220.1723627787627</v>
       </c>
       <c r="L2" t="n">
-        <v>193.0417156788466</v>
+        <v>184.3302697747876</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.22662322715993</v>
+        <v>33.22662322715981</v>
       </c>
       <c r="C3" t="n">
-        <v>31.73550156840219</v>
+        <v>31.73550156840216</v>
       </c>
       <c r="D3" t="n">
-        <v>33.22662322715994</v>
+        <v>33.22662322715982</v>
       </c>
       <c r="E3" t="n">
         <v>31.83223967565387</v>
       </c>
       <c r="F3" t="n">
-        <v>31.83223967565385</v>
+        <v>31.83223967565388</v>
       </c>
       <c r="G3" t="n">
-        <v>33.06800301465275</v>
+        <v>33.06800301465248</v>
       </c>
       <c r="H3" t="n">
-        <v>33.22662322715993</v>
+        <v>33.22662322715982</v>
       </c>
       <c r="I3" t="n">
-        <v>32.22039140212287</v>
+        <v>32.22039140212279</v>
       </c>
       <c r="J3" t="n">
-        <v>33.22662322715993</v>
+        <v>33.22662322715981</v>
       </c>
       <c r="K3" t="n">
-        <v>33.22662322715993</v>
+        <v>33.22662322715982</v>
       </c>
       <c r="L3" t="n">
-        <v>33.22662322715993</v>
+        <v>33.22662322715982</v>
       </c>
     </row>
     <row r="4">
@@ -6931,34 +6931,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.7747808384629</v>
+        <v>131.7747808384625</v>
       </c>
       <c r="C4" t="n">
-        <v>130.5501298970787</v>
+        <v>130.5501298970781</v>
       </c>
       <c r="D4" t="n">
-        <v>131.6209439194172</v>
+        <v>131.6209439194173</v>
       </c>
       <c r="E4" t="n">
         <v>120.9982723016099</v>
       </c>
       <c r="F4" t="n">
-        <v>130.7621232549048</v>
+        <v>130.7621232549047</v>
       </c>
       <c r="G4" t="n">
-        <v>200.6652470418867</v>
+        <v>131.6161606259551</v>
       </c>
       <c r="H4" t="n">
-        <v>199.1443934795146</v>
+        <v>199.1443934795145</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7685490134257</v>
+        <v>130.7685490134256</v>
       </c>
       <c r="J4" t="n">
-        <v>198.9267760943383</v>
+        <v>136.9563448684133</v>
       </c>
       <c r="K4" t="n">
-        <v>131.7035968397684</v>
+        <v>131.7035968397682</v>
       </c>
       <c r="L4" t="n">
         <v>131.7572343690952</v>
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.47212615797127</v>
+        <v>55.47212615797095</v>
       </c>
       <c r="C5" t="n">
-        <v>54.46589433293406</v>
+        <v>54.46589433293389</v>
       </c>
       <c r="D5" t="n">
-        <v>55.47166515620747</v>
+        <v>55.47166515620702</v>
       </c>
       <c r="E5" t="n">
-        <v>54.45562058835189</v>
+        <v>54.45562058835171</v>
       </c>
       <c r="F5" t="n">
-        <v>54.45562058835189</v>
+        <v>54.45562058835171</v>
       </c>
       <c r="G5" t="n">
-        <v>55.31350594546389</v>
+        <v>55.31350594546362</v>
       </c>
       <c r="H5" t="n">
-        <v>55.47212615797127</v>
+        <v>55.47212615797095</v>
       </c>
       <c r="I5" t="n">
-        <v>54.46589433293406</v>
+        <v>54.46589433293389</v>
       </c>
       <c r="J5" t="n">
-        <v>55.47212615797127</v>
+        <v>55.47212615797095</v>
       </c>
       <c r="K5" t="n">
-        <v>55.47212615797127</v>
+        <v>55.47212615797095</v>
       </c>
       <c r="L5" t="n">
-        <v>55.47212615797127</v>
+        <v>55.47212615797095</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122.5694862491231</v>
+        <v>122.5694862491228</v>
       </c>
       <c r="C6" t="n">
-        <v>180.1681926930718</v>
+        <v>180.1681926930717</v>
       </c>
       <c r="D6" t="n">
-        <v>193.3238269298853</v>
+        <v>193.3238269298851</v>
       </c>
       <c r="E6" t="n">
-        <v>164.1405586298904</v>
+        <v>164.1405586298903</v>
       </c>
       <c r="F6" t="n">
         <v>123.4150154580524</v>
       </c>
       <c r="G6" t="n">
-        <v>181.0135569873289</v>
+        <v>181.0135569873285</v>
       </c>
       <c r="H6" t="n">
-        <v>181.1721771998338</v>
+        <v>181.1721771998339</v>
       </c>
       <c r="I6" t="n">
-        <v>180.1659453747989</v>
+        <v>180.1659453747986</v>
       </c>
       <c r="J6" t="n">
-        <v>181.1836943131559</v>
+        <v>181.1836943131556</v>
       </c>
       <c r="K6" t="n">
-        <v>121.4809111775672</v>
+        <v>121.480911177567</v>
       </c>
       <c r="L6" t="n">
-        <v>242.3875881802168</v>
+        <v>242.3875881802165</v>
       </c>
     </row>
     <row r="7">
@@ -7051,34 +7051,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.52466711162199</v>
+        <v>99.5246671116216</v>
       </c>
       <c r="C7" t="n">
-        <v>117.6522966531856</v>
+        <v>117.6522966531854</v>
       </c>
       <c r="D7" t="n">
-        <v>118.6585350897658</v>
+        <v>118.6585350897654</v>
       </c>
       <c r="E7" t="n">
-        <v>139.7323680044332</v>
+        <v>139.7323680044331</v>
       </c>
       <c r="F7" t="n">
-        <v>117.6522927018788</v>
+        <v>117.6522927018792</v>
       </c>
       <c r="G7" t="n">
-        <v>118.4999082657153</v>
+        <v>118.4999082657152</v>
       </c>
       <c r="H7" t="n">
         <v>118.6585284782226</v>
       </c>
       <c r="I7" t="n">
-        <v>117.6522966531856</v>
+        <v>117.6522966531854</v>
       </c>
       <c r="J7" t="n">
         <v>118.6585284782226</v>
       </c>
       <c r="K7" t="n">
-        <v>107.1225141488717</v>
+        <v>107.1225141488714</v>
       </c>
       <c r="L7" t="n">
         <v>118.6585284782226</v>
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.91925181508105</v>
+        <v>81.919251815081</v>
       </c>
       <c r="C8" t="n">
-        <v>49.01955072486185</v>
+        <v>49.01955072486184</v>
       </c>
       <c r="D8" t="n">
-        <v>84.33237363263041</v>
+        <v>84.33237363263036</v>
       </c>
       <c r="E8" t="n">
-        <v>49.01955072486185</v>
+        <v>49.01955072486184</v>
       </c>
       <c r="F8" t="n">
-        <v>49.01955072486185</v>
+        <v>49.01955072486184</v>
       </c>
       <c r="G8" t="n">
-        <v>83.42218042983501</v>
+        <v>83.422180429835</v>
       </c>
       <c r="H8" t="n">
-        <v>84.71911060560545</v>
+        <v>84.71911060560542</v>
       </c>
       <c r="I8" t="n">
-        <v>49.01955072486185</v>
+        <v>49.01955072486184</v>
       </c>
       <c r="J8" t="n">
-        <v>80.70155627603648</v>
+        <v>80.70155627603641</v>
       </c>
       <c r="K8" t="n">
-        <v>83.3918591991339</v>
+        <v>83.39185919913378</v>
       </c>
       <c r="L8" t="n">
-        <v>84.75298020613013</v>
+        <v>84.66968461798592</v>
       </c>
     </row>
     <row r="9">
@@ -7131,34 +7131,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.95270437457911</v>
+        <v>83.95270437457904</v>
       </c>
       <c r="C9" t="n">
-        <v>50.82200272572435</v>
+        <v>50.82200272572432</v>
       </c>
       <c r="D9" t="n">
-        <v>84.93562421601368</v>
+        <v>84.93562421601362</v>
       </c>
       <c r="E9" t="n">
-        <v>50.82200272572435</v>
+        <v>50.82200272572432</v>
       </c>
       <c r="F9" t="n">
-        <v>50.82200272572435</v>
+        <v>50.82200272572432</v>
       </c>
       <c r="G9" t="n">
-        <v>84.54534539894556</v>
+        <v>84.54534539894553</v>
       </c>
       <c r="H9" t="n">
-        <v>85.09517644658482</v>
+        <v>85.09517644658473</v>
       </c>
       <c r="I9" t="n">
-        <v>50.82200272572435</v>
+        <v>50.82200272572432</v>
       </c>
       <c r="J9" t="n">
         <v>83.45914085624518</v>
       </c>
       <c r="K9" t="n">
-        <v>84.55267823689255</v>
+        <v>84.55267823689249</v>
       </c>
       <c r="L9" t="n">
         <v>85.07468780549323</v>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>316.5655078329703</v>
+        <v>316.5655078329702</v>
       </c>
       <c r="C2" t="n">
-        <v>256.649870766724</v>
+        <v>256.6498707667237</v>
       </c>
       <c r="D2" t="n">
-        <v>1241.401210069893</v>
+        <v>1241.401210069891</v>
       </c>
       <c r="E2" t="n">
-        <v>256.649870766724</v>
+        <v>256.6498707667237</v>
       </c>
       <c r="F2" t="n">
-        <v>256.649870766724</v>
+        <v>256.6498707667237</v>
       </c>
       <c r="G2" t="n">
-        <v>669.3938627776456</v>
+        <v>669.3938627776395</v>
       </c>
       <c r="H2" t="n">
-        <v>2049.555477788973</v>
+        <v>2049.555477788967</v>
       </c>
       <c r="I2" t="n">
-        <v>256.649870766724</v>
+        <v>256.6498707667237</v>
       </c>
       <c r="J2" t="n">
-        <v>526.1087458254558</v>
+        <v>526.1087458254543</v>
       </c>
       <c r="K2" t="n">
-        <v>404.3336431986023</v>
+        <v>404.3336431986016</v>
       </c>
       <c r="L2" t="n">
-        <v>1818.056018106403</v>
+        <v>275.5670255199956</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.6113900549776</v>
+        <v>34.61139005497752</v>
       </c>
       <c r="C3" t="n">
-        <v>32.67376047456774</v>
+        <v>32.67376047456767</v>
       </c>
       <c r="D3" t="n">
-        <v>34.6113900549776</v>
+        <v>34.61139005497752</v>
       </c>
       <c r="E3" t="n">
-        <v>32.8065453952843</v>
+        <v>32.8065453952842</v>
       </c>
       <c r="F3" t="n">
-        <v>32.8065453952843</v>
+        <v>32.80654539528411</v>
       </c>
       <c r="G3" t="n">
-        <v>34.43676742127055</v>
+        <v>34.43676742127045</v>
       </c>
       <c r="H3" t="n">
-        <v>34.6113900549776</v>
+        <v>34.61139005497752</v>
       </c>
       <c r="I3" t="n">
-        <v>33.50306314177303</v>
+        <v>33.50306314177295</v>
       </c>
       <c r="J3" t="n">
-        <v>34.6113900549776</v>
+        <v>34.61139005497752</v>
       </c>
       <c r="K3" t="n">
-        <v>34.6113900549776</v>
+        <v>34.61139005497752</v>
       </c>
       <c r="L3" t="n">
-        <v>34.6113900549776</v>
+        <v>34.61139005497752</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>141.1650141487014</v>
+        <v>141.1650141487012</v>
       </c>
       <c r="C4" t="n">
-        <v>139.2105256872709</v>
+        <v>139.2105256872701</v>
       </c>
       <c r="D4" t="n">
-        <v>142.6664362047714</v>
+        <v>142.6664362047709</v>
       </c>
       <c r="E4" t="n">
-        <v>128.923121292685</v>
+        <v>128.9231212926849</v>
       </c>
       <c r="F4" t="n">
-        <v>140.0086932521164</v>
+        <v>140.0086932521163</v>
       </c>
       <c r="G4" t="n">
-        <v>217.8169887367401</v>
+        <v>217.81698873674</v>
       </c>
       <c r="H4" t="n">
-        <v>216.7970388578011</v>
+        <v>216.7970388578009</v>
       </c>
       <c r="I4" t="n">
-        <v>216.8832844572423</v>
+        <v>216.8832844572422</v>
       </c>
       <c r="J4" t="n">
         <v>216.1674631456623</v>
       </c>
       <c r="K4" t="n">
-        <v>140.8870875039467</v>
+        <v>140.8870875039466</v>
       </c>
       <c r="L4" t="n">
-        <v>141.6496897311378</v>
+        <v>141.6496897311377</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.77547768945303</v>
+        <v>60.77547768945291</v>
       </c>
       <c r="C5" t="n">
-        <v>59.66715077624849</v>
+        <v>59.66715077624839</v>
       </c>
       <c r="D5" t="n">
-        <v>60.77496945812464</v>
+        <v>60.77496945812453</v>
       </c>
       <c r="E5" t="n">
-        <v>59.65080003798737</v>
+        <v>59.65080003798707</v>
       </c>
       <c r="F5" t="n">
-        <v>59.65080003798737</v>
+        <v>59.65080003798707</v>
       </c>
       <c r="G5" t="n">
-        <v>60.60085505574597</v>
+        <v>60.60085505574579</v>
       </c>
       <c r="H5" t="n">
-        <v>60.77547768945303</v>
+        <v>60.77547768945291</v>
       </c>
       <c r="I5" t="n">
-        <v>59.66715077624849</v>
+        <v>59.66715077624839</v>
       </c>
       <c r="J5" t="n">
-        <v>60.77547768945303</v>
+        <v>60.77547768945291</v>
       </c>
       <c r="K5" t="n">
-        <v>60.77547768945303</v>
+        <v>60.77547768945291</v>
       </c>
       <c r="L5" t="n">
-        <v>60.77547768945303</v>
+        <v>60.77547768945291</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.9073256110634</v>
+        <v>134.9073256110631</v>
       </c>
       <c r="C6" t="n">
-        <v>199.9535109611101</v>
+        <v>199.9535109609421</v>
       </c>
       <c r="D6" t="n">
-        <v>214.7818504009358</v>
+        <v>214.7818504009348</v>
       </c>
       <c r="E6" t="n">
-        <v>181.8604141575719</v>
+        <v>181.8604141575715</v>
       </c>
       <c r="F6" t="n">
-        <v>135.8866079115128</v>
+        <v>135.8866079115127</v>
       </c>
       <c r="G6" t="n">
-        <v>200.8892390437457</v>
+        <v>200.8892390437455</v>
       </c>
       <c r="H6" t="n">
-        <v>201.0638616774591</v>
+        <v>201.0638616774586</v>
       </c>
       <c r="I6" t="n">
-        <v>199.9555347642482</v>
+        <v>199.9555347642475</v>
       </c>
       <c r="J6" t="n">
-        <v>201.0768633371424</v>
+        <v>201.0768633371422</v>
       </c>
       <c r="K6" t="n">
-        <v>133.6784339884147</v>
+        <v>133.6784339884144</v>
       </c>
       <c r="L6" t="n">
-        <v>270.1698955227847</v>
+        <v>270.1698955227838</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>124.2229361968713</v>
+        <v>124.2229361968708</v>
       </c>
       <c r="C7" t="n">
-        <v>148.95466018339</v>
+        <v>148.9546601833896</v>
       </c>
       <c r="D7" t="n">
-        <v>150.0629817230764</v>
+        <v>150.0629817230758</v>
       </c>
       <c r="E7" t="n">
-        <v>178.7734863954894</v>
+        <v>178.7734863954891</v>
       </c>
       <c r="F7" t="n">
-        <v>148.9546283665273</v>
+        <v>148.9546283665267</v>
       </c>
       <c r="G7" t="n">
-        <v>149.8883644628875</v>
+        <v>149.8883644628867</v>
       </c>
       <c r="H7" t="n">
-        <v>150.0629870965946</v>
+        <v>150.0629870965944</v>
       </c>
       <c r="I7" t="n">
-        <v>148.95466018339</v>
+        <v>148.9546601833896</v>
       </c>
       <c r="J7" t="n">
-        <v>150.0629870965946</v>
+        <v>150.0629870965944</v>
       </c>
       <c r="K7" t="n">
-        <v>135.091157863513</v>
+        <v>135.0911578635126</v>
       </c>
       <c r="L7" t="n">
-        <v>150.0629870965946</v>
+        <v>150.0629870965944</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.42075063025084</v>
+        <v>83.42075063025078</v>
       </c>
       <c r="C8" t="n">
-        <v>50.26824461477715</v>
+        <v>50.26824461477704</v>
       </c>
       <c r="D8" t="n">
-        <v>60.9636531498326</v>
+        <v>60.9636531498324</v>
       </c>
       <c r="E8" t="n">
-        <v>50.26824461477715</v>
+        <v>50.26824461477704</v>
       </c>
       <c r="F8" t="n">
-        <v>50.26824461477715</v>
+        <v>50.26824461477704</v>
       </c>
       <c r="G8" t="n">
-        <v>75.26300686996814</v>
+        <v>75.26300686996811</v>
       </c>
       <c r="H8" t="n">
-        <v>45.42227072347141</v>
+        <v>45.42227072347144</v>
       </c>
       <c r="I8" t="n">
-        <v>50.26824461477715</v>
+        <v>50.26824461477704</v>
       </c>
       <c r="J8" t="n">
-        <v>79.28408502656595</v>
+        <v>79.28408502656583</v>
       </c>
       <c r="K8" t="n">
-        <v>81.3688010898322</v>
+        <v>81.36880108983217</v>
       </c>
       <c r="L8" t="n">
-        <v>54.80499735793246</v>
+        <v>54.80499735793244</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.66469732606491</v>
+        <v>85.66469732606475</v>
       </c>
       <c r="C9" t="n">
-        <v>52.14524681602403</v>
+        <v>52.14524681602387</v>
       </c>
       <c r="D9" t="n">
-        <v>76.51880515048755</v>
+        <v>76.51880515048738</v>
       </c>
       <c r="E9" t="n">
-        <v>52.14524681602403</v>
+        <v>52.14524681602387</v>
       </c>
       <c r="F9" t="n">
-        <v>52.14524681602403</v>
+        <v>52.14524681602387</v>
       </c>
       <c r="G9" t="n">
-        <v>82.2816249131133</v>
+        <v>82.28162491311323</v>
       </c>
       <c r="H9" t="n">
-        <v>70.22861055077956</v>
+        <v>70.22861055077951</v>
       </c>
       <c r="I9" t="n">
-        <v>52.14524681602403</v>
+        <v>52.14524681602387</v>
       </c>
       <c r="J9" t="n">
-        <v>83.98351772845226</v>
+        <v>83.9835177284521</v>
       </c>
       <c r="K9" t="n">
-        <v>84.82934858102344</v>
+        <v>84.82934858102334</v>
       </c>
       <c r="L9" t="n">
-        <v>74.03548656091388</v>
+        <v>86.29142972180347</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>265.9308307436858</v>
+        <v>265.9308307436855</v>
       </c>
       <c r="C2" t="n">
-        <v>217.8343081690804</v>
+        <v>217.8343081690805</v>
       </c>
       <c r="D2" t="n">
-        <v>909.5117132715359</v>
+        <v>909.5117132715357</v>
       </c>
       <c r="E2" t="n">
-        <v>217.8343081690804</v>
+        <v>217.8343081690805</v>
       </c>
       <c r="F2" t="n">
-        <v>217.8343081690804</v>
+        <v>217.8343081690805</v>
       </c>
       <c r="G2" t="n">
-        <v>420.445821814405</v>
+        <v>420.4458218144038</v>
       </c>
       <c r="H2" t="n">
-        <v>360.1082326665043</v>
+        <v>360.1082326665047</v>
       </c>
       <c r="I2" t="n">
-        <v>217.8343081690804</v>
+        <v>217.8343081690805</v>
       </c>
       <c r="J2" t="n">
-        <v>395.1325480538021</v>
+        <v>395.1325480538022</v>
       </c>
       <c r="K2" t="n">
         <v>215.2464833950579</v>
       </c>
       <c r="L2" t="n">
-        <v>183.8666675832683</v>
+        <v>1052.730164150326</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.7297014338904</v>
+        <v>33.72970143389044</v>
       </c>
       <c r="C3" t="n">
-        <v>32.01845253335524</v>
+        <v>32.01845253335527</v>
       </c>
       <c r="D3" t="n">
-        <v>33.7297014338904</v>
+        <v>33.72970143389044</v>
       </c>
       <c r="E3" t="n">
-        <v>32.12981469570171</v>
+        <v>32.12981469570179</v>
       </c>
       <c r="F3" t="n">
-        <v>32.1298146957017</v>
+        <v>32.12981469570179</v>
       </c>
       <c r="G3" t="n">
-        <v>33.56233968423329</v>
+        <v>33.56233968423327</v>
       </c>
       <c r="H3" t="n">
-        <v>33.7297014338904</v>
+        <v>33.72970143389044</v>
       </c>
       <c r="I3" t="n">
-        <v>32.66772664688639</v>
+        <v>32.66772664688642</v>
       </c>
       <c r="J3" t="n">
-        <v>33.7297014338904</v>
+        <v>33.72970143389044</v>
       </c>
       <c r="K3" t="n">
-        <v>33.7297014338904</v>
+        <v>33.72970143389044</v>
       </c>
       <c r="L3" t="n">
-        <v>33.7297014338904</v>
+        <v>33.72970143389044</v>
       </c>
     </row>
     <row r="4">
@@ -7726,34 +7726,34 @@
         <v>202.8904879390038</v>
       </c>
       <c r="C4" t="n">
-        <v>130.9857851743999</v>
+        <v>130.9857851744</v>
       </c>
       <c r="D4" t="n">
-        <v>133.7887871238026</v>
+        <v>133.7888512033063</v>
       </c>
       <c r="E4" t="n">
-        <v>121.4205794822474</v>
+        <v>121.4205794822475</v>
       </c>
       <c r="F4" t="n">
-        <v>131.4801035011089</v>
+        <v>131.4801035011088</v>
       </c>
       <c r="G4" t="n">
-        <v>132.3955682282587</v>
+        <v>202.7231261893463</v>
       </c>
       <c r="H4" t="n">
-        <v>201.3688368238592</v>
+        <v>201.368836823859</v>
       </c>
       <c r="I4" t="n">
         <v>201.8285131519996</v>
       </c>
       <c r="J4" t="n">
-        <v>137.8172108651421</v>
+        <v>137.8172108651422</v>
       </c>
       <c r="K4" t="n">
-        <v>132.2563412442653</v>
+        <v>132.2563412442652</v>
       </c>
       <c r="L4" t="n">
-        <v>132.8343104710651</v>
+        <v>132.834310471065</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.0155695339098</v>
+        <v>57.01556953390967</v>
       </c>
       <c r="C5" t="n">
-        <v>55.95359474690578</v>
+        <v>55.95359474690568</v>
       </c>
       <c r="D5" t="n">
-        <v>57.01510400497793</v>
+        <v>57.01510400497786</v>
       </c>
       <c r="E5" t="n">
-        <v>55.93936264589145</v>
+        <v>55.93936264589135</v>
       </c>
       <c r="F5" t="n">
-        <v>55.93936264589145</v>
+        <v>55.93936264589135</v>
       </c>
       <c r="G5" t="n">
-        <v>56.84820778425261</v>
+        <v>56.84820778425252</v>
       </c>
       <c r="H5" t="n">
-        <v>57.0155695339098</v>
+        <v>57.01556953390967</v>
       </c>
       <c r="I5" t="n">
-        <v>55.95359474690578</v>
+        <v>55.95359474690568</v>
       </c>
       <c r="J5" t="n">
-        <v>57.0155695339098</v>
+        <v>57.01556953390967</v>
       </c>
       <c r="K5" t="n">
-        <v>57.0155695339098</v>
+        <v>57.01556953390967</v>
       </c>
       <c r="L5" t="n">
-        <v>57.0155695339098</v>
+        <v>57.01556953390967</v>
       </c>
     </row>
     <row r="6">
@@ -7806,34 +7806,34 @@
         <v>125.2058614893286</v>
       </c>
       <c r="C6" t="n">
-        <v>184.3173874989527</v>
+        <v>184.3173874989524</v>
       </c>
       <c r="D6" t="n">
-        <v>197.8582076679446</v>
+        <v>197.8582076679447</v>
       </c>
       <c r="E6" t="n">
-        <v>167.8601846811341</v>
+        <v>167.8601846811338</v>
       </c>
       <c r="F6" t="n">
-        <v>126.0431201361576</v>
+        <v>126.0431201361577</v>
       </c>
       <c r="G6" t="n">
-        <v>185.2132246962863</v>
+        <v>185.2132246962859</v>
       </c>
       <c r="H6" t="n">
-        <v>185.3805864459427</v>
+        <v>185.3805864459425</v>
       </c>
       <c r="I6" t="n">
-        <v>184.3186116589391</v>
+        <v>184.318611658939</v>
       </c>
       <c r="J6" t="n">
-        <v>185.3924125084571</v>
+        <v>185.3924125084567</v>
       </c>
       <c r="K6" t="n">
-        <v>124.0880850790902</v>
+        <v>124.08808507909</v>
       </c>
       <c r="L6" t="n">
-        <v>248.2381183963271</v>
+        <v>248.2381183963267</v>
       </c>
     </row>
     <row r="7">
@@ -7843,34 +7843,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107.7447239379978</v>
+        <v>107.7447239379979</v>
       </c>
       <c r="C7" t="n">
-        <v>128.0450351721215</v>
+        <v>128.0450351721216</v>
       </c>
       <c r="D7" t="n">
         <v>129.1070207987558</v>
       </c>
       <c r="E7" t="n">
-        <v>152.6966611550728</v>
+        <v>152.6966611550727</v>
       </c>
       <c r="F7" t="n">
-        <v>128.0450280276257</v>
+        <v>128.0450280276258</v>
       </c>
       <c r="G7" t="n">
-        <v>128.9396482094683</v>
+        <v>128.9396482094682</v>
       </c>
       <c r="H7" t="n">
         <v>129.1070099591255</v>
       </c>
       <c r="I7" t="n">
-        <v>128.0450351721215</v>
+        <v>128.0450351721216</v>
       </c>
       <c r="J7" t="n">
         <v>129.1070099591255</v>
       </c>
       <c r="K7" t="n">
-        <v>102.2080758945706</v>
+        <v>116.7296221014275</v>
       </c>
       <c r="L7" t="n">
         <v>129.1070099591255</v>
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.20628853520014</v>
+        <v>83.20628853520012</v>
       </c>
       <c r="C8" t="n">
-        <v>50.11566601249942</v>
+        <v>50.11566601249941</v>
       </c>
       <c r="D8" t="n">
-        <v>65.60999020229774</v>
+        <v>65.60999020229769</v>
       </c>
       <c r="E8" t="n">
-        <v>50.11566601249942</v>
+        <v>50.11566601249941</v>
       </c>
       <c r="F8" t="n">
-        <v>50.11566601249942</v>
+        <v>50.11566601249941</v>
       </c>
       <c r="G8" t="n">
-        <v>79.23465703093832</v>
+        <v>79.23465703093828</v>
       </c>
       <c r="H8" t="n">
-        <v>81.52405890587141</v>
+        <v>81.52405890587139</v>
       </c>
       <c r="I8" t="n">
-        <v>50.11566601249942</v>
+        <v>50.11566601249941</v>
       </c>
       <c r="J8" t="n">
         <v>80.5230552296828</v>
       </c>
       <c r="K8" t="n">
-        <v>84.47067731035195</v>
+        <v>84.47067731035185</v>
       </c>
       <c r="L8" t="n">
-        <v>66.92237646503153</v>
+        <v>66.92237646503145</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.98844058592077</v>
+        <v>84.98844058592069</v>
       </c>
       <c r="C9" t="n">
-        <v>51.65324228202687</v>
+        <v>51.65324228202682</v>
       </c>
       <c r="D9" t="n">
-        <v>77.82217086475019</v>
+        <v>77.82217086475013</v>
       </c>
       <c r="E9" t="n">
-        <v>51.65324228202687</v>
+        <v>51.65324228202682</v>
       </c>
       <c r="F9" t="n">
-        <v>51.65324228202687</v>
+        <v>51.65324228202682</v>
       </c>
       <c r="G9" t="n">
-        <v>83.32842899262855</v>
+        <v>83.32842899262846</v>
       </c>
       <c r="H9" t="n">
-        <v>84.30917853436458</v>
+        <v>84.30917853436456</v>
       </c>
       <c r="I9" t="n">
-        <v>51.65324228202687</v>
+        <v>51.65324228202682</v>
       </c>
       <c r="J9" t="n">
-        <v>83.89837592077015</v>
+        <v>83.89837592077019</v>
       </c>
       <c r="K9" t="n">
-        <v>85.50359770616886</v>
+        <v>85.5035977061688</v>
       </c>
       <c r="L9" t="n">
-        <v>78.37196492033051</v>
+        <v>78.37196492033048</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
+++ b/Results/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>408.084405070633</v>
+        <v>89.08719837974188</v>
       </c>
       <c r="C2" t="n">
-        <v>375.2051300597033</v>
+        <v>55.0718406655544</v>
       </c>
       <c r="D2" t="n">
-        <v>1490.457482223189</v>
+        <v>90.18934244451401</v>
       </c>
       <c r="E2" t="n">
-        <v>375.2051300597033</v>
+        <v>55.0718406655544</v>
       </c>
       <c r="F2" t="n">
-        <v>375.2051300597033</v>
+        <v>55.0718406655544</v>
       </c>
       <c r="G2" t="n">
-        <v>836.7773601002324</v>
+        <v>89.39799648410961</v>
       </c>
       <c r="H2" t="n">
-        <v>2608.002443786355</v>
+        <v>91.07910972840651</v>
       </c>
       <c r="I2" t="n">
-        <v>375.2051300597033</v>
+        <v>55.0718406655544</v>
       </c>
       <c r="J2" t="n">
-        <v>704.2831307156397</v>
+        <v>89.35467908551625</v>
       </c>
       <c r="K2" t="n">
-        <v>523.5460598837706</v>
+        <v>89.19944303630744</v>
       </c>
       <c r="L2" t="n">
-        <v>2286.972212175716</v>
+        <v>88.97883380379557</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.65687052377778</v>
+        <v>89.69870772797344</v>
       </c>
       <c r="C3" t="n">
-        <v>33.68074942874816</v>
+        <v>55.18734334595216</v>
       </c>
       <c r="D3" t="n">
-        <v>35.65687052377778</v>
+        <v>89.69870772797344</v>
       </c>
       <c r="E3" t="n">
-        <v>33.82480616840537</v>
+        <v>55.18734334595216</v>
       </c>
       <c r="F3" t="n">
-        <v>33.82480616840537</v>
+        <v>55.18734334595216</v>
       </c>
       <c r="G3" t="n">
-        <v>35.48235461852929</v>
+        <v>89.59176980032539</v>
       </c>
       <c r="H3" t="n">
-        <v>35.65687052377778</v>
+        <v>89.69870772797344</v>
       </c>
       <c r="I3" t="n">
-        <v>34.54931642253398</v>
+        <v>55.18734334595216</v>
       </c>
       <c r="J3" t="n">
-        <v>35.65687052377778</v>
+        <v>89.69870772797344</v>
       </c>
       <c r="K3" t="n">
-        <v>35.65687052377778</v>
+        <v>89.69870772797344</v>
       </c>
       <c r="L3" t="n">
-        <v>35.65687052377778</v>
+        <v>89.69870772797344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>149.8979535870586</v>
+        <v>408.0844050706337</v>
       </c>
       <c r="C4" t="n">
-        <v>147.9249159232158</v>
+        <v>375.2051300597042</v>
       </c>
       <c r="D4" t="n">
-        <v>151.5226933284323</v>
+        <v>1490.45748222319</v>
       </c>
       <c r="E4" t="n">
-        <v>136.9025460103956</v>
+        <v>375.2051300597042</v>
       </c>
       <c r="F4" t="n">
-        <v>148.7729653216366</v>
+        <v>375.2051300597042</v>
       </c>
       <c r="G4" t="n">
-        <v>232.6487454311798</v>
+        <v>836.7773601002324</v>
       </c>
       <c r="H4" t="n">
-        <v>231.510278915136</v>
+        <v>2608.002443786352</v>
       </c>
       <c r="I4" t="n">
-        <v>231.7157072351844</v>
+        <v>375.2051300597042</v>
       </c>
       <c r="J4" t="n">
-        <v>230.8249235454228</v>
+        <v>704.2831307156395</v>
       </c>
       <c r="K4" t="n">
-        <v>149.5989656583111</v>
+        <v>523.5460598837708</v>
       </c>
       <c r="L4" t="n">
-        <v>150.5138706559962</v>
+        <v>2286.972212175718</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.83206741890935</v>
+        <v>35.65687052377777</v>
       </c>
       <c r="C5" t="n">
-        <v>63.72451331766555</v>
+        <v>33.68074942874817</v>
       </c>
       <c r="D5" t="n">
-        <v>64.8315037871733</v>
+        <v>35.65687052377777</v>
       </c>
       <c r="E5" t="n">
-        <v>63.71044632745474</v>
+        <v>33.82480616840535</v>
       </c>
       <c r="F5" t="n">
-        <v>63.71044632745474</v>
+        <v>33.82480616840534</v>
       </c>
       <c r="G5" t="n">
-        <v>64.65755151366092</v>
+        <v>35.4823546185293</v>
       </c>
       <c r="H5" t="n">
-        <v>64.83206741890935</v>
+        <v>35.65687052377777</v>
       </c>
       <c r="I5" t="n">
-        <v>63.72451331766555</v>
+        <v>34.54931642253394</v>
       </c>
       <c r="J5" t="n">
-        <v>64.83206741890935</v>
+        <v>35.65687052377777</v>
       </c>
       <c r="K5" t="n">
-        <v>64.83206741890935</v>
+        <v>35.65687052377777</v>
       </c>
       <c r="L5" t="n">
-        <v>64.83206741890935</v>
+        <v>35.65687052377777</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>144.9051130134647</v>
+        <v>149.8979535870588</v>
       </c>
       <c r="C6" t="n">
-        <v>216.0186607187701</v>
+        <v>147.9249159232162</v>
       </c>
       <c r="D6" t="n">
-        <v>232.1000195980187</v>
+        <v>151.5226933284325</v>
       </c>
       <c r="E6" t="n">
-        <v>196.2669723852203</v>
+        <v>136.9025460103956</v>
       </c>
       <c r="F6" t="n">
-        <v>146.0787559854716</v>
+        <v>148.7729653216368</v>
       </c>
       <c r="G6" t="n">
-        <v>216.9502816377243</v>
+        <v>232.6487454311798</v>
       </c>
       <c r="H6" t="n">
-        <v>217.1247975429769</v>
+        <v>231.510278915136</v>
       </c>
       <c r="I6" t="n">
-        <v>216.0172434417289</v>
+        <v>231.7157072351842</v>
       </c>
       <c r="J6" t="n">
-        <v>217.1389907853381</v>
+        <v>230.8249235454228</v>
       </c>
       <c r="K6" t="n">
-        <v>143.5635952952725</v>
+        <v>149.5989656583115</v>
       </c>
       <c r="L6" t="n">
-        <v>292.5642969504912</v>
+        <v>150.5138706559962</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142.750995554981</v>
+        <v>64.83206741890935</v>
       </c>
       <c r="C7" t="n">
-        <v>172.4815900215825</v>
+        <v>63.7245133176655</v>
       </c>
       <c r="D7" t="n">
-        <v>173.5891380332333</v>
+        <v>64.8315037871732</v>
       </c>
       <c r="E7" t="n">
-        <v>208.0681078942028</v>
+        <v>63.7104463274547</v>
       </c>
       <c r="F7" t="n">
-        <v>172.4815530652096</v>
+        <v>63.7104463274547</v>
       </c>
       <c r="G7" t="n">
-        <v>173.4146282175779</v>
+        <v>64.65755151366086</v>
       </c>
       <c r="H7" t="n">
-        <v>173.5891441228264</v>
+        <v>64.83206741890935</v>
       </c>
       <c r="I7" t="n">
-        <v>172.4815900215825</v>
+        <v>63.7245133176655</v>
       </c>
       <c r="J7" t="n">
-        <v>173.5891441228264</v>
+        <v>64.83206741890935</v>
       </c>
       <c r="K7" t="n">
-        <v>134.7584120641641</v>
+        <v>64.83206741890935</v>
       </c>
       <c r="L7" t="n">
-        <v>173.5891441228264</v>
+        <v>64.83206741890935</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.80562123641091</v>
+        <v>144.9051130134646</v>
       </c>
       <c r="C8" t="n">
-        <v>49.11242631413115</v>
+        <v>216.0186607187703</v>
       </c>
       <c r="D8" t="n">
-        <v>59.72123136933297</v>
+        <v>232.1000195980189</v>
       </c>
       <c r="E8" t="n">
-        <v>49.11242631413115</v>
+        <v>196.2669723852202</v>
       </c>
       <c r="F8" t="n">
-        <v>49.11242631413115</v>
+        <v>146.0787559854715</v>
       </c>
       <c r="G8" t="n">
-        <v>74.02051779762998</v>
+        <v>216.9502816377243</v>
       </c>
       <c r="H8" t="n">
-        <v>41.98776974610143</v>
+        <v>217.1247975429769</v>
       </c>
       <c r="I8" t="n">
-        <v>49.11242631413115</v>
+        <v>216.0172434417289</v>
       </c>
       <c r="J8" t="n">
-        <v>77.29911592075361</v>
+        <v>217.1389907853382</v>
       </c>
       <c r="K8" t="n">
-        <v>80.46330989216936</v>
+        <v>143.5635952952724</v>
       </c>
       <c r="L8" t="n">
-        <v>85.14966229775783</v>
+        <v>292.5642969504914</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>142.750995554981</v>
+      </c>
+      <c r="C9" t="n">
+        <v>172.4815900215825</v>
+      </c>
+      <c r="D9" t="n">
+        <v>173.5891380332333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>208.0681078942027</v>
+      </c>
+      <c r="F9" t="n">
+        <v>172.4815530652097</v>
+      </c>
+      <c r="G9" t="n">
+        <v>173.414628217578</v>
+      </c>
+      <c r="H9" t="n">
+        <v>173.5891441228265</v>
+      </c>
+      <c r="I9" t="n">
+        <v>172.4815900215825</v>
+      </c>
+      <c r="J9" t="n">
+        <v>173.5891441228265</v>
+      </c>
+      <c r="K9" t="n">
+        <v>134.7584120641642</v>
+      </c>
+      <c r="L9" t="n">
+        <v>173.5891441228265</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>82.80562123641099</v>
+      </c>
+      <c r="C10" t="n">
+        <v>49.11242631413114</v>
+      </c>
+      <c r="D10" t="n">
+        <v>59.72123136933303</v>
+      </c>
+      <c r="E10" t="n">
+        <v>49.11242631413114</v>
+      </c>
+      <c r="F10" t="n">
+        <v>49.11242631413114</v>
+      </c>
+      <c r="G10" t="n">
+        <v>74.02051779762998</v>
+      </c>
+      <c r="H10" t="n">
+        <v>41.98776974610151</v>
+      </c>
+      <c r="I10" t="n">
+        <v>49.11242631413114</v>
+      </c>
+      <c r="J10" t="n">
+        <v>77.29911592075366</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80.46330989216936</v>
+      </c>
+      <c r="L10" t="n">
+        <v>85.14966229775793</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>85.95082205911766</v>
-      </c>
-      <c r="C9" t="n">
-        <v>52.30773405646393</v>
-      </c>
-      <c r="D9" t="n">
-        <v>76.54949516878368</v>
-      </c>
-      <c r="E9" t="n">
-        <v>52.30773405646393</v>
-      </c>
-      <c r="F9" t="n">
-        <v>52.30773405646393</v>
-      </c>
-      <c r="G9" t="n">
-        <v>82.31302720024728</v>
-      </c>
-      <c r="H9" t="n">
-        <v>69.37048090091683</v>
-      </c>
-      <c r="I9" t="n">
-        <v>52.30773405646393</v>
-      </c>
-      <c r="J9" t="n">
-        <v>83.71282529807674</v>
-      </c>
-      <c r="K9" t="n">
-        <v>84.99730758954985</v>
-      </c>
-      <c r="L9" t="n">
-        <v>72.41003668683855</v>
+      <c r="B11" t="n">
+        <v>85.95082205911768</v>
+      </c>
+      <c r="C11" t="n">
+        <v>52.30773405646394</v>
+      </c>
+      <c r="D11" t="n">
+        <v>76.54949516878374</v>
+      </c>
+      <c r="E11" t="n">
+        <v>52.30773405646394</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52.30773405646394</v>
+      </c>
+      <c r="G11" t="n">
+        <v>82.31302720024735</v>
+      </c>
+      <c r="H11" t="n">
+        <v>69.37048090091689</v>
+      </c>
+      <c r="I11" t="n">
+        <v>52.30773405646394</v>
+      </c>
+      <c r="J11" t="n">
+        <v>83.71282529807682</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.99730758954992</v>
+      </c>
+      <c r="L11" t="n">
+        <v>72.41003668683862</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249.9260087418482</v>
+        <v>86.33248326093258</v>
       </c>
       <c r="C2" t="n">
-        <v>223.4856829529589</v>
+        <v>52.69256537733901</v>
       </c>
       <c r="D2" t="n">
-        <v>232.0214582845723</v>
+        <v>86.30741140370095</v>
       </c>
       <c r="E2" t="n">
-        <v>223.4856829529589</v>
+        <v>52.69256537733901</v>
       </c>
       <c r="F2" t="n">
-        <v>223.4856829529589</v>
+        <v>52.69256537733901</v>
       </c>
       <c r="G2" t="n">
-        <v>240.3477657232995</v>
+        <v>86.27609440910703</v>
       </c>
       <c r="H2" t="n">
-        <v>244.536836761279</v>
+        <v>86.29949248704673</v>
       </c>
       <c r="I2" t="n">
-        <v>223.4856829529589</v>
+        <v>52.69256537733901</v>
       </c>
       <c r="J2" t="n">
-        <v>343.8415473830702</v>
+        <v>86.42456403286191</v>
       </c>
       <c r="K2" t="n">
-        <v>176.9804209411032</v>
+        <v>86.24176569251954</v>
       </c>
       <c r="L2" t="n">
-        <v>191.7092692051725</v>
+        <v>86.23559220209006</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.31081576366508</v>
+        <v>87.04449815292142</v>
       </c>
       <c r="C3" t="n">
-        <v>31.79568093463136</v>
+        <v>52.9087493894964</v>
       </c>
       <c r="D3" t="n">
-        <v>33.31081576366508</v>
+        <v>87.04449815292142</v>
       </c>
       <c r="E3" t="n">
-        <v>31.89424241017442</v>
+        <v>52.9087493894964</v>
       </c>
       <c r="F3" t="n">
-        <v>31.89424241017441</v>
+        <v>52.9087493894964</v>
       </c>
       <c r="G3" t="n">
-        <v>33.15135328481121</v>
+        <v>87.00557963644373</v>
       </c>
       <c r="H3" t="n">
-        <v>33.31081576366508</v>
+        <v>87.04449815292142</v>
       </c>
       <c r="I3" t="n">
-        <v>32.2992502794192</v>
+        <v>52.9087493894964</v>
       </c>
       <c r="J3" t="n">
-        <v>33.31081576366508</v>
+        <v>87.04449815292142</v>
       </c>
       <c r="K3" t="n">
-        <v>33.31081576366508</v>
+        <v>87.04449815292142</v>
       </c>
       <c r="L3" t="n">
-        <v>33.31081576366508</v>
+        <v>87.04449815292142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.7917874784089</v>
+        <v>249.9260087418476</v>
       </c>
       <c r="C4" t="n">
-        <v>130.568532035825</v>
+        <v>223.485682952959</v>
       </c>
       <c r="D4" t="n">
-        <v>199.2634145806902</v>
+        <v>232.0214582845723</v>
       </c>
       <c r="E4" t="n">
-        <v>121.0156238260924</v>
+        <v>223.485682952959</v>
       </c>
       <c r="F4" t="n">
-        <v>130.8055474109712</v>
+        <v>223.485682952959</v>
       </c>
       <c r="G4" t="n">
-        <v>200.7204398214126</v>
+        <v>240.3477657232973</v>
       </c>
       <c r="H4" t="n">
-        <v>199.3373857826484</v>
+        <v>244.5368367612791</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7802219941628</v>
+        <v>223.485682952959</v>
       </c>
       <c r="J4" t="n">
-        <v>137.0134072911319</v>
+        <v>343.8415473830696</v>
       </c>
       <c r="K4" t="n">
-        <v>131.653922565045</v>
+        <v>176.9804209411031</v>
       </c>
       <c r="L4" t="n">
-        <v>131.8123512196127</v>
+        <v>191.7092692051726</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.84331549644753</v>
+        <v>33.31081576366503</v>
       </c>
       <c r="C5" t="n">
-        <v>54.83175001220153</v>
+        <v>31.7956809346313</v>
       </c>
       <c r="D5" t="n">
-        <v>55.84285180090761</v>
+        <v>33.31081576366503</v>
       </c>
       <c r="E5" t="n">
-        <v>54.82123796443658</v>
+        <v>31.89424241017434</v>
       </c>
       <c r="F5" t="n">
-        <v>54.82123796443658</v>
+        <v>31.89424241017434</v>
       </c>
       <c r="G5" t="n">
-        <v>55.68385301759379</v>
+        <v>33.15135328481114</v>
       </c>
       <c r="H5" t="n">
-        <v>55.84331549644753</v>
+        <v>33.31081576366503</v>
       </c>
       <c r="I5" t="n">
-        <v>54.83175001220153</v>
+        <v>32.29925027941913</v>
       </c>
       <c r="J5" t="n">
-        <v>55.84331549644753</v>
+        <v>33.31081576366503</v>
       </c>
       <c r="K5" t="n">
-        <v>55.84331549644753</v>
+        <v>33.31081576366503</v>
       </c>
       <c r="L5" t="n">
-        <v>55.84331549644753</v>
+        <v>33.31081576366503</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123.2157281563321</v>
+        <v>131.7917874784087</v>
       </c>
       <c r="C6" t="n">
-        <v>181.2219897707594</v>
+        <v>130.5685320358247</v>
       </c>
       <c r="D6" t="n">
-        <v>194.4687456562291</v>
+        <v>199.2634145806903</v>
       </c>
       <c r="E6" t="n">
-        <v>165.0814095772338</v>
+        <v>121.0156238260926</v>
       </c>
       <c r="F6" t="n">
-        <v>124.0688756288237</v>
+        <v>130.805547410971</v>
       </c>
       <c r="G6" t="n">
-        <v>182.0719885812205</v>
+        <v>200.7204398214125</v>
       </c>
       <c r="H6" t="n">
-        <v>182.2314510600754</v>
+        <v>199.3373857826484</v>
       </c>
       <c r="I6" t="n">
-        <v>181.2198855758284</v>
+        <v>130.7802219941628</v>
       </c>
       <c r="J6" t="n">
-        <v>182.2430493458924</v>
+        <v>137.0134072911317</v>
       </c>
       <c r="K6" t="n">
-        <v>122.1194808042108</v>
+        <v>131.6539225650449</v>
       </c>
       <c r="L6" t="n">
-        <v>243.8783084524514</v>
+        <v>131.8123512196124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100.068074952067</v>
+        <v>55.84331549644753</v>
       </c>
       <c r="C7" t="n">
-        <v>118.3417052209387</v>
+        <v>54.83175001220153</v>
       </c>
       <c r="D7" t="n">
-        <v>119.3532772737971</v>
+        <v>55.84285180090751</v>
       </c>
       <c r="E7" t="n">
-        <v>140.5964120108708</v>
+        <v>54.82123796443653</v>
       </c>
       <c r="F7" t="n">
-        <v>118.3417003130383</v>
+        <v>54.82123796443653</v>
       </c>
       <c r="G7" t="n">
-        <v>119.1938082263311</v>
+        <v>55.68385301759354</v>
       </c>
       <c r="H7" t="n">
-        <v>119.3532707051843</v>
+        <v>55.84331549644753</v>
       </c>
       <c r="I7" t="n">
-        <v>118.3417052209387</v>
+        <v>54.83175001220153</v>
       </c>
       <c r="J7" t="n">
-        <v>119.3532707051843</v>
+        <v>55.84331549644753</v>
       </c>
       <c r="K7" t="n">
-        <v>108.1793553097614</v>
+        <v>55.84331549644753</v>
       </c>
       <c r="L7" t="n">
-        <v>119.3532707051843</v>
+        <v>55.84331549644753</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.84379479190881</v>
+        <v>123.2157281563321</v>
       </c>
       <c r="C8" t="n">
-        <v>49.47093784397973</v>
+        <v>181.2219897707596</v>
       </c>
       <c r="D8" t="n">
-        <v>83.37140864248084</v>
+        <v>194.4687456562287</v>
       </c>
       <c r="E8" t="n">
-        <v>49.47093784397973</v>
+        <v>165.0814095772337</v>
       </c>
       <c r="F8" t="n">
-        <v>49.47093784397973</v>
+        <v>124.0688756288234</v>
       </c>
       <c r="G8" t="n">
-        <v>83.19051021015085</v>
+        <v>182.0719885812201</v>
       </c>
       <c r="H8" t="n">
-        <v>83.60429983088339</v>
+        <v>182.2314510600753</v>
       </c>
       <c r="I8" t="n">
-        <v>49.47093784397973</v>
+        <v>181.2198855758283</v>
       </c>
       <c r="J8" t="n">
-        <v>80.96316290695047</v>
+        <v>182.2430493458924</v>
       </c>
       <c r="K8" t="n">
-        <v>84.74790920829727</v>
+        <v>122.1194808042107</v>
       </c>
       <c r="L8" t="n">
-        <v>84.86462646123537</v>
+        <v>243.8783084524509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100.0680749520666</v>
+      </c>
+      <c r="C9" t="n">
+        <v>118.3417052209387</v>
+      </c>
+      <c r="D9" t="n">
+        <v>119.353277273798</v>
+      </c>
+      <c r="E9" t="n">
+        <v>140.5964120108703</v>
+      </c>
+      <c r="F9" t="n">
+        <v>118.3417003130387</v>
+      </c>
+      <c r="G9" t="n">
+        <v>119.1938082263306</v>
+      </c>
+      <c r="H9" t="n">
+        <v>119.3532707051847</v>
+      </c>
+      <c r="I9" t="n">
+        <v>118.3417052209387</v>
+      </c>
+      <c r="J9" t="n">
+        <v>119.3532707051847</v>
+      </c>
+      <c r="K9" t="n">
+        <v>108.1793553097612</v>
+      </c>
+      <c r="L9" t="n">
+        <v>119.3532707051847</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>82.84379479190885</v>
+      </c>
+      <c r="C10" t="n">
+        <v>49.4709378439797</v>
+      </c>
+      <c r="D10" t="n">
+        <v>83.37140864248087</v>
+      </c>
+      <c r="E10" t="n">
+        <v>49.4709378439797</v>
+      </c>
+      <c r="F10" t="n">
+        <v>49.4709378439797</v>
+      </c>
+      <c r="G10" t="n">
+        <v>83.19051021015096</v>
+      </c>
+      <c r="H10" t="n">
+        <v>83.60429983088351</v>
+      </c>
+      <c r="I10" t="n">
+        <v>49.4709378439797</v>
+      </c>
+      <c r="J10" t="n">
+        <v>80.96316290695049</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.74790920829747</v>
+      </c>
+      <c r="L10" t="n">
+        <v>84.86462646123557</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>84.42114984482448</v>
-      </c>
-      <c r="C9" t="n">
-        <v>51.12835016847361</v>
-      </c>
-      <c r="D9" t="n">
-        <v>84.63614397100858</v>
-      </c>
-      <c r="E9" t="n">
-        <v>51.12835016847361</v>
-      </c>
-      <c r="F9" t="n">
-        <v>51.12835016847361</v>
-      </c>
-      <c r="G9" t="n">
-        <v>84.5402256622389</v>
-      </c>
-      <c r="H9" t="n">
-        <v>84.73419128725779</v>
-      </c>
-      <c r="I9" t="n">
-        <v>51.12835016847361</v>
-      </c>
-      <c r="J9" t="n">
-        <v>83.65753711587948</v>
-      </c>
-      <c r="K9" t="n">
-        <v>85.19681040392088</v>
-      </c>
-      <c r="L9" t="n">
-        <v>85.2459435446731</v>
+      <c r="B11" t="n">
+        <v>84.42114984482451</v>
+      </c>
+      <c r="C11" t="n">
+        <v>51.1283501684736</v>
+      </c>
+      <c r="D11" t="n">
+        <v>84.63614397100866</v>
+      </c>
+      <c r="E11" t="n">
+        <v>51.1283501684736</v>
+      </c>
+      <c r="F11" t="n">
+        <v>51.1283501684736</v>
+      </c>
+      <c r="G11" t="n">
+        <v>84.540225662239</v>
+      </c>
+      <c r="H11" t="n">
+        <v>84.7341912872579</v>
+      </c>
+      <c r="I11" t="n">
+        <v>51.1283501684736</v>
+      </c>
+      <c r="J11" t="n">
+        <v>83.65753711587955</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.19681040392091</v>
+      </c>
+      <c r="L11" t="n">
+        <v>85.24594354467327</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>153.805889901716</v>
+        <v>33.40145140526609</v>
       </c>
       <c r="C2" t="n">
-        <v>192.7077995843784</v>
+        <v>28.74507043581102</v>
       </c>
       <c r="D2" t="n">
-        <v>835.2240548025441</v>
+        <v>41.31137580257312</v>
       </c>
       <c r="E2" t="n">
-        <v>247.2262879838231</v>
+        <v>45.80984303845523</v>
       </c>
       <c r="F2" t="n">
-        <v>247.2262879838231</v>
+        <v>45.80984303845523</v>
       </c>
       <c r="G2" t="n">
-        <v>484.2795172253802</v>
+        <v>75.90843828229201</v>
       </c>
       <c r="H2" t="n">
-        <v>1242.011838424447</v>
+        <v>41.62697020185193</v>
       </c>
       <c r="I2" t="n">
-        <v>247.2262879838231</v>
+        <v>45.80984303845523</v>
       </c>
       <c r="J2" t="n">
-        <v>550.1007226345787</v>
+        <v>76.04595713162814</v>
       </c>
       <c r="K2" t="n">
-        <v>336.540506871771</v>
+        <v>148.7869607698636</v>
       </c>
       <c r="L2" t="n">
-        <v>539.8332400166147</v>
+        <v>34.29860337162852</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.53663371949874</v>
+        <v>33.35661195148315</v>
       </c>
       <c r="C3" t="n">
-        <v>33.41185162749314</v>
+        <v>28.6217843033294</v>
       </c>
       <c r="D3" t="n">
-        <v>34.53663371949872</v>
+        <v>40.66299568798398</v>
       </c>
       <c r="E3" t="n">
-        <v>32.92683665681617</v>
+        <v>45.89693439221412</v>
       </c>
       <c r="F3" t="n">
-        <v>32.92683665681617</v>
+        <v>45.89693439221412</v>
       </c>
       <c r="G3" t="n">
-        <v>34.37271041065235</v>
+        <v>76.21591075381096</v>
       </c>
       <c r="H3" t="n">
-        <v>34.53663371949874</v>
+        <v>40.66299568798398</v>
       </c>
       <c r="I3" t="n">
-        <v>33.49841119510494</v>
+        <v>45.89693439221412</v>
       </c>
       <c r="J3" t="n">
-        <v>34.53663371949874</v>
+        <v>76.29362166356027</v>
       </c>
       <c r="K3" t="n">
-        <v>34.53663371949872</v>
+        <v>150.4077643485537</v>
       </c>
       <c r="L3" t="n">
-        <v>34.53663371949872</v>
+        <v>33.93635794256128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>213.0214130910863</v>
+        <v>153.8058899017161</v>
       </c>
       <c r="C4" t="n">
-        <v>137.8839071480099</v>
+        <v>192.7077995843798</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5189856248378</v>
+        <v>835.2240548025454</v>
       </c>
       <c r="E4" t="n">
-        <v>126.9957195618488</v>
+        <v>247.2262879838232</v>
       </c>
       <c r="F4" t="n">
-        <v>137.6403108413481</v>
+        <v>247.2262879838232</v>
       </c>
       <c r="G4" t="n">
-        <v>138.5312395566855</v>
+        <v>484.2795172253836</v>
       </c>
       <c r="H4" t="n">
-        <v>212.8123869709358</v>
+        <v>1242.011838424449</v>
       </c>
       <c r="I4" t="n">
-        <v>137.656940341138</v>
+        <v>247.2262879838232</v>
       </c>
       <c r="J4" t="n">
-        <v>211.6303860402627</v>
+        <v>550.100722634579</v>
       </c>
       <c r="K4" t="n">
-        <v>138.5436564598756</v>
+        <v>336.540506871771</v>
       </c>
       <c r="L4" t="n">
-        <v>138.7997071230558</v>
+        <v>539.8332400166149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.53325099782839</v>
+        <v>34.53663371949866</v>
       </c>
       <c r="C5" t="n">
-        <v>60.42451780104112</v>
+        <v>33.41185162749314</v>
       </c>
       <c r="D5" t="n">
-        <v>60.53285247562703</v>
+        <v>34.53663371949866</v>
       </c>
       <c r="E5" t="n">
-        <v>59.49692079225292</v>
+        <v>32.92683665681615</v>
       </c>
       <c r="F5" t="n">
-        <v>59.49692079225292</v>
+        <v>32.92683665681616</v>
       </c>
       <c r="G5" t="n">
-        <v>60.36932768898187</v>
+        <v>34.37271041065224</v>
       </c>
       <c r="H5" t="n">
-        <v>60.53325099782839</v>
+        <v>34.53663371949866</v>
       </c>
       <c r="I5" t="n">
-        <v>59.49502847343457</v>
+        <v>33.49841119510494</v>
       </c>
       <c r="J5" t="n">
-        <v>60.53325099782839</v>
+        <v>34.53663371949866</v>
       </c>
       <c r="K5" t="n">
-        <v>60.53325099782839</v>
+        <v>34.53663371949866</v>
       </c>
       <c r="L5" t="n">
-        <v>60.53325099782839</v>
+        <v>34.53663371949866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>133.863287378185</v>
+        <v>213.0214130910862</v>
       </c>
       <c r="C6" t="n">
-        <v>199.4267306516369</v>
+        <v>137.8839071480098</v>
       </c>
       <c r="D6" t="n">
-        <v>213.1346523504221</v>
+        <v>139.5189856248378</v>
       </c>
       <c r="E6" t="n">
-        <v>180.5389498283029</v>
+        <v>126.9957195618487</v>
       </c>
       <c r="F6" t="n">
-        <v>134.9076558728364</v>
+        <v>137.6403108413482</v>
       </c>
       <c r="G6" t="n">
-        <v>199.3563295361439</v>
+        <v>138.5312395566856</v>
       </c>
       <c r="H6" t="n">
-        <v>199.5202528450558</v>
+        <v>212.8123869709359</v>
       </c>
       <c r="I6" t="n">
-        <v>198.4820303205967</v>
+        <v>137.6569403411382</v>
       </c>
       <c r="J6" t="n">
-        <v>199.5331563247214</v>
+        <v>211.6303860402627</v>
       </c>
       <c r="K6" t="n">
-        <v>132.6436755357947</v>
+        <v>138.5436564598757</v>
       </c>
       <c r="L6" t="n">
-        <v>268.1044434260329</v>
+        <v>138.7997071230557</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118.3131016527689</v>
+        <v>60.53325099782844</v>
       </c>
       <c r="C7" t="n">
-        <v>142.4813102394505</v>
+        <v>60.42451780104115</v>
       </c>
       <c r="D7" t="n">
-        <v>142.5900466263031</v>
+        <v>60.53285247562707</v>
       </c>
       <c r="E7" t="n">
-        <v>169.5668783455391</v>
+        <v>59.49692079225299</v>
       </c>
       <c r="F7" t="n">
-        <v>141.5518037007326</v>
+        <v>59.49692079225299</v>
       </c>
       <c r="G7" t="n">
-        <v>142.4261201273912</v>
+        <v>60.36932768898187</v>
       </c>
       <c r="H7" t="n">
-        <v>142.5900434362378</v>
+        <v>60.53325099782844</v>
       </c>
       <c r="I7" t="n">
-        <v>141.5518209118439</v>
+        <v>59.4950284734346</v>
       </c>
       <c r="J7" t="n">
-        <v>142.5900434362378</v>
+        <v>60.53325099782844</v>
       </c>
       <c r="K7" t="n">
-        <v>128.5238893657265</v>
+        <v>60.53325099782844</v>
       </c>
       <c r="L7" t="n">
-        <v>142.5900434362378</v>
+        <v>60.53325099782844</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.84334298957436</v>
+        <v>133.8632873781848</v>
       </c>
       <c r="C8" t="n">
-        <v>26.23303106593429</v>
+        <v>199.4267306516371</v>
       </c>
       <c r="D8" t="n">
-        <v>23.33283459290335</v>
+        <v>213.134652350422</v>
       </c>
       <c r="E8" t="n">
-        <v>42.17695367714153</v>
+        <v>180.5389498283029</v>
       </c>
       <c r="F8" t="n">
-        <v>42.17695367714153</v>
+        <v>134.907655872836</v>
       </c>
       <c r="G8" t="n">
-        <v>67.26711411372141</v>
+        <v>199.3563295361438</v>
       </c>
       <c r="H8" t="n">
-        <v>17.16958251464334</v>
+        <v>199.5202528450556</v>
       </c>
       <c r="I8" t="n">
-        <v>42.17695367714153</v>
+        <v>198.4820303205966</v>
       </c>
       <c r="J8" t="n">
-        <v>66.13111884643577</v>
+        <v>199.5331563247209</v>
       </c>
       <c r="K8" t="n">
-        <v>144.6296931928793</v>
+        <v>132.6436755357946</v>
       </c>
       <c r="L8" t="n">
-        <v>24.95351044707931</v>
+        <v>268.1044434260322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>118.3131016527691</v>
+      </c>
+      <c r="C9" t="n">
+        <v>142.4813102394505</v>
+      </c>
+      <c r="D9" t="n">
+        <v>142.5900466263031</v>
+      </c>
+      <c r="E9" t="n">
+        <v>169.5668783455394</v>
+      </c>
+      <c r="F9" t="n">
+        <v>141.5518037007329</v>
+      </c>
+      <c r="G9" t="n">
+        <v>142.4261201273912</v>
+      </c>
+      <c r="H9" t="n">
+        <v>142.5900434362377</v>
+      </c>
+      <c r="I9" t="n">
+        <v>141.5518209118441</v>
+      </c>
+      <c r="J9" t="n">
+        <v>142.5900434362377</v>
+      </c>
+      <c r="K9" t="n">
+        <v>128.5238893657265</v>
+      </c>
+      <c r="L9" t="n">
+        <v>142.5900434362377</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>30.84334298957438</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.23303106593429</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23.33283459290334</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42.17695367714153</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.17695367714153</v>
+      </c>
+      <c r="G10" t="n">
+        <v>67.26711411372135</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17.1695825146433</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42.17695367714153</v>
+      </c>
+      <c r="J10" t="n">
+        <v>66.13111884643585</v>
+      </c>
+      <c r="K10" t="n">
+        <v>144.6296931928793</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24.95351044707932</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>32.25790601828464</v>
       </c>
-      <c r="C9" t="n">
-        <v>27.65818010029134</v>
-      </c>
-      <c r="D9" t="n">
-        <v>33.42609727636486</v>
-      </c>
-      <c r="E9" t="n">
-        <v>44.11723995822203</v>
-      </c>
-      <c r="F9" t="n">
-        <v>44.11723995822203</v>
-      </c>
-      <c r="G9" t="n">
-        <v>71.83670729292845</v>
-      </c>
-      <c r="H9" t="n">
-        <v>30.93739233891642</v>
-      </c>
-      <c r="I9" t="n">
-        <v>44.11723995822203</v>
-      </c>
-      <c r="J9" t="n">
-        <v>71.42198596386154</v>
-      </c>
-      <c r="K9" t="n">
-        <v>146.1579199804116</v>
-      </c>
-      <c r="L9" t="n">
-        <v>30.21137913454776</v>
+      <c r="C11" t="n">
+        <v>27.65818010029133</v>
+      </c>
+      <c r="D11" t="n">
+        <v>33.42609727636487</v>
+      </c>
+      <c r="E11" t="n">
+        <v>44.11723995822205</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.11723995822205</v>
+      </c>
+      <c r="G11" t="n">
+        <v>71.83670729292844</v>
+      </c>
+      <c r="H11" t="n">
+        <v>30.9373923389164</v>
+      </c>
+      <c r="I11" t="n">
+        <v>44.11723995822205</v>
+      </c>
+      <c r="J11" t="n">
+        <v>71.42198596386159</v>
+      </c>
+      <c r="K11" t="n">
+        <v>146.1579199804114</v>
+      </c>
+      <c r="L11" t="n">
+        <v>30.21137913454777</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>119.5510801883929</v>
+        <v>33.10074472994638</v>
       </c>
       <c r="C2" t="n">
-        <v>188.7288202762851</v>
+        <v>28.5702824538664</v>
       </c>
       <c r="D2" t="n">
-        <v>597.8941965709472</v>
+        <v>40.68205660176061</v>
       </c>
       <c r="E2" t="n">
-        <v>187.3913349313373</v>
+        <v>45.52746028590076</v>
       </c>
       <c r="F2" t="n">
-        <v>187.3913349313373</v>
+        <v>45.52746028590076</v>
       </c>
       <c r="G2" t="n">
-        <v>330.2349855313158</v>
+        <v>75.45231481758259</v>
       </c>
       <c r="H2" t="n">
-        <v>696.423640509779</v>
+        <v>40.72049269184059</v>
       </c>
       <c r="I2" t="n">
-        <v>187.3913349313373</v>
+        <v>45.52746028590076</v>
       </c>
       <c r="J2" t="n">
-        <v>371.3087594552593</v>
+        <v>75.51363513422372</v>
       </c>
       <c r="K2" t="n">
-        <v>215.5757448959242</v>
+        <v>148.2808403108573</v>
       </c>
       <c r="L2" t="n">
-        <v>247.5610727203473</v>
+        <v>33.7358311380313</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.23209715581746</v>
+        <v>33.08550465615576</v>
       </c>
       <c r="C3" t="n">
-        <v>33.17807866077258</v>
+        <v>28.44123870976441</v>
       </c>
       <c r="D3" t="n">
-        <v>34.23209715581746</v>
+        <v>40.25653954716553</v>
       </c>
       <c r="E3" t="n">
-        <v>32.83400708082713</v>
+        <v>45.66845715049131</v>
       </c>
       <c r="F3" t="n">
-        <v>32.83400708082713</v>
+        <v>45.66845715049131</v>
       </c>
       <c r="G3" t="n">
-        <v>34.0711530998579</v>
+        <v>75.90471222241355</v>
       </c>
       <c r="H3" t="n">
-        <v>34.23209715581746</v>
+        <v>40.25653954716553</v>
       </c>
       <c r="I3" t="n">
-        <v>33.21299540667962</v>
+        <v>45.66845715049131</v>
       </c>
       <c r="J3" t="n">
-        <v>34.23209715581746</v>
+        <v>75.92653731497479</v>
       </c>
       <c r="K3" t="n">
-        <v>34.23209715581746</v>
+        <v>150.0195071405012</v>
       </c>
       <c r="L3" t="n">
-        <v>34.23209715581746</v>
+        <v>33.6428174859602</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>202.4843439176423</v>
+        <v>119.5510801883933</v>
       </c>
       <c r="C4" t="n">
-        <v>132.013600966814</v>
+        <v>188.72882027628</v>
       </c>
       <c r="D4" t="n">
-        <v>201.4621273686066</v>
+        <v>597.894196570948</v>
       </c>
       <c r="E4" t="n">
-        <v>121.602732451836</v>
+        <v>187.3913349313342</v>
       </c>
       <c r="F4" t="n">
-        <v>131.5692274770063</v>
+        <v>187.3913349313342</v>
       </c>
       <c r="G4" t="n">
-        <v>202.3233998616823</v>
+        <v>330.2349855313114</v>
       </c>
       <c r="H4" t="n">
-        <v>202.8321352290338</v>
+        <v>696.4236405097781</v>
       </c>
       <c r="I4" t="n">
-        <v>131.5718918877887</v>
+        <v>187.3913349313342</v>
       </c>
       <c r="J4" t="n">
-        <v>137.8434158859136</v>
+        <v>371.3087594552589</v>
       </c>
       <c r="K4" t="n">
-        <v>132.4198495939635</v>
+        <v>215.575744895925</v>
       </c>
       <c r="L4" t="n">
-        <v>132.6183509954423</v>
+        <v>247.5610727203475</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.3843618591214</v>
+        <v>34.23209715581731</v>
       </c>
       <c r="C5" t="n">
-        <v>58.2808808506657</v>
+        <v>33.17807866077257</v>
       </c>
       <c r="D5" t="n">
-        <v>58.38400981838603</v>
+        <v>34.23209715581731</v>
       </c>
       <c r="E5" t="n">
-        <v>57.40766384957718</v>
+        <v>32.83400708082711</v>
       </c>
       <c r="F5" t="n">
-        <v>57.40766384957718</v>
+        <v>32.83400708082709</v>
       </c>
       <c r="G5" t="n">
-        <v>58.22341780316178</v>
+        <v>34.07115309985783</v>
       </c>
       <c r="H5" t="n">
-        <v>58.3843618591214</v>
+        <v>34.23209715581731</v>
       </c>
       <c r="I5" t="n">
-        <v>57.36526010998357</v>
+        <v>33.21299540667964</v>
       </c>
       <c r="J5" t="n">
-        <v>58.3843618591214</v>
+        <v>34.23209715581731</v>
       </c>
       <c r="K5" t="n">
-        <v>58.3843618591214</v>
+        <v>34.23209715581731</v>
       </c>
       <c r="L5" t="n">
-        <v>58.3843618591214</v>
+        <v>34.23209715581731</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>127.7158787371701</v>
+        <v>202.4843439176424</v>
       </c>
       <c r="C6" t="n">
-        <v>189.4349457283733</v>
+        <v>132.013600966815</v>
       </c>
       <c r="D6" t="n">
-        <v>202.2935839313083</v>
+        <v>201.4621273686065</v>
       </c>
       <c r="E6" t="n">
-        <v>171.620225844499</v>
+        <v>121.602732451836</v>
       </c>
       <c r="F6" t="n">
-        <v>128.6802779504086</v>
+        <v>131.5692274770062</v>
       </c>
       <c r="G6" t="n">
-        <v>189.3243493525409</v>
+        <v>202.3233998616825</v>
       </c>
       <c r="H6" t="n">
-        <v>189.4852934086918</v>
+        <v>202.8321352290335</v>
       </c>
       <c r="I6" t="n">
-        <v>188.4661916593626</v>
+        <v>131.5718918877887</v>
       </c>
       <c r="J6" t="n">
-        <v>189.4974328722932</v>
+        <v>137.8434158859136</v>
       </c>
       <c r="K6" t="n">
-        <v>126.5684801466601</v>
+        <v>132.419849593964</v>
       </c>
       <c r="L6" t="n">
-        <v>254.0086121115727</v>
+        <v>132.6183509954423</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106.3530091326788</v>
+        <v>58.38436185912136</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2268702460903</v>
+        <v>58.2808808506658</v>
       </c>
       <c r="D7" t="n">
-        <v>127.3303565572287</v>
+        <v>58.38400981838603</v>
       </c>
       <c r="E7" t="n">
-        <v>150.5186491323528</v>
+        <v>57.4076638495772</v>
       </c>
       <c r="F7" t="n">
-        <v>126.3112389584276</v>
+        <v>57.4076638495772</v>
       </c>
       <c r="G7" t="n">
-        <v>127.1694071985863</v>
+        <v>58.22341780316172</v>
       </c>
       <c r="H7" t="n">
-        <v>127.3303512545462</v>
+        <v>58.38436185912136</v>
       </c>
       <c r="I7" t="n">
-        <v>126.3112495054083</v>
+        <v>57.36526010998354</v>
       </c>
       <c r="J7" t="n">
-        <v>127.3303512545462</v>
+        <v>58.38436185912136</v>
       </c>
       <c r="K7" t="n">
-        <v>115.1759990750527</v>
+        <v>58.38436185912136</v>
       </c>
       <c r="L7" t="n">
-        <v>127.3303512545462</v>
+        <v>58.38436185912136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.22591955806444</v>
+        <v>127.71587873717</v>
       </c>
       <c r="C8" t="n">
-        <v>25.93977085287131</v>
+        <v>189.4349457283733</v>
       </c>
       <c r="D8" t="n">
-        <v>27.67588858395618</v>
+        <v>202.2935839313083</v>
       </c>
       <c r="E8" t="n">
-        <v>43.11221104488302</v>
+        <v>171.6202258444989</v>
       </c>
       <c r="F8" t="n">
-        <v>43.11221104488302</v>
+        <v>128.6802779504086</v>
       </c>
       <c r="G8" t="n">
-        <v>70.03228799023323</v>
+        <v>189.3243493525407</v>
       </c>
       <c r="H8" t="n">
-        <v>27.12213585216862</v>
+        <v>189.4852934086919</v>
       </c>
       <c r="I8" t="n">
-        <v>43.11221104488302</v>
+        <v>188.4661916593629</v>
       </c>
       <c r="J8" t="n">
-        <v>69.26585897978302</v>
+        <v>189.4974328722932</v>
       </c>
       <c r="K8" t="n">
-        <v>146.7837081064748</v>
+        <v>126.56848014666</v>
       </c>
       <c r="L8" t="n">
-        <v>30.25334329449312</v>
+        <v>254.0086121115727</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>106.3530091326787</v>
+      </c>
+      <c r="C9" t="n">
+        <v>127.2268702460905</v>
+      </c>
+      <c r="D9" t="n">
+        <v>127.3303565572286</v>
+      </c>
+      <c r="E9" t="n">
+        <v>150.5186491323528</v>
+      </c>
+      <c r="F9" t="n">
+        <v>126.3112389584275</v>
+      </c>
+      <c r="G9" t="n">
+        <v>127.1694071985863</v>
+      </c>
+      <c r="H9" t="n">
+        <v>127.330351254546</v>
+      </c>
+      <c r="I9" t="n">
+        <v>126.3112495054083</v>
+      </c>
+      <c r="J9" t="n">
+        <v>127.330351254546</v>
+      </c>
+      <c r="K9" t="n">
+        <v>115.1759990750526</v>
+      </c>
+      <c r="L9" t="n">
+        <v>127.330351254546</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>31.22591955806443</v>
+      </c>
+      <c r="C10" t="n">
+        <v>25.93977085287145</v>
+      </c>
+      <c r="D10" t="n">
+        <v>27.67588858395611</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.11221104488302</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.11221104488302</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70.03228799023339</v>
+      </c>
+      <c r="H10" t="n">
+        <v>27.12213585216859</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.11221104488302</v>
+      </c>
+      <c r="J10" t="n">
+        <v>69.26585897978298</v>
+      </c>
+      <c r="K10" t="n">
+        <v>146.7837081064746</v>
+      </c>
+      <c r="L10" t="n">
+        <v>30.25334329449309</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>32.25462758416879</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27.432106607275</v>
-      </c>
-      <c r="D9" t="n">
-        <v>34.9578203213446</v>
-      </c>
-      <c r="E9" t="n">
-        <v>44.36436016157601</v>
-      </c>
-      <c r="F9" t="n">
-        <v>44.36436016157601</v>
-      </c>
-      <c r="G9" t="n">
-        <v>72.78034307763504</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>32.25462758416875</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27.43210660727503</v>
+      </c>
+      <c r="D11" t="n">
+        <v>34.95782032134454</v>
+      </c>
+      <c r="E11" t="n">
+        <v>44.36436016157599</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.36436016157599</v>
+      </c>
+      <c r="G11" t="n">
+        <v>72.78034307763498</v>
+      </c>
+      <c r="H11" t="n">
         <v>34.74429715375607</v>
       </c>
-      <c r="I9" t="n">
-        <v>44.36436016157601</v>
-      </c>
-      <c r="J9" t="n">
-        <v>72.48300526538904</v>
-      </c>
-      <c r="K9" t="n">
-        <v>146.8085414384957</v>
-      </c>
-      <c r="L9" t="n">
-        <v>32.19360957930047</v>
+      <c r="I11" t="n">
+        <v>44.36436016157599</v>
+      </c>
+      <c r="J11" t="n">
+        <v>72.48300526538898</v>
+      </c>
+      <c r="K11" t="n">
+        <v>146.8085414384956</v>
+      </c>
+      <c r="L11" t="n">
+        <v>32.19360957930049</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100.418520805983</v>
+        <v>32.85726553401672</v>
       </c>
       <c r="C2" t="n">
-        <v>177.3834385069241</v>
+        <v>28.32579711914018</v>
       </c>
       <c r="D2" t="n">
-        <v>445.4929266523063</v>
+        <v>40.09434307589854</v>
       </c>
       <c r="E2" t="n">
-        <v>141.7517452141921</v>
+        <v>45.15640091193279</v>
       </c>
       <c r="F2" t="n">
-        <v>141.7517452141921</v>
+        <v>45.15640091193279</v>
       </c>
       <c r="G2" t="n">
-        <v>239.9327957715607</v>
+        <v>75.1117904164807</v>
       </c>
       <c r="H2" t="n">
-        <v>430.5294371160444</v>
+        <v>40.0319664422056</v>
       </c>
       <c r="I2" t="n">
-        <v>141.7517452141921</v>
+        <v>45.15640091193279</v>
       </c>
       <c r="J2" t="n">
-        <v>228.9780939387207</v>
+        <v>74.9421001746047</v>
       </c>
       <c r="K2" t="n">
-        <v>159.4472261576886</v>
+        <v>148.19934875185</v>
       </c>
       <c r="L2" t="n">
-        <v>163.4816160649817</v>
+        <v>33.39376720580337</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.07085988126749</v>
+        <v>32.86229826685125</v>
       </c>
       <c r="C3" t="n">
-        <v>33.05321759053056</v>
+        <v>28.20802986945298</v>
       </c>
       <c r="D3" t="n">
-        <v>34.07085988126749</v>
+        <v>39.84186305052033</v>
       </c>
       <c r="E3" t="n">
-        <v>32.72429416614</v>
+        <v>45.34673880406852</v>
       </c>
       <c r="F3" t="n">
-        <v>32.72429416614001</v>
+        <v>45.34673880406852</v>
       </c>
       <c r="G3" t="n">
-        <v>33.91154680160085</v>
+        <v>75.66488801477702</v>
       </c>
       <c r="H3" t="n">
-        <v>34.07085988126749</v>
+        <v>39.84186305052033</v>
       </c>
       <c r="I3" t="n">
-        <v>33.06222036230606</v>
+        <v>45.34673880406852</v>
       </c>
       <c r="J3" t="n">
-        <v>34.07085988126749</v>
+        <v>75.50911710128119</v>
       </c>
       <c r="K3" t="n">
-        <v>34.07085988126749</v>
+        <v>150.0049566367722</v>
       </c>
       <c r="L3" t="n">
-        <v>34.07085988126749</v>
+        <v>33.38478444202769</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>132.1687273450329</v>
+        <v>100.4185208059832</v>
       </c>
       <c r="C4" t="n">
-        <v>131.7105805580752</v>
+        <v>177.3834385069206</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5823182428507</v>
+        <v>445.4929266523061</v>
       </c>
       <c r="E4" t="n">
-        <v>121.2574953322677</v>
+        <v>141.7517452141921</v>
       </c>
       <c r="F4" t="n">
-        <v>131.1563751045058</v>
+        <v>141.7517452141921</v>
       </c>
       <c r="G4" t="n">
-        <v>201.5858517744978</v>
+        <v>239.9327957715516</v>
       </c>
       <c r="H4" t="n">
-        <v>202.0734399927275</v>
+        <v>430.5294371160462</v>
       </c>
       <c r="I4" t="n">
-        <v>200.7365253352026</v>
+        <v>141.7517452141921</v>
       </c>
       <c r="J4" t="n">
-        <v>200.4656850174503</v>
+        <v>228.978093938721</v>
       </c>
       <c r="K4" t="n">
-        <v>132.0192215287391</v>
+        <v>159.4472261576889</v>
       </c>
       <c r="L4" t="n">
-        <v>132.1766044600764</v>
+        <v>163.4816160649818</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.84998969825277</v>
+        <v>34.07085988126758</v>
       </c>
       <c r="C5" t="n">
-        <v>57.74972235392073</v>
+        <v>33.0532175905306</v>
       </c>
       <c r="D5" t="n">
-        <v>57.84963342880917</v>
+        <v>34.07085988126758</v>
       </c>
       <c r="E5" t="n">
-        <v>56.89213344579162</v>
+        <v>32.7242941661401</v>
       </c>
       <c r="F5" t="n">
-        <v>56.89213344579162</v>
+        <v>32.7242941661401</v>
       </c>
       <c r="G5" t="n">
-        <v>57.69067661858605</v>
+        <v>33.91154680160087</v>
       </c>
       <c r="H5" t="n">
-        <v>57.84998969825277</v>
+        <v>34.07085988126758</v>
       </c>
       <c r="I5" t="n">
-        <v>56.84135017929124</v>
+        <v>33.0622203623061</v>
       </c>
       <c r="J5" t="n">
-        <v>57.84998969825277</v>
+        <v>34.07085988126758</v>
       </c>
       <c r="K5" t="n">
-        <v>57.84998969825277</v>
+        <v>34.07085988126758</v>
       </c>
       <c r="L5" t="n">
-        <v>57.84998969825277</v>
+        <v>34.07085988126758</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>126.9834917405938</v>
+        <v>132.1687273450332</v>
       </c>
       <c r="C6" t="n">
-        <v>188.3016375712784</v>
+        <v>131.7105805580753</v>
       </c>
       <c r="D6" t="n">
-        <v>201.0636536358903</v>
+        <v>132.5823182428493</v>
       </c>
       <c r="E6" t="n">
-        <v>170.6060054565599</v>
+        <v>121.2574953322679</v>
       </c>
       <c r="F6" t="n">
-        <v>127.9502917859658</v>
+        <v>131.1563751045061</v>
       </c>
       <c r="G6" t="n">
-        <v>188.1815002239895</v>
+        <v>201.5858517744978</v>
       </c>
       <c r="H6" t="n">
-        <v>188.3408133038501</v>
+        <v>202.0734399927277</v>
       </c>
       <c r="I6" t="n">
-        <v>187.3321737846949</v>
+        <v>200.7365253352026</v>
       </c>
       <c r="J6" t="n">
-        <v>188.3528717791559</v>
+        <v>200.4656850174503</v>
       </c>
       <c r="K6" t="n">
-        <v>125.8437479910899</v>
+        <v>132.0192215287393</v>
       </c>
       <c r="L6" t="n">
-        <v>252.4336662964263</v>
+        <v>132.1766044600766</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100.9703769919996</v>
+        <v>57.84998969825285</v>
       </c>
       <c r="C7" t="n">
-        <v>120.3820373431712</v>
+        <v>57.74972235392084</v>
       </c>
       <c r="D7" t="n">
-        <v>120.4823105226754</v>
+        <v>57.84963342880916</v>
       </c>
       <c r="E7" t="n">
-        <v>141.9900116705482</v>
+        <v>56.89213344579176</v>
       </c>
       <c r="F7" t="n">
-        <v>119.4736574774981</v>
+        <v>56.89213344579176</v>
       </c>
       <c r="G7" t="n">
-        <v>120.3229916078365</v>
+        <v>57.69067661858617</v>
       </c>
       <c r="H7" t="n">
-        <v>120.4823046875034</v>
+        <v>57.84998969825285</v>
       </c>
       <c r="I7" t="n">
-        <v>119.4736651685418</v>
+        <v>56.84135017929131</v>
       </c>
       <c r="J7" t="n">
-        <v>120.4823046875034</v>
+        <v>57.84998969825285</v>
       </c>
       <c r="K7" t="n">
-        <v>108.7183496725055</v>
+        <v>57.84998969825285</v>
       </c>
       <c r="L7" t="n">
-        <v>120.4823046875034</v>
+        <v>57.84998969825285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.45153157207486</v>
+        <v>126.9834917405941</v>
       </c>
       <c r="C8" t="n">
-        <v>25.97137153607486</v>
+        <v>188.3016375712785</v>
       </c>
       <c r="D8" t="n">
-        <v>30.97490487506742</v>
+        <v>201.0636536358903</v>
       </c>
       <c r="E8" t="n">
-        <v>43.88821826896708</v>
+        <v>170.60600545656</v>
       </c>
       <c r="F8" t="n">
-        <v>43.88821826896708</v>
+        <v>127.9502917859659</v>
       </c>
       <c r="G8" t="n">
-        <v>71.92636078205602</v>
+        <v>188.1815002239895</v>
       </c>
       <c r="H8" t="n">
-        <v>32.42448717434862</v>
+        <v>188.3408133038496</v>
       </c>
       <c r="I8" t="n">
-        <v>43.88821826896708</v>
+        <v>187.3321737846948</v>
       </c>
       <c r="J8" t="n">
-        <v>72.14072548261412</v>
+        <v>188.3528717791561</v>
       </c>
       <c r="K8" t="n">
-        <v>148.1281191978711</v>
+        <v>125.8437479910902</v>
       </c>
       <c r="L8" t="n">
-        <v>31.76434701938747</v>
+        <v>252.4336662964267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100.9703769920001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>120.3820373431718</v>
+      </c>
+      <c r="D9" t="n">
+        <v>120.4823105226757</v>
+      </c>
+      <c r="E9" t="n">
+        <v>141.990011670549</v>
+      </c>
+      <c r="F9" t="n">
+        <v>119.4736574774984</v>
+      </c>
+      <c r="G9" t="n">
+        <v>120.3229916078371</v>
+      </c>
+      <c r="H9" t="n">
+        <v>120.4823046875037</v>
+      </c>
+      <c r="I9" t="n">
+        <v>119.4736651685425</v>
+      </c>
+      <c r="J9" t="n">
+        <v>120.4823046875037</v>
+      </c>
+      <c r="K9" t="n">
+        <v>108.7183496725058</v>
+      </c>
+      <c r="L9" t="n">
+        <v>120.4823046875037</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>31.45153157207489</v>
+      </c>
+      <c r="C10" t="n">
+        <v>25.97137153607489</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30.97490487506745</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.88821826896708</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.88821826896708</v>
+      </c>
+      <c r="G10" t="n">
+        <v>71.92636078205628</v>
+      </c>
+      <c r="H10" t="n">
+        <v>32.42448717434861</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.88821826896708</v>
+      </c>
+      <c r="J10" t="n">
+        <v>72.14072548261444</v>
+      </c>
+      <c r="K10" t="n">
+        <v>148.1281191978715</v>
+      </c>
+      <c r="L10" t="n">
+        <v>31.76434701938749</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>32.2153621920467</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27.30811044964589</v>
-      </c>
-      <c r="D9" t="n">
-        <v>36.05984884874838</v>
-      </c>
-      <c r="E9" t="n">
-        <v>44.4927694204325</v>
-      </c>
-      <c r="F9" t="n">
-        <v>44.4927694204325</v>
-      </c>
-      <c r="G9" t="n">
-        <v>73.4107486116133</v>
-      </c>
-      <c r="H9" t="n">
-        <v>36.65703678077304</v>
-      </c>
-      <c r="I9" t="n">
-        <v>44.4927694204325</v>
-      </c>
-      <c r="J9" t="n">
-        <v>73.40947125368396</v>
-      </c>
-      <c r="K9" t="n">
-        <v>147.3453817360242</v>
-      </c>
-      <c r="L9" t="n">
-        <v>32.65646301447442</v>
+      <c r="B11" t="n">
+        <v>32.21536219204673</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27.30811044964588</v>
+      </c>
+      <c r="D11" t="n">
+        <v>36.0598488487484</v>
+      </c>
+      <c r="E11" t="n">
+        <v>44.49276942043254</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.49276942043254</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.41074861161331</v>
+      </c>
+      <c r="H11" t="n">
+        <v>36.65703678077308</v>
+      </c>
+      <c r="I11" t="n">
+        <v>44.49276942043254</v>
+      </c>
+      <c r="J11" t="n">
+        <v>73.40947125368405</v>
+      </c>
+      <c r="K11" t="n">
+        <v>147.3453817360244</v>
+      </c>
+      <c r="L11" t="n">
+        <v>32.65646301447448</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116.5107253538644</v>
+        <v>33.9213023547084</v>
       </c>
       <c r="C2" t="n">
-        <v>161.1439906150658</v>
+        <v>28.34702332754322</v>
       </c>
       <c r="D2" t="n">
-        <v>519.905250722758</v>
+        <v>40.35469118577852</v>
       </c>
       <c r="E2" t="n">
-        <v>196.8062126276204</v>
+        <v>45.36107618627991</v>
       </c>
       <c r="F2" t="n">
-        <v>196.8062126276204</v>
+        <v>45.36107618627991</v>
       </c>
       <c r="G2" t="n">
-        <v>349.3963930928408</v>
+        <v>75.33578191951715</v>
       </c>
       <c r="H2" t="n">
-        <v>1004.161385287357</v>
+        <v>40.78229534831904</v>
       </c>
       <c r="I2" t="n">
-        <v>196.8062126276204</v>
+        <v>45.36107618627991</v>
       </c>
       <c r="J2" t="n">
-        <v>528.3968033043258</v>
+        <v>75.50047584327926</v>
       </c>
       <c r="K2" t="n">
-        <v>264.0083523823186</v>
+        <v>148.0414679946408</v>
       </c>
       <c r="L2" t="n">
-        <v>528.9125242425832</v>
+        <v>33.91424202320181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.02595885034167</v>
+        <v>33.92795507855426</v>
       </c>
       <c r="C3" t="n">
-        <v>32.972030736626</v>
+        <v>28.25438016057864</v>
       </c>
       <c r="D3" t="n">
-        <v>34.02595885034167</v>
+        <v>40.04692338278712</v>
       </c>
       <c r="E3" t="n">
-        <v>32.72999941229633</v>
+        <v>45.49878949477511</v>
       </c>
       <c r="F3" t="n">
-        <v>32.72999941229633</v>
+        <v>45.49878949477511</v>
       </c>
       <c r="G3" t="n">
-        <v>33.86541890175346</v>
+        <v>75.78374744652814</v>
       </c>
       <c r="H3" t="n">
-        <v>34.02595885034167</v>
+        <v>40.04692338278712</v>
       </c>
       <c r="I3" t="n">
-        <v>33.00910553105656</v>
+        <v>45.49878949477511</v>
       </c>
       <c r="J3" t="n">
-        <v>34.02595885034167</v>
+        <v>75.76520980725017</v>
       </c>
       <c r="K3" t="n">
-        <v>34.02595885034167</v>
+        <v>149.7338650491218</v>
       </c>
       <c r="L3" t="n">
-        <v>34.02595885034167</v>
+        <v>33.5591361711366</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137.9425585735733</v>
+        <v>116.5107253538644</v>
       </c>
       <c r="C4" t="n">
-        <v>137.2862459675069</v>
+        <v>161.1439906150667</v>
       </c>
       <c r="D4" t="n">
-        <v>138.3324406557909</v>
+        <v>519.905250722758</v>
       </c>
       <c r="E4" t="n">
-        <v>126.422372986562</v>
+        <v>196.8062126276264</v>
       </c>
       <c r="F4" t="n">
-        <v>136.9312803481972</v>
+        <v>196.8062126276264</v>
       </c>
       <c r="G4" t="n">
-        <v>137.782018624985</v>
+        <v>349.3963930928386</v>
       </c>
       <c r="H4" t="n">
-        <v>211.2410754122504</v>
+        <v>1004.161385287359</v>
       </c>
       <c r="I4" t="n">
-        <v>210.5450540265649</v>
+        <v>196.8062126276264</v>
       </c>
       <c r="J4" t="n">
-        <v>143.5282801664664</v>
+        <v>528.3968033043262</v>
       </c>
       <c r="K4" t="n">
-        <v>137.8419955057377</v>
+        <v>264.0083523823186</v>
       </c>
       <c r="L4" t="n">
-        <v>138.0550245343693</v>
+        <v>528.9125242425832</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.31009710967133</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="C5" t="n">
-        <v>59.20651589428829</v>
+        <v>32.97203073662593</v>
       </c>
       <c r="D5" t="n">
-        <v>59.30970625975668</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="E5" t="n">
-        <v>58.36355311814535</v>
+        <v>32.72999941229627</v>
       </c>
       <c r="F5" t="n">
-        <v>58.36355311814535</v>
+        <v>32.72999941229628</v>
       </c>
       <c r="G5" t="n">
-        <v>59.14955716108301</v>
+        <v>33.86541890175346</v>
       </c>
       <c r="H5" t="n">
-        <v>59.31009710967133</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="I5" t="n">
-        <v>58.29324379038611</v>
+        <v>33.00910553105655</v>
       </c>
       <c r="J5" t="n">
-        <v>59.31009710967133</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="K5" t="n">
-        <v>59.31009710967133</v>
+        <v>34.02595885034167</v>
       </c>
       <c r="L5" t="n">
-        <v>59.31009710967133</v>
+        <v>34.02595885034167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>132.1306318650759</v>
+        <v>137.9425585735735</v>
       </c>
       <c r="C6" t="n">
-        <v>196.8384730105102</v>
+        <v>137.2862459675165</v>
       </c>
       <c r="D6" t="n">
-        <v>210.2840526758631</v>
+        <v>138.3324406557909</v>
       </c>
       <c r="E6" t="n">
-        <v>178.2132688003759</v>
+        <v>126.4223729865622</v>
       </c>
       <c r="F6" t="n">
-        <v>133.2078280691441</v>
+        <v>136.9312803481974</v>
       </c>
       <c r="G6" t="n">
-        <v>196.7011136805851</v>
+        <v>137.7820186249853</v>
       </c>
       <c r="H6" t="n">
-        <v>196.861653629224</v>
+        <v>211.2410754122504</v>
       </c>
       <c r="I6" t="n">
-        <v>195.8448003098882</v>
+        <v>210.5450540265649</v>
       </c>
       <c r="J6" t="n">
-        <v>196.8743751342956</v>
+        <v>143.5282801664665</v>
       </c>
       <c r="K6" t="n">
-        <v>130.9282199023592</v>
+        <v>137.8419955057378</v>
       </c>
       <c r="L6" t="n">
-        <v>264.4786185864388</v>
+        <v>138.0550245343693</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114.3183852075002</v>
+        <v>59.31009710967132</v>
       </c>
       <c r="C7" t="n">
-        <v>137.4631423900209</v>
+        <v>59.20651589428837</v>
       </c>
       <c r="D7" t="n">
-        <v>137.5667254559364</v>
+        <v>59.30970625975662</v>
       </c>
       <c r="E7" t="n">
-        <v>163.3779430002516</v>
+        <v>58.3635531181454</v>
       </c>
       <c r="F7" t="n">
-        <v>136.5498554657073</v>
+        <v>58.3635531181454</v>
       </c>
       <c r="G7" t="n">
-        <v>137.4061836568157</v>
+        <v>59.14955716108304</v>
       </c>
       <c r="H7" t="n">
-        <v>137.566723605404</v>
+        <v>59.31009710967132</v>
       </c>
       <c r="I7" t="n">
-        <v>136.5498702861186</v>
+        <v>58.29324379038616</v>
       </c>
       <c r="J7" t="n">
-        <v>137.566723605404</v>
+        <v>59.31009710967132</v>
       </c>
       <c r="K7" t="n">
-        <v>124.096545812724</v>
+        <v>59.31009710967132</v>
       </c>
       <c r="L7" t="n">
-        <v>137.566723605404</v>
+        <v>59.31009710967132</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.24152483911655</v>
+        <v>132.1306318650757</v>
       </c>
       <c r="C8" t="n">
-        <v>26.56487465455825</v>
+        <v>196.8384730105104</v>
       </c>
       <c r="D8" t="n">
-        <v>29.99335019499441</v>
+        <v>210.2840526758631</v>
       </c>
       <c r="E8" t="n">
-        <v>42.92217252002939</v>
+        <v>178.2132688003759</v>
       </c>
       <c r="F8" t="n">
-        <v>42.92217252002939</v>
+        <v>133.207828069144</v>
       </c>
       <c r="G8" t="n">
-        <v>69.85030102319783</v>
+        <v>196.7011136805851</v>
       </c>
       <c r="H8" t="n">
-        <v>21.39156377429394</v>
+        <v>196.861653629224</v>
       </c>
       <c r="I8" t="n">
-        <v>42.92217252002939</v>
+        <v>195.8448003098881</v>
       </c>
       <c r="J8" t="n">
-        <v>66.06874404948603</v>
+        <v>196.8743751342957</v>
       </c>
       <c r="K8" t="n">
-        <v>145.6144610875484</v>
+        <v>130.9282199023592</v>
       </c>
       <c r="L8" t="n">
-        <v>24.78500035835186</v>
+        <v>264.4786185864387</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>114.3183852075006</v>
+      </c>
+      <c r="C9" t="n">
+        <v>137.4631423900213</v>
+      </c>
+      <c r="D9" t="n">
+        <v>137.5667254559369</v>
+      </c>
+      <c r="E9" t="n">
+        <v>163.3779430002521</v>
+      </c>
+      <c r="F9" t="n">
+        <v>136.5498554657076</v>
+      </c>
+      <c r="G9" t="n">
+        <v>137.406183656816</v>
+      </c>
+      <c r="H9" t="n">
+        <v>137.5667236054043</v>
+      </c>
+      <c r="I9" t="n">
+        <v>136.549870286119</v>
+      </c>
+      <c r="J9" t="n">
+        <v>137.5667236054043</v>
+      </c>
+      <c r="K9" t="n">
+        <v>124.0965458127242</v>
+      </c>
+      <c r="L9" t="n">
+        <v>137.5667236054043</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>32.24152483911656</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.56487465455827</v>
+      </c>
+      <c r="D10" t="n">
+        <v>29.99335019499442</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42.92217252002941</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.92217252002941</v>
+      </c>
+      <c r="G10" t="n">
+        <v>69.85030102319782</v>
+      </c>
+      <c r="H10" t="n">
+        <v>21.39156377429389</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42.92217252002941</v>
+      </c>
+      <c r="J10" t="n">
+        <v>66.06874404948613</v>
+      </c>
+      <c r="K10" t="n">
+        <v>145.6144610875487</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24.78500035835187</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>33.15397122142995</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27.57829293816934</v>
-      </c>
-      <c r="D9" t="n">
-        <v>35.78028334649606</v>
-      </c>
-      <c r="E9" t="n">
-        <v>44.18870725157948</v>
-      </c>
-      <c r="F9" t="n">
-        <v>44.18870725157948</v>
-      </c>
-      <c r="G9" t="n">
-        <v>72.63604488813009</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>33.15397122142997</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27.57829293816935</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35.78028334649611</v>
+      </c>
+      <c r="E11" t="n">
+        <v>44.18870725157951</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.18870725157951</v>
+      </c>
+      <c r="G11" t="n">
+        <v>72.63604488813007</v>
+      </c>
+      <c r="H11" t="n">
         <v>32.29404727535101</v>
       </c>
-      <c r="I9" t="n">
-        <v>44.18870725157948</v>
-      </c>
-      <c r="J9" t="n">
-        <v>71.0885530226937</v>
-      </c>
-      <c r="K9" t="n">
-        <v>146.1671260643633</v>
-      </c>
-      <c r="L9" t="n">
-        <v>29.92198226687295</v>
+      <c r="I11" t="n">
+        <v>44.18870725157951</v>
+      </c>
+      <c r="J11" t="n">
+        <v>71.08855302269379</v>
+      </c>
+      <c r="K11" t="n">
+        <v>146.1671260643636</v>
+      </c>
+      <c r="L11" t="n">
+        <v>29.92198226687298</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103.3081020888934</v>
+        <v>33.8565809299646</v>
       </c>
       <c r="C2" t="n">
-        <v>156.3162966363878</v>
+        <v>27.98213977655215</v>
       </c>
       <c r="D2" t="n">
-        <v>155.923416765005</v>
+        <v>39.39451330416586</v>
       </c>
       <c r="E2" t="n">
-        <v>165.7148273278712</v>
+        <v>44.89091607382949</v>
       </c>
       <c r="F2" t="n">
-        <v>165.7148273278712</v>
+        <v>44.89091607382949</v>
       </c>
       <c r="G2" t="n">
-        <v>159.9344149488039</v>
+        <v>74.57926295944313</v>
       </c>
       <c r="H2" t="n">
-        <v>212.7781268534478</v>
+        <v>39.44145446599837</v>
       </c>
       <c r="I2" t="n">
-        <v>165.7148273278712</v>
+        <v>44.89091607382949</v>
       </c>
       <c r="J2" t="n">
-        <v>255.0066875947317</v>
+        <v>74.36311278254256</v>
       </c>
       <c r="K2" t="n">
-        <v>145.1838009934165</v>
+        <v>147.0709033605809</v>
       </c>
       <c r="L2" t="n">
-        <v>186.4247909142287</v>
+        <v>33.01079028702543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.62827358908619</v>
+        <v>33.87599499032788</v>
       </c>
       <c r="C3" t="n">
-        <v>32.69664801578458</v>
+        <v>27.88493567417176</v>
       </c>
       <c r="D3" t="n">
-        <v>33.62827358908619</v>
+        <v>39.47523795533547</v>
       </c>
       <c r="E3" t="n">
-        <v>32.52390506678806</v>
+        <v>45.04973942077052</v>
       </c>
       <c r="F3" t="n">
-        <v>32.52390506678806</v>
+        <v>45.04973942077052</v>
       </c>
       <c r="G3" t="n">
-        <v>33.4732417204274</v>
+        <v>75.21759915152192</v>
       </c>
       <c r="H3" t="n">
-        <v>33.62827358908619</v>
+        <v>39.47523795533547</v>
       </c>
       <c r="I3" t="n">
-        <v>32.64673652425925</v>
+        <v>45.04973942077052</v>
       </c>
       <c r="J3" t="n">
-        <v>33.62827358908619</v>
+        <v>74.8931876035835</v>
       </c>
       <c r="K3" t="n">
-        <v>33.62827358908619</v>
+        <v>148.8771030736763</v>
       </c>
       <c r="L3" t="n">
-        <v>33.62827358908619</v>
+        <v>32.97362430281479</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.697363605214</v>
+        <v>103.3081020888934</v>
       </c>
       <c r="C4" t="n">
-        <v>131.3196972240848</v>
+        <v>156.3162966363878</v>
       </c>
       <c r="D4" t="n">
-        <v>199.521910845467</v>
+        <v>155.9234167650048</v>
       </c>
       <c r="E4" t="n">
-        <v>120.9972741017079</v>
+        <v>165.7148273278713</v>
       </c>
       <c r="F4" t="n">
-        <v>130.742974304654</v>
+        <v>165.7148273278713</v>
       </c>
       <c r="G4" t="n">
-        <v>131.542331736555</v>
+        <v>159.9344149488053</v>
       </c>
       <c r="H4" t="n">
-        <v>200.7975093738141</v>
+        <v>212.7781268534476</v>
       </c>
       <c r="I4" t="n">
-        <v>199.6980143648025</v>
+        <v>165.7148273278713</v>
       </c>
       <c r="J4" t="n">
-        <v>199.355381660611</v>
+        <v>255.0066875947315</v>
       </c>
       <c r="K4" t="n">
-        <v>131.611047208791</v>
+        <v>145.1838009934162</v>
       </c>
       <c r="L4" t="n">
-        <v>131.7112718427867</v>
+        <v>186.4247909142284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.73065617254072</v>
+        <v>33.62827358908617</v>
       </c>
       <c r="C5" t="n">
-        <v>56.63446821961384</v>
+        <v>32.69664801578455</v>
       </c>
       <c r="D5" t="n">
-        <v>56.73030603415411</v>
+        <v>33.62827358908615</v>
       </c>
       <c r="E5" t="n">
-        <v>55.83937550330999</v>
+        <v>32.52390506678814</v>
       </c>
       <c r="F5" t="n">
-        <v>55.83937550330999</v>
+        <v>32.52390506678816</v>
       </c>
       <c r="G5" t="n">
-        <v>56.57562430388204</v>
+        <v>33.47324172042733</v>
       </c>
       <c r="H5" t="n">
-        <v>56.73065617254072</v>
+        <v>33.62827358908617</v>
       </c>
       <c r="I5" t="n">
-        <v>55.74911910771399</v>
+        <v>32.64673652425931</v>
       </c>
       <c r="J5" t="n">
-        <v>56.73065617254072</v>
+        <v>33.62827358908617</v>
       </c>
       <c r="K5" t="n">
-        <v>56.73065617254072</v>
+        <v>33.62827358908617</v>
       </c>
       <c r="L5" t="n">
-        <v>56.73065617254072</v>
+        <v>33.62827358908617</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.2615926882042</v>
+        <v>131.6973636052138</v>
       </c>
       <c r="C6" t="n">
-        <v>185.6332263063183</v>
+        <v>131.3196972240848</v>
       </c>
       <c r="D6" t="n">
-        <v>198.1487729629225</v>
+        <v>199.5219108454671</v>
       </c>
       <c r="E6" t="n">
-        <v>168.2269113245814</v>
+        <v>120.9972741017079</v>
       </c>
       <c r="F6" t="n">
-        <v>126.2477181164814</v>
+        <v>130.7429743046539</v>
       </c>
       <c r="G6" t="n">
-        <v>185.4757884713497</v>
+        <v>131.542331736555</v>
       </c>
       <c r="H6" t="n">
-        <v>185.630820340174</v>
+        <v>200.7975093738138</v>
       </c>
       <c r="I6" t="n">
-        <v>184.6492832751813</v>
+        <v>199.6980143648026</v>
       </c>
       <c r="J6" t="n">
-        <v>185.6426846268948</v>
+        <v>199.355381660611</v>
       </c>
       <c r="K6" t="n">
-        <v>124.140203290446</v>
+        <v>131.6110472087957</v>
       </c>
       <c r="L6" t="n">
-        <v>248.6915266194226</v>
+        <v>131.7112718427867</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.7741154661531</v>
+        <v>56.73065617254065</v>
       </c>
       <c r="C7" t="n">
-        <v>121.458261677585</v>
+        <v>56.63446821961378</v>
       </c>
       <c r="D7" t="n">
-        <v>121.5544554869211</v>
+        <v>56.73030603415412</v>
       </c>
       <c r="E7" t="n">
-        <v>143.3989981540275</v>
+        <v>55.83937550331004</v>
       </c>
       <c r="F7" t="n">
-        <v>120.5729078292145</v>
+        <v>55.83937550331004</v>
       </c>
       <c r="G7" t="n">
-        <v>121.3994177618533</v>
+        <v>56.57562430388197</v>
       </c>
       <c r="H7" t="n">
-        <v>121.5544496305119</v>
+        <v>56.73065617254065</v>
       </c>
       <c r="I7" t="n">
-        <v>120.5729125656852</v>
+        <v>55.74911910771394</v>
       </c>
       <c r="J7" t="n">
-        <v>121.5544496305119</v>
+        <v>56.73065617254065</v>
       </c>
       <c r="K7" t="n">
-        <v>110.0936487955069</v>
+        <v>56.73065617254065</v>
       </c>
       <c r="L7" t="n">
-        <v>121.5544496305119</v>
+        <v>56.73065617254065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.39178077874355</v>
+        <v>125.2615926882041</v>
       </c>
       <c r="C8" t="n">
-        <v>26.14046043465797</v>
+        <v>185.6332263063185</v>
       </c>
       <c r="D8" t="n">
-        <v>37.66585374732854</v>
+        <v>198.148772962922</v>
       </c>
       <c r="E8" t="n">
-        <v>43.00548765412405</v>
+        <v>168.2269113245815</v>
       </c>
       <c r="F8" t="n">
-        <v>43.00548765412404</v>
+        <v>126.2477181164817</v>
       </c>
       <c r="G8" t="n">
-        <v>73.36617402600244</v>
+        <v>185.4757884713495</v>
       </c>
       <c r="H8" t="n">
-        <v>36.73633216987946</v>
+        <v>185.6308203401739</v>
       </c>
       <c r="I8" t="n">
-        <v>43.00548765412405</v>
+        <v>184.6492832751815</v>
       </c>
       <c r="J8" t="n">
-        <v>70.91445016173651</v>
+        <v>185.6426846268948</v>
       </c>
       <c r="K8" t="n">
-        <v>147.3391243831613</v>
+        <v>124.1402032904459</v>
       </c>
       <c r="L8" t="n">
-        <v>30.8623264211345</v>
+        <v>248.6915266194224</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>101.7741154661532</v>
+      </c>
+      <c r="C9" t="n">
+        <v>121.4582616775852</v>
+      </c>
+      <c r="D9" t="n">
+        <v>121.5544554869212</v>
+      </c>
+      <c r="E9" t="n">
+        <v>143.3989981540277</v>
+      </c>
+      <c r="F9" t="n">
+        <v>120.5729078292145</v>
+      </c>
+      <c r="G9" t="n">
+        <v>121.3994177618534</v>
+      </c>
+      <c r="H9" t="n">
+        <v>121.5544496305119</v>
+      </c>
+      <c r="I9" t="n">
+        <v>120.5729125656853</v>
+      </c>
+      <c r="J9" t="n">
+        <v>121.5544496305119</v>
+      </c>
+      <c r="K9" t="n">
+        <v>110.0936487955071</v>
+      </c>
+      <c r="L9" t="n">
+        <v>121.5544496305119</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>32.39178077874357</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.14046043465797</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37.66585374732857</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.00548765412404</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.00548765412404</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.36617402600244</v>
+      </c>
+      <c r="H10" t="n">
+        <v>36.73633216987943</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.00548765412404</v>
+      </c>
+      <c r="J10" t="n">
+        <v>70.91445016173643</v>
+      </c>
+      <c r="K10" t="n">
+        <v>147.3391243831615</v>
+      </c>
+      <c r="L10" t="n">
+        <v>30.86232642113446</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>33.18125873378368</v>
       </c>
-      <c r="C9" t="n">
-        <v>27.18839798326062</v>
-      </c>
-      <c r="D9" t="n">
-        <v>38.5712377233574</v>
-      </c>
-      <c r="E9" t="n">
-        <v>43.96077500536157</v>
-      </c>
-      <c r="F9" t="n">
-        <v>43.96077500536157</v>
-      </c>
-      <c r="G9" t="n">
-        <v>73.73685862718983</v>
-      </c>
-      <c r="H9" t="n">
-        <v>38.19524360524102</v>
-      </c>
-      <c r="I9" t="n">
-        <v>43.96077500536157</v>
-      </c>
-      <c r="J9" t="n">
-        <v>72.55277456701825</v>
-      </c>
-      <c r="K9" t="n">
-        <v>146.3711181551492</v>
-      </c>
-      <c r="L9" t="n">
-        <v>32.05014302255375</v>
+      <c r="C11" t="n">
+        <v>27.18839798326061</v>
+      </c>
+      <c r="D11" t="n">
+        <v>38.57123772335736</v>
+      </c>
+      <c r="E11" t="n">
+        <v>43.96077500536155</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.96077500536155</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.73685862718997</v>
+      </c>
+      <c r="H11" t="n">
+        <v>38.195243605241</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.96077500536155</v>
+      </c>
+      <c r="J11" t="n">
+        <v>72.55277456701826</v>
+      </c>
+      <c r="K11" t="n">
+        <v>146.3711181551494</v>
+      </c>
+      <c r="L11" t="n">
+        <v>32.05014302255377</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86.92518736735556</v>
+        <v>34.34584336690688</v>
       </c>
       <c r="C2" t="n">
-        <v>141.6176582057836</v>
+        <v>27.87136307572392</v>
       </c>
       <c r="D2" t="n">
-        <v>151.7213545127888</v>
+        <v>39.26983939312101</v>
       </c>
       <c r="E2" t="n">
-        <v>143.9515846879989</v>
+        <v>44.76292873733853</v>
       </c>
       <c r="F2" t="n">
-        <v>143.9515846879989</v>
+        <v>44.76292873733853</v>
       </c>
       <c r="G2" t="n">
-        <v>141.849543930333</v>
+        <v>74.67258459091641</v>
       </c>
       <c r="H2" t="n">
-        <v>171.8332732477231</v>
+        <v>39.27883074140027</v>
       </c>
       <c r="I2" t="n">
-        <v>143.9515846879989</v>
+        <v>44.76292873733854</v>
       </c>
       <c r="J2" t="n">
-        <v>170.1108745309248</v>
+        <v>74.22404022551929</v>
       </c>
       <c r="K2" t="n">
-        <v>127.6838917263954</v>
+        <v>147.5190123655618</v>
       </c>
       <c r="L2" t="n">
-        <v>144.2087629792356</v>
+        <v>32.88934763998532</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.79074347757878</v>
+        <v>34.39235706155206</v>
       </c>
       <c r="C3" t="n">
-        <v>32.85673704833354</v>
+        <v>27.78985401122028</v>
       </c>
       <c r="D3" t="n">
-        <v>33.79074347757878</v>
+        <v>39.35400566421426</v>
       </c>
       <c r="E3" t="n">
-        <v>32.63546364679188</v>
+        <v>44.94575399473958</v>
       </c>
       <c r="F3" t="n">
-        <v>32.63546364679188</v>
+        <v>44.94575399473959</v>
       </c>
       <c r="G3" t="n">
-        <v>33.63529491039907</v>
+        <v>75.33373529632456</v>
       </c>
       <c r="H3" t="n">
-        <v>33.79074347757878</v>
+        <v>39.35400566421426</v>
       </c>
       <c r="I3" t="n">
-        <v>32.80670207419735</v>
+        <v>44.94575399473959</v>
       </c>
       <c r="J3" t="n">
-        <v>33.79074347757878</v>
+        <v>74.84846176535845</v>
       </c>
       <c r="K3" t="n">
-        <v>33.79074347757878</v>
+        <v>149.3534215129015</v>
       </c>
       <c r="L3" t="n">
-        <v>33.79074347757878</v>
+        <v>32.89456717638561</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.927204396142</v>
+        <v>86.9251873673569</v>
       </c>
       <c r="C4" t="n">
-        <v>131.4820307778944</v>
+        <v>141.6176582057864</v>
       </c>
       <c r="D4" t="n">
-        <v>131.7932744471843</v>
+        <v>151.7213545127889</v>
       </c>
       <c r="E4" t="n">
-        <v>121.1296542517467</v>
+        <v>143.9515846879988</v>
       </c>
       <c r="F4" t="n">
-        <v>130.8939203906291</v>
+        <v>143.9515846879988</v>
       </c>
       <c r="G4" t="n">
-        <v>200.7717558289623</v>
+        <v>141.8495439303346</v>
       </c>
       <c r="H4" t="n">
-        <v>131.8732538115618</v>
+        <v>171.8332732477233</v>
       </c>
       <c r="I4" t="n">
-        <v>199.9431629927599</v>
+        <v>143.9515846879988</v>
       </c>
       <c r="J4" t="n">
-        <v>137.0247404079103</v>
+        <v>170.1108745309249</v>
       </c>
       <c r="K4" t="n">
-        <v>131.7712084456769</v>
+        <v>127.6838917263959</v>
       </c>
       <c r="L4" t="n">
-        <v>131.8623487078521</v>
+        <v>144.2087629792355</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.71134648959034</v>
+        <v>33.79074347757921</v>
       </c>
       <c r="C5" t="n">
-        <v>56.6148390463138</v>
+        <v>32.85673704833336</v>
       </c>
       <c r="D5" t="n">
-        <v>56.71098530310019</v>
+        <v>33.79074347757921</v>
       </c>
       <c r="E5" t="n">
-        <v>55.80884218235551</v>
+        <v>32.63546364679186</v>
       </c>
       <c r="F5" t="n">
-        <v>55.80884218235551</v>
+        <v>32.63546364679186</v>
       </c>
       <c r="G5" t="n">
-        <v>56.55589792241049</v>
+        <v>33.6352949103996</v>
       </c>
       <c r="H5" t="n">
-        <v>56.71134648959034</v>
+        <v>33.79074347757921</v>
       </c>
       <c r="I5" t="n">
-        <v>55.72730508620849</v>
+        <v>32.80670207419731</v>
       </c>
       <c r="J5" t="n">
-        <v>56.71134648959034</v>
+        <v>33.79074347757921</v>
       </c>
       <c r="K5" t="n">
-        <v>56.71134648959034</v>
+        <v>33.79074347757921</v>
       </c>
       <c r="L5" t="n">
-        <v>56.71134648959034</v>
+        <v>33.79074347757921</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.2571714960268</v>
+        <v>200.9272043961423</v>
       </c>
       <c r="C6" t="n">
-        <v>185.5529856882498</v>
+        <v>131.4820307778948</v>
       </c>
       <c r="D6" t="n">
-        <v>198.0632183965422</v>
+        <v>131.7932744471843</v>
       </c>
       <c r="E6" t="n">
-        <v>168.1637095604815</v>
+        <v>121.1296542517469</v>
       </c>
       <c r="F6" t="n">
-        <v>126.2334675816813</v>
+        <v>130.8939203906289</v>
       </c>
       <c r="G6" t="n">
-        <v>185.4037513954277</v>
+        <v>200.7717558289626</v>
       </c>
       <c r="H6" t="n">
-        <v>185.5591999627806</v>
+        <v>131.8732538115617</v>
       </c>
       <c r="I6" t="n">
-        <v>184.5751585592252</v>
+        <v>199.9431629927599</v>
       </c>
       <c r="J6" t="n">
-        <v>185.5710510411588</v>
+        <v>137.0247404079103</v>
       </c>
       <c r="K6" t="n">
-        <v>124.1370303577366</v>
+        <v>131.771208445677</v>
       </c>
       <c r="L6" t="n">
-        <v>248.5497110724198</v>
+        <v>131.8623487078526</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.44146068101634</v>
+        <v>56.71134648959037</v>
       </c>
       <c r="C7" t="n">
-        <v>117.1755986651605</v>
+        <v>56.61483904631376</v>
       </c>
       <c r="D7" t="n">
-        <v>117.2721121205854</v>
+        <v>56.71098530310028</v>
       </c>
       <c r="E7" t="n">
-        <v>138.0182302848613</v>
+        <v>55.80884218235547</v>
       </c>
       <c r="F7" t="n">
-        <v>116.2880603817456</v>
+        <v>55.80884218235547</v>
       </c>
       <c r="G7" t="n">
-        <v>117.1166575412573</v>
+        <v>56.5558979224107</v>
       </c>
       <c r="H7" t="n">
-        <v>117.2721061084367</v>
+        <v>56.71134648959037</v>
       </c>
       <c r="I7" t="n">
-        <v>116.2880647050551</v>
+        <v>55.72730508620839</v>
       </c>
       <c r="J7" t="n">
-        <v>117.2721061084367</v>
+        <v>56.71134648959037</v>
       </c>
       <c r="K7" t="n">
-        <v>106.3615587228332</v>
+        <v>56.71134648959037</v>
       </c>
       <c r="L7" t="n">
-        <v>117.2721061084367</v>
+        <v>56.71134648959037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33.29705702209451</v>
+        <v>125.2571714960268</v>
       </c>
       <c r="C8" t="n">
-        <v>26.39622116569852</v>
+        <v>185.5529856882494</v>
       </c>
       <c r="D8" t="n">
-        <v>37.64883896859979</v>
+        <v>198.063218396542</v>
       </c>
       <c r="E8" t="n">
-        <v>43.42870921131165</v>
+        <v>168.1637095604811</v>
       </c>
       <c r="F8" t="n">
-        <v>43.42870921131165</v>
+        <v>126.233467581681</v>
       </c>
       <c r="G8" t="n">
-        <v>73.91222430035756</v>
+        <v>185.4037513954273</v>
       </c>
       <c r="H8" t="n">
-        <v>37.49758219044011</v>
+        <v>185.5591999627804</v>
       </c>
       <c r="I8" t="n">
-        <v>43.42870921131165</v>
+        <v>184.575158559225</v>
       </c>
       <c r="J8" t="n">
-        <v>72.83781372266697</v>
+        <v>185.571051041159</v>
       </c>
       <c r="K8" t="n">
-        <v>148.2423148102326</v>
+        <v>124.1370303577365</v>
       </c>
       <c r="L8" t="n">
-        <v>31.67508742391209</v>
+        <v>248.5497110724195</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>98.44146068101625</v>
+      </c>
+      <c r="C9" t="n">
+        <v>117.1755986651604</v>
+      </c>
+      <c r="D9" t="n">
+        <v>117.2721121205852</v>
+      </c>
+      <c r="E9" t="n">
+        <v>138.0182302848612</v>
+      </c>
+      <c r="F9" t="n">
+        <v>116.2880603817455</v>
+      </c>
+      <c r="G9" t="n">
+        <v>117.1166575412573</v>
+      </c>
+      <c r="H9" t="n">
+        <v>117.2721061084371</v>
+      </c>
+      <c r="I9" t="n">
+        <v>116.2880647050551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>117.2721061084371</v>
+      </c>
+      <c r="K9" t="n">
+        <v>106.3615587228329</v>
+      </c>
+      <c r="L9" t="n">
+        <v>117.2721061084371</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>33.29705702209457</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.39622116569849</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37.64883896859978</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.42870921131162</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.42870921131162</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.91222430035762</v>
+      </c>
+      <c r="H10" t="n">
+        <v>37.49758219044018</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.42870921131162</v>
+      </c>
+      <c r="J10" t="n">
+        <v>72.83781372266694</v>
+      </c>
+      <c r="K10" t="n">
+        <v>148.2423148102326</v>
+      </c>
+      <c r="L10" t="n">
+        <v>31.67508742391203</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>33.84747835843963</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27.23725568976714</v>
-      </c>
-      <c r="D9" t="n">
-        <v>38.49398311257272</v>
-      </c>
-      <c r="E9" t="n">
-        <v>44.07266852634394</v>
-      </c>
-      <c r="F9" t="n">
-        <v>44.07266852634394</v>
-      </c>
-      <c r="G9" t="n">
-        <v>74.02579255766463</v>
-      </c>
-      <c r="H9" t="n">
-        <v>38.43415214476232</v>
-      </c>
-      <c r="I9" t="n">
-        <v>44.07266852634394</v>
-      </c>
-      <c r="J9" t="n">
-        <v>73.30918895853964</v>
-      </c>
-      <c r="K9" t="n">
-        <v>147.0134552749604</v>
-      </c>
-      <c r="L9" t="n">
-        <v>32.33448046635829</v>
+      <c r="B11" t="n">
+        <v>33.84747835843961</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27.23725568976715</v>
+      </c>
+      <c r="D11" t="n">
+        <v>38.49398311257259</v>
+      </c>
+      <c r="E11" t="n">
+        <v>44.07266852634393</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.07266852634393</v>
+      </c>
+      <c r="G11" t="n">
+        <v>74.02579255766476</v>
+      </c>
+      <c r="H11" t="n">
+        <v>38.43415214476247</v>
+      </c>
+      <c r="I11" t="n">
+        <v>44.07266852634393</v>
+      </c>
+      <c r="J11" t="n">
+        <v>73.30918895853955</v>
+      </c>
+      <c r="K11" t="n">
+        <v>147.0134552749605</v>
+      </c>
+      <c r="L11" t="n">
+        <v>32.33448046635844</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117.2070136106024</v>
+        <v>33.97441391177394</v>
       </c>
       <c r="C2" t="n">
-        <v>170.7281443133367</v>
+        <v>28.24397897426898</v>
       </c>
       <c r="D2" t="n">
-        <v>210.5820383690381</v>
+        <v>39.650874602581</v>
       </c>
       <c r="E2" t="n">
-        <v>192.2063230167401</v>
+        <v>45.02504457497191</v>
       </c>
       <c r="F2" t="n">
-        <v>192.2063230167401</v>
+        <v>45.02504457497191</v>
       </c>
       <c r="G2" t="n">
-        <v>224.9475555846267</v>
+        <v>74.76004292357743</v>
       </c>
       <c r="H2" t="n">
-        <v>852.5641928623509</v>
+        <v>40.26940047996243</v>
       </c>
       <c r="I2" t="n">
-        <v>192.2063230167401</v>
+        <v>45.02504457497191</v>
       </c>
       <c r="J2" t="n">
-        <v>219.1738397841669</v>
+        <v>74.40975269071573</v>
       </c>
       <c r="K2" t="n">
-        <v>188.0485449347547</v>
+        <v>147.1413538339636</v>
       </c>
       <c r="L2" t="n">
-        <v>455.2073439299704</v>
+        <v>33.47718544864282</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.72171754742904</v>
+        <v>33.98381806313689</v>
       </c>
       <c r="C3" t="n">
-        <v>32.76300080770094</v>
+        <v>28.14174587918269</v>
       </c>
       <c r="D3" t="n">
-        <v>33.72171754742904</v>
+        <v>39.68112719175725</v>
       </c>
       <c r="E3" t="n">
-        <v>32.56907445155267</v>
+        <v>45.1641422196183</v>
       </c>
       <c r="F3" t="n">
-        <v>32.56907445155267</v>
+        <v>45.1641422196183</v>
       </c>
       <c r="G3" t="n">
-        <v>33.56547923848701</v>
+        <v>75.33707651473692</v>
       </c>
       <c r="H3" t="n">
-        <v>33.72171754742904</v>
+        <v>39.68112719175725</v>
       </c>
       <c r="I3" t="n">
-        <v>32.73223316531977</v>
+        <v>45.1641422196183</v>
       </c>
       <c r="J3" t="n">
-        <v>33.72171754742904</v>
+        <v>74.99128858688927</v>
       </c>
       <c r="K3" t="n">
-        <v>33.72171754742904</v>
+        <v>148.9068181524989</v>
       </c>
       <c r="L3" t="n">
-        <v>33.72171754742904</v>
+        <v>33.19027156537108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137.3438594480404</v>
+        <v>117.2070136106042</v>
       </c>
       <c r="C4" t="n">
-        <v>136.8909562929621</v>
+        <v>170.7281443133369</v>
       </c>
       <c r="D4" t="n">
-        <v>137.2788259825617</v>
+        <v>210.5820383690378</v>
       </c>
       <c r="E4" t="n">
-        <v>126.046184595153</v>
+        <v>192.2063230167421</v>
       </c>
       <c r="F4" t="n">
-        <v>136.3782980015123</v>
+        <v>192.2063230167421</v>
       </c>
       <c r="G4" t="n">
-        <v>137.1876211391085</v>
+        <v>224.9475555846509</v>
       </c>
       <c r="H4" t="n">
-        <v>210.044948688043</v>
+        <v>852.5641928623425</v>
       </c>
       <c r="I4" t="n">
-        <v>136.3543750659295</v>
+        <v>192.2063230167421</v>
       </c>
       <c r="J4" t="n">
-        <v>142.8032961962975</v>
+        <v>219.1738397841711</v>
       </c>
       <c r="K4" t="n">
-        <v>137.2499876868072</v>
+        <v>188.048544934756</v>
       </c>
       <c r="L4" t="n">
-        <v>137.4335861061834</v>
+        <v>455.2073439299542</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.34728117734694</v>
+        <v>33.72171754742261</v>
       </c>
       <c r="C5" t="n">
-        <v>58.24962076688345</v>
+        <v>32.76300080770101</v>
       </c>
       <c r="D5" t="n">
-        <v>58.34689487976114</v>
+        <v>33.72171754742261</v>
       </c>
       <c r="E5" t="n">
-        <v>57.44130239751575</v>
+        <v>32.56907445155262</v>
       </c>
       <c r="F5" t="n">
-        <v>57.44130239751575</v>
+        <v>32.56907445155272</v>
       </c>
       <c r="G5" t="n">
-        <v>58.19104286844237</v>
+        <v>33.56547923851569</v>
       </c>
       <c r="H5" t="n">
-        <v>58.34728117734694</v>
+        <v>33.72171754742261</v>
       </c>
       <c r="I5" t="n">
-        <v>57.3577967952272</v>
+        <v>32.73223316531979</v>
       </c>
       <c r="J5" t="n">
-        <v>58.34728117734694</v>
+        <v>33.72171754742261</v>
       </c>
       <c r="K5" t="n">
-        <v>58.34728117734694</v>
+        <v>33.72171754742261</v>
       </c>
       <c r="L5" t="n">
-        <v>58.34728117734694</v>
+        <v>33.72171754742261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130.6741056816122</v>
+        <v>137.3438594480326</v>
       </c>
       <c r="C6" t="n">
-        <v>194.541211285477</v>
+        <v>136.8909562929624</v>
       </c>
       <c r="D6" t="n">
-        <v>207.7902934841363</v>
+        <v>137.2788259825396</v>
       </c>
       <c r="E6" t="n">
-        <v>176.1710966923448</v>
+        <v>126.0461845951529</v>
       </c>
       <c r="F6" t="n">
-        <v>131.7593083651292</v>
+        <v>136.3782980015124</v>
       </c>
       <c r="G6" t="n">
-        <v>194.3897949124838</v>
+        <v>137.1876211391254</v>
       </c>
       <c r="H6" t="n">
-        <v>194.5460332213927</v>
+        <v>210.0449486880529</v>
       </c>
       <c r="I6" t="n">
-        <v>193.5565488392565</v>
+        <v>136.3543750659294</v>
       </c>
       <c r="J6" t="n">
-        <v>194.5585858897985</v>
+        <v>142.8032961962689</v>
       </c>
       <c r="K6" t="n">
-        <v>129.4876518351719</v>
+        <v>137.2499876868195</v>
       </c>
       <c r="L6" t="n">
-        <v>261.2656024249559</v>
+        <v>137.4335861061879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.9861373151955</v>
+        <v>58.3472811773301</v>
       </c>
       <c r="C7" t="n">
-        <v>133.2441535787596</v>
+        <v>58.24962076688351</v>
       </c>
       <c r="D7" t="n">
-        <v>133.3418133853675</v>
+        <v>58.34689487974249</v>
       </c>
       <c r="E7" t="n">
-        <v>158.1502893127419</v>
+        <v>57.44130239751585</v>
       </c>
       <c r="F7" t="n">
-        <v>132.3523163163816</v>
+        <v>57.44130239751585</v>
       </c>
       <c r="G7" t="n">
-        <v>133.1855756803097</v>
+        <v>58.19104286842315</v>
       </c>
       <c r="H7" t="n">
-        <v>133.3418139892143</v>
+        <v>58.3472811773301</v>
       </c>
       <c r="I7" t="n">
-        <v>132.3523296071033</v>
+        <v>57.35779679522718</v>
       </c>
       <c r="J7" t="n">
-        <v>133.3418139892143</v>
+        <v>58.3472811773301</v>
       </c>
       <c r="K7" t="n">
-        <v>120.3888468728054</v>
+        <v>58.3472811773301</v>
       </c>
       <c r="L7" t="n">
-        <v>133.3418139892143</v>
+        <v>58.3472811773301</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32.27810950553072</v>
+        <v>130.6741056816122</v>
       </c>
       <c r="C8" t="n">
-        <v>26.23087880769721</v>
+        <v>194.541211285477</v>
       </c>
       <c r="D8" t="n">
-        <v>36.76953651602059</v>
+        <v>207.7902934841447</v>
       </c>
       <c r="E8" t="n">
-        <v>42.6868038162866</v>
+        <v>176.1710966923452</v>
       </c>
       <c r="F8" t="n">
-        <v>42.6868038162866</v>
+        <v>131.7593083651293</v>
       </c>
       <c r="G8" t="n">
-        <v>72.18879924185971</v>
+        <v>194.3897949124528</v>
       </c>
       <c r="H8" t="n">
-        <v>24.10937738589742</v>
+        <v>194.5460332214081</v>
       </c>
       <c r="I8" t="n">
-        <v>42.6868038162866</v>
+        <v>193.5565488392568</v>
       </c>
       <c r="J8" t="n">
-        <v>72.07282876433422</v>
+        <v>194.5585858897833</v>
       </c>
       <c r="K8" t="n">
-        <v>146.528901826598</v>
+        <v>129.4876518351789</v>
       </c>
       <c r="L8" t="n">
-        <v>25.88255655688679</v>
+        <v>261.265602424933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>110.986137315198</v>
+      </c>
+      <c r="C9" t="n">
+        <v>133.2441535787596</v>
+      </c>
+      <c r="D9" t="n">
+        <v>133.3418133853483</v>
+      </c>
+      <c r="E9" t="n">
+        <v>158.1502893127422</v>
+      </c>
+      <c r="F9" t="n">
+        <v>132.3523163163817</v>
+      </c>
+      <c r="G9" t="n">
+        <v>133.1855756802995</v>
+      </c>
+      <c r="H9" t="n">
+        <v>133.3418139892062</v>
+      </c>
+      <c r="I9" t="n">
+        <v>132.3523296071033</v>
+      </c>
+      <c r="J9" t="n">
+        <v>133.3418139892062</v>
+      </c>
+      <c r="K9" t="n">
+        <v>120.3888468727974</v>
+      </c>
+      <c r="L9" t="n">
+        <v>133.3418139892062</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>32.27810950552493</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.23087880769727</v>
+      </c>
+      <c r="D10" t="n">
+        <v>36.76953651602211</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42.6868038162866</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.6868038162866</v>
+      </c>
+      <c r="G10" t="n">
+        <v>72.18879924185453</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24.10937738589389</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42.6868038162866</v>
+      </c>
+      <c r="J10" t="n">
+        <v>72.07282876434073</v>
+      </c>
+      <c r="K10" t="n">
+        <v>146.5289018265881</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25.88255655688492</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>33.19831108230301</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27.37452836717105</v>
-      </c>
-      <c r="D9" t="n">
-        <v>38.32609156643042</v>
-      </c>
-      <c r="E9" t="n">
-        <v>43.89784770664694</v>
-      </c>
-      <c r="F9" t="n">
-        <v>43.89784770664694</v>
-      </c>
-      <c r="G9" t="n">
-        <v>73.32756673144793</v>
-      </c>
-      <c r="H9" t="n">
-        <v>33.18420469407806</v>
-      </c>
-      <c r="I9" t="n">
-        <v>43.89784770664694</v>
-      </c>
-      <c r="J9" t="n">
-        <v>73.08184417087111</v>
-      </c>
-      <c r="K9" t="n">
-        <v>146.0593943277162</v>
-      </c>
-      <c r="L9" t="n">
-        <v>30.15215183147875</v>
+      <c r="B11" t="n">
+        <v>33.19831108228986</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27.37452836717108</v>
+      </c>
+      <c r="D11" t="n">
+        <v>38.32609156643257</v>
+      </c>
+      <c r="E11" t="n">
+        <v>43.89784770664692</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.89784770664692</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.3275667314516</v>
+      </c>
+      <c r="H11" t="n">
+        <v>33.18420469407236</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.89784770664692</v>
+      </c>
+      <c r="J11" t="n">
+        <v>73.08184417087661</v>
+      </c>
+      <c r="K11" t="n">
+        <v>146.0593943277045</v>
+      </c>
+      <c r="L11" t="n">
+        <v>30.15215183147569</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105.0010829990157</v>
+        <v>36.88740153893889</v>
       </c>
       <c r="C2" t="n">
-        <v>160.9552989639604</v>
+        <v>28.11113015759472</v>
       </c>
       <c r="D2" t="n">
-        <v>153.8711174156846</v>
+        <v>39.17265355028189</v>
       </c>
       <c r="E2" t="n">
-        <v>162.5264268503054</v>
+        <v>44.75892988768288</v>
       </c>
       <c r="F2" t="n">
-        <v>162.5264268503054</v>
+        <v>44.75892988768288</v>
       </c>
       <c r="G2" t="n">
-        <v>148.7471545456568</v>
+        <v>74.62633315256521</v>
       </c>
       <c r="H2" t="n">
-        <v>177.0006965532546</v>
+        <v>39.18453274564625</v>
       </c>
       <c r="I2" t="n">
-        <v>162.5264268503054</v>
+        <v>44.75892988768288</v>
       </c>
       <c r="J2" t="n">
-        <v>184.6527149429444</v>
+        <v>73.95528912536</v>
       </c>
       <c r="K2" t="n">
-        <v>140.6410254781322</v>
+        <v>145.9370482633361</v>
       </c>
       <c r="L2" t="n">
-        <v>149.250121799302</v>
+        <v>32.79169270648031</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.5037840796044</v>
+        <v>36.95336304310676</v>
       </c>
       <c r="C3" t="n">
-        <v>32.5741836968126</v>
+        <v>28.01092066142786</v>
       </c>
       <c r="D3" t="n">
-        <v>33.5037840796044</v>
+        <v>39.2525486171146</v>
       </c>
       <c r="E3" t="n">
-        <v>32.47553282567203</v>
+        <v>44.91958782100335</v>
       </c>
       <c r="F3" t="n">
-        <v>32.47553282567203</v>
+        <v>44.91958782100335</v>
       </c>
       <c r="G3" t="n">
-        <v>33.34899031876839</v>
+        <v>75.27856940077341</v>
       </c>
       <c r="H3" t="n">
-        <v>33.5037840796044</v>
+        <v>39.2525486171146</v>
       </c>
       <c r="I3" t="n">
-        <v>32.52367694594559</v>
+        <v>44.91958782100335</v>
       </c>
       <c r="J3" t="n">
-        <v>33.5037840796044</v>
+        <v>74.55879913316083</v>
       </c>
       <c r="K3" t="n">
-        <v>33.5037840796044</v>
+        <v>147.730842648073</v>
       </c>
       <c r="L3" t="n">
-        <v>33.5037840796044</v>
+        <v>32.78995789503968</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.482666765566</v>
+        <v>105.0010829990435</v>
       </c>
       <c r="C4" t="n">
-        <v>131.2281554049258</v>
+        <v>160.9552989639603</v>
       </c>
       <c r="D4" t="n">
-        <v>131.5100896033991</v>
+        <v>153.871117415695</v>
       </c>
       <c r="E4" t="n">
-        <v>120.9068795828337</v>
+        <v>162.526426850305</v>
       </c>
       <c r="F4" t="n">
-        <v>130.6338412324735</v>
+        <v>162.526426850305</v>
       </c>
       <c r="G4" t="n">
-        <v>131.4281822119391</v>
+        <v>148.747154545653</v>
       </c>
       <c r="H4" t="n">
-        <v>200.5628122960844</v>
+        <v>177.0006965532708</v>
       </c>
       <c r="I4" t="n">
-        <v>199.5025596319072</v>
+        <v>162.526426850305</v>
       </c>
       <c r="J4" t="n">
-        <v>136.739175051391</v>
+        <v>184.6527149429406</v>
       </c>
       <c r="K4" t="n">
-        <v>131.503676044034</v>
+        <v>140.6410254781424</v>
       </c>
       <c r="L4" t="n">
-        <v>131.5851703431967</v>
+        <v>149.2501217993164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.30216384740891</v>
+        <v>33.5037840796095</v>
       </c>
       <c r="C5" t="n">
-        <v>56.20670945622776</v>
+        <v>32.57418369681272</v>
       </c>
       <c r="D5" t="n">
-        <v>56.30182022899709</v>
+        <v>33.5037840796095</v>
       </c>
       <c r="E5" t="n">
-        <v>55.43235596457356</v>
+        <v>32.47553282567209</v>
       </c>
       <c r="F5" t="n">
-        <v>55.43235596457356</v>
+        <v>32.47553282567208</v>
       </c>
       <c r="G5" t="n">
-        <v>56.14737008657285</v>
+        <v>33.34899031875851</v>
       </c>
       <c r="H5" t="n">
-        <v>56.30216384740891</v>
+        <v>33.5037840796095</v>
       </c>
       <c r="I5" t="n">
-        <v>55.32205671375012</v>
+        <v>32.52367694594559</v>
       </c>
       <c r="J5" t="n">
-        <v>56.30216384740891</v>
+        <v>33.50378407960947</v>
       </c>
       <c r="K5" t="n">
-        <v>56.30216384740891</v>
+        <v>33.5037840796095</v>
       </c>
       <c r="L5" t="n">
-        <v>56.30216384740891</v>
+        <v>33.5037840796095</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>124.5656577336879</v>
+        <v>200.4826667655686</v>
       </c>
       <c r="C6" t="n">
-        <v>184.5357783245752</v>
+        <v>131.2281554049264</v>
       </c>
       <c r="D6" t="n">
-        <v>196.9441665627685</v>
+        <v>131.5100896034104</v>
       </c>
       <c r="E6" t="n">
-        <v>167.2433731964458</v>
+        <v>120.9068795828336</v>
       </c>
       <c r="F6" t="n">
-        <v>125.5518108613358</v>
+        <v>130.6338412324736</v>
       </c>
       <c r="G6" t="n">
-        <v>184.3587815645624</v>
+        <v>131.4281822119451</v>
       </c>
       <c r="H6" t="n">
-        <v>184.5135753255587</v>
+        <v>200.562812296062</v>
       </c>
       <c r="I6" t="n">
-        <v>183.5334681917394</v>
+        <v>199.5025596319101</v>
       </c>
       <c r="J6" t="n">
-        <v>184.5253568127216</v>
+        <v>136.7391750513885</v>
       </c>
       <c r="K6" t="n">
-        <v>123.4520943866019</v>
+        <v>131.5036760440714</v>
       </c>
       <c r="L6" t="n">
-        <v>247.134188017606</v>
+        <v>131.5851703432029</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>101.2172381219478</v>
+        <v>56.30216384740316</v>
       </c>
       <c r="C7" t="n">
-        <v>120.7571982606062</v>
+        <v>56.20670945622783</v>
       </c>
       <c r="D7" t="n">
-        <v>120.8526585284269</v>
+        <v>56.301820229005</v>
       </c>
       <c r="E7" t="n">
-        <v>142.5313976221664</v>
+        <v>55.43235596457372</v>
       </c>
       <c r="F7" t="n">
-        <v>119.8725413279381</v>
+        <v>55.43235596457372</v>
       </c>
       <c r="G7" t="n">
-        <v>120.6978588909513</v>
+        <v>56.14737008656836</v>
       </c>
       <c r="H7" t="n">
-        <v>120.8526526517872</v>
+        <v>56.30216384740316</v>
       </c>
       <c r="I7" t="n">
-        <v>119.8725455181286</v>
+        <v>55.32205671375017</v>
       </c>
       <c r="J7" t="n">
-        <v>120.8526526517872</v>
+        <v>56.30216384740316</v>
       </c>
       <c r="K7" t="n">
-        <v>96.12815932653584</v>
+        <v>56.30216384740316</v>
       </c>
       <c r="L7" t="n">
-        <v>120.8526526517872</v>
+        <v>56.30216384740316</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35.4277855194338</v>
+        <v>124.5656577336805</v>
       </c>
       <c r="C8" t="n">
-        <v>26.15520119506519</v>
+        <v>184.5357783245749</v>
       </c>
       <c r="D8" t="n">
-        <v>37.49116327904923</v>
+        <v>196.944166562765</v>
       </c>
       <c r="E8" t="n">
-        <v>42.95031178758201</v>
+        <v>167.2433731964455</v>
       </c>
       <c r="F8" t="n">
-        <v>42.95031178758201</v>
+        <v>125.5518108613357</v>
       </c>
       <c r="G8" t="n">
-        <v>73.69008582645812</v>
+        <v>184.3587815645678</v>
       </c>
       <c r="H8" t="n">
-        <v>37.28158345346971</v>
+        <v>184.5135753255611</v>
       </c>
       <c r="I8" t="n">
-        <v>42.95031178758201</v>
+        <v>183.5334681917393</v>
       </c>
       <c r="J8" t="n">
-        <v>72.20771984761974</v>
+        <v>184.5253568127218</v>
       </c>
       <c r="K8" t="n">
-        <v>146.3011687607509</v>
+        <v>123.4520943866026</v>
       </c>
       <c r="L8" t="n">
-        <v>31.46085570954309</v>
+        <v>247.134188017616</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>101.2172381219262</v>
+      </c>
+      <c r="C9" t="n">
+        <v>120.7571982606062</v>
+      </c>
+      <c r="D9" t="n">
+        <v>120.852658528422</v>
+      </c>
+      <c r="E9" t="n">
+        <v>142.5313976221663</v>
+      </c>
+      <c r="F9" t="n">
+        <v>119.8725413279382</v>
+      </c>
+      <c r="G9" t="n">
+        <v>120.6978588909523</v>
+      </c>
+      <c r="H9" t="n">
+        <v>120.8526526517925</v>
+      </c>
+      <c r="I9" t="n">
+        <v>119.8725455181287</v>
+      </c>
+      <c r="J9" t="n">
+        <v>120.8526526517925</v>
+      </c>
+      <c r="K9" t="n">
+        <v>96.12815932651461</v>
+      </c>
+      <c r="L9" t="n">
+        <v>120.8526526517925</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>35.42778551943088</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.1552011950652</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37.49116327904503</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42.95031178758202</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.95031178758202</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.69008582645201</v>
+      </c>
+      <c r="H10" t="n">
+        <v>37.28158345348076</v>
+      </c>
+      <c r="I10" t="n">
+        <v>42.95031178758202</v>
+      </c>
+      <c r="J10" t="n">
+        <v>72.20771984762284</v>
+      </c>
+      <c r="K10" t="n">
+        <v>146.3011687607615</v>
+      </c>
+      <c r="L10" t="n">
+        <v>31.46085570954817</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>36.19325890396074</v>
-      </c>
-      <c r="C9" t="n">
-        <v>27.26677188657279</v>
-      </c>
-      <c r="D9" t="n">
-        <v>38.37121760825907</v>
-      </c>
-      <c r="E9" t="n">
-        <v>43.8629030167658</v>
-      </c>
-      <c r="F9" t="n">
-        <v>43.8629030167658</v>
-      </c>
-      <c r="G9" t="n">
-        <v>73.90356806406105</v>
-      </c>
-      <c r="H9" t="n">
-        <v>38.28773731509725</v>
-      </c>
-      <c r="I9" t="n">
-        <v>43.8629030167658</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>36.19325890394067</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27.26677188657272</v>
+      </c>
+      <c r="D11" t="n">
+        <v>38.37121760825617</v>
+      </c>
+      <c r="E11" t="n">
+        <v>43.86290301676581</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.86290301676581</v>
+      </c>
+      <c r="G11" t="n">
+        <v>73.9035680640589</v>
+      </c>
+      <c r="H11" t="n">
+        <v>38.28773731509603</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.86290301676581</v>
+      </c>
+      <c r="J11" t="n">
         <v>72.8855405579931</v>
       </c>
-      <c r="K9" t="n">
-        <v>145.2865420884976</v>
-      </c>
-      <c r="L9" t="n">
-        <v>32.18694697647827</v>
+      <c r="K11" t="n">
+        <v>145.2865420884945</v>
+      </c>
+      <c r="L11" t="n">
+        <v>32.186946976477</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.50171429729468</v>
+        <v>45.24467441112654</v>
       </c>
       <c r="C2" t="n">
-        <v>145.2453453550544</v>
+        <v>28.0568306136895</v>
       </c>
       <c r="D2" t="n">
-        <v>150.6824351342627</v>
+        <v>39.00142339752708</v>
       </c>
       <c r="E2" t="n">
-        <v>143.5835784117008</v>
+        <v>44.5420244224511</v>
       </c>
       <c r="F2" t="n">
-        <v>143.5835784117008</v>
+        <v>44.5420244224511</v>
       </c>
       <c r="G2" t="n">
-        <v>141.4268071456558</v>
+        <v>75.35206144783456</v>
       </c>
       <c r="H2" t="n">
-        <v>168.2831851021036</v>
+        <v>39.00790153809702</v>
       </c>
       <c r="I2" t="n">
-        <v>143.5835784117008</v>
+        <v>44.5420244224511</v>
       </c>
       <c r="J2" t="n">
-        <v>172.3479023195403</v>
+        <v>73.8507771728051</v>
       </c>
       <c r="K2" t="n">
-        <v>133.9161247780786</v>
+        <v>146.821189822564</v>
       </c>
       <c r="L2" t="n">
-        <v>143.041028333478</v>
+        <v>32.67818604053397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.61630938278153</v>
+        <v>45.46180785323433</v>
       </c>
       <c r="C3" t="n">
-        <v>32.67636053982793</v>
+        <v>27.97436344059896</v>
       </c>
       <c r="D3" t="n">
-        <v>33.61630938278153</v>
+        <v>39.08280138801116</v>
       </c>
       <c r="E3" t="n">
-        <v>32.52772857580768</v>
+        <v>44.72200266534513</v>
       </c>
       <c r="F3" t="n">
-        <v>32.52772857580768</v>
+        <v>44.72200266534513</v>
       </c>
       <c r="G3" t="n">
-        <v>33.46039835451734</v>
+        <v>76.02475366054716</v>
       </c>
       <c r="H3" t="n">
-        <v>33.61630938278153</v>
+        <v>39.08280138801116</v>
       </c>
       <c r="I3" t="n">
-        <v>32.62910221331591</v>
+        <v>44.72200266534513</v>
       </c>
       <c r="J3" t="n">
-        <v>33.61630938278153</v>
+        <v>74.46698458815968</v>
       </c>
       <c r="K3" t="n">
-        <v>33.61630938278153</v>
+        <v>148.6374055986924</v>
       </c>
       <c r="L3" t="n">
-        <v>33.61630938278153</v>
+        <v>32.68152144643538</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.6669424567116</v>
+        <v>89.50171429729465</v>
       </c>
       <c r="C4" t="n">
-        <v>131.3237103280792</v>
+        <v>145.2453453550544</v>
       </c>
       <c r="D4" t="n">
-        <v>131.6284017707448</v>
+        <v>150.6824351342631</v>
       </c>
       <c r="E4" t="n">
-        <v>120.9809375554102</v>
+        <v>143.5835784117008</v>
       </c>
       <c r="F4" t="n">
-        <v>130.7319653110395</v>
+        <v>143.5835784117008</v>
       </c>
       <c r="G4" t="n">
-        <v>131.53724884559</v>
+        <v>141.4268071456579</v>
       </c>
       <c r="H4" t="n">
-        <v>200.8203924446276</v>
+        <v>168.2831851021037</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7059527043886</v>
+        <v>143.5835784117008</v>
       </c>
       <c r="J4" t="n">
-        <v>199.3425360137321</v>
+        <v>172.3479023195407</v>
       </c>
       <c r="K4" t="n">
-        <v>131.6197014004368</v>
+        <v>133.9161247780786</v>
       </c>
       <c r="L4" t="n">
-        <v>131.701937727521</v>
+        <v>143.0410283334782</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.24527014434253</v>
+        <v>33.61630938278149</v>
       </c>
       <c r="C5" t="n">
-        <v>56.14899886390223</v>
+        <v>32.676360539828</v>
       </c>
       <c r="D5" t="n">
-        <v>56.24491404948765</v>
+        <v>33.61630938278149</v>
       </c>
       <c r="E5" t="n">
-        <v>55.35995003870709</v>
+        <v>32.52772857580765</v>
       </c>
       <c r="F5" t="n">
-        <v>55.35995003870709</v>
+        <v>32.52772857580765</v>
       </c>
       <c r="G5" t="n">
-        <v>56.08935911607843</v>
+        <v>33.46039835451729</v>
       </c>
       <c r="H5" t="n">
-        <v>56.24527014434253</v>
+        <v>33.61630938278149</v>
       </c>
       <c r="I5" t="n">
-        <v>55.25806297487691</v>
+        <v>32.62910221331587</v>
       </c>
       <c r="J5" t="n">
-        <v>56.24527014434253</v>
+        <v>33.61630938278149</v>
       </c>
       <c r="K5" t="n">
-        <v>56.24527014434253</v>
+        <v>33.61630938278149</v>
       </c>
       <c r="L5" t="n">
-        <v>56.24527014434253</v>
+        <v>33.61630938278149</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>124.4918271690012</v>
+        <v>200.6669424567114</v>
       </c>
       <c r="C6" t="n">
-        <v>184.3490014215259</v>
+        <v>131.3237103280788</v>
       </c>
       <c r="D6" t="n">
-        <v>196.7446250809782</v>
+        <v>131.6284017707447</v>
       </c>
       <c r="E6" t="n">
-        <v>167.0795997208623</v>
+        <v>120.98093755541</v>
       </c>
       <c r="F6" t="n">
-        <v>125.4625689579048</v>
+        <v>130.7319653110397</v>
       </c>
       <c r="G6" t="n">
-        <v>184.179712940037</v>
+        <v>131.53724884559</v>
       </c>
       <c r="H6" t="n">
-        <v>184.3356239684703</v>
+        <v>200.8203924446277</v>
       </c>
       <c r="I6" t="n">
-        <v>183.3484167988354</v>
+        <v>130.7059527043887</v>
       </c>
       <c r="J6" t="n">
-        <v>184.3473849919537</v>
+        <v>199.3425360137321</v>
       </c>
       <c r="K6" t="n">
-        <v>123.3801979191126</v>
+        <v>131.6197014004368</v>
       </c>
       <c r="L6" t="n">
-        <v>246.8474737856494</v>
+        <v>131.7019377275211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.02799802763577</v>
+        <v>56.24527014434253</v>
       </c>
       <c r="C7" t="n">
-        <v>116.6602399798673</v>
+        <v>56.14899886390224</v>
       </c>
       <c r="D7" t="n">
-        <v>116.7565171672969</v>
+        <v>56.24491404948754</v>
       </c>
       <c r="E7" t="n">
-        <v>137.3816114510198</v>
+        <v>55.35995003870715</v>
       </c>
       <c r="F7" t="n">
-        <v>115.7692999776295</v>
+        <v>55.35995003870715</v>
       </c>
       <c r="G7" t="n">
-        <v>116.6006002320433</v>
+        <v>56.08935911607844</v>
       </c>
       <c r="H7" t="n">
-        <v>116.7565112603075</v>
+        <v>56.24527014434253</v>
       </c>
       <c r="I7" t="n">
-        <v>115.7693040908418</v>
+        <v>55.25806297487699</v>
       </c>
       <c r="J7" t="n">
-        <v>116.7565112603075</v>
+        <v>56.24527014434253</v>
       </c>
       <c r="K7" t="n">
-        <v>105.464885530983</v>
+        <v>56.24527014434253</v>
       </c>
       <c r="L7" t="n">
-        <v>116.7565112603075</v>
+        <v>56.24527014434253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44.30375310203687</v>
+        <v>124.4918271690011</v>
       </c>
       <c r="C8" t="n">
-        <v>26.49319365273436</v>
+        <v>184.3490014215258</v>
       </c>
       <c r="D8" t="n">
-        <v>37.40071364713583</v>
+        <v>196.7446250809781</v>
       </c>
       <c r="E8" t="n">
-        <v>43.21151611283793</v>
+        <v>167.0795997208623</v>
       </c>
       <c r="F8" t="n">
-        <v>43.21151611283793</v>
+        <v>125.4625689579047</v>
       </c>
       <c r="G8" t="n">
-        <v>74.61104781532535</v>
+        <v>184.1797129400368</v>
       </c>
       <c r="H8" t="n">
-        <v>37.30069431176201</v>
+        <v>184.3356239684704</v>
       </c>
       <c r="I8" t="n">
-        <v>43.21151611283793</v>
+        <v>183.3484167988354</v>
       </c>
       <c r="J8" t="n">
-        <v>72.40233319802165</v>
+        <v>184.3473849919537</v>
       </c>
       <c r="K8" t="n">
-        <v>147.3726130245866</v>
+        <v>123.3801979191127</v>
       </c>
       <c r="L8" t="n">
-        <v>31.48462319114587</v>
+        <v>246.8474737856495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>98.02799802763593</v>
+      </c>
+      <c r="C9" t="n">
+        <v>116.6602399798675</v>
+      </c>
+      <c r="D9" t="n">
+        <v>116.7565171672971</v>
+      </c>
+      <c r="E9" t="n">
+        <v>137.3816114510202</v>
+      </c>
+      <c r="F9" t="n">
+        <v>115.7692999776297</v>
+      </c>
+      <c r="G9" t="n">
+        <v>116.6006002320436</v>
+      </c>
+      <c r="H9" t="n">
+        <v>116.7565112603077</v>
+      </c>
+      <c r="I9" t="n">
+        <v>115.7693040908422</v>
+      </c>
+      <c r="J9" t="n">
+        <v>116.7565112603077</v>
+      </c>
+      <c r="K9" t="n">
+        <v>105.4648855309831</v>
+      </c>
+      <c r="L9" t="n">
+        <v>116.7565112603077</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>44.30375310203686</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26.49319365273439</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37.40071364713587</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.21151611283797</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.21151611283797</v>
+      </c>
+      <c r="G10" t="n">
+        <v>74.61104781532542</v>
+      </c>
+      <c r="H10" t="n">
+        <v>37.300694311762</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.21151611283797</v>
+      </c>
+      <c r="J10" t="n">
+        <v>72.40233319802165</v>
+      </c>
+      <c r="K10" t="n">
+        <v>147.3726130245867</v>
+      </c>
+      <c r="L10" t="n">
+        <v>31.48462319114595</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>44.71775580883019</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>44.7177558088302</v>
+      </c>
+      <c r="C11" t="n">
         <v>27.38289364000307</v>
       </c>
-      <c r="D9" t="n">
-        <v>38.2360681149332</v>
-      </c>
-      <c r="E9" t="n">
-        <v>43.8547482274253</v>
-      </c>
-      <c r="F9" t="n">
-        <v>43.8547482274253</v>
-      </c>
-      <c r="G9" t="n">
-        <v>74.7088207830455</v>
-      </c>
-      <c r="H9" t="n">
-        <v>38.19703713916533</v>
-      </c>
-      <c r="I9" t="n">
-        <v>43.8547482274253</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="D11" t="n">
+        <v>38.23606811493322</v>
+      </c>
+      <c r="E11" t="n">
+        <v>43.85474822742532</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.85474822742532</v>
+      </c>
+      <c r="G11" t="n">
+        <v>74.70882078304545</v>
+      </c>
+      <c r="H11" t="n">
+        <v>38.19703713916538</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.85474822742532</v>
+      </c>
+      <c r="J11" t="n">
         <v>72.91135421063868</v>
       </c>
-      <c r="K9" t="n">
-        <v>146.2457051706908</v>
-      </c>
-      <c r="L9" t="n">
-        <v>32.13359352008882</v>
+      <c r="K11" t="n">
+        <v>146.2457051706909</v>
+      </c>
+      <c r="L11" t="n">
+        <v>32.1335935200888</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>381.2745780932896</v>
+        <v>88.7702670876036</v>
       </c>
       <c r="C2" t="n">
-        <v>285.5522713084166</v>
+        <v>54.53105205444177</v>
       </c>
       <c r="D2" t="n">
-        <v>1345.572469537031</v>
+        <v>89.83049016048983</v>
       </c>
       <c r="E2" t="n">
-        <v>285.5522713084166</v>
+        <v>54.53105205444177</v>
       </c>
       <c r="F2" t="n">
-        <v>285.5522713084166</v>
+        <v>54.53105205444177</v>
       </c>
       <c r="G2" t="n">
-        <v>773.8248026204978</v>
+        <v>89.0656276815718</v>
       </c>
       <c r="H2" t="n">
-        <v>2275.070907381289</v>
+        <v>90.60987460402424</v>
       </c>
       <c r="I2" t="n">
-        <v>285.5522713084166</v>
+        <v>54.53105205444177</v>
       </c>
       <c r="J2" t="n">
-        <v>590.6128384072333</v>
+        <v>88.96578129376219</v>
       </c>
       <c r="K2" t="n">
-        <v>431.510748293862</v>
+        <v>88.81993394079416</v>
       </c>
       <c r="L2" t="n">
-        <v>384.7268137327308</v>
+        <v>88.73630236930528</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.05370851408649</v>
+        <v>89.37897008043177</v>
       </c>
       <c r="C3" t="n">
-        <v>33.06614660054102</v>
+        <v>54.71488517218057</v>
       </c>
       <c r="D3" t="n">
-        <v>35.05370851408649</v>
+        <v>89.37897008043177</v>
       </c>
       <c r="E3" t="n">
-        <v>33.20395281434634</v>
+        <v>54.71488517218057</v>
       </c>
       <c r="F3" t="n">
-        <v>33.20395281434634</v>
+        <v>54.71488517218057</v>
       </c>
       <c r="G3" t="n">
-        <v>34.87706058458205</v>
+        <v>89.26153742966123</v>
       </c>
       <c r="H3" t="n">
-        <v>35.05370851408649</v>
+        <v>89.37897008043177</v>
       </c>
       <c r="I3" t="n">
-        <v>33.93253831391753</v>
+        <v>54.71488517218057</v>
       </c>
       <c r="J3" t="n">
-        <v>35.05370851408649</v>
+        <v>89.37897008043177</v>
       </c>
       <c r="K3" t="n">
-        <v>35.05370851408649</v>
+        <v>89.37897008043177</v>
       </c>
       <c r="L3" t="n">
-        <v>35.05370851408649</v>
+        <v>89.37897008043177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>141.7819755406586</v>
+        <v>381.2745780932826</v>
       </c>
       <c r="C4" t="n">
-        <v>139.7428540264058</v>
+        <v>285.5522713084181</v>
       </c>
       <c r="D4" t="n">
-        <v>143.2749109140186</v>
+        <v>1345.572469537034</v>
       </c>
       <c r="E4" t="n">
-        <v>129.4423862782562</v>
+        <v>285.5522713084181</v>
       </c>
       <c r="F4" t="n">
-        <v>140.6164400263043</v>
+        <v>285.5522713084181</v>
       </c>
       <c r="G4" t="n">
-        <v>141.6053276111544</v>
+        <v>773.8248026204863</v>
       </c>
       <c r="H4" t="n">
-        <v>218.0475372878674</v>
+        <v>2275.070907381293</v>
       </c>
       <c r="I4" t="n">
-        <v>218.15259380392</v>
+        <v>285.5522713084181</v>
       </c>
       <c r="J4" t="n">
-        <v>147.5348807260577</v>
+        <v>590.6128384072333</v>
       </c>
       <c r="K4" t="n">
-        <v>141.4247255743489</v>
+        <v>431.5107482938619</v>
       </c>
       <c r="L4" t="n">
-        <v>142.3465365764484</v>
+        <v>384.7268137327285</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.02132674843702</v>
+        <v>35.05370851408657</v>
       </c>
       <c r="C5" t="n">
-        <v>60.90015654826821</v>
+        <v>33.06614660054094</v>
       </c>
       <c r="D5" t="n">
-        <v>62.0208076168955</v>
+        <v>35.05370851408657</v>
       </c>
       <c r="E5" t="n">
-        <v>60.88421851417654</v>
+        <v>33.20395281434624</v>
       </c>
       <c r="F5" t="n">
-        <v>60.88421851417654</v>
+        <v>33.20395281434624</v>
       </c>
       <c r="G5" t="n">
-        <v>61.84467881893269</v>
+        <v>34.8770605845821</v>
       </c>
       <c r="H5" t="n">
-        <v>62.02132674843702</v>
+        <v>35.05370851408657</v>
       </c>
       <c r="I5" t="n">
-        <v>60.90015654826821</v>
+        <v>33.93253831391756</v>
       </c>
       <c r="J5" t="n">
-        <v>62.02132674843702</v>
+        <v>35.05370851408657</v>
       </c>
       <c r="K5" t="n">
-        <v>62.02132674843702</v>
+        <v>35.05370851408657</v>
       </c>
       <c r="L5" t="n">
-        <v>62.02132674843702</v>
+        <v>35.05370851408657</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>136.7985931882245</v>
+        <v>141.7819755406585</v>
       </c>
       <c r="C6" t="n">
-        <v>202.9061601087477</v>
+        <v>139.7428540264053</v>
       </c>
       <c r="D6" t="n">
-        <v>217.9693434758</v>
+        <v>143.2749109140185</v>
       </c>
       <c r="E6" t="n">
-        <v>184.5193740068171</v>
+        <v>129.4423862782561</v>
       </c>
       <c r="F6" t="n">
-        <v>137.7993165626652</v>
+        <v>140.6164400263041</v>
       </c>
       <c r="G6" t="n">
-        <v>203.8520875733495</v>
+        <v>141.6053276111544</v>
       </c>
       <c r="H6" t="n">
-        <v>204.0287355028582</v>
+        <v>218.0475372878672</v>
       </c>
       <c r="I6" t="n">
-        <v>202.9075653026847</v>
+        <v>218.1525938039198</v>
       </c>
       <c r="J6" t="n">
-        <v>204.0419481568231</v>
+        <v>147.5348807260576</v>
       </c>
       <c r="K6" t="n">
-        <v>135.5497587783372</v>
+        <v>141.4247255743492</v>
       </c>
       <c r="L6" t="n">
-        <v>274.2562408478589</v>
+        <v>142.3465365764482</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>127.260837712171</v>
+        <v>62.02132674843699</v>
       </c>
       <c r="C7" t="n">
-        <v>152.7641146610617</v>
+        <v>60.90015654826812</v>
       </c>
       <c r="D7" t="n">
-        <v>153.8852816137555</v>
+        <v>62.02080761689533</v>
       </c>
       <c r="E7" t="n">
-        <v>183.488118404021</v>
+        <v>60.8842185141765</v>
       </c>
       <c r="F7" t="n">
-        <v>152.7640820194908</v>
+        <v>60.8842185141765</v>
       </c>
       <c r="G7" t="n">
-        <v>153.7086369317261</v>
+        <v>61.84467881893261</v>
       </c>
       <c r="H7" t="n">
-        <v>153.8852848612306</v>
+        <v>62.02132674843699</v>
       </c>
       <c r="I7" t="n">
-        <v>152.7641146610617</v>
+        <v>60.90015654826812</v>
       </c>
       <c r="J7" t="n">
-        <v>153.8852848612306</v>
+        <v>62.02132674843699</v>
       </c>
       <c r="K7" t="n">
-        <v>138.4589742549274</v>
+        <v>62.02132674843699</v>
       </c>
       <c r="L7" t="n">
-        <v>153.8852848612306</v>
+        <v>62.02132674843699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.51026184614432</v>
+        <v>136.7985931882244</v>
       </c>
       <c r="C8" t="n">
-        <v>50.19248364649622</v>
+        <v>202.9061601087472</v>
       </c>
       <c r="D8" t="n">
-        <v>60.30404095652334</v>
+        <v>217.9693434757997</v>
       </c>
       <c r="E8" t="n">
-        <v>50.19248364649622</v>
+        <v>184.5193740068169</v>
       </c>
       <c r="F8" t="n">
-        <v>50.19248364649622</v>
+        <v>137.7993165626652</v>
       </c>
       <c r="G8" t="n">
-        <v>73.81764499207196</v>
+        <v>203.8520875733497</v>
       </c>
       <c r="H8" t="n">
-        <v>44.82315303607827</v>
+        <v>204.0287355028578</v>
       </c>
       <c r="I8" t="n">
-        <v>50.19248364649622</v>
+        <v>202.9075653026846</v>
       </c>
       <c r="J8" t="n">
-        <v>78.50002505779855</v>
+        <v>204.0419481568228</v>
       </c>
       <c r="K8" t="n">
-        <v>81.47811170890142</v>
+        <v>135.5497587783372</v>
       </c>
       <c r="L8" t="n">
-        <v>83.31851410510208</v>
+        <v>274.2562408478586</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>127.2608377121705</v>
+      </c>
+      <c r="C9" t="n">
+        <v>152.7641146610616</v>
+      </c>
+      <c r="D9" t="n">
+        <v>153.8852816137554</v>
+      </c>
+      <c r="E9" t="n">
+        <v>183.4881184040208</v>
+      </c>
+      <c r="F9" t="n">
+        <v>152.7640820194905</v>
+      </c>
+      <c r="G9" t="n">
+        <v>153.7086369317257</v>
+      </c>
+      <c r="H9" t="n">
+        <v>153.8852848612303</v>
+      </c>
+      <c r="I9" t="n">
+        <v>152.7641146610616</v>
+      </c>
+      <c r="J9" t="n">
+        <v>153.8852848612303</v>
+      </c>
+      <c r="K9" t="n">
+        <v>138.4589742549268</v>
+      </c>
+      <c r="L9" t="n">
+        <v>153.8852848612303</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>82.51026184614439</v>
+      </c>
+      <c r="C10" t="n">
+        <v>50.19248364649623</v>
+      </c>
+      <c r="D10" t="n">
+        <v>60.30404095652328</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50.19248364649623</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50.19248364649623</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.81764499207195</v>
+      </c>
+      <c r="H10" t="n">
+        <v>44.82315303607819</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50.19248364649623</v>
+      </c>
+      <c r="J10" t="n">
+        <v>78.5000250577986</v>
+      </c>
+      <c r="K10" t="n">
+        <v>81.47811170890138</v>
+      </c>
+      <c r="L10" t="n">
+        <v>83.31851410510207</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>85.64498295172851</v>
-      </c>
-      <c r="C9" t="n">
-        <v>52.47334494821683</v>
-      </c>
-      <c r="D9" t="n">
-        <v>76.60130475281011</v>
-      </c>
-      <c r="E9" t="n">
-        <v>52.47334494821683</v>
-      </c>
-      <c r="F9" t="n">
-        <v>52.47334494821683</v>
-      </c>
-      <c r="G9" t="n">
-        <v>82.03860740570381</v>
-      </c>
-      <c r="H9" t="n">
-        <v>70.33683585787949</v>
-      </c>
-      <c r="I9" t="n">
-        <v>52.47334494821683</v>
-      </c>
-      <c r="J9" t="n">
-        <v>84.01582663932349</v>
-      </c>
-      <c r="K9" t="n">
-        <v>85.22501820320618</v>
-      </c>
-      <c r="L9" t="n">
-        <v>72.54471448837192</v>
+      <c r="B11" t="n">
+        <v>85.64498295172848</v>
+      </c>
+      <c r="C11" t="n">
+        <v>52.47334494821678</v>
+      </c>
+      <c r="D11" t="n">
+        <v>76.60130475281004</v>
+      </c>
+      <c r="E11" t="n">
+        <v>52.47334494821678</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52.47334494821678</v>
+      </c>
+      <c r="G11" t="n">
+        <v>82.03860740570374</v>
+      </c>
+      <c r="H11" t="n">
+        <v>70.33683585787941</v>
+      </c>
+      <c r="I11" t="n">
+        <v>52.47334494821678</v>
+      </c>
+      <c r="J11" t="n">
+        <v>84.01582663932339</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.22501820320613</v>
+      </c>
+      <c r="L11" t="n">
+        <v>72.54471448837188</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>357.320404550043</v>
+        <v>88.58903049270424</v>
       </c>
       <c r="C2" t="n">
-        <v>310.9108229218027</v>
+        <v>54.49921054403549</v>
       </c>
       <c r="D2" t="n">
-        <v>1167.408800558758</v>
+        <v>89.56709148281949</v>
       </c>
       <c r="E2" t="n">
-        <v>310.9108229218027</v>
+        <v>54.49921054403549</v>
       </c>
       <c r="F2" t="n">
-        <v>310.9108229218027</v>
+        <v>54.49921054403549</v>
       </c>
       <c r="G2" t="n">
-        <v>703.3856293162812</v>
+        <v>88.88335267220663</v>
       </c>
       <c r="H2" t="n">
-        <v>1870.277896935655</v>
+        <v>90.16009098663807</v>
       </c>
       <c r="I2" t="n">
-        <v>310.9108229218027</v>
+        <v>54.49921054403549</v>
       </c>
       <c r="J2" t="n">
-        <v>435.5786231657926</v>
+        <v>88.65685134486596</v>
       </c>
       <c r="K2" t="n">
-        <v>389.9986793564685</v>
+        <v>88.64122954600484</v>
       </c>
       <c r="L2" t="n">
-        <v>405.0260966396121</v>
+        <v>88.60748677920668</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.81194185608432</v>
+        <v>89.19846028472014</v>
       </c>
       <c r="C3" t="n">
-        <v>32.92908681963621</v>
+        <v>54.62609843006826</v>
       </c>
       <c r="D3" t="n">
-        <v>34.81194185608431</v>
+        <v>89.19846028472014</v>
       </c>
       <c r="E3" t="n">
-        <v>33.05770550550919</v>
+        <v>54.62609843006826</v>
       </c>
       <c r="F3" t="n">
-        <v>33.0577055055092</v>
+        <v>54.62609843006826</v>
       </c>
       <c r="G3" t="n">
-        <v>34.63760372951079</v>
+        <v>89.09184550609575</v>
       </c>
       <c r="H3" t="n">
-        <v>34.81194185608431</v>
+        <v>89.19846028472014</v>
       </c>
       <c r="I3" t="n">
-        <v>33.70554288309895</v>
+        <v>54.62609843006826</v>
       </c>
       <c r="J3" t="n">
-        <v>34.81194185608431</v>
+        <v>89.19846028472014</v>
       </c>
       <c r="K3" t="n">
-        <v>34.81194185608431</v>
+        <v>89.19846028472014</v>
       </c>
       <c r="L3" t="n">
-        <v>34.81194185608431</v>
+        <v>89.19846028472014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134.299176277331</v>
+        <v>357.3204045500447</v>
       </c>
       <c r="C4" t="n">
-        <v>132.4464959709916</v>
+        <v>310.9108229218106</v>
       </c>
       <c r="D4" t="n">
-        <v>135.5527057286754</v>
+        <v>1167.40880055876</v>
       </c>
       <c r="E4" t="n">
-        <v>122.8509843030582</v>
+        <v>310.9108229218106</v>
       </c>
       <c r="F4" t="n">
-        <v>133.1799401441012</v>
+        <v>310.9108229218106</v>
       </c>
       <c r="G4" t="n">
-        <v>134.1248381507573</v>
+        <v>703.3856293162819</v>
       </c>
       <c r="H4" t="n">
-        <v>205.1904368445294</v>
+        <v>1870.277896935659</v>
       </c>
       <c r="I4" t="n">
-        <v>205.2617490708836</v>
+        <v>310.9108229218106</v>
       </c>
       <c r="J4" t="n">
-        <v>139.6228423184341</v>
+        <v>435.5786231657925</v>
       </c>
       <c r="K4" t="n">
-        <v>133.9712959439493</v>
+        <v>389.9986793564684</v>
       </c>
       <c r="L4" t="n">
-        <v>134.7912689163543</v>
+        <v>405.0260966396113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.58135786773288</v>
+        <v>34.81194185608437</v>
       </c>
       <c r="C5" t="n">
-        <v>58.47495889474739</v>
+        <v>32.92908681963622</v>
       </c>
       <c r="D5" t="n">
-        <v>59.58087690934614</v>
+        <v>34.81194185608436</v>
       </c>
       <c r="E5" t="n">
-        <v>58.45809254351603</v>
+        <v>33.0577055055092</v>
       </c>
       <c r="F5" t="n">
-        <v>58.45809254351603</v>
+        <v>33.05770550550924</v>
       </c>
       <c r="G5" t="n">
-        <v>59.40701974115914</v>
+        <v>34.63760372951071</v>
       </c>
       <c r="H5" t="n">
-        <v>59.58135786773288</v>
+        <v>34.81194185608436</v>
       </c>
       <c r="I5" t="n">
-        <v>58.47495889474739</v>
+        <v>33.70554288309889</v>
       </c>
       <c r="J5" t="n">
-        <v>59.58135786773288</v>
+        <v>34.81194185608436</v>
       </c>
       <c r="K5" t="n">
-        <v>59.58135786773288</v>
+        <v>34.81194185608436</v>
       </c>
       <c r="L5" t="n">
-        <v>59.58135786773288</v>
+        <v>34.81194185608436</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>129.0547373113981</v>
+        <v>134.2991762773311</v>
       </c>
       <c r="C6" t="n">
-        <v>190.1727873985254</v>
+        <v>132.4464959709915</v>
       </c>
       <c r="D6" t="n">
-        <v>204.1858422930963</v>
+        <v>135.5527057286753</v>
       </c>
       <c r="E6" t="n">
-        <v>173.1543155908026</v>
+        <v>122.8509843030583</v>
       </c>
       <c r="F6" t="n">
-        <v>129.9110879159078</v>
+        <v>133.1799401441013</v>
       </c>
       <c r="G6" t="n">
-        <v>191.1081704235963</v>
+        <v>134.1248381507575</v>
       </c>
       <c r="H6" t="n">
-        <v>191.2825085501777</v>
+        <v>205.1904368445296</v>
       </c>
       <c r="I6" t="n">
-        <v>190.1761095771845</v>
+        <v>205.2617490708836</v>
       </c>
       <c r="J6" t="n">
-        <v>191.2947380945587</v>
+        <v>139.6228423184341</v>
       </c>
       <c r="K6" t="n">
-        <v>127.8988245124881</v>
+        <v>133.9712959439494</v>
       </c>
       <c r="L6" t="n">
-        <v>256.2846190146925</v>
+        <v>134.7912689163544</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115.3511704170623</v>
+        <v>59.58135786773281</v>
       </c>
       <c r="C7" t="n">
-        <v>137.5398396878741</v>
+        <v>58.4749588947475</v>
       </c>
       <c r="D7" t="n">
-        <v>138.646238216651</v>
+        <v>59.58087690934617</v>
       </c>
       <c r="E7" t="n">
-        <v>164.4218208820925</v>
+        <v>58.45809254351617</v>
       </c>
       <c r="F7" t="n">
-        <v>137.5398131099859</v>
+        <v>58.45809254351617</v>
       </c>
       <c r="G7" t="n">
-        <v>138.4719005342858</v>
+        <v>59.40701974115929</v>
       </c>
       <c r="H7" t="n">
-        <v>138.6462386608595</v>
+        <v>59.58135786773281</v>
       </c>
       <c r="I7" t="n">
-        <v>137.5398396878741</v>
+        <v>58.4749588947475</v>
       </c>
       <c r="J7" t="n">
-        <v>138.6462386608595</v>
+        <v>59.58135786773281</v>
       </c>
       <c r="K7" t="n">
-        <v>125.1489844467876</v>
+        <v>59.58135786773281</v>
       </c>
       <c r="L7" t="n">
-        <v>138.6462386608595</v>
+        <v>59.58135786773281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.39769039231626</v>
+        <v>129.0547373113982</v>
       </c>
       <c r="C8" t="n">
-        <v>48.94555537842009</v>
+        <v>190.1727873985255</v>
       </c>
       <c r="D8" t="n">
-        <v>61.91260541270383</v>
+        <v>204.1858422930966</v>
       </c>
       <c r="E8" t="n">
-        <v>48.94555537842009</v>
+        <v>173.1543155908026</v>
       </c>
       <c r="F8" t="n">
-        <v>48.94555537842009</v>
+        <v>129.911087915908</v>
       </c>
       <c r="G8" t="n">
-        <v>73.96284792895791</v>
+        <v>191.1081704235965</v>
       </c>
       <c r="H8" t="n">
-        <v>50.23033143572361</v>
+        <v>191.282508550178</v>
       </c>
       <c r="I8" t="n">
-        <v>48.94555537842009</v>
+        <v>190.1761095771847</v>
       </c>
       <c r="J8" t="n">
-        <v>81.04215391208034</v>
+        <v>191.2947380945586</v>
       </c>
       <c r="K8" t="n">
-        <v>81.31244832562955</v>
+        <v>127.8988245124881</v>
       </c>
       <c r="L8" t="n">
-        <v>82.12306672292127</v>
+        <v>256.2846190146927</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>115.3511704170624</v>
+      </c>
+      <c r="C9" t="n">
+        <v>137.5398396878743</v>
+      </c>
+      <c r="D9" t="n">
+        <v>138.6462382166514</v>
+      </c>
+      <c r="E9" t="n">
+        <v>164.4218208820929</v>
+      </c>
+      <c r="F9" t="n">
+        <v>137.5398131099862</v>
+      </c>
+      <c r="G9" t="n">
+        <v>138.471900534286</v>
+      </c>
+      <c r="H9" t="n">
+        <v>138.6462386608595</v>
+      </c>
+      <c r="I9" t="n">
+        <v>137.5398396878743</v>
+      </c>
+      <c r="J9" t="n">
+        <v>138.6462386608595</v>
+      </c>
+      <c r="K9" t="n">
+        <v>125.1489844467877</v>
+      </c>
+      <c r="L9" t="n">
+        <v>138.6462386608595</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>82.39769039231624</v>
+      </c>
+      <c r="C10" t="n">
+        <v>48.94555537842013</v>
+      </c>
+      <c r="D10" t="n">
+        <v>61.91260541270382</v>
+      </c>
+      <c r="E10" t="n">
+        <v>48.94555537842013</v>
+      </c>
+      <c r="F10" t="n">
+        <v>48.94555537842013</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.96284792895796</v>
+      </c>
+      <c r="H10" t="n">
+        <v>50.23033143572361</v>
+      </c>
+      <c r="I10" t="n">
+        <v>48.94555537842013</v>
+      </c>
+      <c r="J10" t="n">
+        <v>81.04215391208029</v>
+      </c>
+      <c r="K10" t="n">
+        <v>81.31244832562955</v>
+      </c>
+      <c r="L10" t="n">
+        <v>82.12306672292128</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>85.49465851889289</v>
-      </c>
-      <c r="C9" t="n">
-        <v>51.91454535271899</v>
-      </c>
-      <c r="D9" t="n">
-        <v>77.15194056119208</v>
-      </c>
-      <c r="E9" t="n">
-        <v>51.91454535271899</v>
-      </c>
-      <c r="F9" t="n">
-        <v>51.91454535271899</v>
-      </c>
-      <c r="G9" t="n">
-        <v>81.99961056135419</v>
-      </c>
-      <c r="H9" t="n">
-        <v>72.42946817628636</v>
-      </c>
-      <c r="I9" t="n">
-        <v>51.91454535271899</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>85.49465851889282</v>
+      </c>
+      <c r="C11" t="n">
+        <v>51.91454535271903</v>
+      </c>
+      <c r="D11" t="n">
+        <v>77.15194056119192</v>
+      </c>
+      <c r="E11" t="n">
+        <v>51.91454535271903</v>
+      </c>
+      <c r="F11" t="n">
+        <v>51.91454535271903</v>
+      </c>
+      <c r="G11" t="n">
+        <v>81.99961056135426</v>
+      </c>
+      <c r="H11" t="n">
+        <v>72.42946817628631</v>
+      </c>
+      <c r="I11" t="n">
+        <v>51.91454535271903</v>
+      </c>
+      <c r="J11" t="n">
         <v>84.94570595270878</v>
       </c>
-      <c r="K9" t="n">
-        <v>85.05306897338977</v>
-      </c>
-      <c r="L9" t="n">
-        <v>73.45431974453197</v>
+      <c r="K11" t="n">
+        <v>85.05306897338966</v>
+      </c>
+      <c r="L11" t="n">
+        <v>73.45431974453192</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>345.0097914306155</v>
+        <v>88.38732466453652</v>
       </c>
       <c r="C2" t="n">
-        <v>380.3518801804897</v>
+        <v>54.68181214837875</v>
       </c>
       <c r="D2" t="n">
-        <v>1001.124622959806</v>
+        <v>89.20825278796826</v>
       </c>
       <c r="E2" t="n">
-        <v>380.3518801804897</v>
+        <v>54.68181214837875</v>
       </c>
       <c r="F2" t="n">
-        <v>380.3518801804897</v>
+        <v>54.68181214837875</v>
       </c>
       <c r="G2" t="n">
-        <v>635.5935111793624</v>
+        <v>88.64797612508416</v>
       </c>
       <c r="H2" t="n">
-        <v>1528.35700033744</v>
+        <v>89.66755195649066</v>
       </c>
       <c r="I2" t="n">
-        <v>380.3518801804897</v>
+        <v>54.68181214837875</v>
       </c>
       <c r="J2" t="n">
-        <v>415.0992448875517</v>
+        <v>88.44056262535182</v>
       </c>
       <c r="K2" t="n">
-        <v>345.0022874284989</v>
+        <v>88.40349945726555</v>
       </c>
       <c r="L2" t="n">
-        <v>333.6159697977549</v>
+        <v>89.67538766999201</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.94946777382383</v>
+        <v>89.00333247790189</v>
       </c>
       <c r="C3" t="n">
-        <v>33.19681298878074</v>
+        <v>54.71909535626888</v>
       </c>
       <c r="D3" t="n">
-        <v>34.94946777382382</v>
+        <v>89.00333247790189</v>
       </c>
       <c r="E3" t="n">
-        <v>33.32196722453119</v>
+        <v>54.71909535626888</v>
       </c>
       <c r="F3" t="n">
-        <v>33.32196722453118</v>
+        <v>54.71909535626888</v>
       </c>
       <c r="G3" t="n">
-        <v>34.78032765816592</v>
+        <v>88.92101252532277</v>
       </c>
       <c r="H3" t="n">
-        <v>34.94946777382382</v>
+        <v>89.00333247790189</v>
       </c>
       <c r="I3" t="n">
-        <v>33.87628201344185</v>
+        <v>54.71909535626888</v>
       </c>
       <c r="J3" t="n">
-        <v>34.94946777382383</v>
+        <v>89.00333247790189</v>
       </c>
       <c r="K3" t="n">
-        <v>34.94946777382382</v>
+        <v>89.00333247790189</v>
       </c>
       <c r="L3" t="n">
-        <v>34.94946777382382</v>
+        <v>89.00333247790189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134.4699045980825</v>
+        <v>345.0097914306153</v>
       </c>
       <c r="C4" t="n">
-        <v>132.8904627543526</v>
+        <v>380.3518801804901</v>
       </c>
       <c r="D4" t="n">
-        <v>135.5011180171968</v>
+        <v>1001.124622959805</v>
       </c>
       <c r="E4" t="n">
-        <v>123.2903713109616</v>
+        <v>380.3518801804901</v>
       </c>
       <c r="F4" t="n">
-        <v>133.4401629507974</v>
+        <v>380.3518801804901</v>
       </c>
       <c r="G4" t="n">
-        <v>206.0553486986319</v>
+        <v>635.5935111793599</v>
       </c>
       <c r="H4" t="n">
-        <v>205.0146052317651</v>
+        <v>1528.357000337439</v>
       </c>
       <c r="I4" t="n">
-        <v>133.3967188377007</v>
+        <v>380.3518801804901</v>
       </c>
       <c r="J4" t="n">
-        <v>204.4887274102061</v>
+        <v>415.0992448875521</v>
       </c>
       <c r="K4" t="n">
-        <v>134.1265469985591</v>
+        <v>345.0022874284989</v>
       </c>
       <c r="L4" t="n">
-        <v>134.9238791410878</v>
+        <v>333.6159697977561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.45185443031092</v>
+        <v>34.9494677738238</v>
       </c>
       <c r="C5" t="n">
-        <v>58.37866866992894</v>
+        <v>33.19681298878072</v>
       </c>
       <c r="D5" t="n">
-        <v>59.45137056682825</v>
+        <v>34.9494677738238</v>
       </c>
       <c r="E5" t="n">
-        <v>58.36445883501111</v>
+        <v>33.32196722453114</v>
       </c>
       <c r="F5" t="n">
-        <v>58.36445883501111</v>
+        <v>33.32196722453114</v>
       </c>
       <c r="G5" t="n">
-        <v>59.28271431465303</v>
+        <v>34.78032765816596</v>
       </c>
       <c r="H5" t="n">
-        <v>59.45185443031087</v>
+        <v>34.9494677738238</v>
       </c>
       <c r="I5" t="n">
-        <v>58.37866866992894</v>
+        <v>33.87628201344179</v>
       </c>
       <c r="J5" t="n">
-        <v>59.45185443031087</v>
+        <v>34.9494677738238</v>
       </c>
       <c r="K5" t="n">
-        <v>59.45185443031087</v>
+        <v>34.9494677738238</v>
       </c>
       <c r="L5" t="n">
-        <v>59.45185443031087</v>
+        <v>34.9494677738238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>128.6180072326251</v>
+        <v>134.4699045980826</v>
       </c>
       <c r="C6" t="n">
-        <v>189.3510889303554</v>
+        <v>132.890462754352</v>
       </c>
       <c r="D6" t="n">
-        <v>203.2412454121649</v>
+        <v>135.5011180171971</v>
       </c>
       <c r="E6" t="n">
-        <v>172.4473965637616</v>
+        <v>123.2903713109615</v>
       </c>
       <c r="F6" t="n">
-        <v>129.4958237707507</v>
+        <v>133.4401629507974</v>
       </c>
       <c r="G6" t="n">
-        <v>190.2559947462466</v>
+        <v>206.055348698632</v>
       </c>
       <c r="H6" t="n">
-        <v>190.4251348619173</v>
+        <v>205.0146052317653</v>
       </c>
       <c r="I6" t="n">
-        <v>189.3519491015226</v>
+        <v>133.3967188377006</v>
       </c>
       <c r="J6" t="n">
-        <v>190.4372817378197</v>
+        <v>204.4887274102062</v>
       </c>
       <c r="K6" t="n">
-        <v>127.4699081047086</v>
+        <v>134.1265469985592</v>
       </c>
       <c r="L6" t="n">
-        <v>254.9878479027276</v>
+        <v>134.9238791410878</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.7435237796735</v>
+        <v>59.4518544303111</v>
       </c>
       <c r="C7" t="n">
-        <v>131.6288303324234</v>
+        <v>58.378668669929</v>
       </c>
       <c r="D7" t="n">
-        <v>132.7020168030294</v>
+        <v>59.45137056682838</v>
       </c>
       <c r="E7" t="n">
-        <v>156.968437485867</v>
+        <v>58.36445883501111</v>
       </c>
       <c r="F7" t="n">
-        <v>131.6288079142497</v>
+        <v>58.36445883501111</v>
       </c>
       <c r="G7" t="n">
-        <v>132.5328759771474</v>
+        <v>59.28271431465318</v>
       </c>
       <c r="H7" t="n">
-        <v>132.7020160928052</v>
+        <v>59.4518544303111</v>
       </c>
       <c r="I7" t="n">
-        <v>131.6288303324234</v>
+        <v>58.378668669929</v>
       </c>
       <c r="J7" t="n">
-        <v>132.7020160928052</v>
+        <v>59.4518544303111</v>
       </c>
       <c r="K7" t="n">
-        <v>119.9791797076493</v>
+        <v>59.4518544303111</v>
       </c>
       <c r="L7" t="n">
-        <v>132.7020160928052</v>
+        <v>59.4518544303111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.38731958798306</v>
+        <v>128.6180072326256</v>
       </c>
       <c r="C8" t="n">
-        <v>47.14022944300176</v>
+        <v>189.3510889303552</v>
       </c>
       <c r="D8" t="n">
-        <v>65.19383225152059</v>
+        <v>203.2412454121652</v>
       </c>
       <c r="E8" t="n">
-        <v>47.14022944300176</v>
+        <v>172.4473965637616</v>
       </c>
       <c r="F8" t="n">
-        <v>47.14022944300176</v>
+        <v>129.4958237707507</v>
       </c>
       <c r="G8" t="n">
-        <v>75.18482252195334</v>
+        <v>190.2559947462467</v>
       </c>
       <c r="H8" t="n">
-        <v>56.19565468020518</v>
+        <v>190.4251348619177</v>
       </c>
       <c r="I8" t="n">
-        <v>47.14022944300176</v>
+        <v>189.3519491015227</v>
       </c>
       <c r="J8" t="n">
-        <v>81.33355098670822</v>
+        <v>190.43728173782</v>
       </c>
       <c r="K8" t="n">
-        <v>82.05611081099724</v>
+        <v>127.4699081047087</v>
       </c>
       <c r="L8" t="n">
-        <v>55.91613403412285</v>
+        <v>254.987847902728</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>110.7435237796737</v>
+      </c>
+      <c r="C9" t="n">
+        <v>131.6288303324234</v>
+      </c>
+      <c r="D9" t="n">
+        <v>132.7020168030295</v>
+      </c>
+      <c r="E9" t="n">
+        <v>156.968437485867</v>
+      </c>
+      <c r="F9" t="n">
+        <v>131.6288079142496</v>
+      </c>
+      <c r="G9" t="n">
+        <v>132.5328759771477</v>
+      </c>
+      <c r="H9" t="n">
+        <v>132.7020160928056</v>
+      </c>
+      <c r="I9" t="n">
+        <v>131.6288303324234</v>
+      </c>
+      <c r="J9" t="n">
+        <v>132.7020160928056</v>
+      </c>
+      <c r="K9" t="n">
+        <v>119.9791797076495</v>
+      </c>
+      <c r="L9" t="n">
+        <v>132.7020160928056</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>82.38731958798309</v>
+      </c>
+      <c r="C10" t="n">
+        <v>47.14022944300176</v>
+      </c>
+      <c r="D10" t="n">
+        <v>65.19383225152062</v>
+      </c>
+      <c r="E10" t="n">
+        <v>47.14022944300176</v>
+      </c>
+      <c r="F10" t="n">
+        <v>47.14022944300176</v>
+      </c>
+      <c r="G10" t="n">
+        <v>75.18482252195339</v>
+      </c>
+      <c r="H10" t="n">
+        <v>56.19565468020515</v>
+      </c>
+      <c r="I10" t="n">
+        <v>47.14022944300176</v>
+      </c>
+      <c r="J10" t="n">
+        <v>81.33355098670823</v>
+      </c>
+      <c r="K10" t="n">
+        <v>82.05611081099732</v>
+      </c>
+      <c r="L10" t="n">
+        <v>55.91613403412288</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>85.37701771564134</v>
-      </c>
-      <c r="C9" t="n">
-        <v>51.23340400542963</v>
-      </c>
-      <c r="D9" t="n">
-        <v>78.37485430858953</v>
-      </c>
-      <c r="E9" t="n">
-        <v>51.23340400542963</v>
-      </c>
-      <c r="F9" t="n">
-        <v>51.23340400542963</v>
-      </c>
-      <c r="G9" t="n">
-        <v>82.39796589891084</v>
-      </c>
-      <c r="H9" t="n">
-        <v>74.73995400667296</v>
-      </c>
-      <c r="I9" t="n">
-        <v>51.23340400542963</v>
-      </c>
-      <c r="J9" t="n">
-        <v>84.9507876047153</v>
-      </c>
-      <c r="K9" t="n">
-        <v>85.24249145934209</v>
-      </c>
-      <c r="L9" t="n">
-        <v>74.62060693542736</v>
+      <c r="B11" t="n">
+        <v>85.37701771564141</v>
+      </c>
+      <c r="C11" t="n">
+        <v>51.23340400542961</v>
+      </c>
+      <c r="D11" t="n">
+        <v>78.37485430858958</v>
+      </c>
+      <c r="E11" t="n">
+        <v>51.23340400542961</v>
+      </c>
+      <c r="F11" t="n">
+        <v>51.23340400542961</v>
+      </c>
+      <c r="G11" t="n">
+        <v>82.39796589891085</v>
+      </c>
+      <c r="H11" t="n">
+        <v>74.73995400667302</v>
+      </c>
+      <c r="I11" t="n">
+        <v>51.23340400542961</v>
+      </c>
+      <c r="J11" t="n">
+        <v>84.9507876047154</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.24249145934219</v>
+      </c>
+      <c r="L11" t="n">
+        <v>74.62060693542743</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263.1095135082437</v>
+        <v>86.73484466505677</v>
       </c>
       <c r="C2" t="n">
-        <v>212.8372987128301</v>
+        <v>52.84423112636306</v>
       </c>
       <c r="D2" t="n">
-        <v>440.3969237609145</v>
+        <v>86.95078955766354</v>
       </c>
       <c r="E2" t="n">
-        <v>212.8372987128301</v>
+        <v>52.84423112636306</v>
       </c>
       <c r="F2" t="n">
-        <v>212.8372987128301</v>
+        <v>52.84423112636306</v>
       </c>
       <c r="G2" t="n">
-        <v>334.4289273895753</v>
+        <v>86.75433887309592</v>
       </c>
       <c r="H2" t="n">
-        <v>772.1002534568697</v>
+        <v>87.27459628112896</v>
       </c>
       <c r="I2" t="n">
-        <v>212.8372987128301</v>
+        <v>52.84423112636306</v>
       </c>
       <c r="J2" t="n">
-        <v>483.3446987475294</v>
+        <v>86.95145260002708</v>
       </c>
       <c r="K2" t="n">
-        <v>298.5960871682577</v>
+        <v>86.77889006568246</v>
       </c>
       <c r="L2" t="n">
-        <v>616.1880475395417</v>
+        <v>86.64460076629165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.63820744180546</v>
+        <v>87.455720698855</v>
       </c>
       <c r="C3" t="n">
-        <v>31.97665851092988</v>
+        <v>53.0928469711636</v>
       </c>
       <c r="D3" t="n">
-        <v>33.63820744180546</v>
+        <v>87.455720698855</v>
       </c>
       <c r="E3" t="n">
-        <v>32.08849482241193</v>
+        <v>53.0928469711636</v>
       </c>
       <c r="F3" t="n">
-        <v>32.08849482241195</v>
+        <v>53.0928469711636</v>
       </c>
       <c r="G3" t="n">
-        <v>33.47455129833418</v>
+        <v>87.39803270018656</v>
       </c>
       <c r="H3" t="n">
-        <v>33.63820744180546</v>
+        <v>87.455720698855</v>
       </c>
       <c r="I3" t="n">
-        <v>32.59983744444525</v>
+        <v>53.0928469711636</v>
       </c>
       <c r="J3" t="n">
-        <v>33.63820744180546</v>
+        <v>87.455720698855</v>
       </c>
       <c r="K3" t="n">
-        <v>33.63820744180546</v>
+        <v>87.455720698855</v>
       </c>
       <c r="L3" t="n">
-        <v>33.63820744180546</v>
+        <v>87.455720698855</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>214.2026974050947</v>
+        <v>263.1095135082413</v>
       </c>
       <c r="C4" t="n">
-        <v>138.0467334658711</v>
+        <v>212.83729871283</v>
       </c>
       <c r="D4" t="n">
-        <v>212.4923650129745</v>
+        <v>440.3969237609141</v>
       </c>
       <c r="E4" t="n">
-        <v>127.7854253159413</v>
+        <v>212.83729871283</v>
       </c>
       <c r="F4" t="n">
-        <v>138.4618717427943</v>
+        <v>212.83729871283</v>
       </c>
       <c r="G4" t="n">
-        <v>214.0390412616235</v>
+        <v>334.4289273895758</v>
       </c>
       <c r="H4" t="n">
-        <v>139.7177036088965</v>
+        <v>772.1002534568687</v>
       </c>
       <c r="I4" t="n">
-        <v>213.1643274077341</v>
+        <v>212.83729871283</v>
       </c>
       <c r="J4" t="n">
-        <v>212.261914522395</v>
+        <v>483.3446987475309</v>
       </c>
       <c r="K4" t="n">
-        <v>139.4820227926549</v>
+        <v>298.5960871682572</v>
       </c>
       <c r="L4" t="n">
-        <v>139.6496323002268</v>
+        <v>616.18804753954</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.23051881390278</v>
+        <v>33.63820744180531</v>
       </c>
       <c r="C5" t="n">
-        <v>57.19214881654259</v>
+        <v>31.97665851092988</v>
       </c>
       <c r="D5" t="n">
-        <v>58.23002295009228</v>
+        <v>33.63820744180531</v>
       </c>
       <c r="E5" t="n">
-        <v>57.17881194638593</v>
+        <v>32.088494822412</v>
       </c>
       <c r="F5" t="n">
-        <v>57.17881194638593</v>
+        <v>32.088494822412</v>
       </c>
       <c r="G5" t="n">
-        <v>58.06686267043166</v>
+        <v>33.47455129833415</v>
       </c>
       <c r="H5" t="n">
-        <v>58.23051881390278</v>
+        <v>33.63820744180535</v>
       </c>
       <c r="I5" t="n">
-        <v>57.19214881654259</v>
+        <v>32.59983744444514</v>
       </c>
       <c r="J5" t="n">
-        <v>58.23051881390278</v>
+        <v>33.63820744180531</v>
       </c>
       <c r="K5" t="n">
-        <v>58.23051881390278</v>
+        <v>33.63820744180531</v>
       </c>
       <c r="L5" t="n">
-        <v>58.23051881390278</v>
+        <v>33.63820744180531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130.9935658837267</v>
+        <v>214.2026974050945</v>
       </c>
       <c r="C6" t="n">
-        <v>193.9258444297275</v>
+        <v>138.0467334658709</v>
       </c>
       <c r="D6" t="n">
-        <v>208.2284442455254</v>
+        <v>212.4923650129744</v>
       </c>
       <c r="E6" t="n">
-        <v>176.4304239764211</v>
+        <v>127.7854253159413</v>
       </c>
       <c r="F6" t="n">
-        <v>131.9752932306715</v>
+        <v>138.4618717427943</v>
       </c>
       <c r="G6" t="n">
-        <v>194.8001434207057</v>
+        <v>214.0390412616235</v>
       </c>
       <c r="H6" t="n">
-        <v>194.9637995641792</v>
+        <v>139.7177036088966</v>
       </c>
       <c r="I6" t="n">
-        <v>193.9254295668169</v>
+        <v>213.1643274077342</v>
       </c>
       <c r="J6" t="n">
-        <v>194.9763715534227</v>
+        <v>212.2619145223948</v>
       </c>
       <c r="K6" t="n">
-        <v>129.8052859502818</v>
+        <v>139.482022792655</v>
       </c>
       <c r="L6" t="n">
-        <v>261.7860577523523</v>
+        <v>139.6496323002268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114.6552643166906</v>
+        <v>58.23051881390281</v>
       </c>
       <c r="C7" t="n">
-        <v>136.9417234701413</v>
+        <v>57.19214881654258</v>
       </c>
       <c r="D7" t="n">
-        <v>137.9800958430005</v>
+        <v>58.23002295009231</v>
       </c>
       <c r="E7" t="n">
-        <v>163.8580673405841</v>
+        <v>57.17881194638596</v>
       </c>
       <c r="F7" t="n">
-        <v>136.9417102295396</v>
+        <v>57.17881194638596</v>
       </c>
       <c r="G7" t="n">
-        <v>137.8164373240302</v>
+        <v>58.06686267043167</v>
       </c>
       <c r="H7" t="n">
-        <v>137.9800934675014</v>
+        <v>58.23051881390281</v>
       </c>
       <c r="I7" t="n">
-        <v>136.9417234701413</v>
+        <v>57.19214881654258</v>
       </c>
       <c r="J7" t="n">
-        <v>137.9800934675014</v>
+        <v>58.23051881390281</v>
       </c>
       <c r="K7" t="n">
-        <v>124.4655968529838</v>
+        <v>58.23051881390281</v>
       </c>
       <c r="L7" t="n">
-        <v>137.9800934675014</v>
+        <v>58.23051881390281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.3406927548664</v>
+        <v>130.9935658837266</v>
       </c>
       <c r="C8" t="n">
-        <v>50.28925301458091</v>
+        <v>193.9258444297272</v>
       </c>
       <c r="D8" t="n">
-        <v>78.81931578808607</v>
+        <v>208.2284442455251</v>
       </c>
       <c r="E8" t="n">
-        <v>50.28925301458091</v>
+        <v>176.430423976421</v>
       </c>
       <c r="F8" t="n">
-        <v>50.28925301458091</v>
+        <v>131.9752932306715</v>
       </c>
       <c r="G8" t="n">
-        <v>81.69404077387041</v>
+        <v>194.8001434207056</v>
       </c>
       <c r="H8" t="n">
-        <v>72.32456476665591</v>
+        <v>194.9637995641792</v>
       </c>
       <c r="I8" t="n">
-        <v>50.28925301458091</v>
+        <v>193.9254295668167</v>
       </c>
       <c r="J8" t="n">
-        <v>78.86998044411247</v>
+        <v>194.976371553423</v>
       </c>
       <c r="K8" t="n">
-        <v>82.42318706102391</v>
+        <v>129.8052859502819</v>
       </c>
       <c r="L8" t="n">
-        <v>76.82008402308804</v>
+        <v>261.7860577523519</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>114.6552643166906</v>
+      </c>
+      <c r="C9" t="n">
+        <v>136.9417234701412</v>
+      </c>
+      <c r="D9" t="n">
+        <v>137.9800958430005</v>
+      </c>
+      <c r="E9" t="n">
+        <v>163.8580673405842</v>
+      </c>
+      <c r="F9" t="n">
+        <v>136.9417102295394</v>
+      </c>
+      <c r="G9" t="n">
+        <v>137.8164373240302</v>
+      </c>
+      <c r="H9" t="n">
+        <v>137.9800934675013</v>
+      </c>
+      <c r="I9" t="n">
+        <v>136.9417234701412</v>
+      </c>
+      <c r="J9" t="n">
+        <v>137.9800934675013</v>
+      </c>
+      <c r="K9" t="n">
+        <v>124.4655968529837</v>
+      </c>
+      <c r="L9" t="n">
+        <v>137.9800934675013</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>83.34069275486644</v>
+      </c>
+      <c r="C10" t="n">
+        <v>50.28925301458101</v>
+      </c>
+      <c r="D10" t="n">
+        <v>78.8193157880861</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50.28925301458101</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50.28925301458101</v>
+      </c>
+      <c r="G10" t="n">
+        <v>81.69404077387048</v>
+      </c>
+      <c r="H10" t="n">
+        <v>72.32456476665593</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50.28925301458101</v>
+      </c>
+      <c r="J10" t="n">
+        <v>78.86998044411243</v>
+      </c>
+      <c r="K10" t="n">
+        <v>82.423187061024</v>
+      </c>
+      <c r="L10" t="n">
+        <v>76.82008402308806</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>84.86249383672597</v>
-      </c>
-      <c r="C9" t="n">
-        <v>51.56858694159409</v>
-      </c>
-      <c r="D9" t="n">
-        <v>83.02119780067414</v>
-      </c>
-      <c r="E9" t="n">
-        <v>51.56858694159409</v>
-      </c>
-      <c r="F9" t="n">
-        <v>51.56858694159409</v>
-      </c>
-      <c r="G9" t="n">
-        <v>84.15900436907832</v>
-      </c>
-      <c r="H9" t="n">
-        <v>80.38987211184552</v>
-      </c>
-      <c r="I9" t="n">
-        <v>51.56858694159409</v>
-      </c>
-      <c r="J9" t="n">
-        <v>83.04491342298843</v>
-      </c>
-      <c r="K9" t="n">
-        <v>84.48907122273616</v>
-      </c>
-      <c r="L9" t="n">
-        <v>82.21481856686553</v>
+      <c r="B11" t="n">
+        <v>84.86249383672602</v>
+      </c>
+      <c r="C11" t="n">
+        <v>51.56858694159416</v>
+      </c>
+      <c r="D11" t="n">
+        <v>83.02119780067423</v>
+      </c>
+      <c r="E11" t="n">
+        <v>51.56858694159416</v>
+      </c>
+      <c r="F11" t="n">
+        <v>51.56858694159416</v>
+      </c>
+      <c r="G11" t="n">
+        <v>84.15900436907833</v>
+      </c>
+      <c r="H11" t="n">
+        <v>80.38987211184556</v>
+      </c>
+      <c r="I11" t="n">
+        <v>51.56858694159416</v>
+      </c>
+      <c r="J11" t="n">
+        <v>83.04491342298846</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.48907122273621</v>
+      </c>
+      <c r="L11" t="n">
+        <v>82.21481856686563</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>285.2659720949189</v>
+        <v>86.33948125334919</v>
       </c>
       <c r="C2" t="n">
-        <v>236.9056470670311</v>
+        <v>52.60580191476957</v>
       </c>
       <c r="D2" t="n">
-        <v>213.0237994451819</v>
+        <v>86.24661784012423</v>
       </c>
       <c r="E2" t="n">
-        <v>236.9056470670311</v>
+        <v>52.60580191476957</v>
       </c>
       <c r="F2" t="n">
-        <v>236.9056470670311</v>
+        <v>52.60580191476957</v>
       </c>
       <c r="G2" t="n">
-        <v>238.3089004329057</v>
+        <v>86.24325077536747</v>
       </c>
       <c r="H2" t="n">
-        <v>200.3980045520702</v>
+        <v>86.20894551023595</v>
       </c>
       <c r="I2" t="n">
-        <v>236.9056470670311</v>
+        <v>52.60580191476957</v>
       </c>
       <c r="J2" t="n">
-        <v>357.6430660008749</v>
+        <v>86.41454029772171</v>
       </c>
       <c r="K2" t="n">
-        <v>253.0880904942373</v>
+        <v>86.30542875084889</v>
       </c>
       <c r="L2" t="n">
-        <v>148.403265510218</v>
+        <v>86.15733520153636</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.28094375305024</v>
+        <v>87.00978097872458</v>
       </c>
       <c r="C3" t="n">
-        <v>31.7851580729625</v>
+        <v>52.80340993087947</v>
       </c>
       <c r="D3" t="n">
-        <v>33.28094375305024</v>
+        <v>87.00978097872458</v>
       </c>
       <c r="E3" t="n">
-        <v>31.8816266522107</v>
+        <v>52.80340993087947</v>
       </c>
       <c r="F3" t="n">
-        <v>31.88162665221073</v>
+        <v>52.80340993087947</v>
       </c>
       <c r="G3" t="n">
-        <v>33.12195595555992</v>
+        <v>86.97373784863491</v>
       </c>
       <c r="H3" t="n">
-        <v>33.28094375305024</v>
+        <v>87.00978097872458</v>
       </c>
       <c r="I3" t="n">
-        <v>32.27236615059999</v>
+        <v>52.80340993087947</v>
       </c>
       <c r="J3" t="n">
-        <v>33.28094375305024</v>
+        <v>87.00978097872458</v>
       </c>
       <c r="K3" t="n">
-        <v>33.28094375305024</v>
+        <v>87.00978097872458</v>
       </c>
       <c r="L3" t="n">
-        <v>33.28094375305024</v>
+        <v>87.00978097872458</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.9253611120565</v>
+        <v>285.265972094919</v>
       </c>
       <c r="C4" t="n">
-        <v>130.6411545052313</v>
+        <v>236.9056470670308</v>
       </c>
       <c r="D4" t="n">
-        <v>131.7514941767832</v>
+        <v>213.0237994451818</v>
       </c>
       <c r="E4" t="n">
-        <v>121.0854719911459</v>
+        <v>236.9056470670308</v>
       </c>
       <c r="F4" t="n">
-        <v>130.8660650746295</v>
+        <v>236.9056470670308</v>
       </c>
       <c r="G4" t="n">
-        <v>200.7663733145665</v>
+        <v>238.3089004329044</v>
       </c>
       <c r="H4" t="n">
-        <v>199.3001751003806</v>
+        <v>200.3980045520703</v>
       </c>
       <c r="I4" t="n">
-        <v>199.9167835096068</v>
+        <v>236.9056470670308</v>
       </c>
       <c r="J4" t="n">
-        <v>137.0715725540497</v>
+        <v>357.6430660008741</v>
       </c>
       <c r="K4" t="n">
-        <v>131.858576056692</v>
+        <v>253.0880904942375</v>
       </c>
       <c r="L4" t="n">
-        <v>131.8595782927523</v>
+        <v>148.4032655102179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.63327993831443</v>
+        <v>33.2809437530503</v>
       </c>
       <c r="C5" t="n">
-        <v>54.62470233586426</v>
+        <v>31.78515807296248</v>
       </c>
       <c r="D5" t="n">
-        <v>55.6328158219775</v>
+        <v>33.2809437530503</v>
       </c>
       <c r="E5" t="n">
-        <v>54.61518042919583</v>
+        <v>31.88162665221068</v>
       </c>
       <c r="F5" t="n">
-        <v>54.61518042919583</v>
+        <v>31.88162665221069</v>
       </c>
       <c r="G5" t="n">
-        <v>55.47429214082409</v>
+        <v>33.12195595555995</v>
       </c>
       <c r="H5" t="n">
-        <v>55.63327993831443</v>
+        <v>33.2809437530503</v>
       </c>
       <c r="I5" t="n">
-        <v>54.62470233586426</v>
+        <v>32.27236615059995</v>
       </c>
       <c r="J5" t="n">
-        <v>55.63327993831443</v>
+        <v>33.2809437530503</v>
       </c>
       <c r="K5" t="n">
-        <v>55.63327993831443</v>
+        <v>33.2809437530503</v>
       </c>
       <c r="L5" t="n">
-        <v>55.63327993831443</v>
+        <v>33.2809437530503</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122.8687481522071</v>
+        <v>200.9253611120563</v>
       </c>
       <c r="C6" t="n">
-        <v>180.6373370463933</v>
+        <v>130.6411545052312</v>
       </c>
       <c r="D6" t="n">
-        <v>193.8301168568931</v>
+        <v>131.7514941767832</v>
       </c>
       <c r="E6" t="n">
-        <v>164.5627263000814</v>
+        <v>121.085471991146</v>
       </c>
       <c r="F6" t="n">
-        <v>123.7178173521552</v>
+        <v>130.8660650746296</v>
       </c>
       <c r="G6" t="n">
-        <v>181.4839234608899</v>
+        <v>200.7663733145665</v>
       </c>
       <c r="H6" t="n">
-        <v>181.6429112583783</v>
+        <v>199.3001751003806</v>
       </c>
       <c r="I6" t="n">
-        <v>180.63433365593</v>
+        <v>199.9167835096066</v>
       </c>
       <c r="J6" t="n">
-        <v>181.6544620707871</v>
+        <v>137.0715725540495</v>
       </c>
       <c r="K6" t="n">
-        <v>121.7769878973451</v>
+        <v>131.858576056692</v>
       </c>
       <c r="L6" t="n">
-        <v>243.037439243298</v>
+        <v>131.8595782927521</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102.927539859104</v>
+        <v>55.63327993831446</v>
       </c>
       <c r="C7" t="n">
-        <v>121.9857763219378</v>
+        <v>54.62470233586424</v>
       </c>
       <c r="D7" t="n">
-        <v>122.9943610380561</v>
+        <v>55.63281582197749</v>
       </c>
       <c r="E7" t="n">
-        <v>145.1424556353148</v>
+        <v>54.61518042919577</v>
       </c>
       <c r="F7" t="n">
-        <v>121.9857722712166</v>
+        <v>54.61518042919577</v>
       </c>
       <c r="G7" t="n">
-        <v>122.8353661268978</v>
+        <v>55.47429214082408</v>
       </c>
       <c r="H7" t="n">
-        <v>122.994353924388</v>
+        <v>55.63327993831446</v>
       </c>
       <c r="I7" t="n">
-        <v>121.9857763219378</v>
+        <v>54.62470233586424</v>
       </c>
       <c r="J7" t="n">
-        <v>122.994353924388</v>
+        <v>55.63327993831446</v>
       </c>
       <c r="K7" t="n">
-        <v>111.3675660384918</v>
+        <v>55.63327993831446</v>
       </c>
       <c r="L7" t="n">
-        <v>122.994353924388</v>
+        <v>55.63327993831446</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.94083714248636</v>
+        <v>122.8687481522071</v>
       </c>
       <c r="C8" t="n">
-        <v>49.00888205668735</v>
+        <v>180.6373370463934</v>
       </c>
       <c r="D8" t="n">
-        <v>83.88906616831397</v>
+        <v>193.8301168568931</v>
       </c>
       <c r="E8" t="n">
-        <v>49.00888205668735</v>
+        <v>164.5627263000814</v>
       </c>
       <c r="F8" t="n">
-        <v>49.00888205668735</v>
+        <v>123.7178173521551</v>
       </c>
       <c r="G8" t="n">
-        <v>83.18561544015186</v>
+        <v>181.4839234608899</v>
       </c>
       <c r="H8" t="n">
-        <v>84.72338556762921</v>
+        <v>181.6429112583781</v>
       </c>
       <c r="I8" t="n">
-        <v>49.00888205668735</v>
+        <v>180.6343336559298</v>
       </c>
       <c r="J8" t="n">
-        <v>80.42104120477583</v>
+        <v>181.6544620707871</v>
       </c>
       <c r="K8" t="n">
-        <v>82.65951970173666</v>
+        <v>121.7769878973452</v>
       </c>
       <c r="L8" t="n">
-        <v>85.77940665992564</v>
+        <v>243.0374392432981</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>102.9275398591038</v>
+      </c>
+      <c r="C9" t="n">
+        <v>121.9857763219375</v>
+      </c>
+      <c r="D9" t="n">
+        <v>122.9943610380559</v>
+      </c>
+      <c r="E9" t="n">
+        <v>145.1424556353145</v>
+      </c>
+      <c r="F9" t="n">
+        <v>121.9857722712164</v>
+      </c>
+      <c r="G9" t="n">
+        <v>122.8353661268975</v>
+      </c>
+      <c r="H9" t="n">
+        <v>122.9943539243879</v>
+      </c>
+      <c r="I9" t="n">
+        <v>121.9857763219375</v>
+      </c>
+      <c r="J9" t="n">
+        <v>122.9943539243879</v>
+      </c>
+      <c r="K9" t="n">
+        <v>111.3675660384915</v>
+      </c>
+      <c r="L9" t="n">
+        <v>122.9943539243879</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>81.9408371424864</v>
+      </c>
+      <c r="C10" t="n">
+        <v>49.00888205668732</v>
+      </c>
+      <c r="D10" t="n">
+        <v>83.88906616831406</v>
+      </c>
+      <c r="E10" t="n">
+        <v>49.00888205668732</v>
+      </c>
+      <c r="F10" t="n">
+        <v>49.00888205668732</v>
+      </c>
+      <c r="G10" t="n">
+        <v>83.18561544015189</v>
+      </c>
+      <c r="H10" t="n">
+        <v>84.72338556762926</v>
+      </c>
+      <c r="I10" t="n">
+        <v>49.00888205668732</v>
+      </c>
+      <c r="J10" t="n">
+        <v>80.42104120477589</v>
+      </c>
+      <c r="K10" t="n">
+        <v>82.65951970173666</v>
+      </c>
+      <c r="L10" t="n">
+        <v>85.77940665992568</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>84.03309565409519</v>
-      </c>
-      <c r="C9" t="n">
-        <v>50.87927963956933</v>
-      </c>
-      <c r="D9" t="n">
-        <v>84.82668265625935</v>
-      </c>
-      <c r="E9" t="n">
-        <v>50.87927963956933</v>
-      </c>
-      <c r="F9" t="n">
-        <v>50.87927963956933</v>
-      </c>
-      <c r="G9" t="n">
-        <v>84.5196430074779</v>
-      </c>
-      <c r="H9" t="n">
-        <v>85.16862831187768</v>
-      </c>
-      <c r="I9" t="n">
-        <v>50.87927963956933</v>
-      </c>
-      <c r="J9" t="n">
-        <v>83.41664270350721</v>
-      </c>
-      <c r="K9" t="n">
-        <v>84.32604600635929</v>
-      </c>
-      <c r="L9" t="n">
-        <v>85.59751096551254</v>
+      <c r="B11" t="n">
+        <v>84.03309565409522</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50.87927963956932</v>
+      </c>
+      <c r="D11" t="n">
+        <v>84.82668265625941</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50.87927963956932</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50.87927963956932</v>
+      </c>
+      <c r="G11" t="n">
+        <v>84.51964300747787</v>
+      </c>
+      <c r="H11" t="n">
+        <v>85.1686283118778</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50.87927963956932</v>
+      </c>
+      <c r="J11" t="n">
+        <v>83.41664270350726</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.32604600635928</v>
+      </c>
+      <c r="L11" t="n">
+        <v>85.59751096551256</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>280.1251672319885</v>
+        <v>86.2127487400932</v>
       </c>
       <c r="C2" t="n">
-        <v>232.4446421807874</v>
+        <v>52.49531535501211</v>
       </c>
       <c r="D2" t="n">
-        <v>190.4656419959192</v>
+        <v>86.09769046437994</v>
       </c>
       <c r="E2" t="n">
-        <v>232.4446421807874</v>
+        <v>52.49531535501211</v>
       </c>
       <c r="F2" t="n">
-        <v>232.4446421807874</v>
+        <v>52.49531535501211</v>
       </c>
       <c r="G2" t="n">
-        <v>225.044384883719</v>
+        <v>86.10594717921956</v>
       </c>
       <c r="H2" t="n">
-        <v>190.9620489182183</v>
+        <v>86.08127613978976</v>
       </c>
       <c r="I2" t="n">
-        <v>232.4446421807874</v>
+        <v>52.49531535501211</v>
       </c>
       <c r="J2" t="n">
-        <v>343.6046109463699</v>
+        <v>86.27324057259004</v>
       </c>
       <c r="K2" t="n">
-        <v>220.1723627787627</v>
+        <v>86.14268154974134</v>
       </c>
       <c r="L2" t="n">
-        <v>184.3302697747876</v>
+        <v>86.07921717088986</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.22662322715981</v>
+        <v>86.88634749929969</v>
       </c>
       <c r="C3" t="n">
-        <v>31.73550156840216</v>
+        <v>52.69713514139267</v>
       </c>
       <c r="D3" t="n">
-        <v>33.22662322715982</v>
+        <v>86.88634749929969</v>
       </c>
       <c r="E3" t="n">
-        <v>31.83223967565387</v>
+        <v>52.69713514139267</v>
       </c>
       <c r="F3" t="n">
-        <v>31.83223967565388</v>
+        <v>52.69713514139267</v>
       </c>
       <c r="G3" t="n">
-        <v>33.06800301465248</v>
+        <v>86.85205042967412</v>
       </c>
       <c r="H3" t="n">
-        <v>33.22662322715982</v>
+        <v>86.88634749929969</v>
       </c>
       <c r="I3" t="n">
-        <v>32.22039140212279</v>
+        <v>52.69713514139267</v>
       </c>
       <c r="J3" t="n">
-        <v>33.22662322715981</v>
+        <v>86.88634749929969</v>
       </c>
       <c r="K3" t="n">
-        <v>33.22662322715982</v>
+        <v>86.88634749929969</v>
       </c>
       <c r="L3" t="n">
-        <v>33.22662322715982</v>
+        <v>86.88634749929969</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>131.7747808384625</v>
+        <v>280.1251672319867</v>
       </c>
       <c r="C4" t="n">
-        <v>130.5501298970781</v>
+        <v>232.4446421807875</v>
       </c>
       <c r="D4" t="n">
-        <v>131.6209439194173</v>
+        <v>190.465641995919</v>
       </c>
       <c r="E4" t="n">
-        <v>120.9982723016099</v>
+        <v>232.4446421807875</v>
       </c>
       <c r="F4" t="n">
-        <v>130.7621232549047</v>
+        <v>232.4446421807875</v>
       </c>
       <c r="G4" t="n">
-        <v>131.6161606259551</v>
+        <v>225.0443848837222</v>
       </c>
       <c r="H4" t="n">
-        <v>199.1443934795145</v>
+        <v>190.9620489182184</v>
       </c>
       <c r="I4" t="n">
-        <v>130.7685490134256</v>
+        <v>232.4446421807875</v>
       </c>
       <c r="J4" t="n">
-        <v>136.9563448684133</v>
+        <v>343.6046109463704</v>
       </c>
       <c r="K4" t="n">
-        <v>131.7035968397682</v>
+        <v>220.1723627787632</v>
       </c>
       <c r="L4" t="n">
-        <v>131.7572343690952</v>
+        <v>184.3302697747877</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.47212615797095</v>
+        <v>33.22662322715978</v>
       </c>
       <c r="C5" t="n">
-        <v>54.46589433293389</v>
+        <v>31.73550156840216</v>
       </c>
       <c r="D5" t="n">
-        <v>55.47166515620702</v>
+        <v>33.22662322715978</v>
       </c>
       <c r="E5" t="n">
-        <v>54.45562058835171</v>
+        <v>31.83223967565387</v>
       </c>
       <c r="F5" t="n">
-        <v>54.45562058835171</v>
+        <v>31.83223967565387</v>
       </c>
       <c r="G5" t="n">
-        <v>55.31350594546362</v>
+        <v>33.06800301465243</v>
       </c>
       <c r="H5" t="n">
-        <v>55.47212615797095</v>
+        <v>33.22662322715978</v>
       </c>
       <c r="I5" t="n">
-        <v>54.46589433293389</v>
+        <v>32.22039140212276</v>
       </c>
       <c r="J5" t="n">
-        <v>55.47212615797095</v>
+        <v>33.22662322715978</v>
       </c>
       <c r="K5" t="n">
-        <v>55.47212615797095</v>
+        <v>33.22662322715978</v>
       </c>
       <c r="L5" t="n">
-        <v>55.47212615797095</v>
+        <v>33.22662322715978</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122.5694862491228</v>
+        <v>131.7747808384626</v>
       </c>
       <c r="C6" t="n">
-        <v>180.1681926930717</v>
+        <v>130.5501298970783</v>
       </c>
       <c r="D6" t="n">
-        <v>193.3238269298851</v>
+        <v>131.6209439194172</v>
       </c>
       <c r="E6" t="n">
-        <v>164.1405586298903</v>
+        <v>120.99827230161</v>
       </c>
       <c r="F6" t="n">
-        <v>123.4150154580524</v>
+        <v>130.7621232549047</v>
       </c>
       <c r="G6" t="n">
-        <v>181.0135569873285</v>
+        <v>131.616160625955</v>
       </c>
       <c r="H6" t="n">
-        <v>181.1721771998339</v>
+        <v>199.1443934795144</v>
       </c>
       <c r="I6" t="n">
-        <v>180.1659453747986</v>
+        <v>130.7685490134256</v>
       </c>
       <c r="J6" t="n">
-        <v>181.1836943131556</v>
+        <v>136.9563448684131</v>
       </c>
       <c r="K6" t="n">
-        <v>121.480911177567</v>
+        <v>131.7035968397678</v>
       </c>
       <c r="L6" t="n">
-        <v>242.3875881802165</v>
+        <v>131.7572343690951</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99.5246671116216</v>
+        <v>55.47212615797098</v>
       </c>
       <c r="C7" t="n">
-        <v>117.6522966531854</v>
+        <v>54.4658943329339</v>
       </c>
       <c r="D7" t="n">
-        <v>118.6585350897654</v>
+        <v>55.47166515620697</v>
       </c>
       <c r="E7" t="n">
-        <v>139.7323680044331</v>
+        <v>54.45562058835168</v>
       </c>
       <c r="F7" t="n">
-        <v>117.6522927018792</v>
+        <v>54.45562058835168</v>
       </c>
       <c r="G7" t="n">
-        <v>118.4999082657152</v>
+        <v>55.31350594546365</v>
       </c>
       <c r="H7" t="n">
-        <v>118.6585284782226</v>
+        <v>55.47212615797098</v>
       </c>
       <c r="I7" t="n">
-        <v>117.6522966531854</v>
+        <v>54.4658943329339</v>
       </c>
       <c r="J7" t="n">
-        <v>118.6585284782226</v>
+        <v>55.47212615797098</v>
       </c>
       <c r="K7" t="n">
-        <v>107.1225141488714</v>
+        <v>55.47212615797098</v>
       </c>
       <c r="L7" t="n">
-        <v>118.6585284782226</v>
+        <v>55.47212615797098</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.919251815081</v>
+        <v>122.5694862491229</v>
       </c>
       <c r="C8" t="n">
-        <v>49.01955072486184</v>
+        <v>180.1681926930719</v>
       </c>
       <c r="D8" t="n">
-        <v>84.33237363263036</v>
+        <v>193.323826929885</v>
       </c>
       <c r="E8" t="n">
-        <v>49.01955072486184</v>
+        <v>164.1405586298904</v>
       </c>
       <c r="F8" t="n">
-        <v>49.01955072486184</v>
+        <v>123.4150154580525</v>
       </c>
       <c r="G8" t="n">
-        <v>83.422180429835</v>
+        <v>181.0135569873286</v>
       </c>
       <c r="H8" t="n">
-        <v>84.71911060560542</v>
+        <v>181.1721771998334</v>
       </c>
       <c r="I8" t="n">
-        <v>49.01955072486184</v>
+        <v>180.1659453747993</v>
       </c>
       <c r="J8" t="n">
-        <v>80.70155627603641</v>
+        <v>181.1836943131555</v>
       </c>
       <c r="K8" t="n">
-        <v>83.39185919913378</v>
+        <v>121.4809111775669</v>
       </c>
       <c r="L8" t="n">
-        <v>84.66968461798592</v>
+        <v>242.3875881802163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>99.52466711162177</v>
+      </c>
+      <c r="C9" t="n">
+        <v>117.6522966531856</v>
+      </c>
+      <c r="D9" t="n">
+        <v>118.6585350897656</v>
+      </c>
+      <c r="E9" t="n">
+        <v>139.7323680044332</v>
+      </c>
+      <c r="F9" t="n">
+        <v>117.6522927018794</v>
+      </c>
+      <c r="G9" t="n">
+        <v>118.4999082657153</v>
+      </c>
+      <c r="H9" t="n">
+        <v>118.6585284782226</v>
+      </c>
+      <c r="I9" t="n">
+        <v>117.6522966531856</v>
+      </c>
+      <c r="J9" t="n">
+        <v>118.6585284782225</v>
+      </c>
+      <c r="K9" t="n">
+        <v>107.1225141488716</v>
+      </c>
+      <c r="L9" t="n">
+        <v>118.6585284782225</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>81.91925181508095</v>
+      </c>
+      <c r="C10" t="n">
+        <v>49.01955072486188</v>
+      </c>
+      <c r="D10" t="n">
+        <v>84.33237363263036</v>
+      </c>
+      <c r="E10" t="n">
+        <v>49.01955072486188</v>
+      </c>
+      <c r="F10" t="n">
+        <v>49.01955072486188</v>
+      </c>
+      <c r="G10" t="n">
+        <v>83.42218042983498</v>
+      </c>
+      <c r="H10" t="n">
+        <v>84.71911060560537</v>
+      </c>
+      <c r="I10" t="n">
+        <v>49.01955072486188</v>
+      </c>
+      <c r="J10" t="n">
+        <v>80.7015562760364</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.39185919913385</v>
+      </c>
+      <c r="L10" t="n">
+        <v>84.66968461798596</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>83.95270437457904</v>
-      </c>
-      <c r="C9" t="n">
-        <v>50.82200272572432</v>
-      </c>
-      <c r="D9" t="n">
-        <v>84.93562421601362</v>
-      </c>
-      <c r="E9" t="n">
-        <v>50.82200272572432</v>
-      </c>
-      <c r="F9" t="n">
-        <v>50.82200272572432</v>
-      </c>
-      <c r="G9" t="n">
-        <v>84.54534539894553</v>
-      </c>
-      <c r="H9" t="n">
-        <v>85.09517644658473</v>
-      </c>
-      <c r="I9" t="n">
-        <v>50.82200272572432</v>
-      </c>
-      <c r="J9" t="n">
-        <v>83.45914085624518</v>
-      </c>
-      <c r="K9" t="n">
-        <v>84.55267823689249</v>
-      </c>
-      <c r="L9" t="n">
-        <v>85.07468780549323</v>
+      <c r="B11" t="n">
+        <v>83.95270437457896</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50.82200272572429</v>
+      </c>
+      <c r="D11" t="n">
+        <v>84.93562421601359</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50.82200272572429</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50.82200272572429</v>
+      </c>
+      <c r="G11" t="n">
+        <v>84.54534539894549</v>
+      </c>
+      <c r="H11" t="n">
+        <v>85.09517644658469</v>
+      </c>
+      <c r="I11" t="n">
+        <v>50.82200272572429</v>
+      </c>
+      <c r="J11" t="n">
+        <v>83.45914085624504</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.55267823689245</v>
+      </c>
+      <c r="L11" t="n">
+        <v>85.07468780549314</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>316.5655078329702</v>
+        <v>88.10095453918882</v>
       </c>
       <c r="C2" t="n">
-        <v>256.6498707667237</v>
+        <v>53.88721940734136</v>
       </c>
       <c r="D2" t="n">
-        <v>1241.401210069891</v>
+        <v>89.17311328372517</v>
       </c>
       <c r="E2" t="n">
-        <v>256.6498707667237</v>
+        <v>53.88721940734136</v>
       </c>
       <c r="F2" t="n">
-        <v>256.6498707667237</v>
+        <v>53.88721940734136</v>
       </c>
       <c r="G2" t="n">
-        <v>669.3938627776395</v>
+        <v>88.3808044471498</v>
       </c>
       <c r="H2" t="n">
-        <v>2049.555477788967</v>
+        <v>89.95429721545874</v>
       </c>
       <c r="I2" t="n">
-        <v>256.6498707667237</v>
+        <v>53.88721940734136</v>
       </c>
       <c r="J2" t="n">
-        <v>526.1087458254543</v>
+        <v>88.3019709740239</v>
       </c>
       <c r="K2" t="n">
-        <v>404.3336431986016</v>
+        <v>88.19924937421321</v>
       </c>
       <c r="L2" t="n">
-        <v>275.5670255199956</v>
+        <v>89.49200270593769</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.61139005497752</v>
+        <v>88.77512458573808</v>
       </c>
       <c r="C3" t="n">
-        <v>32.67376047456767</v>
+        <v>54.09672898985767</v>
       </c>
       <c r="D3" t="n">
-        <v>34.61139005497752</v>
+        <v>88.77512458573808</v>
       </c>
       <c r="E3" t="n">
-        <v>32.8065453952842</v>
+        <v>54.09672898985767</v>
       </c>
       <c r="F3" t="n">
-        <v>32.80654539528411</v>
+        <v>54.09672898985767</v>
       </c>
       <c r="G3" t="n">
-        <v>34.43676742127045</v>
+        <v>88.66770316843878</v>
       </c>
       <c r="H3" t="n">
-        <v>34.61139005497752</v>
+        <v>88.77512458573808</v>
       </c>
       <c r="I3" t="n">
-        <v>33.50306314177295</v>
+        <v>54.09672898985767</v>
       </c>
       <c r="J3" t="n">
-        <v>34.61139005497752</v>
+        <v>88.77512458573808</v>
       </c>
       <c r="K3" t="n">
-        <v>34.61139005497752</v>
+        <v>88.77512458573808</v>
       </c>
       <c r="L3" t="n">
-        <v>34.61139005497752</v>
+        <v>88.77512458573808</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>141.1650141487012</v>
+        <v>316.5655078329701</v>
       </c>
       <c r="C4" t="n">
-        <v>139.2105256872701</v>
+        <v>256.6498707667192</v>
       </c>
       <c r="D4" t="n">
-        <v>142.6664362047709</v>
+        <v>1241.401210069893</v>
       </c>
       <c r="E4" t="n">
-        <v>128.9231212926849</v>
+        <v>256.6498707667192</v>
       </c>
       <c r="F4" t="n">
-        <v>140.0086932521163</v>
+        <v>256.6498707667192</v>
       </c>
       <c r="G4" t="n">
-        <v>217.81698873674</v>
+        <v>669.3938627776458</v>
       </c>
       <c r="H4" t="n">
-        <v>216.7970388578009</v>
+        <v>2049.555477788973</v>
       </c>
       <c r="I4" t="n">
-        <v>216.8832844572422</v>
+        <v>256.6498707667192</v>
       </c>
       <c r="J4" t="n">
-        <v>216.1674631456623</v>
+        <v>526.1087458254536</v>
       </c>
       <c r="K4" t="n">
-        <v>140.8870875039466</v>
+        <v>404.3336431986017</v>
       </c>
       <c r="L4" t="n">
-        <v>141.6496897311377</v>
+        <v>275.5670255200047</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.77547768945291</v>
+        <v>34.61139005497742</v>
       </c>
       <c r="C5" t="n">
-        <v>59.66715077624839</v>
+        <v>32.67376047456762</v>
       </c>
       <c r="D5" t="n">
-        <v>60.77496945812453</v>
+        <v>34.61139005497742</v>
       </c>
       <c r="E5" t="n">
-        <v>59.65080003798707</v>
+        <v>32.80654539528419</v>
       </c>
       <c r="F5" t="n">
-        <v>59.65080003798707</v>
+        <v>32.8065453952842</v>
       </c>
       <c r="G5" t="n">
-        <v>60.60085505574579</v>
+        <v>34.43676742127047</v>
       </c>
       <c r="H5" t="n">
-        <v>60.77547768945291</v>
+        <v>34.61139005497742</v>
       </c>
       <c r="I5" t="n">
-        <v>59.66715077624839</v>
+        <v>33.50306314177283</v>
       </c>
       <c r="J5" t="n">
-        <v>60.77547768945291</v>
+        <v>34.61139005497742</v>
       </c>
       <c r="K5" t="n">
-        <v>60.77547768945291</v>
+        <v>34.61139005497742</v>
       </c>
       <c r="L5" t="n">
-        <v>60.77547768945291</v>
+        <v>34.61139005497742</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>134.9073256110631</v>
+        <v>141.1650141487015</v>
       </c>
       <c r="C6" t="n">
-        <v>199.9535109609421</v>
+        <v>139.2105256872699</v>
       </c>
       <c r="D6" t="n">
-        <v>214.7818504009348</v>
+        <v>142.6664362047711</v>
       </c>
       <c r="E6" t="n">
-        <v>181.8604141575715</v>
+        <v>128.9231212926848</v>
       </c>
       <c r="F6" t="n">
-        <v>135.8866079115127</v>
+        <v>140.0086932521163</v>
       </c>
       <c r="G6" t="n">
-        <v>200.8892390437455</v>
+        <v>217.8169887367399</v>
       </c>
       <c r="H6" t="n">
-        <v>201.0638616774586</v>
+        <v>216.7970388578011</v>
       </c>
       <c r="I6" t="n">
-        <v>199.9555347642475</v>
+        <v>216.883284457242</v>
       </c>
       <c r="J6" t="n">
-        <v>201.0768633371422</v>
+        <v>216.1674631456622</v>
       </c>
       <c r="K6" t="n">
-        <v>133.6784339884144</v>
+        <v>140.8870875039467</v>
       </c>
       <c r="L6" t="n">
-        <v>270.1698955227838</v>
+        <v>141.6496897311378</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>124.2229361968708</v>
+        <v>60.77547768945296</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9546601833896</v>
+        <v>59.66715077624835</v>
       </c>
       <c r="D7" t="n">
-        <v>150.0629817230758</v>
+        <v>60.77496945812462</v>
       </c>
       <c r="E7" t="n">
-        <v>178.7734863954891</v>
+        <v>59.65080003798726</v>
       </c>
       <c r="F7" t="n">
-        <v>148.9546283665267</v>
+        <v>59.65080003798726</v>
       </c>
       <c r="G7" t="n">
-        <v>149.8883644628867</v>
+        <v>60.6008550557459</v>
       </c>
       <c r="H7" t="n">
-        <v>150.0629870965944</v>
+        <v>60.77547768945296</v>
       </c>
       <c r="I7" t="n">
-        <v>148.9546601833896</v>
+        <v>59.66715077624835</v>
       </c>
       <c r="J7" t="n">
-        <v>150.0629870965944</v>
+        <v>60.77547768945296</v>
       </c>
       <c r="K7" t="n">
-        <v>135.0911578635126</v>
+        <v>60.77547768945296</v>
       </c>
       <c r="L7" t="n">
-        <v>150.0629870965944</v>
+        <v>60.77547768945296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.42075063025078</v>
+        <v>134.9073256110632</v>
       </c>
       <c r="C8" t="n">
-        <v>50.26824461477704</v>
+        <v>199.9535109609425</v>
       </c>
       <c r="D8" t="n">
-        <v>60.9636531498324</v>
+        <v>214.7818504009352</v>
       </c>
       <c r="E8" t="n">
-        <v>50.26824461477704</v>
+        <v>181.8604141575715</v>
       </c>
       <c r="F8" t="n">
-        <v>50.26824461477704</v>
+        <v>135.8866079115126</v>
       </c>
       <c r="G8" t="n">
-        <v>75.26300686996811</v>
+        <v>200.8892390437453</v>
       </c>
       <c r="H8" t="n">
-        <v>45.42227072347144</v>
+        <v>201.0638616774587</v>
       </c>
       <c r="I8" t="n">
-        <v>50.26824461477704</v>
+        <v>199.9555347642477</v>
       </c>
       <c r="J8" t="n">
-        <v>79.28408502656583</v>
+        <v>201.0768633371419</v>
       </c>
       <c r="K8" t="n">
-        <v>81.36880108983217</v>
+        <v>133.6784339884145</v>
       </c>
       <c r="L8" t="n">
-        <v>54.80499735793244</v>
+        <v>270.1698955227843</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>124.222936196871</v>
+      </c>
+      <c r="C9" t="n">
+        <v>148.9546601833898</v>
+      </c>
+      <c r="D9" t="n">
+        <v>150.0629817230761</v>
+      </c>
+      <c r="E9" t="n">
+        <v>178.7734863954891</v>
+      </c>
+      <c r="F9" t="n">
+        <v>148.954628366527</v>
+      </c>
+      <c r="G9" t="n">
+        <v>149.8883644628873</v>
+      </c>
+      <c r="H9" t="n">
+        <v>150.0629870965943</v>
+      </c>
+      <c r="I9" t="n">
+        <v>148.9546601833898</v>
+      </c>
+      <c r="J9" t="n">
+        <v>150.0629870965943</v>
+      </c>
+      <c r="K9" t="n">
+        <v>135.0911578635128</v>
+      </c>
+      <c r="L9" t="n">
+        <v>150.0629870965943</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>83.42075063025061</v>
+      </c>
+      <c r="C10" t="n">
+        <v>50.26824461477699</v>
+      </c>
+      <c r="D10" t="n">
+        <v>60.9636531498323</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50.26824461477699</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50.26824461477699</v>
+      </c>
+      <c r="G10" t="n">
+        <v>75.263006869968</v>
+      </c>
+      <c r="H10" t="n">
+        <v>45.4222707234713</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50.26824461477699</v>
+      </c>
+      <c r="J10" t="n">
+        <v>79.28408502656589</v>
+      </c>
+      <c r="K10" t="n">
+        <v>81.36880108983206</v>
+      </c>
+      <c r="L10" t="n">
+        <v>54.80499735793228</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>85.66469732606475</v>
-      </c>
-      <c r="C9" t="n">
-        <v>52.14524681602387</v>
-      </c>
-      <c r="D9" t="n">
-        <v>76.51880515048738</v>
-      </c>
-      <c r="E9" t="n">
-        <v>52.14524681602387</v>
-      </c>
-      <c r="F9" t="n">
-        <v>52.14524681602387</v>
-      </c>
-      <c r="G9" t="n">
-        <v>82.28162491311323</v>
-      </c>
-      <c r="H9" t="n">
-        <v>70.22861055077951</v>
-      </c>
-      <c r="I9" t="n">
-        <v>52.14524681602387</v>
-      </c>
-      <c r="J9" t="n">
-        <v>83.9835177284521</v>
-      </c>
-      <c r="K9" t="n">
-        <v>84.82934858102334</v>
-      </c>
-      <c r="L9" t="n">
-        <v>86.29142972180347</v>
+      <c r="B11" t="n">
+        <v>85.66469732606471</v>
+      </c>
+      <c r="C11" t="n">
+        <v>52.14524681602384</v>
+      </c>
+      <c r="D11" t="n">
+        <v>76.51880515048742</v>
+      </c>
+      <c r="E11" t="n">
+        <v>52.14524681602384</v>
+      </c>
+      <c r="F11" t="n">
+        <v>52.14524681602384</v>
+      </c>
+      <c r="G11" t="n">
+        <v>82.28162491311316</v>
+      </c>
+      <c r="H11" t="n">
+        <v>70.22861055077955</v>
+      </c>
+      <c r="I11" t="n">
+        <v>52.14524681602384</v>
+      </c>
+      <c r="J11" t="n">
+        <v>83.98351772845211</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.82934858102328</v>
+      </c>
+      <c r="L11" t="n">
+        <v>86.29142972180341</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>265.9308307436855</v>
+        <v>87.06208277845413</v>
       </c>
       <c r="C2" t="n">
-        <v>217.8343081690805</v>
+        <v>53.12866213053262</v>
       </c>
       <c r="D2" t="n">
-        <v>909.5117132715357</v>
+        <v>87.90218487482977</v>
       </c>
       <c r="E2" t="n">
-        <v>217.8343081690805</v>
+        <v>53.12866213053262</v>
       </c>
       <c r="F2" t="n">
-        <v>217.8343081690805</v>
+        <v>53.12866213053262</v>
       </c>
       <c r="G2" t="n">
-        <v>420.4458218144038</v>
+        <v>87.17507919936533</v>
       </c>
       <c r="H2" t="n">
-        <v>360.1082326665047</v>
+        <v>87.14824056919028</v>
       </c>
       <c r="I2" t="n">
-        <v>217.8343081690805</v>
+        <v>53.12866213053262</v>
       </c>
       <c r="J2" t="n">
-        <v>395.1325480538022</v>
+        <v>87.19289781827112</v>
       </c>
       <c r="K2" t="n">
-        <v>215.2464833950579</v>
+        <v>87.00193897664025</v>
       </c>
       <c r="L2" t="n">
-        <v>1052.730164150326</v>
+        <v>86.94768184496182</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.72970143389044</v>
+        <v>87.7637119833025</v>
       </c>
       <c r="C3" t="n">
-        <v>32.01845253335527</v>
+        <v>53.35832428671247</v>
       </c>
       <c r="D3" t="n">
-        <v>33.72970143389044</v>
+        <v>87.7637119833025</v>
       </c>
       <c r="E3" t="n">
-        <v>32.12981469570179</v>
+        <v>53.35832428671247</v>
       </c>
       <c r="F3" t="n">
-        <v>32.12981469570179</v>
+        <v>53.35832428671247</v>
       </c>
       <c r="G3" t="n">
-        <v>33.56233968423327</v>
+        <v>87.68877409701382</v>
       </c>
       <c r="H3" t="n">
-        <v>33.72970143389044</v>
+        <v>87.7637119833025</v>
       </c>
       <c r="I3" t="n">
-        <v>32.66772664688642</v>
+        <v>53.35832428671247</v>
       </c>
       <c r="J3" t="n">
-        <v>33.72970143389044</v>
+        <v>87.7637119833025</v>
       </c>
       <c r="K3" t="n">
-        <v>33.72970143389044</v>
+        <v>87.7637119833025</v>
       </c>
       <c r="L3" t="n">
-        <v>33.72970143389044</v>
+        <v>87.7637119833025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>202.8904879390038</v>
+        <v>265.9308307436853</v>
       </c>
       <c r="C4" t="n">
-        <v>130.9857851744</v>
+        <v>217.8343081690804</v>
       </c>
       <c r="D4" t="n">
-        <v>133.7888512033063</v>
+        <v>909.5117132715344</v>
       </c>
       <c r="E4" t="n">
-        <v>121.4205794822475</v>
+        <v>217.8343081690804</v>
       </c>
       <c r="F4" t="n">
-        <v>131.4801035011088</v>
+        <v>217.8343081690804</v>
       </c>
       <c r="G4" t="n">
-        <v>202.7231261893463</v>
+        <v>420.4458218144039</v>
       </c>
       <c r="H4" t="n">
-        <v>201.368836823859</v>
+        <v>360.1082326665051</v>
       </c>
       <c r="I4" t="n">
-        <v>201.8285131519996</v>
+        <v>217.8343081690804</v>
       </c>
       <c r="J4" t="n">
-        <v>137.8172108651422</v>
+        <v>395.1325480538021</v>
       </c>
       <c r="K4" t="n">
-        <v>132.2563412442652</v>
+        <v>215.2464833950577</v>
       </c>
       <c r="L4" t="n">
-        <v>132.834310471065</v>
+        <v>1052.730164150325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.01556953390967</v>
+        <v>33.72970143389043</v>
       </c>
       <c r="C5" t="n">
-        <v>55.95359474690568</v>
+        <v>32.01845253335532</v>
       </c>
       <c r="D5" t="n">
-        <v>57.01510400497786</v>
+        <v>33.72970143389043</v>
       </c>
       <c r="E5" t="n">
-        <v>55.93936264589135</v>
+        <v>32.12981469570177</v>
       </c>
       <c r="F5" t="n">
-        <v>55.93936264589135</v>
+        <v>32.1298146957018</v>
       </c>
       <c r="G5" t="n">
-        <v>56.84820778425252</v>
+        <v>33.56233968423326</v>
       </c>
       <c r="H5" t="n">
-        <v>57.01556953390967</v>
+        <v>33.72970143389043</v>
       </c>
       <c r="I5" t="n">
-        <v>55.95359474690568</v>
+        <v>32.66772664688642</v>
       </c>
       <c r="J5" t="n">
-        <v>57.01556953390967</v>
+        <v>33.72970143389043</v>
       </c>
       <c r="K5" t="n">
-        <v>57.01556953390967</v>
+        <v>33.72970143389043</v>
       </c>
       <c r="L5" t="n">
-        <v>57.01556953390967</v>
+        <v>33.72970143389043</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>125.2058614893286</v>
+        <v>202.8904879390038</v>
       </c>
       <c r="C6" t="n">
-        <v>184.3173874989524</v>
+        <v>130.9857851743997</v>
       </c>
       <c r="D6" t="n">
-        <v>197.8582076679447</v>
+        <v>133.7888512033063</v>
       </c>
       <c r="E6" t="n">
-        <v>167.8601846811338</v>
+        <v>121.4205794822474</v>
       </c>
       <c r="F6" t="n">
-        <v>126.0431201361577</v>
+        <v>131.4801035011088</v>
       </c>
       <c r="G6" t="n">
-        <v>185.2132246962859</v>
+        <v>202.7231261893461</v>
       </c>
       <c r="H6" t="n">
-        <v>185.3805864459425</v>
+        <v>201.3688368238591</v>
       </c>
       <c r="I6" t="n">
-        <v>184.318611658939</v>
+        <v>201.8285131519996</v>
       </c>
       <c r="J6" t="n">
-        <v>185.3924125084567</v>
+        <v>137.8172108651421</v>
       </c>
       <c r="K6" t="n">
-        <v>124.08808507909</v>
+        <v>132.2563412442653</v>
       </c>
       <c r="L6" t="n">
-        <v>248.2381183963267</v>
+        <v>132.834310471065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107.7447239379979</v>
+        <v>57.01556953390964</v>
       </c>
       <c r="C7" t="n">
-        <v>128.0450351721216</v>
+        <v>55.95359474690561</v>
       </c>
       <c r="D7" t="n">
-        <v>129.1070207987558</v>
+        <v>57.01510400497784</v>
       </c>
       <c r="E7" t="n">
-        <v>152.6966611550727</v>
+        <v>55.93936264589145</v>
       </c>
       <c r="F7" t="n">
-        <v>128.0450280276258</v>
+        <v>55.93936264589145</v>
       </c>
       <c r="G7" t="n">
-        <v>128.9396482094682</v>
+        <v>56.84820778425258</v>
       </c>
       <c r="H7" t="n">
-        <v>129.1070099591255</v>
+        <v>57.01556953390964</v>
       </c>
       <c r="I7" t="n">
-        <v>128.0450351721216</v>
+        <v>55.95359474690561</v>
       </c>
       <c r="J7" t="n">
-        <v>129.1070099591255</v>
+        <v>57.01556953390964</v>
       </c>
       <c r="K7" t="n">
-        <v>116.7296221014275</v>
+        <v>57.01556953390964</v>
       </c>
       <c r="L7" t="n">
-        <v>129.1070099591255</v>
+        <v>57.01556953390964</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.20628853520012</v>
+        <v>125.2058614893289</v>
       </c>
       <c r="C8" t="n">
-        <v>50.11566601249941</v>
+        <v>184.3173874989532</v>
       </c>
       <c r="D8" t="n">
-        <v>65.60999020229769</v>
+        <v>197.8582076679455</v>
       </c>
       <c r="E8" t="n">
-        <v>50.11566601249941</v>
+        <v>167.8601846811344</v>
       </c>
       <c r="F8" t="n">
-        <v>50.11566601249941</v>
+        <v>126.0431201361581</v>
       </c>
       <c r="G8" t="n">
-        <v>79.23465703093828</v>
+        <v>185.2132246962865</v>
       </c>
       <c r="H8" t="n">
-        <v>81.52405890587139</v>
+        <v>185.3805864459433</v>
       </c>
       <c r="I8" t="n">
-        <v>50.11566601249941</v>
+        <v>184.3186116589396</v>
       </c>
       <c r="J8" t="n">
-        <v>80.5230552296828</v>
+        <v>185.3924125084575</v>
       </c>
       <c r="K8" t="n">
-        <v>84.47067731035185</v>
+        <v>124.0880850790904</v>
       </c>
       <c r="L8" t="n">
-        <v>66.92237646503145</v>
+        <v>248.2381183963276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>107.7447239379977</v>
+      </c>
+      <c r="C9" t="n">
+        <v>128.0450351721213</v>
+      </c>
+      <c r="D9" t="n">
+        <v>129.1070207987555</v>
+      </c>
+      <c r="E9" t="n">
+        <v>152.6966611550724</v>
+      </c>
+      <c r="F9" t="n">
+        <v>128.0450280276255</v>
+      </c>
+      <c r="G9" t="n">
+        <v>128.9396482094683</v>
+      </c>
+      <c r="H9" t="n">
+        <v>129.1070099591253</v>
+      </c>
+      <c r="I9" t="n">
+        <v>128.0450351721213</v>
+      </c>
+      <c r="J9" t="n">
+        <v>129.1070099591253</v>
+      </c>
+      <c r="K9" t="n">
+        <v>116.7296221014276</v>
+      </c>
+      <c r="L9" t="n">
+        <v>129.1070099591253</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>83.20628853520019</v>
+      </c>
+      <c r="C10" t="n">
+        <v>50.11566601249942</v>
+      </c>
+      <c r="D10" t="n">
+        <v>65.60999020229777</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50.11566601249942</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50.11566601249942</v>
+      </c>
+      <c r="G10" t="n">
+        <v>79.23465703093844</v>
+      </c>
+      <c r="H10" t="n">
+        <v>81.52405890587144</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50.11566601249942</v>
+      </c>
+      <c r="J10" t="n">
+        <v>80.52305522968283</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.47067731035197</v>
+      </c>
+      <c r="L10" t="n">
+        <v>66.92237646503158</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>84.98844058592069</v>
-      </c>
-      <c r="C9" t="n">
-        <v>51.65324228202682</v>
-      </c>
-      <c r="D9" t="n">
-        <v>77.82217086475013</v>
-      </c>
-      <c r="E9" t="n">
-        <v>51.65324228202682</v>
-      </c>
-      <c r="F9" t="n">
-        <v>51.65324228202682</v>
-      </c>
-      <c r="G9" t="n">
-        <v>83.32842899262846</v>
-      </c>
-      <c r="H9" t="n">
-        <v>84.30917853436456</v>
-      </c>
-      <c r="I9" t="n">
-        <v>51.65324228202682</v>
-      </c>
-      <c r="J9" t="n">
-        <v>83.89837592077019</v>
-      </c>
-      <c r="K9" t="n">
-        <v>85.5035977061688</v>
-      </c>
-      <c r="L9" t="n">
-        <v>78.37196492033048</v>
+      <c r="B11" t="n">
+        <v>84.98844058592081</v>
+      </c>
+      <c r="C11" t="n">
+        <v>51.65324228202684</v>
+      </c>
+      <c r="D11" t="n">
+        <v>77.82217086475026</v>
+      </c>
+      <c r="E11" t="n">
+        <v>51.65324228202684</v>
+      </c>
+      <c r="F11" t="n">
+        <v>51.65324228202684</v>
+      </c>
+      <c r="G11" t="n">
+        <v>83.3284289926285</v>
+      </c>
+      <c r="H11" t="n">
+        <v>84.30917853436458</v>
+      </c>
+      <c r="I11" t="n">
+        <v>51.65324228202684</v>
+      </c>
+      <c r="J11" t="n">
+        <v>83.89837592077023</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.50359770616882</v>
+      </c>
+      <c r="L11" t="n">
+        <v>78.3719649203305</v>
       </c>
     </row>
   </sheetData>
